--- a/results/cross_validation/global/metrics_summary.xlsx
+++ b/results/cross_validation/global/metrics_summary.xlsx
@@ -480,25 +480,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8284194915297212</v>
+        <v>0.002100854051636625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7029273874420006</v>
+        <v>-0.03313127500792068</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6752431143687416</v>
+        <v>0.1499899731737249</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.106440983495443</v>
+        <v>-5.560093126966859</v>
       </c>
       <c r="F2" t="n">
-        <v>-8.42424309875395</v>
+        <v>-11.35642945124785</v>
       </c>
       <c r="G2" t="n">
-        <v>-9.760807300145476</v>
+        <v>-36.82205196766856</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.847483564842401</v>
+        <v>-8.936602498944305</v>
       </c>
     </row>
     <row r="3">
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0510402179012508</v>
+        <v>0.09053978670866247</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0762882153426198</v>
+        <v>0.1250576028800978</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006834181377787287</v>
+        <v>0.01316214816609958</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01369398448223255</v>
+        <v>0.02376200770946218</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04058870226876315</v>
+        <v>0.04794572948620329</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03007716086576454</v>
+        <v>0.0601899539622931</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03642041037306969</v>
+        <v>0.0601095381521364</v>
       </c>
     </row>
     <row r="4">
@@ -536,25 +536,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006215860389692663</v>
+        <v>0.03615096976637657</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02583840607083716</v>
+        <v>0.08985838572690592</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003149599855510444</v>
+        <v>0.0008243678813678033</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0006886079941580234</v>
+        <v>0.002144533174698487</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004037631334069078</v>
+        <v>0.005293868823923773</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001930789524482166</v>
+        <v>0.006786333004272577</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006504375883131689</v>
+        <v>0.02350974306292419</v>
       </c>
     </row>
     <row r="5">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07884072798809422</v>
+        <v>0.1901340836525018</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1607432924598634</v>
+        <v>0.299763883293011</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01774711203410415</v>
+        <v>0.02871180735111956</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02624134131781421</v>
+        <v>0.0463091046631058</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06354235858125726</v>
+        <v>0.07275897761736193</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04394075015839131</v>
+        <v>0.08237920249840112</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06517593042325408</v>
+        <v>0.1200095098459169</v>
       </c>
     </row>
     <row r="6">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59.06624971323075</v>
+        <v>59.65675944222733</v>
       </c>
       <c r="C6" t="n">
-        <v>42.47542710159512</v>
+        <v>65.39380667480289</v>
       </c>
       <c r="D6" t="n">
-        <v>34.04122338653708</v>
+        <v>124.8963146215416</v>
       </c>
       <c r="E6" t="n">
-        <v>104.7972505954806</v>
+        <v>241.49523289282</v>
       </c>
       <c r="F6" t="n">
-        <v>5707.151343654814</v>
+        <v>6676.140047443704</v>
       </c>
       <c r="G6" t="n">
-        <v>804.2231613208912</v>
+        <v>1540.903089398291</v>
       </c>
       <c r="H6" t="n">
-        <v>1125.292442628758</v>
+        <v>1451.414208412231</v>
       </c>
     </row>
     <row r="7">
@@ -620,25 +620,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05582525481386853</v>
+        <v>0.3251754226209727</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1072086680169859</v>
+        <v>0.7466805050224208</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09764753767926325</v>
+        <v>0.25608006556484</v>
       </c>
       <c r="E7" t="n">
-        <v>1.264828641289087</v>
+        <v>3.940058222624694</v>
       </c>
       <c r="F7" t="n">
-        <v>5.660198543120067</v>
+        <v>7.422269087102205</v>
       </c>
       <c r="G7" t="n">
-        <v>6.459187485421562</v>
+        <v>22.70373204680712</v>
       </c>
       <c r="H7" t="n">
-        <v>2.274149355056805</v>
+        <v>5.898999224957042</v>
       </c>
     </row>
     <row r="8">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-80.37106914199437</v>
+        <v>-54.44087557748635</v>
       </c>
       <c r="C8" t="n">
-        <v>-48.83839929803149</v>
+        <v>-34.14280509720521</v>
       </c>
       <c r="D8" t="n">
-        <v>-163.3243641012907</v>
+        <v>-147.1187670640544</v>
       </c>
       <c r="E8" t="n">
-        <v>-146.8976063545537</v>
+        <v>-127.0415010736833</v>
       </c>
       <c r="F8" t="n">
-        <v>-137.3145236224105</v>
+        <v>-134.2713547971913</v>
       </c>
       <c r="G8" t="n">
-        <v>-143.9958307121568</v>
+        <v>-117.8282689978348</v>
       </c>
       <c r="H8" t="n">
-        <v>-120.1236322050729</v>
+        <v>-102.4739287679092</v>
       </c>
     </row>
     <row r="9">
@@ -676,25 +676,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-77.87142910982573</v>
+        <v>-53.60766223343013</v>
       </c>
       <c r="C9" t="n">
-        <v>-46.71424869472486</v>
+        <v>-33.434754896103</v>
       </c>
       <c r="D9" t="n">
-        <v>-160.1907967881204</v>
+        <v>-146.0742446263309</v>
       </c>
       <c r="E9" t="n">
-        <v>-143.7640390413834</v>
+        <v>-125.9969786359599</v>
       </c>
       <c r="F9" t="n">
-        <v>-133.540234008346</v>
+        <v>-133.0132582591699</v>
       </c>
       <c r="G9" t="n">
-        <v>-140.4616692211129</v>
+        <v>-116.6502151674868</v>
       </c>
       <c r="H9" t="n">
-        <v>-117.0904028105856</v>
+        <v>-101.4628523030801</v>
       </c>
     </row>
   </sheetData>
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9605642836688431</v>
+        <v>0.331546280217436</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9561688443063221</v>
+        <v>0.09118594931806967</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9462325466841454</v>
+        <v>-0.2006696832854042</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6345581042498005</v>
+        <v>-1.354649803442872</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.02101721102478127</v>
+        <v>-3.567107225193233</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1291228163078628</v>
+        <v>-13.27163631511512</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6009382306986988</v>
+        <v>-2.995221799583522</v>
       </c>
     </row>
     <row r="3">
@@ -783,25 +783,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02292539529518449</v>
+        <v>0.1209436757691309</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03476944909042561</v>
+        <v>0.1396096560438465</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003355702716111643</v>
+        <v>0.02593733574072732</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005433023016124926</v>
+        <v>0.02126771828734387</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01067806406673616</v>
+        <v>0.03849118315855927</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006773421125315325</v>
+        <v>0.0481473847837457</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01398917588498303</v>
+        <v>0.06573282563055892</v>
       </c>
     </row>
     <row r="4">
@@ -811,25 +811,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001428640754520523</v>
+        <v>0.02421612475789399</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003812290838982081</v>
+        <v>0.0790456793785307</v>
       </c>
       <c r="D4" t="n">
-        <v>5.214545732128446e-05</v>
+        <v>0.001164449232120451</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001194651133288657</v>
+        <v>0.0007697489228503174</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004374347139244044</v>
+        <v>0.001956687136066302</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001562597021285361</v>
+        <v>0.002560730354689189</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001001039430034282</v>
+        <v>0.01828556996369182</v>
       </c>
     </row>
     <row r="5">
@@ -839,25 +839,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03779736438590029</v>
+        <v>0.1556153101654654</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06174375141649624</v>
+        <v>0.2811506346756676</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007221181158320602</v>
+        <v>0.03412402719669018</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01093000975886416</v>
+        <v>0.02774434938596177</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02091493996941909</v>
+        <v>0.04423445643462008</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01250038807911723</v>
+        <v>0.05060365949898474</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02518460579468627</v>
+        <v>0.09891207289289827</v>
       </c>
     </row>
     <row r="6">
@@ -867,25 +867,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43.64585343886349</v>
+        <v>110.2893003810302</v>
       </c>
       <c r="C6" t="n">
-        <v>47.39739131029629</v>
+        <v>51.00633179652403</v>
       </c>
       <c r="D6" t="n">
-        <v>23.28075810671715</v>
+        <v>113.8889881287924</v>
       </c>
       <c r="E6" t="n">
-        <v>58.24117515621439</v>
+        <v>83.93773672923757</v>
       </c>
       <c r="F6" t="n">
-        <v>509.0185419865456</v>
+        <v>826.065963129341</v>
       </c>
       <c r="G6" t="n">
-        <v>111.5875569865318</v>
+        <v>637.3899984450466</v>
       </c>
       <c r="H6" t="n">
-        <v>132.1952128308615</v>
+        <v>303.763053101662</v>
       </c>
     </row>
     <row r="7">
@@ -895,25 +895,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01283076342751145</v>
+        <v>0.218987403265295</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01581795029539083</v>
+        <v>0.3294761907695506</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01616673781488129</v>
+        <v>0.7250320388962114</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1097161943043901</v>
+        <v>1.416867530557714</v>
       </c>
       <c r="F7" t="n">
-        <v>0.613222735214363</v>
+        <v>2.746003697106433</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2613725368991311</v>
+        <v>8.569566811565641</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1715211529926113</v>
+        <v>2.334322278693474</v>
       </c>
     </row>
     <row r="8">
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-105.3675407369604</v>
+        <v>-57.25252144175437</v>
       </c>
       <c r="C8" t="n">
-        <v>-77.54287500689874</v>
+        <v>-32.06594060457713</v>
       </c>
       <c r="D8" t="n">
-        <v>-201.0909432531406</v>
+        <v>-135.8656483834819</v>
       </c>
       <c r="E8" t="n">
-        <v>-183.6822095255992</v>
+        <v>-144.558369580724</v>
       </c>
       <c r="F8" t="n">
-        <v>-195.0991603040539</v>
+        <v>-156.1490642850594</v>
       </c>
       <c r="G8" t="n">
-        <v>-204.3357882636687</v>
+        <v>-137.2191063930966</v>
       </c>
       <c r="H8" t="n">
-        <v>-161.1864195150536</v>
+        <v>-110.5184417814489</v>
       </c>
     </row>
     <row r="9">
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-102.8679007047917</v>
+        <v>-54.75288140958572</v>
       </c>
       <c r="C9" t="n">
-        <v>-75.41872440359211</v>
+        <v>-29.9417900012705</v>
       </c>
       <c r="D9" t="n">
-        <v>-197.9573759399704</v>
+        <v>-132.7320810703116</v>
       </c>
       <c r="E9" t="n">
-        <v>-180.548642212429</v>
+        <v>-141.4248022675538</v>
       </c>
       <c r="F9" t="n">
-        <v>-191.3248706899894</v>
+        <v>-152.374774670995</v>
       </c>
       <c r="G9" t="n">
-        <v>-200.8016267726248</v>
+        <v>-133.6849449020527</v>
       </c>
       <c r="H9" t="n">
-        <v>-158.1531901205663</v>
+        <v>-107.4852123869616</v>
       </c>
     </row>
   </sheetData>
@@ -1030,25 +1030,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9599726745169764</v>
+        <v>0.3307557763126662</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9596793247795545</v>
+        <v>0.09293049533622266</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9448744910366358</v>
+        <v>-0.1358623228320213</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6470038135196563</v>
+        <v>-1.179941776537619</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02191569661993853</v>
+        <v>-3.626318925167627</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1903941298781625</v>
+        <v>-12.93141010460596</v>
       </c>
       <c r="H2" t="n">
-        <v>0.620640021725154</v>
+        <v>-2.90830780958239</v>
       </c>
     </row>
     <row r="3">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02315409014120591</v>
+        <v>0.116776638764425</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03243122615759742</v>
+        <v>0.1397175461902264</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00339576337078674</v>
+        <v>0.02546367005717043</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005360708627100644</v>
+        <v>0.0208287604259797</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01009073169191027</v>
+        <v>0.03871076016519584</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006622142990447115</v>
+        <v>0.04783706391415683</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01350911049650801</v>
+        <v>0.06488907325285902</v>
       </c>
     </row>
     <row r="4">
@@ -1086,25 +1086,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001450073025155768</v>
+        <v>0.02424476240417073</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003506960707099209</v>
+        <v>0.07889394446080078</v>
       </c>
       <c r="D4" t="n">
-        <v>5.346254467506206e-05</v>
+        <v>0.001101596907150273</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001153965374877482</v>
+        <v>0.0007126358373600718</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004190409552583176</v>
+        <v>0.001982055222676008</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001452659163378365</v>
+        <v>0.002499684265405862</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0009483666143356569</v>
+        <v>0.01823911318292729</v>
       </c>
     </row>
     <row r="5">
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03807982438451847</v>
+        <v>0.1557072972091248</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05921959732300794</v>
+        <v>0.2808806587517211</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00731180857757245</v>
+        <v>0.03319031345363091</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01074227803995727</v>
+        <v>0.02669523997569739</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02047048986366271</v>
+        <v>0.04452027878030423</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01205263109606514</v>
+        <v>0.04999684255436399</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02464610488079733</v>
+        <v>0.0984984384541404</v>
       </c>
     </row>
     <row r="6">
@@ -1142,25 +1142,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43.73003213397153</v>
+        <v>100.4814146796877</v>
       </c>
       <c r="C6" t="n">
-        <v>47.63615812538023</v>
+        <v>50.94072757827941</v>
       </c>
       <c r="D6" t="n">
-        <v>23.86141884034713</v>
+        <v>110.784373490879</v>
       </c>
       <c r="E6" t="n">
-        <v>57.85902632758197</v>
+        <v>78.00054220560912</v>
       </c>
       <c r="F6" t="n">
-        <v>410.1958514404799</v>
+        <v>813.6667445539605</v>
       </c>
       <c r="G6" t="n">
-        <v>114.5223274879149</v>
+        <v>682.4901603844278</v>
       </c>
       <c r="H6" t="n">
-        <v>116.3008023926126</v>
+        <v>306.0606604821406</v>
       </c>
     </row>
     <row r="7">
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01302324876251611</v>
+        <v>0.2192446007891197</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01455107506110309</v>
+        <v>0.3288466125216938</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01657507647028181</v>
+        <v>0.6860596293692232</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1059796335203445</v>
+        <v>1.311962756094876</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2937186196826993</v>
+        <v>2.781566232412323</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2429834471779878</v>
+        <v>8.365345620735146</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1144718501124888</v>
+        <v>2.28217090865373</v>
       </c>
     </row>
     <row r="8">
@@ -1198,25 +1198,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-105.1144031479037</v>
+        <v>-57.23242936041268</v>
       </c>
       <c r="C8" t="n">
-        <v>-78.79508268032514</v>
+        <v>-32.09476205432935</v>
       </c>
       <c r="D8" t="n">
-        <v>-200.5671142243376</v>
+        <v>-137.0308827811828</v>
       </c>
       <c r="E8" t="n">
-        <v>-184.4098603843661</v>
+        <v>-146.1773403163912</v>
       </c>
       <c r="F8" t="n">
-        <v>-196.2160893368801</v>
+        <v>-155.8141455155057</v>
       </c>
       <c r="G8" t="n">
-        <v>-206.0866701436225</v>
+        <v>-137.798180374113</v>
       </c>
       <c r="H8" t="n">
-        <v>-161.8648699862392</v>
+        <v>-111.0246234003225</v>
       </c>
     </row>
     <row r="9">
@@ -1226,25 +1226,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-102.6147631157351</v>
+        <v>-54.73278932824403</v>
       </c>
       <c r="C9" t="n">
-        <v>-76.67093207701851</v>
+        <v>-29.97061145102272</v>
       </c>
       <c r="D9" t="n">
-        <v>-197.4335469111674</v>
+        <v>-133.8973154680125</v>
       </c>
       <c r="E9" t="n">
-        <v>-181.2762930711959</v>
+        <v>-143.043773003221</v>
       </c>
       <c r="F9" t="n">
-        <v>-192.4417997228156</v>
+        <v>-152.0398559014413</v>
       </c>
       <c r="G9" t="n">
-        <v>-202.5525086525787</v>
+        <v>-134.2640188830692</v>
       </c>
       <c r="H9" t="n">
-        <v>-158.8316405917519</v>
+        <v>-107.9913940058351</v>
       </c>
     </row>
   </sheetData>
@@ -1305,25 +1305,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9601625574371938</v>
+        <v>0.3316407729906283</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9587816245798723</v>
+        <v>0.09263665014470535</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9453603350759208</v>
+        <v>-0.2032044365803733</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6420958470441605</v>
+        <v>-1.373819190321971</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008315384809658988</v>
+        <v>-3.622611767873734</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1716764811385471</v>
+        <v>-13.19183194151631</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6143987050142256</v>
+        <v>-2.994531652192842</v>
       </c>
     </row>
     <row r="3">
@@ -1333,25 +1333,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02308718425428442</v>
+        <v>0.1213126001216255</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03311522912620044</v>
+        <v>0.139697020500897</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003382705643326649</v>
+        <v>0.0259604709208272</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005391459285312099</v>
+        <v>0.02131534455075716</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01025554972529559</v>
+        <v>0.03869651129138112</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006662903593421538</v>
+        <v>0.04807886705590172</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01364917193797346</v>
+        <v>0.06584346907356495</v>
       </c>
     </row>
     <row r="4">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001443194121876012</v>
+        <v>0.02421270156086983</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003585039739998054</v>
+        <v>0.07891950215632515</v>
       </c>
       <c r="D4" t="n">
-        <v>5.299135703173977e-05</v>
+        <v>0.00116690751983191</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000117000980705748</v>
+        <v>0.0007760155085992099</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004248677409792372</v>
+        <v>0.001980466964150278</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000148624385558719</v>
+        <v>0.002546411220050436</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0009619530543582515</v>
+        <v>0.0182670008216378</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1389,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03798939486061882</v>
+        <v>0.1556043108685291</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05987520137751566</v>
+        <v>0.2809261507163852</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007279516263580965</v>
+        <v>0.0341600281005726</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01081669915943621</v>
+        <v>0.02785705491611075</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02061232012606143</v>
+        <v>0.04450243773267121</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01219116013998335</v>
+        <v>0.05046197796411112</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02479404865453274</v>
+        <v>0.09891866004972999</v>
       </c>
     </row>
     <row r="6">
@@ -1417,25 +1417,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43.69816116491739</v>
+        <v>111.2067286072691</v>
       </c>
       <c r="C6" t="n">
-        <v>47.56636585836899</v>
+        <v>50.95185539473217</v>
       </c>
       <c r="D6" t="n">
-        <v>23.66570875591387</v>
+        <v>114.0662834181936</v>
       </c>
       <c r="E6" t="n">
-        <v>58.04798860781163</v>
+        <v>84.55445230664559</v>
       </c>
       <c r="F6" t="n">
-        <v>429.5888964430966</v>
+        <v>814.5581489406782</v>
       </c>
       <c r="G6" t="n">
-        <v>112.8978943347214</v>
+        <v>644.6056757346033</v>
       </c>
       <c r="H6" t="n">
-        <v>119.2441691941383</v>
+        <v>303.3238574003537</v>
       </c>
     </row>
     <row r="7">
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01296146865415507</v>
+        <v>0.2189566591954204</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01487504044403696</v>
+        <v>0.3289526564660161</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01642899342714599</v>
+        <v>0.7265563324759887</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1074531465732459</v>
+        <v>1.428377935905222</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2978027919757878</v>
+        <v>2.779339714474052</v>
       </c>
       <c r="G7" t="n">
-        <v>0.248601092728327</v>
+        <v>8.521664140617856</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1163537556337831</v>
+        <v>2.333974573189093</v>
       </c>
     </row>
     <row r="8">
@@ -1473,25 +1473,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-105.1952401879427</v>
+        <v>-57.25492473557465</v>
       </c>
       <c r="C8" t="n">
-        <v>-78.4647857987374</v>
+        <v>-32.08990359081518</v>
       </c>
       <c r="D8" t="n">
-        <v>-200.7530163842459</v>
+        <v>-135.8213616727241</v>
       </c>
       <c r="E8" t="n">
-        <v>-184.119893063126</v>
+        <v>-144.3880991061225</v>
       </c>
       <c r="F8" t="n">
-        <v>-195.8570485143633</v>
+        <v>-155.8349881616455</v>
       </c>
       <c r="G8" t="n">
-        <v>-205.5381200912078</v>
+        <v>-137.3536866183779</v>
       </c>
       <c r="H8" t="n">
-        <v>-161.6546840066038</v>
+        <v>-110.4571606475433</v>
       </c>
     </row>
     <row r="9">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-102.6956001557741</v>
+        <v>-54.755284703406</v>
       </c>
       <c r="C9" t="n">
-        <v>-76.34063519543076</v>
+        <v>-29.96575298750855</v>
       </c>
       <c r="D9" t="n">
-        <v>-197.6194490710756</v>
+        <v>-132.6877943595539</v>
       </c>
       <c r="E9" t="n">
-        <v>-180.9863257499557</v>
+        <v>-141.2545317929522</v>
       </c>
       <c r="F9" t="n">
-        <v>-192.0827589002989</v>
+        <v>-152.060698547581</v>
       </c>
       <c r="G9" t="n">
-        <v>-202.0039586001639</v>
+        <v>-133.819525127334</v>
       </c>
       <c r="H9" t="n">
-        <v>-158.6214546121165</v>
+        <v>-107.423931253056</v>
       </c>
     </row>
   </sheetData>
@@ -1580,25 +1580,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5745882953537023</v>
+        <v>-0.09529870371211535</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6568247773002451</v>
+        <v>-0.1788667693046333</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1511924596886298</v>
+        <v>0.7671246277580815</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3274683387802064</v>
+        <v>0.512285256138577</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.772623014544634</v>
+        <v>-1.620846392404832</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.562418933459</v>
+        <v>-10.53627035621973</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4303816123030872</v>
+        <v>-1.858645389624109</v>
       </c>
     </row>
     <row r="3">
@@ -1608,25 +1608,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06569900849660007</v>
+        <v>0.09768352273144207</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07987894493467175</v>
+        <v>0.1394714634909062</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01616134701169525</v>
+        <v>0.008666708424569739</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00895331228301984</v>
+        <v>0.00678498525134294</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02059987631856957</v>
+        <v>0.02365116902482537</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01486820463796063</v>
+        <v>0.03051213772780049</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03436011561375286</v>
+        <v>0.05112833110848113</v>
       </c>
     </row>
     <row r="4">
@@ -1636,25 +1636,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01541142282301023</v>
+        <v>0.03967947110067679</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02984826060273414</v>
+        <v>0.1025339832791288</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001116464581698474</v>
+        <v>0.000225850250207748</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004339572374626174</v>
+        <v>0.0001594368292884267</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001187875720498618</v>
+        <v>0.001122850016162548</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004597695596677506</v>
+        <v>0.002069929265909452</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008076291754178639</v>
+        <v>0.02429858679022896</v>
       </c>
     </row>
     <row r="5">
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1241427517940948</v>
+        <v>0.1991970659941476</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1727664915506886</v>
+        <v>0.3202092804387918</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03341353889815436</v>
+        <v>0.01502831494904695</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02083164029697656</v>
+        <v>0.01262682974021693</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03446557297505176</v>
+        <v>0.03350895426841231</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02144223774860615</v>
+        <v>0.04549647531303334</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0678437055439287</v>
+        <v>0.1043444867839415</v>
       </c>
     </row>
     <row r="6">
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.79396205994987</v>
+        <v>59.08507670510761</v>
       </c>
       <c r="C6" t="n">
-        <v>56.18778685668866</v>
+        <v>91.61134957091917</v>
       </c>
       <c r="D6" t="n">
-        <v>114.6400178604583</v>
+        <v>55.44486085180752</v>
       </c>
       <c r="E6" t="n">
-        <v>131.3203652199833</v>
+        <v>46.30325350940905</v>
       </c>
       <c r="F6" t="n">
-        <v>2278.903155445175</v>
+        <v>2910.292526195482</v>
       </c>
       <c r="G6" t="n">
-        <v>403.7153644115958</v>
+        <v>696.3946837265512</v>
       </c>
       <c r="H6" t="n">
-        <v>507.7601086423085</v>
+        <v>643.1886250932126</v>
       </c>
     </row>
     <row r="7">
@@ -1720,25 +1720,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1384115073699965</v>
+        <v>0.7177304817682169</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1238463492318404</v>
+        <v>0.8558676381735604</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6922785262275559</v>
+        <v>0.07252070684772097</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7970885434005717</v>
+        <v>0.1489260289389288</v>
       </c>
       <c r="F7" t="n">
-        <v>1.665236834735479</v>
+        <v>1.579079825465527</v>
       </c>
       <c r="G7" t="n">
-        <v>1.538095037458935</v>
+        <v>6.929660114704114</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8258261330707297</v>
+        <v>1.717297465983011</v>
       </c>
     </row>
     <row r="8">
@@ -1748,25 +1748,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-68.93498714697273</v>
+        <v>-44.85766253809521</v>
       </c>
       <c r="C8" t="n">
-        <v>-50.67443068159825</v>
+        <v>-24.16341486748521</v>
       </c>
       <c r="D8" t="n">
-        <v>-140.7493524058823</v>
+        <v>-166.308406148316</v>
       </c>
       <c r="E8" t="n">
-        <v>-160.5938557581208</v>
+        <v>-173.6211181449624</v>
       </c>
       <c r="F8" t="n">
-        <v>-173.1253055731099</v>
+        <v>-166.5890143821832</v>
       </c>
       <c r="G8" t="n">
-        <v>-182.4348436299078</v>
+        <v>-138.3257802403265</v>
       </c>
       <c r="H8" t="n">
-        <v>-129.4187958659319</v>
+        <v>-118.9775660535614</v>
       </c>
     </row>
     <row r="9">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-68.10177380291651</v>
+        <v>-40.69159581781413</v>
       </c>
       <c r="C9" t="n">
-        <v>-49.96638048049604</v>
+        <v>-20.62316386197416</v>
       </c>
       <c r="D9" t="n">
-        <v>-139.7048299681588</v>
+        <v>-161.0857939596989</v>
       </c>
       <c r="E9" t="n">
-        <v>-159.5493333203973</v>
+        <v>-168.3985059563453</v>
       </c>
       <c r="F9" t="n">
-        <v>-171.8672090350884</v>
+        <v>-160.2985316920758</v>
       </c>
       <c r="G9" t="n">
-        <v>-181.2567897995598</v>
+        <v>-132.4355110885868</v>
       </c>
       <c r="H9" t="n">
-        <v>-128.4077194011028</v>
+        <v>-113.9221837294158</v>
       </c>
     </row>
   </sheetData>
@@ -1855,25 +1855,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9541294116774045</v>
+        <v>-0.1420423896512613</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9631493965794795</v>
+        <v>-0.09505119107743987</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9381172559484049</v>
+        <v>-0.4667254325745378</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8016544712030442</v>
+        <v>-3.195442231201792</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.03975161620129053</v>
+        <v>-7.84724024372605</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.4361228765266454</v>
+        <v>-29.43687168321477</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5301960071133996</v>
+        <v>-6.863895528574308</v>
       </c>
     </row>
     <row r="3">
@@ -1883,25 +1883,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0257911309731838</v>
+        <v>0.1098273070686085</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0286948142732736</v>
+        <v>0.140665499239454</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00352439279474574</v>
+        <v>0.03308348626255192</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003995137495313579</v>
+        <v>0.03338706694411277</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01030906473449286</v>
+        <v>0.0518409399565822</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009383485713902533</v>
+        <v>0.06816552619403783</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01361633766415202</v>
+        <v>0.07282830427755786</v>
       </c>
     </row>
     <row r="4">
@@ -1911,25 +1911,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001661757361301382</v>
+        <v>0.04137285823705832</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003205145189709777</v>
+        <v>0.09524397789408702</v>
       </c>
       <c r="D4" t="n">
-        <v>6.001593510315817e-05</v>
+        <v>0.001422478911118617</v>
       </c>
       <c r="E4" t="n">
-        <v>6.484032441698821e-05</v>
+        <v>0.001371514835720522</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004454611008260561</v>
+        <v>0.003790425825584689</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002576805743774777</v>
+        <v>0.005461225293307173</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0009491500809558065</v>
+        <v>0.02477708016614606</v>
       </c>
     </row>
     <row r="5">
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04076465823849602</v>
+        <v>0.2034031913148324</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05661400171079392</v>
+        <v>0.3086162307690362</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007746995230614136</v>
+        <v>0.03771576475585</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00805234899994953</v>
+        <v>0.03703396867364504</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02110594941778398</v>
+        <v>0.06156643424451905</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01605243203933528</v>
+        <v>0.0739001034729125</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02505606427282881</v>
+        <v>0.1203726155384659</v>
       </c>
     </row>
     <row r="6">
@@ -1967,25 +1967,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46.03281913021944</v>
+        <v>65.8133842892974</v>
       </c>
       <c r="C6" t="n">
-        <v>49.74904977849758</v>
+        <v>76.44978129266008</v>
       </c>
       <c r="D6" t="n">
-        <v>25.42180791899665</v>
+        <v>102.2690307876132</v>
       </c>
       <c r="E6" t="n">
-        <v>43.97048593467004</v>
+        <v>87.54297765786771</v>
       </c>
       <c r="F6" t="n">
-        <v>394.3375252373449</v>
+        <v>3230.535748595226</v>
       </c>
       <c r="G6" t="n">
-        <v>197.5854969894635</v>
+        <v>996.8018573557155</v>
       </c>
       <c r="H6" t="n">
-        <v>126.1828641648654</v>
+        <v>759.9021299963966</v>
       </c>
     </row>
     <row r="7">
@@ -1995,25 +1995,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01492440664968962</v>
+        <v>0.7481474353226385</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01329878265895299</v>
+        <v>0.7953722836981858</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01860683437005075</v>
+        <v>0.8870267300202889</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05954904686617864</v>
+        <v>2.524185459491084</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6244746152619308</v>
+        <v>5.31865074239145</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8620344787201158</v>
+        <v>18.2747687253395</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2654813607544864</v>
+        <v>4.75802522937719</v>
       </c>
     </row>
     <row r="8">
@@ -2023,25 +2023,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-102.7979529484597</v>
+        <v>-44.14721359189583</v>
       </c>
       <c r="C8" t="n">
-        <v>-80.14496832951109</v>
+        <v>-25.26970236774682</v>
       </c>
       <c r="D8" t="n">
-        <v>-198.1389093649711</v>
+        <v>-127.6624385632549</v>
       </c>
       <c r="E8" t="n">
-        <v>-196.5152400130188</v>
+        <v>-128.4286280404083</v>
       </c>
       <c r="F8" t="n">
-        <v>-194.6264163964341</v>
+        <v>-134.9571996902541</v>
       </c>
       <c r="G8" t="n">
-        <v>-192.3309557738359</v>
+        <v>-115.0419704410031</v>
       </c>
       <c r="H8" t="n">
-        <v>-160.7590738043718</v>
+        <v>-95.91785878242717</v>
       </c>
     </row>
     <row r="9">
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-100.2983129162911</v>
+        <v>-39.98114687161475</v>
       </c>
       <c r="C9" t="n">
-        <v>-78.02081772620446</v>
+        <v>-21.72945136223577</v>
       </c>
       <c r="D9" t="n">
-        <v>-195.0053420518008</v>
+        <v>-122.4398263746378</v>
       </c>
       <c r="E9" t="n">
-        <v>-193.3816726998485</v>
+        <v>-123.2060158517912</v>
       </c>
       <c r="F9" t="n">
-        <v>-190.8521267823697</v>
+        <v>-128.6667170001467</v>
       </c>
       <c r="G9" t="n">
-        <v>-188.796794282792</v>
+        <v>-109.1517012892634</v>
       </c>
       <c r="H9" t="n">
-        <v>-157.7258444098844</v>
+        <v>-90.86247645828159</v>
       </c>
     </row>
   </sheetData>
@@ -2130,25 +2130,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.912209158539979</v>
+        <v>0.2166211764498494</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8852940020622088</v>
+        <v>0.05862168772670395</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8313103277463768</v>
+        <v>-1.013781923018405</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6380365761857613</v>
+        <v>0.2738968890435887</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4545527545382828</v>
+        <v>-0.1327446125925906</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6307799250125548</v>
+        <v>-1.704010051176522</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7253637906808607</v>
+        <v>-0.383566138927896</v>
       </c>
     </row>
     <row r="3">
@@ -2158,25 +2158,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03328100652028372</v>
+        <v>0.08805736027465022</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0575754983976625</v>
+        <v>0.1275520822036686</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008089257614176957</v>
+        <v>0.0267797362630982</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009639719401722455</v>
+        <v>0.01167813116860228</v>
       </c>
       <c r="F3" t="n">
-        <v>0.009032413891585447</v>
+        <v>0.01391048592906202</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006408358623672829</v>
+        <v>0.01719541542512284</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02067104240818398</v>
+        <v>0.04752886854403402</v>
       </c>
     </row>
     <row r="4">
@@ -2186,25 +2186,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0031804056234258</v>
+        <v>0.02837952540671537</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009976753252198945</v>
+        <v>0.08187801254835597</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0001636008321496776</v>
+        <v>0.001953032417292595</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001183279803157289</v>
+        <v>0.0002373673939622514</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0002336861290907364</v>
+        <v>0.0004853021185230773</v>
       </c>
       <c r="G4" t="n">
-        <v>6.624839876136814e-05</v>
+        <v>0.0004851749627405309</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002289837035990376</v>
+        <v>0.01890306914126497</v>
       </c>
     </row>
     <row r="5">
@@ -2214,25 +2214,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05639508509990742</v>
+        <v>0.1684622373314428</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09988369863095252</v>
+        <v>0.2861433426595069</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01279065409389518</v>
+        <v>0.04419312635798235</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0108778665332743</v>
+        <v>0.01540673209873695</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01528679590662269</v>
+        <v>0.02202957372540552</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008139311934148252</v>
+        <v>0.02202668751175562</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03389556869980006</v>
+        <v>0.09304361661413835</v>
       </c>
     </row>
     <row r="6">
@@ -2242,25 +2242,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32.17041905348329</v>
+        <v>64.17425988554947</v>
       </c>
       <c r="C6" t="n">
-        <v>45.36782853579493</v>
+        <v>53.03025651789808</v>
       </c>
       <c r="D6" t="n">
-        <v>38.47101636253234</v>
+        <v>136.1536183766771</v>
       </c>
       <c r="E6" t="n">
-        <v>43.61078820156202</v>
+        <v>51.18139053149687</v>
       </c>
       <c r="F6" t="n">
-        <v>251.4139474289248</v>
+        <v>677.6169516028521</v>
       </c>
       <c r="G6" t="n">
-        <v>90.4122119201004</v>
+        <v>158.1520874270289</v>
       </c>
       <c r="H6" t="n">
-        <v>83.57436858373296</v>
+        <v>190.0514273902504</v>
       </c>
     </row>
     <row r="7">
@@ -2270,25 +2270,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02856353637440437</v>
+        <v>0.256379314849746</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04139552665787664</v>
+        <v>0.3412281024658381</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05072142225859174</v>
+        <v>1.214003399195253</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1086718567304926</v>
+        <v>0.219497090462697</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1637977539288787</v>
+        <v>0.6833261905214868</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1108123963753666</v>
+        <v>1.62608527565375</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08399374872093511</v>
+        <v>0.7234198955247951</v>
       </c>
     </row>
     <row r="8">
@@ -2298,25 +2298,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-89.76269110839642</v>
+        <v>-54.55548461336332</v>
       </c>
       <c r="C8" t="n">
-        <v>-61.11246350529294</v>
+        <v>-31.53787186829827</v>
       </c>
       <c r="D8" t="n">
-        <v>-175.0797019937009</v>
+        <v>-125.0058125986938</v>
       </c>
       <c r="E8" t="n">
-        <v>-181.8830561939221</v>
+        <v>-169.2639300642646</v>
       </c>
       <c r="F8" t="n">
-        <v>-209.3998234632946</v>
+        <v>-192.3992123405254</v>
       </c>
       <c r="G8" t="n">
-        <v>-222.9303823127142</v>
+        <v>-177.1440236198893</v>
       </c>
       <c r="H8" t="n">
-        <v>-156.6946864295535</v>
+        <v>-124.9843891841725</v>
       </c>
     </row>
     <row r="9">
@@ -2326,25 +2326,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-86.42983773217156</v>
+        <v>-52.05584458119467</v>
       </c>
       <c r="C9" t="n">
-        <v>-58.28026270088409</v>
+        <v>-29.41372126499164</v>
       </c>
       <c r="D9" t="n">
-        <v>-170.9016122428072</v>
+        <v>-121.8722452855235</v>
       </c>
       <c r="E9" t="n">
-        <v>-177.7049664430284</v>
+        <v>-166.1303627510944</v>
       </c>
       <c r="F9" t="n">
-        <v>-204.3674373112086</v>
+        <v>-188.6249227264609</v>
       </c>
       <c r="G9" t="n">
-        <v>-218.2181669913224</v>
+        <v>-173.6098621288455</v>
       </c>
       <c r="H9" t="n">
-        <v>-152.650380570237</v>
+        <v>-121.9511597896851</v>
       </c>
     </row>
   </sheetData>
@@ -2405,25 +2405,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7126942758079293</v>
+        <v>0.4672794090282077</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7123365349622541</v>
+        <v>0.3138847756431935</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7603655739549162</v>
+        <v>0.5289350788612099</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1937708921914141</v>
+        <v>-0.7390396217752573</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.0758087402591</v>
+        <v>0.173927657111413</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.974672759275135</v>
+        <v>-3.792948401954259</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5098093345000915</v>
+        <v>-0.5079935171809153</v>
       </c>
     </row>
     <row r="3">
@@ -2433,25 +2433,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04163651853851061</v>
+        <v>0.07941173171249488</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07716481520106851</v>
+        <v>0.1071582079812342</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01168713643817648</v>
+        <v>0.01371820929239961</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01383103340773538</v>
+        <v>0.01646183879681055</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02704074650411473</v>
+        <v>0.01529145811184021</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01868552079057424</v>
+        <v>0.01558739510473607</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03167429514669665</v>
+        <v>0.04127147349991925</v>
       </c>
     </row>
     <row r="4">
@@ -2461,25 +2461,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01040824675634297</v>
+        <v>0.01929891017177407</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02502002913492471</v>
+        <v>0.05967606244703398</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002324054044858342</v>
+        <v>0.0004568543649723824</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003902507528086852</v>
+        <v>0.0005685023198346721</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001746199976899854</v>
+        <v>0.0003539144248407396</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0005337394158422709</v>
+        <v>0.0008599888751610404</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00638847857355072</v>
+        <v>0.01353570543393615</v>
       </c>
     </row>
     <row r="5">
@@ -2489,25 +2489,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1020208153091464</v>
+        <v>0.1389205174615113</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1581772080134325</v>
+        <v>0.2442868446049316</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01524484845729318</v>
+        <v>0.02137415179539021</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01975476531899797</v>
+        <v>0.02384328668272627</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04178755768048491</v>
+        <v>0.01881261345057458</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02310280103888424</v>
+        <v>0.029325566919687</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06001466596970655</v>
+        <v>0.07942716348580349</v>
       </c>
     </row>
     <row r="6">
@@ -2517,25 +2517,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.66271439283052</v>
+        <v>63.09802878655775</v>
       </c>
       <c r="C6" t="n">
-        <v>48.68066247419407</v>
+        <v>49.66486361865586</v>
       </c>
       <c r="D6" t="n">
-        <v>39.99140460717705</v>
+        <v>41.15516395496186</v>
       </c>
       <c r="E6" t="n">
-        <v>30.3421786201176</v>
+        <v>97.57248178548949</v>
       </c>
       <c r="F6" t="n">
-        <v>3832.269033079705</v>
+        <v>1214.07219112323</v>
       </c>
       <c r="G6" t="n">
-        <v>410.1218336052762</v>
+        <v>220.5487054557235</v>
       </c>
       <c r="H6" t="n">
-        <v>733.0113044632168</v>
+        <v>281.018572454103</v>
       </c>
     </row>
     <row r="7">
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09347748998706129</v>
+        <v>0.1748254144117795</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1038130599057711</v>
+        <v>0.2491078110199658</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07205301159666522</v>
+        <v>0.1431392743971177</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7168088863687807</v>
+        <v>1.047219676312923</v>
       </c>
       <c r="F7" t="n">
-        <v>2.44792992412312</v>
+        <v>0.2495694429639647</v>
       </c>
       <c r="G7" t="n">
-        <v>1.785550890747261</v>
+        <v>2.879973025597782</v>
       </c>
       <c r="H7" t="n">
-        <v>0.869938877121443</v>
+        <v>0.7906391074505889</v>
       </c>
     </row>
     <row r="8">
@@ -2573,25 +2573,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-61.6076661052181</v>
+        <v>-61.11101309163962</v>
       </c>
       <c r="C8" t="n">
-        <v>-39.3211791421795</v>
+        <v>-36.28236454541154</v>
       </c>
       <c r="D8" t="n">
-        <v>-159.7075728412415</v>
+        <v>-155.5140637754144</v>
       </c>
       <c r="E8" t="n">
-        <v>-148.8231424600981</v>
+        <v>-150.9226084473208</v>
       </c>
       <c r="F8" t="n">
-        <v>-149.1081456392258</v>
+        <v>-200.6078407065868</v>
       </c>
       <c r="G8" t="n">
-        <v>-164.8544677621223</v>
+        <v>-163.4061865118315</v>
       </c>
       <c r="H8" t="n">
-        <v>-120.5703623250142</v>
+        <v>-127.9740128463674</v>
       </c>
     </row>
     <row r="9">
@@ -2601,25 +2601,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-54.94195935276837</v>
+        <v>-58.61137305947097</v>
       </c>
       <c r="C9" t="n">
-        <v>-33.65677753336182</v>
+        <v>-34.15821394210491</v>
       </c>
       <c r="D9" t="n">
-        <v>-151.3513933394541</v>
+        <v>-152.3804964622441</v>
       </c>
       <c r="E9" t="n">
-        <v>-140.4669629583107</v>
+        <v>-147.7890411341506</v>
       </c>
       <c r="F9" t="n">
-        <v>-139.0433733350539</v>
+        <v>-196.8335510925224</v>
       </c>
       <c r="G9" t="n">
-        <v>-155.4300371193387</v>
+        <v>-159.8720250207876</v>
       </c>
       <c r="H9" t="n">
-        <v>-112.4817506063813</v>
+        <v>-124.9407834518801</v>
       </c>
     </row>
   </sheetData>
@@ -2680,25 +2680,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6091871904353768</v>
+        <v>0.4154479296916136</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3192841414117227</v>
+        <v>-0.1322314722456337</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03531135761680015</v>
+        <v>0.5113957962081657</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3854158469685276</v>
+        <v>-0.1940476005628766</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.653782775033653</v>
+        <v>0.5814349952326638</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.672574900106149</v>
+        <v>-0.5361319581706192</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7913318054407382</v>
+        <v>0.1076446150255523</v>
       </c>
     </row>
     <row r="3">
@@ -2708,25 +2708,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06543720209508468</v>
+        <v>0.08090448150904299</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1100648223636634</v>
+        <v>0.1531763699905859</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0143905110446029</v>
+        <v>0.01285350415709671</v>
       </c>
       <c r="E3" t="n">
-        <v>0.008620451101219855</v>
+        <v>0.007964628447193176</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02027738792087542</v>
+        <v>0.008387825507727181</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0183788852209626</v>
+        <v>0.009808009722161141</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03952820995773481</v>
+        <v>0.04551580322230118</v>
       </c>
     </row>
     <row r="4">
@@ -2736,25 +2736,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01415800596708242</v>
+        <v>0.02117661319422033</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05920644323827909</v>
+        <v>0.09847779737808317</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009355870015678716</v>
+        <v>0.0004738645422939216</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004529006200176796</v>
+        <v>0.0003903412104090321</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001136960960578933</v>
+        <v>0.000179325932160729</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00083839050527011</v>
+        <v>0.0002756249982301989</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01278804804879935</v>
+        <v>0.0201622612092329</v>
       </c>
     </row>
     <row r="5">
@@ -2764,25 +2764,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.118987419364748</v>
+        <v>0.1455218650039242</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2433237416247726</v>
+        <v>0.3138117228181305</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03058736669881655</v>
+        <v>0.02176842994554089</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02128146188629155</v>
+        <v>0.019757054699753</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03371885170908008</v>
+        <v>0.01339126327725391</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02895497375702679</v>
+        <v>0.01660195766258302</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07947563584012259</v>
+        <v>0.08847538223453093</v>
       </c>
     </row>
     <row r="6">
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.25784289138527</v>
+        <v>86.9889906939441</v>
       </c>
       <c r="C6" t="n">
-        <v>78.16372995605754</v>
+        <v>102.0047354106846</v>
       </c>
       <c r="D6" t="n">
-        <v>97.2159466431858</v>
+        <v>74.42378552135858</v>
       </c>
       <c r="E6" t="n">
-        <v>92.18219227690216</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>2536.900252179159</v>
+        <v>734.2250479169257</v>
       </c>
       <c r="G6" t="n">
-        <v>607.9926535041488</v>
+        <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>578.9521029084731</v>
+        <v>199.6070932571522</v>
       </c>
     </row>
     <row r="7">
@@ -2820,25 +2820,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1271544470463447</v>
+        <v>0.1921892503284702</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2456592678432786</v>
+        <v>0.8212077996766968</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2900615036160575</v>
+        <v>0.1489129663171561</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8318835690491414</v>
+        <v>0.7209750380322987</v>
       </c>
       <c r="F7" t="n">
-        <v>1.593861410365002</v>
+        <v>0.1276950295827134</v>
       </c>
       <c r="G7" t="n">
-        <v>2.804718686771068</v>
+        <v>0.9260650498998939</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9822231474484822</v>
+        <v>0.4895075223062048</v>
       </c>
     </row>
     <row r="8">
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-70.37707537683175</v>
+        <v>-57.53258357646907</v>
       </c>
       <c r="C8" t="n">
-        <v>-40.40087356795317</v>
+        <v>-26.76886245311874</v>
       </c>
       <c r="D8" t="n">
-        <v>-144.4610647465382</v>
+        <v>-152.7463701101039</v>
       </c>
       <c r="E8" t="n">
-        <v>-159.6965946065761</v>
+        <v>-156.8182753599861</v>
       </c>
       <c r="F8" t="n">
-        <v>-174.2643064069132</v>
+        <v>-216.2839445028378</v>
       </c>
       <c r="G8" t="n">
-        <v>-168.0166376627819</v>
+        <v>-188.715263636421</v>
       </c>
       <c r="H8" t="n">
-        <v>-126.2027587279324</v>
+        <v>-133.1442166064894</v>
       </c>
     </row>
     <row r="9">
@@ -2876,25 +2876,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-69.54386203277554</v>
+        <v>-54.1997302002442</v>
       </c>
       <c r="C9" t="n">
-        <v>-39.69282336685096</v>
+        <v>-23.93666164870989</v>
       </c>
       <c r="D9" t="n">
-        <v>-143.4165423088147</v>
+        <v>-148.5682803592102</v>
       </c>
       <c r="E9" t="n">
-        <v>-158.6520721688527</v>
+        <v>-152.6401856090924</v>
       </c>
       <c r="F9" t="n">
-        <v>-173.0062098688917</v>
+        <v>-211.2515583507519</v>
       </c>
       <c r="G9" t="n">
-        <v>-166.838583832434</v>
+        <v>-184.0030483150292</v>
       </c>
       <c r="H9" t="n">
-        <v>-125.1916822631033</v>
+        <v>-129.099910747173</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/global/metrics_summary.xlsx
+++ b/results/cross_validation/global/metrics_summary.xlsx
@@ -480,25 +480,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002100854051636625</v>
+        <v>0.001663351572512517</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.03313127500792068</v>
+        <v>-0.03272044035445809</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1499899731737249</v>
+        <v>0.1890316278398306</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.560093126966859</v>
+        <v>-5.324041223028572</v>
       </c>
       <c r="F2" t="n">
-        <v>-11.35642945124785</v>
+        <v>-7.838853170663739</v>
       </c>
       <c r="G2" t="n">
-        <v>-36.82205196766856</v>
+        <v>-20.95917759134523</v>
       </c>
       <c r="H2" t="n">
-        <v>-8.936602498944305</v>
+        <v>-5.660682907663276</v>
       </c>
     </row>
     <row r="3">
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09053978670866247</v>
+        <v>0.09056733275072082</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1250576028800978</v>
+        <v>0.1250165168603797</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01316214816609958</v>
+        <v>0.01274456315708121</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02376200770946218</v>
+        <v>0.02329346183725459</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04794572948620329</v>
+        <v>0.04728687099602898</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0601899539622931</v>
+        <v>0.05954658642743729</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0601095381521364</v>
+        <v>0.05974255533815043</v>
       </c>
     </row>
     <row r="4">
@@ -536,25 +536,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03615096976637657</v>
+        <v>0.03616681920262446</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08985838572690592</v>
+        <v>0.08982265266988415</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0008243678813678033</v>
+        <v>0.0007865039913824574</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002144533174698487</v>
+        <v>0.002067366413625316</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005293868823923773</v>
+        <v>0.005049499021874248</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006786333004272577</v>
+        <v>0.006513663051811642</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02350974306292419</v>
+        <v>0.02340108405853371</v>
       </c>
     </row>
     <row r="5">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1901340836525018</v>
+        <v>0.1901757587144704</v>
       </c>
       <c r="C5" t="n">
-        <v>0.299763883293011</v>
+        <v>0.2997042753613705</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02871180735111956</v>
+        <v>0.02804467848598834</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0463091046631058</v>
+        <v>0.04546830119572664</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07275897761736193</v>
+        <v>0.07105982706054279</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08237920249840112</v>
+        <v>0.08070726765175266</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1200095098459169</v>
+        <v>0.1191933514116419</v>
       </c>
     </row>
     <row r="6">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59.65675944222733</v>
+        <v>59.6515542544264</v>
       </c>
       <c r="C6" t="n">
-        <v>65.39380667480289</v>
+        <v>65.31538262675627</v>
       </c>
       <c r="D6" t="n">
-        <v>124.8963146215416</v>
+        <v>121.8175499779077</v>
       </c>
       <c r="E6" t="n">
-        <v>241.49523289282</v>
+        <v>236.4519569224191</v>
       </c>
       <c r="F6" t="n">
-        <v>6676.140047443704</v>
+        <v>6054.035375294063</v>
       </c>
       <c r="G6" t="n">
-        <v>1540.903089398291</v>
+        <v>1421.89189412533</v>
       </c>
       <c r="H6" t="n">
-        <v>1451.414208412231</v>
+        <v>1326.527285533484</v>
       </c>
     </row>
     <row r="7">
@@ -620,25 +620,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3251754226209727</v>
+        <v>0.3253177679700834</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7466805050224208</v>
+        <v>0.7463839779505127</v>
       </c>
       <c r="D7" t="n">
-        <v>0.25608006556484</v>
+        <v>0.2443410644420186</v>
       </c>
       <c r="E7" t="n">
-        <v>3.940058222624694</v>
+        <v>3.798319046796219</v>
       </c>
       <c r="F7" t="n">
-        <v>7.422269087102205</v>
+        <v>5.311381201028868</v>
       </c>
       <c r="G7" t="n">
-        <v>22.70373204680712</v>
+        <v>13.18562568307967</v>
       </c>
       <c r="H7" t="n">
-        <v>5.898999224957042</v>
+        <v>3.935228123544563</v>
       </c>
     </row>
     <row r="8">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-54.44087557748635</v>
+        <v>-54.43342401060718</v>
       </c>
       <c r="C8" t="n">
-        <v>-34.14280509720521</v>
+        <v>-34.14877117873696</v>
       </c>
       <c r="D8" t="n">
-        <v>-147.1187670640544</v>
+        <v>-148.1061679728599</v>
       </c>
       <c r="E8" t="n">
-        <v>-127.0415010736833</v>
+        <v>-127.8110746590462</v>
       </c>
       <c r="F8" t="n">
-        <v>-134.2713547971913</v>
+        <v>-140.7885885935385</v>
       </c>
       <c r="G8" t="n">
-        <v>-117.8282689978348</v>
+        <v>-123.8463325059322</v>
       </c>
       <c r="H8" t="n">
-        <v>-102.4739287679092</v>
+        <v>-104.8557264867868</v>
       </c>
     </row>
     <row r="9">
@@ -676,25 +676,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-53.60766223343013</v>
+        <v>-53.60021066655096</v>
       </c>
       <c r="C9" t="n">
-        <v>-33.434754896103</v>
+        <v>-33.44072097763475</v>
       </c>
       <c r="D9" t="n">
-        <v>-146.0742446263309</v>
+        <v>-147.0616455351364</v>
       </c>
       <c r="E9" t="n">
-        <v>-125.9969786359599</v>
+        <v>-126.7665522213228</v>
       </c>
       <c r="F9" t="n">
-        <v>-133.0132582591699</v>
+        <v>-139.4927517275341</v>
       </c>
       <c r="G9" t="n">
-        <v>-116.6502151674868</v>
+        <v>-122.627456681064</v>
       </c>
       <c r="H9" t="n">
-        <v>-101.4628523030801</v>
+        <v>-103.8315563015405</v>
       </c>
     </row>
   </sheetData>
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.331546280217436</v>
+        <v>0.3333144153604205</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09118594931806967</v>
+        <v>0.09289578951368505</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2006696832854042</v>
+        <v>-0.1936108405065735</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.354649803442872</v>
+        <v>-1.33743936311624</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.567107225193233</v>
+        <v>-2.805955399847335</v>
       </c>
       <c r="G2" t="n">
-        <v>-13.27163631511512</v>
+        <v>-7.795029474124064</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.995221799583522</v>
+        <v>-1.950970812120018</v>
       </c>
     </row>
     <row r="3">
@@ -783,25 +783,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1209436757691309</v>
+        <v>0.1192476519149277</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1396096560438465</v>
+        <v>0.1387153365666276</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02593733574072732</v>
+        <v>0.02539369155019026</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02126771828734387</v>
+        <v>0.02056039625413864</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03849118315855927</v>
+        <v>0.04026316259577434</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0481473847837457</v>
+        <v>0.04892091772553721</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06573282563055892</v>
+        <v>0.06551685943453263</v>
       </c>
     </row>
     <row r="4">
@@ -811,25 +811,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02421612475789399</v>
+        <v>0.0241520703889165</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0790456793785307</v>
+        <v>0.07889696305995075</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001164449232120451</v>
+        <v>0.001157603332562983</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007697489228503174</v>
+        <v>0.0007641227282952568</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001956687136066302</v>
+        <v>0.002174282986463839</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002560730354689189</v>
+        <v>0.002608834428652517</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01828556996369182</v>
+        <v>0.01829231282080698</v>
       </c>
     </row>
     <row r="5">
@@ -839,25 +839,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1556153101654654</v>
+        <v>0.1554093639035837</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2811506346756676</v>
+        <v>0.2808860321553045</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03412402719669018</v>
+        <v>0.03402357025009256</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02774434938596177</v>
+        <v>0.02764276990996483</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04423445643462008</v>
+        <v>0.04662920743979935</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05060365949898474</v>
+        <v>0.05107675037287041</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09891207289289827</v>
+        <v>0.09927794900526922</v>
       </c>
     </row>
     <row r="6">
@@ -867,25 +867,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>110.2893003810302</v>
+        <v>108.351117620765</v>
       </c>
       <c r="C6" t="n">
-        <v>51.00633179652403</v>
+        <v>50.9626062962645</v>
       </c>
       <c r="D6" t="n">
-        <v>113.8889881287924</v>
+        <v>114.21602366519</v>
       </c>
       <c r="E6" t="n">
-        <v>83.93773672923757</v>
+        <v>85.25558862230646</v>
       </c>
       <c r="F6" t="n">
-        <v>826.065963129341</v>
+        <v>892.2730965893073</v>
       </c>
       <c r="G6" t="n">
-        <v>637.3899984450466</v>
+        <v>631.7734709423003</v>
       </c>
       <c r="H6" t="n">
-        <v>303.763053101662</v>
+        <v>313.8053172893556</v>
       </c>
     </row>
     <row r="7">
@@ -895,25 +895,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.218987403265295</v>
+        <v>0.2184121246641154</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3294761907695506</v>
+        <v>0.32885913728786</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7250320388962114</v>
+        <v>0.7207871489695324</v>
       </c>
       <c r="E7" t="n">
-        <v>1.416867530557714</v>
+        <v>1.406533389689357</v>
       </c>
       <c r="F7" t="n">
-        <v>2.746003697106433</v>
+        <v>2.289617236089451</v>
       </c>
       <c r="G7" t="n">
-        <v>8.569566811565641</v>
+        <v>5.283670052674553</v>
       </c>
       <c r="H7" t="n">
-        <v>2.334322278693474</v>
+        <v>1.707979848229145</v>
       </c>
     </row>
     <row r="8">
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-57.25252144175437</v>
+        <v>-57.29754792686073</v>
       </c>
       <c r="C8" t="n">
-        <v>-32.06594060457713</v>
+        <v>-32.09418814309497</v>
       </c>
       <c r="D8" t="n">
-        <v>-135.8656483834819</v>
+        <v>-135.9894735797111</v>
       </c>
       <c r="E8" t="n">
-        <v>-144.558369580724</v>
+        <v>-144.7124249939473</v>
       </c>
       <c r="F8" t="n">
-        <v>-156.1490642850594</v>
+        <v>-159.5385209150676</v>
       </c>
       <c r="G8" t="n">
-        <v>-137.2191063930966</v>
+        <v>-142.72129341135</v>
       </c>
       <c r="H8" t="n">
-        <v>-110.5184417814489</v>
+        <v>-112.0589081616719</v>
       </c>
     </row>
     <row r="9">
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-54.75288140958572</v>
+        <v>-54.79790789469208</v>
       </c>
       <c r="C9" t="n">
-        <v>-29.9417900012705</v>
+        <v>-29.97003753978834</v>
       </c>
       <c r="D9" t="n">
-        <v>-132.7320810703116</v>
+        <v>-132.8559062665409</v>
       </c>
       <c r="E9" t="n">
-        <v>-141.4248022675538</v>
+        <v>-141.578857680777</v>
       </c>
       <c r="F9" t="n">
-        <v>-152.374774670995</v>
+        <v>-155.6510103170546</v>
       </c>
       <c r="G9" t="n">
-        <v>-133.6849449020527</v>
+        <v>-139.0646659367454</v>
       </c>
       <c r="H9" t="n">
-        <v>-107.4852123869616</v>
+        <v>-108.9863976059331</v>
       </c>
     </row>
   </sheetData>
@@ -1030,25 +1030,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3307557763126662</v>
+        <v>0.319504139343572</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09293049533622266</v>
+        <v>0.09470939783730981</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1358623228320213</v>
+        <v>-0.166816907499501</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.179941776537619</v>
+        <v>-1.257931702675925</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.626318925167627</v>
+        <v>-2.86089965534522</v>
       </c>
       <c r="G2" t="n">
-        <v>-12.93141010460596</v>
+        <v>-7.691836386543272</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.90830780958239</v>
+        <v>-1.927211852480506</v>
       </c>
     </row>
     <row r="3">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.116776638764425</v>
+        <v>0.1114331050688294</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1397175461902264</v>
+        <v>0.1388219872430558</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02546367005717043</v>
+        <v>0.0251631811328527</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0208287604259797</v>
+        <v>0.02037888788503277</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03871076016519584</v>
+        <v>0.04050427645591751</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04783706391415683</v>
+        <v>0.04870905585450708</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06488907325285902</v>
+        <v>0.06416841560669923</v>
       </c>
     </row>
     <row r="4">
@@ -1086,25 +1086,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02424476240417073</v>
+        <v>0.02465237632942908</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07889394446080078</v>
+        <v>0.0787392213283392</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001101596907150273</v>
+        <v>0.001131617688759436</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007126358373600718</v>
+        <v>0.0007381312046755679</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001982055222676008</v>
+        <v>0.002205671783068699</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002499684265405862</v>
+        <v>0.002578224675669679</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01823911318292729</v>
+        <v>0.01834087383499028</v>
       </c>
     </row>
     <row r="5">
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1557072972091248</v>
+        <v>0.1570107522733048</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2808806587517211</v>
+        <v>0.2806050985430222</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03319031345363091</v>
+        <v>0.0336395256916538</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02669523997569739</v>
+        <v>0.02716857016251624</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04452027878030423</v>
+        <v>0.04696458009041174</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04999684255436399</v>
+        <v>0.05077622155763147</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0984984384541404</v>
+        <v>0.09936079138642338</v>
       </c>
     </row>
     <row r="6">
@@ -1142,25 +1142,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100.4814146796877</v>
+        <v>89.60779352000679</v>
       </c>
       <c r="C6" t="n">
-        <v>50.94072757827941</v>
+        <v>50.89470494412509</v>
       </c>
       <c r="D6" t="n">
-        <v>110.784373490879</v>
+        <v>112.9442229685745</v>
       </c>
       <c r="E6" t="n">
-        <v>78.00054220560912</v>
+        <v>82.66932211572338</v>
       </c>
       <c r="F6" t="n">
-        <v>813.6667445539605</v>
+        <v>879.7168451142232</v>
       </c>
       <c r="G6" t="n">
-        <v>682.4901603844278</v>
+        <v>650.5774289899554</v>
       </c>
       <c r="H6" t="n">
-        <v>306.0606604821406</v>
+        <v>311.0683862754347</v>
       </c>
     </row>
     <row r="7">
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2192446007891197</v>
+        <v>0.2229054216275288</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3288466125216938</v>
+        <v>0.3282046355786445</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6860596293692232</v>
+        <v>0.7046744092639639</v>
       </c>
       <c r="E7" t="n">
-        <v>1.311962756094876</v>
+        <v>1.358792405292101</v>
       </c>
       <c r="F7" t="n">
-        <v>2.781566232412323</v>
+        <v>2.322627733703429</v>
       </c>
       <c r="G7" t="n">
-        <v>8.365345620735146</v>
+        <v>5.221711346471902</v>
       </c>
       <c r="H7" t="n">
-        <v>2.28217090865373</v>
+        <v>1.693152658656262</v>
       </c>
     </row>
     <row r="8">
@@ -1198,25 +1198,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-57.23242936041268</v>
+        <v>-56.94899366549602</v>
       </c>
       <c r="C8" t="n">
-        <v>-32.09476205432935</v>
+        <v>-32.12420823997971</v>
       </c>
       <c r="D8" t="n">
-        <v>-137.0308827811828</v>
+        <v>-136.4662488274812</v>
       </c>
       <c r="E8" t="n">
-        <v>-146.1773403163912</v>
+        <v>-145.4391682660981</v>
       </c>
       <c r="F8" t="n">
-        <v>-155.8141455155057</v>
+        <v>-159.1515251299366</v>
       </c>
       <c r="G8" t="n">
-        <v>-137.798180374113</v>
+        <v>-143.0163556777663</v>
       </c>
       <c r="H8" t="n">
-        <v>-111.0246234003225</v>
+        <v>-112.1910833011263</v>
       </c>
     </row>
     <row r="9">
@@ -1226,25 +1226,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-54.73278932824403</v>
+        <v>-54.44935363332737</v>
       </c>
       <c r="C9" t="n">
-        <v>-29.97061145102272</v>
+        <v>-30.00005763667308</v>
       </c>
       <c r="D9" t="n">
-        <v>-133.8973154680125</v>
+        <v>-133.3326815143109</v>
       </c>
       <c r="E9" t="n">
-        <v>-143.043773003221</v>
+        <v>-142.3056009529278</v>
       </c>
       <c r="F9" t="n">
-        <v>-152.0398559014413</v>
+        <v>-155.2640145319236</v>
       </c>
       <c r="G9" t="n">
-        <v>-134.2640188830692</v>
+        <v>-139.3597282031617</v>
       </c>
       <c r="H9" t="n">
-        <v>-107.9913940058351</v>
+        <v>-109.1185727453874</v>
       </c>
     </row>
   </sheetData>
@@ -1305,25 +1305,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3316407729906283</v>
+        <v>0.3337078937759935</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09263665014470535</v>
+        <v>0.09440499026404847</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2032044365803733</v>
+        <v>-0.203820250307752</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.373819190321971</v>
+        <v>-1.357785907750257</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.622611767873734</v>
+        <v>-2.850288995731308</v>
       </c>
       <c r="G2" t="n">
-        <v>-13.19183194151631</v>
+        <v>-7.815523066445619</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.994531652192842</v>
+        <v>-1.966550889365816</v>
       </c>
     </row>
     <row r="3">
@@ -1333,25 +1333,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1213126001216255</v>
+        <v>0.1196180544920949</v>
       </c>
       <c r="C3" t="n">
-        <v>0.139697020500897</v>
+        <v>0.1388016918536132</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0259604709208272</v>
+        <v>0.02549364516208428</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02131534455075716</v>
+        <v>0.02060687554233496</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03869651129138112</v>
+        <v>0.04045859016056189</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04807886705590172</v>
+        <v>0.04897105277782494</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06584346907356495</v>
+        <v>0.06565831833141904</v>
       </c>
     </row>
     <row r="4">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02421270156086983</v>
+        <v>0.02413781581583378</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07891950215632515</v>
+        <v>0.07876569770534764</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00116690751983191</v>
+        <v>0.001167504756384109</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007760155085992099</v>
+        <v>0.0007707741338642974</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001980466964150278</v>
+        <v>0.002199610078647618</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002546411220050436</v>
+        <v>0.002614913361005449</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0182670008216378</v>
+        <v>0.01827605264184715</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1389,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1556043108685291</v>
+        <v>0.1553634957634314</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2809261507163852</v>
+        <v>0.2806522718692077</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0341600281005726</v>
+        <v>0.03416876872794963</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02785705491611075</v>
+        <v>0.02776281927082149</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04450243773267121</v>
+        <v>0.04690000083846074</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05046197796411112</v>
+        <v>0.05113622357004328</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09891866004972999</v>
+        <v>0.09933059667331906</v>
       </c>
     </row>
     <row r="6">
@@ -1417,25 +1417,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111.2067286072691</v>
+        <v>109.2876742196977</v>
       </c>
       <c r="C6" t="n">
-        <v>50.95185539473217</v>
+        <v>50.90618425027012</v>
       </c>
       <c r="D6" t="n">
-        <v>114.0662834181936</v>
+        <v>114.7982976042387</v>
       </c>
       <c r="E6" t="n">
-        <v>84.55445230664559</v>
+        <v>85.90025575665345</v>
       </c>
       <c r="F6" t="n">
-        <v>814.5581489406782</v>
+        <v>881.8008013385287</v>
       </c>
       <c r="G6" t="n">
-        <v>644.6056757346033</v>
+        <v>631.0976587851221</v>
       </c>
       <c r="H6" t="n">
-        <v>303.3238574003537</v>
+        <v>312.2984786590851</v>
       </c>
     </row>
     <row r="7">
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2189566591954204</v>
+        <v>0.2182841029382856</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3289526564660161</v>
+        <v>0.3283144913145288</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7265563324759887</v>
+        <v>0.726926656843589</v>
       </c>
       <c r="E7" t="n">
-        <v>1.428377935905222</v>
+        <v>1.418750628437564</v>
       </c>
       <c r="F7" t="n">
-        <v>2.779339714474052</v>
+        <v>2.316252851548891</v>
       </c>
       <c r="G7" t="n">
-        <v>8.521664140617856</v>
+        <v>5.29597471857278</v>
       </c>
       <c r="H7" t="n">
-        <v>2.333974573189093</v>
+        <v>1.717417241609273</v>
       </c>
     </row>
     <row r="8">
@@ -1473,25 +1473,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-57.25492473557465</v>
+        <v>-57.30758430377068</v>
       </c>
       <c r="C8" t="n">
-        <v>-32.08990359081518</v>
+        <v>-32.11916527800361</v>
       </c>
       <c r="D8" t="n">
-        <v>-135.8213616727241</v>
+        <v>-135.8106163832158</v>
       </c>
       <c r="E8" t="n">
-        <v>-144.3880991061225</v>
+        <v>-144.5304187696303</v>
       </c>
       <c r="F8" t="n">
-        <v>-155.8349881616455</v>
+        <v>-159.2258296252229</v>
       </c>
       <c r="G8" t="n">
-        <v>-137.3536866183779</v>
+        <v>-142.6631078390196</v>
       </c>
       <c r="H8" t="n">
-        <v>-110.4571606475433</v>
+        <v>-111.9427870331438</v>
       </c>
     </row>
     <row r="9">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-54.755284703406</v>
+        <v>-54.80794427160203</v>
       </c>
       <c r="C9" t="n">
-        <v>-29.96575298750855</v>
+        <v>-29.99501467469698</v>
       </c>
       <c r="D9" t="n">
-        <v>-132.6877943595539</v>
+        <v>-132.6770490700456</v>
       </c>
       <c r="E9" t="n">
-        <v>-141.2545317929522</v>
+        <v>-141.39685145646</v>
       </c>
       <c r="F9" t="n">
-        <v>-152.060698547581</v>
+        <v>-155.3383190272099</v>
       </c>
       <c r="G9" t="n">
-        <v>-133.819525127334</v>
+        <v>-139.006480364415</v>
       </c>
       <c r="H9" t="n">
-        <v>-107.423931253056</v>
+        <v>-108.8702764774049</v>
       </c>
     </row>
   </sheetData>
@@ -1580,25 +1580,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.09529870371211535</v>
+        <v>-0.117199633104103</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1788667693046333</v>
+        <v>-0.1712522393397011</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7671246277580815</v>
+        <v>0.7801518592174388</v>
       </c>
       <c r="E2" t="n">
-        <v>0.512285256138577</v>
+        <v>0.4404838898331672</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.620846392404832</v>
+        <v>-0.2990812084588097</v>
       </c>
       <c r="G2" t="n">
-        <v>-10.53627035621973</v>
+        <v>-5.319049271839268</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.858645389624109</v>
+        <v>-0.7809911006152127</v>
       </c>
     </row>
     <row r="3">
@@ -1608,25 +1608,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09768352273144207</v>
+        <v>0.09854004890833891</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1394714634909062</v>
+        <v>0.1395040336380065</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008666708424569739</v>
+        <v>0.008094474764050119</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00678498525134294</v>
+        <v>0.00728730371905797</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02365116902482537</v>
+        <v>0.02002196576581363</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03051213772780049</v>
+        <v>0.02846332387881019</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05112833110848113</v>
+        <v>0.05031852511234621</v>
       </c>
     </row>
     <row r="4">
@@ -1636,25 +1636,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03967947110067679</v>
+        <v>0.04047287776859497</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1025339832791288</v>
+        <v>0.1018716963197947</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000225850250207748</v>
+        <v>0.0002132160095996273</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001594368292884267</v>
+        <v>0.0001829091198566285</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001122850016162548</v>
+        <v>0.0007421448421860577</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002069929265909452</v>
+        <v>0.001874394320704394</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02429858679022896</v>
+        <v>0.0242262063967894</v>
       </c>
     </row>
     <row r="5">
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1991970659941476</v>
+        <v>0.2011787209637117</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3202092804387918</v>
+        <v>0.3191734580440465</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01502831494904695</v>
+        <v>0.01460191801098839</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01262682974021693</v>
+        <v>0.01352438981457679</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03350895426841231</v>
+        <v>0.02724233547598402</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04549647531303334</v>
+        <v>0.04329427584224495</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1043444867839415</v>
+        <v>0.1031691830252587</v>
       </c>
     </row>
     <row r="6">
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59.08507670510761</v>
+        <v>63.04289633115836</v>
       </c>
       <c r="C6" t="n">
-        <v>91.61134957091917</v>
+        <v>90.97130859813264</v>
       </c>
       <c r="D6" t="n">
-        <v>55.44486085180752</v>
+        <v>51.21402207623373</v>
       </c>
       <c r="E6" t="n">
-        <v>46.30325350940905</v>
+        <v>51.1446390887355</v>
       </c>
       <c r="F6" t="n">
-        <v>2910.292526195482</v>
+        <v>1823.226219007351</v>
       </c>
       <c r="G6" t="n">
-        <v>696.3946837265512</v>
+        <v>611.6262230412211</v>
       </c>
       <c r="H6" t="n">
-        <v>643.1886250932126</v>
+        <v>448.5375513571387</v>
       </c>
     </row>
     <row r="7">
@@ -1720,25 +1720,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7177304817682169</v>
+        <v>0.7319818087384948</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8558676381735604</v>
+        <v>0.8503717184515333</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07252070684772097</v>
+        <v>0.06860369344148812</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1489260289389288</v>
+        <v>0.1704828694339495</v>
       </c>
       <c r="F7" t="n">
-        <v>1.579079825465527</v>
+        <v>0.7854877278543464</v>
       </c>
       <c r="G7" t="n">
-        <v>6.929660114704114</v>
+        <v>3.799053715152548</v>
       </c>
       <c r="H7" t="n">
-        <v>1.717297465983011</v>
+        <v>1.067663588845393</v>
       </c>
     </row>
     <row r="8">
@@ -1748,25 +1748,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-44.85766253809521</v>
+        <v>-44.52109463688944</v>
       </c>
       <c r="C8" t="n">
-        <v>-24.16341486748521</v>
+        <v>-24.26061705064528</v>
       </c>
       <c r="D8" t="n">
-        <v>-166.308406148316</v>
+        <v>-167.5173003077838</v>
       </c>
       <c r="E8" t="n">
-        <v>-173.6211181449624</v>
+        <v>-170.736943966904</v>
       </c>
       <c r="F8" t="n">
-        <v>-166.5890143821832</v>
+        <v>-184.5610854760995</v>
       </c>
       <c r="G8" t="n">
-        <v>-138.3257802403265</v>
+        <v>-146.9867425175628</v>
       </c>
       <c r="H8" t="n">
-        <v>-118.9775660535614</v>
+        <v>-123.0972973259808</v>
       </c>
     </row>
     <row r="9">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-40.69159581781413</v>
+        <v>-40.35502791660836</v>
       </c>
       <c r="C9" t="n">
-        <v>-20.62316386197416</v>
+        <v>-20.72036604513423</v>
       </c>
       <c r="D9" t="n">
-        <v>-161.0857939596989</v>
+        <v>-162.2946881191667</v>
       </c>
       <c r="E9" t="n">
-        <v>-168.3985059563453</v>
+        <v>-165.5143317782869</v>
       </c>
       <c r="F9" t="n">
-        <v>-160.2985316920758</v>
+        <v>-178.0819011460779</v>
       </c>
       <c r="G9" t="n">
-        <v>-132.4355110885868</v>
+        <v>-140.8923633932218</v>
       </c>
       <c r="H9" t="n">
-        <v>-113.9221837294158</v>
+        <v>-117.9764463997493</v>
       </c>
     </row>
   </sheetData>
@@ -1855,25 +1855,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1420423896512613</v>
+        <v>-0.1427800551611953</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.09505119107743987</v>
+        <v>-0.09395794021847181</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4667254325745378</v>
+        <v>-0.4382659730750043</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.195442231201792</v>
+        <v>-3.237729339158538</v>
       </c>
       <c r="F2" t="n">
-        <v>-7.84724024372605</v>
+        <v>-5.407688303345405</v>
       </c>
       <c r="G2" t="n">
-        <v>-29.43687168321477</v>
+        <v>-16.75372956065652</v>
       </c>
       <c r="H2" t="n">
-        <v>-6.863895528574308</v>
+        <v>-4.345691861935856</v>
       </c>
     </row>
     <row r="3">
@@ -1883,25 +1883,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1098273070686085</v>
+        <v>0.1095761547686033</v>
       </c>
       <c r="C3" t="n">
-        <v>0.140665499239454</v>
+        <v>0.1415094595570456</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03308348626255192</v>
+        <v>0.03269689211656298</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03338706694411277</v>
+        <v>0.03355336032276531</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0518409399565822</v>
+        <v>0.05006333579629021</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06816552619403783</v>
+        <v>0.06646797991500987</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07282830427755786</v>
+        <v>0.07231119707937954</v>
       </c>
     </row>
     <row r="4">
@@ -1911,25 +1911,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04137285823705832</v>
+        <v>0.04139958170270672</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09524397789408702</v>
+        <v>0.09514889050320277</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001422478911118617</v>
+        <v>0.001394877984550608</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001371514835720522</v>
+        <v>0.001385338740979201</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003790425825584689</v>
+        <v>0.003660612434156771</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005461225293307173</v>
+        <v>0.00526621781667645</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02477708016614606</v>
+        <v>0.02470925319704542</v>
       </c>
     </row>
     <row r="5">
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2034031913148324</v>
+        <v>0.203468871581642</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3086162307690362</v>
+        <v>0.3084621378762761</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03771576475585</v>
+        <v>0.03734806533879109</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03703396867364504</v>
+        <v>0.03722013891671015</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06156643424451905</v>
+        <v>0.06050299524946489</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0739001034729125</v>
+        <v>0.07256871100327227</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1203726155384659</v>
+        <v>0.1199284866610261</v>
       </c>
     </row>
     <row r="6">
@@ -1967,25 +1967,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65.8133842892974</v>
+        <v>66.3769369366095</v>
       </c>
       <c r="C6" t="n">
-        <v>76.44978129266008</v>
+        <v>76.14952673580005</v>
       </c>
       <c r="D6" t="n">
-        <v>102.2690307876132</v>
+        <v>102.6520051903698</v>
       </c>
       <c r="E6" t="n">
-        <v>87.54297765786771</v>
+        <v>87.92758930303314</v>
       </c>
       <c r="F6" t="n">
-        <v>3230.535748595226</v>
+        <v>2976.657333039772</v>
       </c>
       <c r="G6" t="n">
-        <v>996.8018573557155</v>
+        <v>926.686659706301</v>
       </c>
       <c r="H6" t="n">
-        <v>759.9021299963966</v>
+        <v>706.0750084853142</v>
       </c>
     </row>
     <row r="7">
@@ -1995,25 +1995,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7481474353226385</v>
+        <v>0.7486274474805067</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7953722836981858</v>
+        <v>0.794583210835567</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8870267300202889</v>
+        <v>0.8699124130233735</v>
       </c>
       <c r="E7" t="n">
-        <v>2.524185459491084</v>
+        <v>2.549577077732494</v>
       </c>
       <c r="F7" t="n">
-        <v>5.31865074239145</v>
+        <v>3.854737839415063</v>
       </c>
       <c r="G7" t="n">
-        <v>18.2747687253395</v>
+        <v>10.66461044133726</v>
       </c>
       <c r="H7" t="n">
-        <v>4.75802522937719</v>
+        <v>3.247008071637377</v>
       </c>
     </row>
     <row r="8">
@@ -2023,25 +2023,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-44.14721359189583</v>
+        <v>-44.13623653402153</v>
       </c>
       <c r="C8" t="n">
-        <v>-25.26970236774682</v>
+        <v>-25.28468518715447</v>
       </c>
       <c r="D8" t="n">
-        <v>-127.6624385632549</v>
+        <v>-128.0739150099296</v>
       </c>
       <c r="E8" t="n">
-        <v>-128.4286280404083</v>
+        <v>-128.218022409381</v>
       </c>
       <c r="F8" t="n">
-        <v>-134.9571996902541</v>
+        <v>-141.4733699734217</v>
       </c>
       <c r="G8" t="n">
-        <v>-115.0419704410031</v>
+        <v>-121.161071398271</v>
       </c>
       <c r="H8" t="n">
-        <v>-95.91785878242717</v>
+        <v>-98.05788341869656</v>
       </c>
     </row>
     <row r="9">
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-39.98114687161475</v>
+        <v>-39.97016981374045</v>
       </c>
       <c r="C9" t="n">
-        <v>-21.72945136223577</v>
+        <v>-21.74443418164342</v>
       </c>
       <c r="D9" t="n">
-        <v>-122.4398263746378</v>
+        <v>-122.8513028213125</v>
       </c>
       <c r="E9" t="n">
-        <v>-123.2060158517912</v>
+        <v>-122.9954102207639</v>
       </c>
       <c r="F9" t="n">
-        <v>-128.6667170001467</v>
+        <v>-134.9941856434</v>
       </c>
       <c r="G9" t="n">
-        <v>-109.1517012892634</v>
+        <v>-115.06669227393</v>
       </c>
       <c r="H9" t="n">
-        <v>-90.86247645828159</v>
+        <v>-92.93703249246505</v>
       </c>
     </row>
   </sheetData>
@@ -2130,25 +2130,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2166211764498494</v>
+        <v>0.1957961099240777</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05862168772670395</v>
+        <v>0.5614443707030103</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.013781923018405</v>
+        <v>-0.9990140556772715</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2738968890435887</v>
+        <v>0.2904263758946746</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1327446125925906</v>
+        <v>0.06283310263669417</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.704010051176522</v>
+        <v>-0.6589496550415832</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.383566138927896</v>
+        <v>-0.09124395859339966</v>
       </c>
     </row>
     <row r="3">
@@ -2158,25 +2158,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08805736027465022</v>
+        <v>0.08725118325504667</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1275520822036686</v>
+        <v>0.1106093350118139</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0267797362630982</v>
+        <v>0.02645399349677775</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01167813116860228</v>
+        <v>0.01084006189548839</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01391048592906202</v>
+        <v>0.01502939583773318</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01719541542512284</v>
+        <v>0.0171880641797468</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04752886854403402</v>
+        <v>0.04456200561276779</v>
       </c>
     </row>
     <row r="4">
@@ -2186,25 +2186,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02837952540671537</v>
+        <v>0.02913395670712546</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08187801254835597</v>
+        <v>0.03814413700695755</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001953032417292595</v>
+        <v>0.001938710050346188</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002373673939622514</v>
+        <v>0.0002319638071187692</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004853021185230773</v>
+        <v>0.0005353888383704848</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004851749627405309</v>
+        <v>0.0004920876033681214</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01890306914126497</v>
+        <v>0.01174604066888109</v>
       </c>
     </row>
     <row r="5">
@@ -2214,25 +2214,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1684622373314428</v>
+        <v>0.1706867209454955</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2861433426595069</v>
+        <v>0.1953052406029023</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04419312635798235</v>
+        <v>0.04403078525697887</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01540673209873695</v>
+        <v>0.01523035807585525</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02202957372540552</v>
+        <v>0.02313847096008042</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02202668751175562</v>
+        <v>0.02218304765734685</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09304361661413835</v>
+        <v>0.0784291039164432</v>
       </c>
     </row>
     <row r="6">
@@ -2242,25 +2242,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64.17425988554947</v>
+        <v>63.77184326654584</v>
       </c>
       <c r="C6" t="n">
-        <v>53.03025651789808</v>
+        <v>76.14763501369201</v>
       </c>
       <c r="D6" t="n">
-        <v>136.1536183766771</v>
+        <v>135.951006943091</v>
       </c>
       <c r="E6" t="n">
-        <v>51.18139053149687</v>
+        <v>51.12793604359983</v>
       </c>
       <c r="F6" t="n">
-        <v>677.6169516028521</v>
+        <v>616.9198280399702</v>
       </c>
       <c r="G6" t="n">
-        <v>158.1520874270289</v>
+        <v>156.6353970716035</v>
       </c>
       <c r="H6" t="n">
-        <v>190.0514273902504</v>
+        <v>183.4256077297504</v>
       </c>
     </row>
     <row r="7">
@@ -2270,25 +2270,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.256379314849746</v>
+        <v>0.2631549367177645</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3412281024658381</v>
+        <v>0.1597675846939672</v>
       </c>
       <c r="D7" t="n">
-        <v>1.214003399195253</v>
+        <v>1.205122627476848</v>
       </c>
       <c r="E7" t="n">
-        <v>0.219497090462697</v>
+        <v>0.2145344618965808</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6833261905214868</v>
+        <v>0.2830248413958511</v>
       </c>
       <c r="G7" t="n">
-        <v>1.62608527565375</v>
+        <v>0.9990587156696654</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7234198955247951</v>
+        <v>0.5207771946417795</v>
       </c>
     </row>
     <row r="8">
@@ -2298,25 +2298,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-54.55548461336332</v>
+        <v>-54.10946509511469</v>
       </c>
       <c r="C8" t="n">
-        <v>-31.53787186829827</v>
+        <v>-42.99574823565924</v>
       </c>
       <c r="D8" t="n">
-        <v>-125.0058125986938</v>
+        <v>-125.1603814409253</v>
       </c>
       <c r="E8" t="n">
-        <v>-169.2639300642646</v>
+        <v>-169.7475132475909</v>
       </c>
       <c r="F8" t="n">
-        <v>-192.3992123405254</v>
+        <v>-197.3779664079223</v>
       </c>
       <c r="G8" t="n">
-        <v>-177.1440236198893</v>
+        <v>-184.4213450423931</v>
       </c>
       <c r="H8" t="n">
-        <v>-124.9843891841725</v>
+        <v>-128.9687365782676</v>
       </c>
     </row>
     <row r="9">
@@ -2326,25 +2326,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-52.05584458119467</v>
+        <v>-51.60982506294604</v>
       </c>
       <c r="C9" t="n">
-        <v>-29.41372126499164</v>
+        <v>-40.87159763235261</v>
       </c>
       <c r="D9" t="n">
-        <v>-121.8722452855235</v>
+        <v>-122.0268141277551</v>
       </c>
       <c r="E9" t="n">
-        <v>-166.1303627510944</v>
+        <v>-166.6139459344206</v>
       </c>
       <c r="F9" t="n">
-        <v>-188.6249227264609</v>
+        <v>-193.4904558099093</v>
       </c>
       <c r="G9" t="n">
-        <v>-173.6098621288455</v>
+        <v>-180.7647175677885</v>
       </c>
       <c r="H9" t="n">
-        <v>-121.9511597896851</v>
+        <v>-125.8962260225287</v>
       </c>
     </row>
   </sheetData>
@@ -2405,25 +2405,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4672794090282077</v>
+        <v>0.388573642429357</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3138847756431935</v>
+        <v>0.08269627568224336</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5289350788612099</v>
+        <v>0.2763956449424692</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7390396217752573</v>
+        <v>-2.684415734905244</v>
       </c>
       <c r="F2" t="n">
-        <v>0.173927657111413</v>
+        <v>0.1252399153763205</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.792948401954259</v>
+        <v>-0.405520439325862</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5079935171809153</v>
+        <v>-0.369505115966786</v>
       </c>
     </row>
     <row r="3">
@@ -2433,25 +2433,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07941173171249488</v>
+        <v>0.09308377686957382</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1071582079812342</v>
+        <v>0.1204230468066506</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01371820929239961</v>
+        <v>0.01696662440548801</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01646183879681055</v>
+        <v>0.02571396332236429</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01529145811184021</v>
+        <v>0.01677434970125955</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01558739510473607</v>
+        <v>0.01326734691044377</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04127147349991925</v>
+        <v>0.04770485133596336</v>
       </c>
     </row>
     <row r="4">
@@ -2461,25 +2461,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01929891017177407</v>
+        <v>0.02215019008348347</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05967606244703398</v>
+        <v>0.07978408347752361</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004568543649723824</v>
+        <v>0.0007017754735841584</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0005685023198346721</v>
+        <v>0.001204457256925968</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003539144248407396</v>
+        <v>0.0004997367991519887</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008599888751610404</v>
+        <v>0.0004169139083701945</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01353570543393615</v>
+        <v>0.01745952616650656</v>
       </c>
     </row>
     <row r="5">
@@ -2489,25 +2489,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1389205174615113</v>
+        <v>0.148829399257954</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2442868446049316</v>
+        <v>0.2824607644922098</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02137415179539021</v>
+        <v>0.02649104515839567</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02384328668272627</v>
+        <v>0.0347052914830861</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01881261345057458</v>
+        <v>0.02235479365040055</v>
       </c>
       <c r="G5" t="n">
-        <v>0.029325566919687</v>
+        <v>0.02041846978522618</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07942716348580349</v>
+        <v>0.08920996063787873</v>
       </c>
     </row>
     <row r="6">
@@ -2517,25 +2517,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63.09802878655775</v>
+        <v>116.5479589393113</v>
       </c>
       <c r="C6" t="n">
-        <v>49.66486361865586</v>
+        <v>52.31405913473655</v>
       </c>
       <c r="D6" t="n">
-        <v>41.15516395496186</v>
+        <v>53.23628632182861</v>
       </c>
       <c r="E6" t="n">
-        <v>97.57248178548949</v>
+        <v>184.1310307870058</v>
       </c>
       <c r="F6" t="n">
-        <v>1214.07219112323</v>
+        <v>859.1947521575255</v>
       </c>
       <c r="G6" t="n">
-        <v>220.5487054557235</v>
+        <v>67.70501303635743</v>
       </c>
       <c r="H6" t="n">
-        <v>281.018572454103</v>
+        <v>222.1881833961276</v>
       </c>
     </row>
     <row r="7">
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1748254144117795</v>
+        <v>0.2009330403296314</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2491078110199658</v>
+        <v>0.3330399757295935</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1431392743971177</v>
+        <v>0.2195725493487682</v>
       </c>
       <c r="E7" t="n">
-        <v>1.047219676312923</v>
+        <v>2.216335681102843</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2495694429639647</v>
+        <v>0.2647778411465103</v>
       </c>
       <c r="G7" t="n">
-        <v>2.879973025597782</v>
+        <v>0.8478959430672356</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7906391074505889</v>
+        <v>0.680425838454097</v>
       </c>
     </row>
     <row r="8">
@@ -2573,25 +2573,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-61.11101309163962</v>
+        <v>-56.76845641497199</v>
       </c>
       <c r="C8" t="n">
-        <v>-36.28236454541154</v>
+        <v>-29.92646874383618</v>
       </c>
       <c r="D8" t="n">
-        <v>-155.5140637754144</v>
+        <v>-144.4998379092331</v>
       </c>
       <c r="E8" t="n">
-        <v>-150.9226084473208</v>
+        <v>-133.1562506765798</v>
       </c>
       <c r="F8" t="n">
-        <v>-200.6078407065868</v>
+        <v>-197.2385829955752</v>
       </c>
       <c r="G8" t="n">
-        <v>-163.4061865118315</v>
+        <v>-186.5657703056981</v>
       </c>
       <c r="H8" t="n">
-        <v>-127.9740128463674</v>
+        <v>-124.6925611743157</v>
       </c>
     </row>
     <row r="9">
@@ -2601,25 +2601,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-58.61137305947097</v>
+        <v>-53.43560303874713</v>
       </c>
       <c r="C9" t="n">
-        <v>-34.15821394210491</v>
+        <v>-27.09426793942734</v>
       </c>
       <c r="D9" t="n">
-        <v>-152.3804964622441</v>
+        <v>-140.3217481583394</v>
       </c>
       <c r="E9" t="n">
-        <v>-147.7890411341506</v>
+        <v>-128.9781609256861</v>
       </c>
       <c r="F9" t="n">
-        <v>-196.8335510925224</v>
+        <v>-192.0552355315579</v>
       </c>
       <c r="G9" t="n">
-        <v>-159.8720250207876</v>
+        <v>-181.6902670062253</v>
       </c>
       <c r="H9" t="n">
-        <v>-124.9407834518801</v>
+        <v>-120.5958804333305</v>
       </c>
     </row>
   </sheetData>
@@ -2680,25 +2680,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4154479296916136</v>
+        <v>0.4160371688545427</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1322314722456337</v>
+        <v>-0.1744479621228598</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5113957962081657</v>
+        <v>0.5113001675652505</v>
       </c>
       <c r="E2" t="n">
         <v>-0.1940476005628766</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5814349952326638</v>
+        <v>0.3781789969541642</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.5361319581706192</v>
+        <v>-0.4923188150382027</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1076446150255523</v>
+        <v>0.07411699260833637</v>
       </c>
     </row>
     <row r="3">
@@ -2708,25 +2708,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08090448150904299</v>
+        <v>0.08089614687204208</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1531763699905859</v>
+        <v>0.1603815088074834</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01285350415709671</v>
+        <v>0.01250813742399264</v>
       </c>
       <c r="E3" t="n">
         <v>0.007964628447193176</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008387825507727181</v>
+        <v>0.01067223468603384</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009808009722161141</v>
+        <v>0.01208447606300628</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04551580322230118</v>
+        <v>0.0474178553832919</v>
       </c>
     </row>
     <row r="4">
@@ -2736,25 +2736,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02117661319422033</v>
+        <v>0.02115526678135816</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09847779737808317</v>
+        <v>0.1021496498552959</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004738645422939216</v>
+        <v>0.0004739572861196061</v>
       </c>
       <c r="E4" t="n">
         <v>0.0003903412104090321</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000179325932160729</v>
+        <v>0.0003552366450754184</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002756249982301989</v>
+        <v>0.0004426605635207759</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0201622612092329</v>
+        <v>0.02082785205696315</v>
       </c>
     </row>
     <row r="5">
@@ -2764,25 +2764,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1455218650039242</v>
+        <v>0.1454485021626492</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3138117228181305</v>
+        <v>0.3196085885192948</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02176842994554089</v>
+        <v>0.02177056007822505</v>
       </c>
       <c r="E5" t="n">
         <v>0.019757054699753</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01339126327725391</v>
+        <v>0.01884772254346446</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01660195766258302</v>
+        <v>0.02103950007772941</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08847538223453093</v>
+        <v>0.09107865468018599</v>
       </c>
     </row>
     <row r="6">
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>86.9889906939441</v>
+        <v>87.11165220167459</v>
       </c>
       <c r="C6" t="n">
-        <v>102.0047354106846</v>
+        <v>105.1190193297718</v>
       </c>
       <c r="D6" t="n">
-        <v>74.42378552135858</v>
+        <v>80.17169683903896</v>
       </c>
       <c r="E6" t="n">
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>734.2250479169257</v>
+        <v>680.6682464131393</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>199.6070932571522</v>
+        <v>192.1784357972708</v>
       </c>
     </row>
     <row r="7">
@@ -2820,25 +2820,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1921892503284702</v>
+        <v>0.191997536090588</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8212077996766968</v>
+        <v>0.8516782870711304</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1489129663171561</v>
+        <v>0.1489417198307086</v>
       </c>
       <c r="E7" t="n">
         <v>0.7209750380322987</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1276950295827134</v>
+        <v>0.1887949665653036</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9260650498998939</v>
+        <v>0.9000110138118509</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4895075223062048</v>
+        <v>0.5003997602336466</v>
       </c>
     </row>
     <row r="8">
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-57.53258357646907</v>
+        <v>-57.54972852961666</v>
       </c>
       <c r="C8" t="n">
-        <v>-26.76886245311874</v>
+        <v>-26.21974578212182</v>
       </c>
       <c r="D8" t="n">
-        <v>-152.7463701101039</v>
+        <v>-152.7422604340293</v>
       </c>
       <c r="E8" t="n">
         <v>-156.8182753599861</v>
       </c>
       <c r="F8" t="n">
-        <v>-216.2839445028378</v>
+        <v>-206.4536123875911</v>
       </c>
       <c r="G8" t="n">
-        <v>-188.715263636421</v>
+        <v>-185.0676825979553</v>
       </c>
       <c r="H8" t="n">
-        <v>-133.1442166064894</v>
+        <v>-130.8085508485501</v>
       </c>
     </row>
     <row r="9">
@@ -2876,25 +2876,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-54.1997302002442</v>
+        <v>-54.2168751533918</v>
       </c>
       <c r="C9" t="n">
-        <v>-23.93666164870989</v>
+        <v>-23.38754497771298</v>
       </c>
       <c r="D9" t="n">
-        <v>-148.5682803592102</v>
+        <v>-148.5641706831356</v>
       </c>
       <c r="E9" t="n">
         <v>-152.6401856090924</v>
       </c>
       <c r="F9" t="n">
-        <v>-211.2515583507519</v>
+        <v>-201.2702649235738</v>
       </c>
       <c r="G9" t="n">
-        <v>-184.0030483150292</v>
+        <v>-180.1921792984825</v>
       </c>
       <c r="H9" t="n">
-        <v>-129.099910747173</v>
+        <v>-126.7118701075648</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/global/metrics_summary.xlsx
+++ b/results/cross_validation/global/metrics_summary.xlsx
@@ -480,25 +480,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001663351572512517</v>
+        <v>0.8245235144174925</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.03272044035445809</v>
+        <v>0.7028825702379756</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1890316278398306</v>
+        <v>0.6471994149263223</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.324041223028572</v>
+        <v>-1.135128212284497</v>
       </c>
       <c r="F2" t="n">
-        <v>-7.838853170663739</v>
+        <v>-8.432646046390996</v>
       </c>
       <c r="G2" t="n">
-        <v>-20.95917759134523</v>
+        <v>-10.14105545746683</v>
       </c>
       <c r="H2" t="n">
-        <v>-5.660682907663276</v>
+        <v>-2.922370702760089</v>
       </c>
     </row>
     <row r="3">
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09056733275072082</v>
+        <v>0.05557159978665211</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1250165168603797</v>
+        <v>0.07787467265025019</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01274456315708121</v>
+        <v>0.00978186673668022</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02329346183725459</v>
+        <v>0.01539495580554709</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04728687099602898</v>
+        <v>0.04167585431337851</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05954658642743729</v>
+        <v>0.03286760052192549</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05974255533815043</v>
+        <v>0.03886109163573893</v>
       </c>
     </row>
     <row r="4">
@@ -536,25 +536,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03616681920262446</v>
+        <v>0.006357000254744677</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08982265266988415</v>
+        <v>0.02584230412494111</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007865039913824574</v>
+        <v>0.0003421576942432357</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002067366413625316</v>
+        <v>0.0006979860186216389</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005049499021874248</v>
+        <v>0.004041231411478198</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006513663051811642</v>
+        <v>0.001999016669377678</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02340108405853371</v>
+        <v>0.006546616028901089</v>
       </c>
     </row>
     <row r="5">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1901757587144704</v>
+        <v>0.07973079865864055</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2997042753613705</v>
+        <v>0.1607554170936119</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02804467848598834</v>
+        <v>0.01849750508158426</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04546830119572664</v>
+        <v>0.02641942502443304</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07105982706054279</v>
+        <v>0.06357068043900582</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08070726765175266</v>
+        <v>0.04471036422774565</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1191933514116419</v>
+        <v>0.0656140317541702</v>
       </c>
     </row>
     <row r="6">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59.6515542544264</v>
+        <v>64.49544346753329</v>
       </c>
       <c r="C6" t="n">
-        <v>65.31538262675627</v>
+        <v>42.47463489742543</v>
       </c>
       <c r="D6" t="n">
-        <v>121.8175499779077</v>
+        <v>34.00089466270601</v>
       </c>
       <c r="E6" t="n">
-        <v>236.4519569224191</v>
+        <v>104.5416530167692</v>
       </c>
       <c r="F6" t="n">
-        <v>6054.035375294063</v>
+        <v>5704.042675874145</v>
       </c>
       <c r="G6" t="n">
-        <v>1421.89189412533</v>
+        <v>805.9335525700744</v>
       </c>
       <c r="H6" t="n">
-        <v>1326.527285533484</v>
+        <v>1125.914809081442</v>
       </c>
     </row>
     <row r="7">
@@ -620,25 +620,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3253177679700834</v>
+        <v>0.05859284585307353</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7463839779505127</v>
+        <v>0.1087248418160661</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2443410644420186</v>
+        <v>0.1075796859080736</v>
       </c>
       <c r="E7" t="n">
-        <v>3.798319046796219</v>
+        <v>1.285054107796768</v>
       </c>
       <c r="F7" t="n">
-        <v>5.311381201028868</v>
+        <v>5.668245351810668</v>
       </c>
       <c r="G7" t="n">
-        <v>13.18562568307967</v>
+        <v>6.690431897817227</v>
       </c>
       <c r="H7" t="n">
-        <v>3.935228123544563</v>
+        <v>2.319771455166979</v>
       </c>
     </row>
     <row r="8">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-54.43342401060718</v>
+        <v>-79.98937740623107</v>
       </c>
       <c r="C8" t="n">
-        <v>-34.14877117873696</v>
+        <v>-48.83613652681768</v>
       </c>
       <c r="D8" t="n">
-        <v>-148.1061679728599</v>
+        <v>-161.5850154907845</v>
       </c>
       <c r="E8" t="n">
-        <v>-127.8110746590462</v>
+        <v>-146.6135412066414</v>
       </c>
       <c r="F8" t="n">
-        <v>-140.7885885935385</v>
+        <v>-137.2913515444137</v>
       </c>
       <c r="G8" t="n">
-        <v>-123.8463325059322</v>
+        <v>-143.162397231369</v>
       </c>
       <c r="H8" t="n">
-        <v>-104.8557264867868</v>
+        <v>-119.5796365677095</v>
       </c>
     </row>
     <row r="9">
@@ -676,25 +676,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-53.60021066655096</v>
+        <v>-77.48973737406243</v>
       </c>
       <c r="C9" t="n">
-        <v>-33.44072097763475</v>
+        <v>-46.71198592351104</v>
       </c>
       <c r="D9" t="n">
-        <v>-147.0616455351364</v>
+        <v>-158.4514481776143</v>
       </c>
       <c r="E9" t="n">
-        <v>-126.7665522213228</v>
+        <v>-143.4799738934711</v>
       </c>
       <c r="F9" t="n">
-        <v>-139.4927517275341</v>
+        <v>-133.5170619303492</v>
       </c>
       <c r="G9" t="n">
-        <v>-122.627456681064</v>
+        <v>-139.6282357403251</v>
       </c>
       <c r="H9" t="n">
-        <v>-103.8315563015405</v>
+        <v>-116.5464071732222</v>
       </c>
     </row>
   </sheetData>
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3333144153604205</v>
+        <v>0.9602995013907358</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09289578951368505</v>
+        <v>0.9561599566955046</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1936108405065735</v>
+        <v>0.9448221858734958</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.33743936311624</v>
+        <v>0.6342634465475654</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.805955399847335</v>
+        <v>-0.02137195166994377</v>
       </c>
       <c r="G2" t="n">
-        <v>-7.795029474124064</v>
+        <v>0.1247326788059616</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.950970812120018</v>
+        <v>0.5998176362738866</v>
       </c>
     </row>
     <row r="3">
@@ -783,25 +783,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1192476519149277</v>
+        <v>0.02392232348444865</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1387153365666276</v>
+        <v>0.03544988279783913</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02539369155019026</v>
+        <v>0.004337362248359345</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02056039625413864</v>
+        <v>0.005613596395764563</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04026316259577434</v>
+        <v>0.01096022204060342</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04892091772553721</v>
+        <v>0.00736789239832406</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06551685943453263</v>
+        <v>0.01460854656088986</v>
       </c>
     </row>
     <row r="4">
@@ -811,25 +811,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0241520703889165</v>
+        <v>0.001438233042648428</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07889696305995075</v>
+        <v>0.003813063854358109</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001157603332562983</v>
+        <v>5.351327195493111e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007641227282952568</v>
+        <v>0.000119561438671417</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002174282986463839</v>
+        <v>0.0004375866955667885</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002608834428652517</v>
+        <v>0.0001570474154722732</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01829231282080698</v>
+        <v>0.001003167619778658</v>
       </c>
     </row>
     <row r="5">
@@ -839,25 +839,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1554093639035837</v>
+        <v>0.03792404306832841</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2808860321553045</v>
+        <v>0.06175001096646145</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03402357025009256</v>
+        <v>0.007315276615065975</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02764276990996483</v>
+        <v>0.01093441533285694</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04662920743979935</v>
+        <v>0.02091857298112824</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05107675037287041</v>
+        <v>0.01253185602663361</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09927794900526922</v>
+        <v>0.0252290291650791</v>
       </c>
     </row>
     <row r="6">
@@ -867,25 +867,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>108.351117620765</v>
+        <v>44.33087895072465</v>
       </c>
       <c r="C6" t="n">
-        <v>50.9626062962645</v>
+        <v>47.39739131029629</v>
       </c>
       <c r="D6" t="n">
-        <v>114.21602366519</v>
+        <v>23.28075810671715</v>
       </c>
       <c r="E6" t="n">
-        <v>85.25558862230646</v>
+        <v>58.24117515621439</v>
       </c>
       <c r="F6" t="n">
-        <v>892.2730965893073</v>
+        <v>509.0185419865456</v>
       </c>
       <c r="G6" t="n">
-        <v>631.7734709423003</v>
+        <v>111.5875569865318</v>
       </c>
       <c r="H6" t="n">
-        <v>313.8053172893556</v>
+        <v>132.309383749505</v>
       </c>
     </row>
     <row r="7">
@@ -895,25 +895,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2184121246641154</v>
+        <v>0.01441691271263315</v>
       </c>
       <c r="C7" t="n">
-        <v>0.32885913728786</v>
+        <v>0.01732115768939931</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7207871489695324</v>
+        <v>0.01809080352831973</v>
       </c>
       <c r="E7" t="n">
-        <v>1.406533389689357</v>
+        <v>0.1113046590428004</v>
       </c>
       <c r="F7" t="n">
-        <v>2.289617236089451</v>
+        <v>0.6164357923757599</v>
       </c>
       <c r="G7" t="n">
-        <v>5.283670052674553</v>
+        <v>0.2641901295490421</v>
       </c>
       <c r="H7" t="n">
-        <v>1.707979848229145</v>
+        <v>0.1736265758163258</v>
       </c>
     </row>
     <row r="8">
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-57.29754792686073</v>
+        <v>-105.2537795334761</v>
       </c>
       <c r="C8" t="n">
-        <v>-32.09418814309497</v>
+        <v>-77.53983377638646</v>
       </c>
       <c r="D8" t="n">
-        <v>-135.9894735797111</v>
+        <v>-200.5471980789759</v>
       </c>
       <c r="E8" t="n">
-        <v>-144.7124249939473</v>
+        <v>-183.6652839389968</v>
       </c>
       <c r="F8" t="n">
-        <v>-159.5385209150676</v>
+        <v>-195.0901284730635</v>
       </c>
       <c r="G8" t="n">
-        <v>-142.72129341135</v>
+        <v>-204.215106932018</v>
       </c>
       <c r="H8" t="n">
-        <v>-112.0589081616719</v>
+        <v>-161.0518884554861</v>
       </c>
     </row>
     <row r="9">
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-54.79790789469208</v>
+        <v>-102.7541395013075</v>
       </c>
       <c r="C9" t="n">
-        <v>-29.97003753978834</v>
+        <v>-75.41568317307983</v>
       </c>
       <c r="D9" t="n">
-        <v>-132.8559062665409</v>
+        <v>-197.4136307658057</v>
       </c>
       <c r="E9" t="n">
-        <v>-141.578857680777</v>
+        <v>-180.5317166258266</v>
       </c>
       <c r="F9" t="n">
-        <v>-155.6510103170546</v>
+        <v>-191.3158388589991</v>
       </c>
       <c r="G9" t="n">
-        <v>-139.0646659367454</v>
+        <v>-200.6809454409741</v>
       </c>
       <c r="H9" t="n">
-        <v>-108.9863976059331</v>
+        <v>-158.0186590609988</v>
       </c>
     </row>
   </sheetData>
@@ -1030,25 +1030,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.319504139343572</v>
+        <v>0.9583890237326176</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09470939783730981</v>
+        <v>0.9587807365876686</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.166816907499501</v>
+        <v>0.9403646022292164</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.257931702675925</v>
+        <v>0.6564548350897044</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.86089965534522</v>
+        <v>-0.001603093227251051</v>
       </c>
       <c r="G2" t="n">
-        <v>-7.691836386543272</v>
+        <v>0.1859981204947476</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.927211852480506</v>
+        <v>0.6163973708177839</v>
       </c>
     </row>
     <row r="3">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1114331050688294</v>
+        <v>0.02372181626213336</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1388219872430558</v>
+        <v>0.03469444570080295</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0251631811328527</v>
+        <v>0.005079727589309769</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02037888788503277</v>
+        <v>0.006334688357229453</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04050427645591751</v>
+        <v>0.01135506020129942</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04870905585450708</v>
+        <v>0.00726873306880133</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06416841560669923</v>
+        <v>0.01474241186326272</v>
       </c>
     </row>
     <row r="4">
@@ -1086,25 +1086,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02465237632942908</v>
+        <v>0.001507444064963047</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0787392213283392</v>
+        <v>0.003585116974661152</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001131617688759436</v>
+        <v>5.783638423464707e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007381312046755679</v>
+        <v>0.000112306942736655</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002205671783068699</v>
+        <v>0.0004291171175380187</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002578224675669679</v>
+        <v>0.0001460546832611981</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01834087383499028</v>
+        <v>0.000972979361232453</v>
       </c>
     </row>
     <row r="5">
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1570107522733048</v>
+        <v>0.03882581699028428</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2806050985430222</v>
+        <v>0.05987584633774418</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0336395256916538</v>
+        <v>0.007605023618283317</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02716857016251624</v>
+        <v>0.01059749700338033</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04696458009041174</v>
+        <v>0.02071514222828361</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05077622155763147</v>
+        <v>0.01208530857120322</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09936079138642338</v>
+        <v>0.02495077245819649</v>
       </c>
     </row>
     <row r="6">
@@ -1142,25 +1142,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>89.60779352000679</v>
+        <v>46.20093768476104</v>
       </c>
       <c r="C6" t="n">
-        <v>50.89470494412509</v>
+        <v>47.4523253543209</v>
       </c>
       <c r="D6" t="n">
-        <v>112.9442229685745</v>
+        <v>25.0890561296105</v>
       </c>
       <c r="E6" t="n">
-        <v>82.66932211572338</v>
+        <v>56.29214912684242</v>
       </c>
       <c r="F6" t="n">
-        <v>879.7168451142232</v>
+        <v>435.4420171018974</v>
       </c>
       <c r="G6" t="n">
-        <v>650.5774289899554</v>
+        <v>117.9191023712806</v>
       </c>
       <c r="H6" t="n">
-        <v>311.0683862754347</v>
+        <v>121.3992646281188</v>
       </c>
     </row>
     <row r="7">
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2229054216275288</v>
+        <v>0.01603850372568886</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3282046355786445</v>
+        <v>0.01737536090596223</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7046744092639639</v>
+        <v>0.02043110480019935</v>
       </c>
       <c r="E7" t="n">
-        <v>1.358792405292101</v>
+        <v>0.1056421643330044</v>
       </c>
       <c r="F7" t="n">
-        <v>2.322627733703429</v>
+        <v>0.606562619900904</v>
       </c>
       <c r="G7" t="n">
-        <v>5.221711346471902</v>
+        <v>0.2468028021298586</v>
       </c>
       <c r="H7" t="n">
-        <v>1.693152658656262</v>
+        <v>0.1688087592992696</v>
       </c>
     </row>
     <row r="8">
@@ -1198,25 +1198,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-56.94899366549602</v>
+        <v>-100.4547754874086</v>
       </c>
       <c r="C8" t="n">
-        <v>-32.12420823997971</v>
+        <v>-74.46446264821429</v>
       </c>
       <c r="D8" t="n">
-        <v>-136.4662488274812</v>
+        <v>-194.9157424013009</v>
       </c>
       <c r="E8" t="n">
-        <v>-145.4391682660981</v>
+        <v>-180.9797723751756</v>
       </c>
       <c r="F8" t="n">
-        <v>-159.1515251299366</v>
+        <v>-191.5982975510451</v>
       </c>
       <c r="G8" t="n">
-        <v>-143.0163556777663</v>
+        <v>-201.9567071238727</v>
       </c>
       <c r="H8" t="n">
-        <v>-112.1910833011263</v>
+        <v>-157.3949595978362</v>
       </c>
     </row>
     <row r="9">
@@ -1226,25 +1226,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-54.44935363332737</v>
+        <v>-96.28870876712753</v>
       </c>
       <c r="C9" t="n">
-        <v>-30.00005763667308</v>
+        <v>-70.92421164270324</v>
       </c>
       <c r="D9" t="n">
-        <v>-133.3326815143109</v>
+        <v>-189.6931302126837</v>
       </c>
       <c r="E9" t="n">
-        <v>-142.3056009529278</v>
+        <v>-175.7571601865585</v>
       </c>
       <c r="F9" t="n">
-        <v>-155.2640145319236</v>
+        <v>-185.3078148609377</v>
       </c>
       <c r="G9" t="n">
-        <v>-139.3597282031617</v>
+        <v>-196.066437972133</v>
       </c>
       <c r="H9" t="n">
-        <v>-109.1185727453874</v>
+        <v>-152.3395772736906</v>
       </c>
     </row>
   </sheetData>
@@ -1305,25 +1305,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3337078937759935</v>
+        <v>0.9599133534651896</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09440499026404847</v>
+        <v>0.9587748798422706</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.203820250307752</v>
+        <v>0.9441522489268525</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.357785907750257</v>
+        <v>0.6418911746522162</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.850288995731308</v>
+        <v>0.00804518072053384</v>
       </c>
       <c r="G2" t="n">
-        <v>-7.815523066445619</v>
+        <v>0.1679343801947063</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.966550889365816</v>
+        <v>0.6134518696336281</v>
       </c>
     </row>
     <row r="3">
@@ -1333,25 +1333,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1196180544920949</v>
+        <v>0.02403206999893837</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1388016918536132</v>
+        <v>0.03370779392908423</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02549364516208428</v>
+        <v>0.004290091295638785</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02060687554233496</v>
+        <v>0.005508380573490652</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04045859016056189</v>
+        <v>0.0105006652309145</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04897105277782494</v>
+        <v>0.007210507365215334</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06565831833141904</v>
+        <v>0.01420825139888031</v>
       </c>
     </row>
     <row r="4">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02413781581583378</v>
+        <v>0.001452222053500328</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07876569770534764</v>
+        <v>0.003585626375257002</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001167504756384109</v>
+        <v>5.416299899805363e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007707741338642974</v>
+        <v>0.0001170678893190823</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002199610078647618</v>
+        <v>0.0004249835045992343</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002614913361005449</v>
+        <v>0.0001492958230355173</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01827605264184715</v>
+        <v>0.000963893107451536</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1389,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1553634957634314</v>
+        <v>0.03810803135167608</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2806522718692077</v>
+        <v>0.05988009999371245</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03416876872794963</v>
+        <v>0.007359551548705508</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02776281927082149</v>
+        <v>0.0108197915561753</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04690000083846074</v>
+        <v>0.02061512805197276</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05113622357004328</v>
+        <v>0.01221866699094125</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09933059667331906</v>
+        <v>0.02483354491553055</v>
       </c>
     </row>
     <row r="6">
@@ -1417,25 +1417,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>109.2876742196977</v>
+        <v>44.34980295984725</v>
       </c>
       <c r="C6" t="n">
-        <v>50.90618425027012</v>
+        <v>47.56636585836899</v>
       </c>
       <c r="D6" t="n">
-        <v>114.7982976042387</v>
+        <v>23.66570875591387</v>
       </c>
       <c r="E6" t="n">
-        <v>85.90025575665345</v>
+        <v>58.04798860781163</v>
       </c>
       <c r="F6" t="n">
-        <v>881.8008013385287</v>
+        <v>429.5888964430966</v>
       </c>
       <c r="G6" t="n">
-        <v>631.0976587851221</v>
+        <v>112.8978943347214</v>
       </c>
       <c r="H6" t="n">
-        <v>312.2984786590851</v>
+        <v>119.35277615996</v>
       </c>
     </row>
     <row r="7">
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2182841029382856</v>
+        <v>0.01454254939789336</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3283144913145288</v>
+        <v>0.01637747450999872</v>
       </c>
       <c r="D7" t="n">
-        <v>0.726926656843589</v>
+        <v>0.01829223942124291</v>
       </c>
       <c r="E7" t="n">
-        <v>1.418750628437564</v>
+        <v>0.1090145951268585</v>
       </c>
       <c r="F7" t="n">
-        <v>2.316252851548891</v>
+        <v>0.2993839342370594</v>
       </c>
       <c r="G7" t="n">
-        <v>5.29597471857278</v>
+        <v>0.251224193017713</v>
       </c>
       <c r="H7" t="n">
-        <v>1.717417241609273</v>
+        <v>0.1181391642851276</v>
       </c>
     </row>
     <row r="8">
@@ -1473,25 +1473,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-57.30758430377068</v>
+        <v>-105.0892275626898</v>
       </c>
       <c r="C8" t="n">
-        <v>-32.11916527800361</v>
+        <v>-78.46233148591278</v>
       </c>
       <c r="D8" t="n">
-        <v>-135.8106163832158</v>
+        <v>-200.2937637171649</v>
       </c>
       <c r="E8" t="n">
-        <v>-144.5304187696303</v>
+        <v>-184.1078873579834</v>
       </c>
       <c r="F8" t="n">
-        <v>-159.2258296252229</v>
+        <v>-195.8499652650201</v>
       </c>
       <c r="G8" t="n">
-        <v>-142.6631078390196</v>
+        <v>-205.4299399391919</v>
       </c>
       <c r="H8" t="n">
-        <v>-111.9427870331438</v>
+        <v>-161.5388525546605</v>
       </c>
     </row>
     <row r="9">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-54.80794427160203</v>
+        <v>-102.5895875305211</v>
       </c>
       <c r="C9" t="n">
-        <v>-29.99501467469698</v>
+        <v>-76.33818088260615</v>
       </c>
       <c r="D9" t="n">
-        <v>-132.6770490700456</v>
+        <v>-197.1601964039947</v>
       </c>
       <c r="E9" t="n">
-        <v>-141.39685145646</v>
+        <v>-180.9743200448131</v>
       </c>
       <c r="F9" t="n">
-        <v>-155.3383190272099</v>
+        <v>-192.0756756509556</v>
       </c>
       <c r="G9" t="n">
-        <v>-139.006480364415</v>
+        <v>-201.895778448148</v>
       </c>
       <c r="H9" t="n">
-        <v>-108.8702764774049</v>
+        <v>-158.5056231601731</v>
       </c>
     </row>
   </sheetData>
@@ -1580,25 +1580,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.117199633104103</v>
+        <v>0.5713644573991081</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1712522393397011</v>
+        <v>0.6181158218243014</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7801518592174388</v>
+        <v>0.04366783323165824</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4404838898331672</v>
+        <v>-0.3000636229541132</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2990812084588097</v>
+        <v>-0.7712169871726116</v>
       </c>
       <c r="G2" t="n">
-        <v>-5.319049271839268</v>
+        <v>-1.379889255139418</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7809911006152127</v>
+        <v>-0.2030036254685125</v>
       </c>
     </row>
     <row r="3">
@@ -1608,25 +1608,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09854004890833891</v>
+        <v>0.06601384471495238</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1395040336380065</v>
+        <v>0.08306954478431279</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008094474764050119</v>
+        <v>0.0141359557104953</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00728730371905797</v>
+        <v>0.008859642238705478</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02002196576581363</v>
+        <v>0.01754324431866501</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02846332387881019</v>
+        <v>0.01432669395685222</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05031852511234621</v>
+        <v>0.03399148762066386</v>
       </c>
     </row>
     <row r="4">
@@ -1636,25 +1636,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04047287776859497</v>
+        <v>0.01552821305066142</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1018716963197947</v>
+        <v>0.03321503918778503</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002132160095996273</v>
+        <v>0.0009274826147007622</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001829091198566285</v>
+        <v>0.0004249984740586878</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007421448421860577</v>
+        <v>0.0007588430319448275</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001874394320704394</v>
+        <v>0.0004270186348554659</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0242262063967894</v>
+        <v>0.008546932499001033</v>
       </c>
     </row>
     <row r="5">
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2011787209637117</v>
+        <v>0.1246122508048924</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3191734580440465</v>
+        <v>0.1822499360432948</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01460191801098839</v>
+        <v>0.03045459923723775</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01352438981457679</v>
+        <v>0.02061549111854209</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02724233547598402</v>
+        <v>0.0275471056908857</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04329427584224495</v>
+        <v>0.02066442921678375</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1031691830252587</v>
+        <v>0.06769063535193942</v>
       </c>
     </row>
     <row r="6">
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63.04289633115836</v>
+        <v>62.0702365003909</v>
       </c>
       <c r="C6" t="n">
-        <v>90.97130859813264</v>
+        <v>56.69006712006034</v>
       </c>
       <c r="D6" t="n">
-        <v>51.21402207623373</v>
+        <v>102.6685174826312</v>
       </c>
       <c r="E6" t="n">
-        <v>51.1446390887355</v>
+        <v>132.7884231816046</v>
       </c>
       <c r="F6" t="n">
-        <v>1823.226219007351</v>
+        <v>2328.675278609207</v>
       </c>
       <c r="G6" t="n">
-        <v>611.6262230412211</v>
+        <v>387.2321028320212</v>
       </c>
       <c r="H6" t="n">
-        <v>448.5375513571387</v>
+        <v>511.687437620986</v>
       </c>
     </row>
     <row r="7">
@@ -1720,25 +1720,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7319818087384948</v>
+        <v>0.1399604119157306</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8503717184515333</v>
+        <v>0.1383157808841591</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06860369344148812</v>
+        <v>0.2880488878607931</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1704828694339495</v>
+        <v>0.7816331716361501</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7854877278543464</v>
+        <v>1.06479257254829</v>
       </c>
       <c r="G7" t="n">
-        <v>3.799053715152548</v>
+        <v>1.429531379172448</v>
       </c>
       <c r="H7" t="n">
-        <v>1.067663588845393</v>
+        <v>0.6403803673362619</v>
       </c>
     </row>
     <row r="8">
@@ -1748,25 +1748,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-44.52109463688944</v>
+        <v>-68.80664411744465</v>
       </c>
       <c r="C8" t="n">
-        <v>-24.26061705064528</v>
+        <v>-49.07128777065565</v>
       </c>
       <c r="D8" t="n">
-        <v>-167.5173003077838</v>
+        <v>-144.6437666662422</v>
       </c>
       <c r="E8" t="n">
-        <v>-170.736943966904</v>
+        <v>-161.0319245694255</v>
       </c>
       <c r="F8" t="n">
-        <v>-184.5610854760995</v>
+        <v>-184.7766058856992</v>
       </c>
       <c r="G8" t="n">
-        <v>-146.9867425175628</v>
+        <v>-184.208389704165</v>
       </c>
       <c r="H8" t="n">
-        <v>-123.0972973259808</v>
+        <v>-132.0897697856054</v>
       </c>
     </row>
     <row r="9">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-40.35502791660836</v>
+        <v>-67.97343077338843</v>
       </c>
       <c r="C9" t="n">
-        <v>-20.72036604513423</v>
+        <v>-48.36323756955344</v>
       </c>
       <c r="D9" t="n">
-        <v>-162.2946881191667</v>
+        <v>-143.5992442285188</v>
       </c>
       <c r="E9" t="n">
-        <v>-165.5143317782869</v>
+        <v>-159.987402131702</v>
       </c>
       <c r="F9" t="n">
-        <v>-178.0819011460779</v>
+        <v>-183.5185093476777</v>
       </c>
       <c r="G9" t="n">
-        <v>-140.8923633932218</v>
+        <v>-183.0303358738171</v>
       </c>
       <c r="H9" t="n">
-        <v>-117.9764463997493</v>
+        <v>-131.0786933207762</v>
       </c>
     </row>
   </sheetData>
@@ -1855,25 +1855,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1427800551611953</v>
+        <v>0.9542085305407768</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.09395794021847181</v>
+        <v>0.962750514330728</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4382659730750043</v>
+        <v>0.9162628542538097</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.237729339158538</v>
+        <v>0.7782291204858959</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.407688303345405</v>
+        <v>-0.06812133250092867</v>
       </c>
       <c r="G2" t="n">
-        <v>-16.75372956065652</v>
+        <v>-0.4461008389656653</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.345691861935856</v>
+        <v>0.5162048080241027</v>
       </c>
     </row>
     <row r="3">
@@ -1883,25 +1883,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1095761547686033</v>
+        <v>0.02942697744209305</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1415094595570456</v>
+        <v>0.03401955114676428</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03269689211656298</v>
+        <v>0.006482692701807968</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03355336032276531</v>
+        <v>0.006840297290143872</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05006333579629021</v>
+        <v>0.0135091011708011</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06646797991500987</v>
+        <v>0.01081050918305486</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07231119707937954</v>
+        <v>0.01684818815577752</v>
       </c>
     </row>
     <row r="4">
@@ -1911,25 +1911,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04139958170270672</v>
+        <v>0.00165889111610082</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09514889050320277</v>
+        <v>0.003239838665587426</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001394877984550608</v>
+        <v>8.121105781341823e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001385338740979201</v>
+        <v>7.249820987220567e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003660612434156771</v>
+        <v>0.0004576155469995863</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00526621781667645</v>
+        <v>0.0002594708996584328</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02470925319704542</v>
+        <v>0.0009615875826719816</v>
       </c>
     </row>
     <row r="5">
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.203468871581642</v>
+        <v>0.04072948705914205</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3084621378762761</v>
+        <v>0.05691958068703095</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03734806533879109</v>
+        <v>0.009011717805913489</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03722013891671015</v>
+        <v>0.008514588062390667</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06050299524946489</v>
+        <v>0.02139195051881867</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07256871100327227</v>
+        <v>0.01610810043606734</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1199284866610261</v>
+        <v>0.02544590409489386</v>
       </c>
     </row>
     <row r="6">
@@ -1967,25 +1967,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66.3769369366095</v>
+        <v>41.42657081980384</v>
       </c>
       <c r="C6" t="n">
-        <v>76.14952673580005</v>
+        <v>49.95926746932337</v>
       </c>
       <c r="D6" t="n">
-        <v>102.6520051903698</v>
+        <v>26.27954298061155</v>
       </c>
       <c r="E6" t="n">
-        <v>87.92758930303314</v>
+        <v>31.22402326342302</v>
       </c>
       <c r="F6" t="n">
-        <v>2976.657333039772</v>
+        <v>400.6225654032144</v>
       </c>
       <c r="G6" t="n">
-        <v>926.686659706301</v>
+        <v>192.8049226637588</v>
       </c>
       <c r="H6" t="n">
-        <v>706.0750084853142</v>
+        <v>123.7194821000225</v>
       </c>
     </row>
     <row r="7">
@@ -1995,25 +1995,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7486274474805067</v>
+        <v>0.01789866461903753</v>
       </c>
       <c r="C7" t="n">
-        <v>0.794583210835567</v>
+        <v>0.0164427327666928</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8699124130233735</v>
+        <v>0.02817799146432648</v>
       </c>
       <c r="E7" t="n">
-        <v>2.549577077732494</v>
+        <v>0.0695820126011418</v>
       </c>
       <c r="F7" t="n">
-        <v>3.854737839415063</v>
+        <v>0.6475134612663568</v>
       </c>
       <c r="G7" t="n">
-        <v>10.66461044133726</v>
+        <v>0.8740237626389212</v>
       </c>
       <c r="H7" t="n">
-        <v>3.247008071637377</v>
+        <v>0.2756064375594128</v>
       </c>
     </row>
     <row r="8">
@@ -2023,25 +2023,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-44.13623653402153</v>
+        <v>-96.82730033698465</v>
       </c>
       <c r="C8" t="n">
-        <v>-25.28468518715447</v>
+        <v>-73.98347617484207</v>
       </c>
       <c r="D8" t="n">
-        <v>-128.0739150099296</v>
+        <v>-185.7876419421018</v>
       </c>
       <c r="E8" t="n">
-        <v>-128.218022409381</v>
+        <v>-188.1709224443531</v>
       </c>
       <c r="F8" t="n">
-        <v>-141.4733699734217</v>
+        <v>-187.9265097281223</v>
       </c>
       <c r="G8" t="n">
-        <v>-121.161071398271</v>
+        <v>-186.1647840405857</v>
       </c>
       <c r="H8" t="n">
-        <v>-98.05788341869656</v>
+        <v>-153.1434391111649</v>
       </c>
     </row>
     <row r="9">
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-39.97016981374045</v>
+        <v>-91.82802027264735</v>
       </c>
       <c r="C9" t="n">
-        <v>-21.74443418164342</v>
+        <v>-69.7351749682288</v>
       </c>
       <c r="D9" t="n">
-        <v>-122.8513028213125</v>
+        <v>-179.5205073157613</v>
       </c>
       <c r="E9" t="n">
-        <v>-122.9954102207639</v>
+        <v>-181.9037878180125</v>
       </c>
       <c r="F9" t="n">
-        <v>-134.9941856434</v>
+        <v>-180.3779304999934</v>
       </c>
       <c r="G9" t="n">
-        <v>-115.06669227393</v>
+        <v>-179.096461058498</v>
       </c>
       <c r="H9" t="n">
-        <v>-92.93703249246505</v>
+        <v>-147.0769803221902</v>
       </c>
     </row>
   </sheetData>
@@ -2130,25 +2130,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1957961099240777</v>
+        <v>0.9105776172149236</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5614443707030103</v>
+        <v>0.8869258942381365</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.9990140556772715</v>
+        <v>0.7740717701741627</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2904263758946746</v>
+        <v>0.5607232372410142</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06283310263669417</v>
+        <v>0.3908637960471666</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.6589496550415832</v>
+        <v>0.4347321475190357</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.09124395859339966</v>
+        <v>0.6596490770724066</v>
       </c>
     </row>
     <row r="3">
@@ -2158,25 +2158,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08725118325504667</v>
+        <v>0.03365908248070212</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1106093350118139</v>
+        <v>0.05798995378424721</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02645399349677775</v>
+        <v>0.01290522178020167</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01084006189548839</v>
+        <v>0.01121529641685443</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01502939583773318</v>
+        <v>0.01196166342597936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0171880641797468</v>
+        <v>0.00925168441758816</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04456200561276779</v>
+        <v>0.02283048371759549</v>
       </c>
     </row>
     <row r="4">
@@ -2186,25 +2186,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02913395670712546</v>
+        <v>0.003239511597565719</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03814413700695755</v>
+        <v>0.009834816597916456</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001938710050346188</v>
+        <v>0.0002191126813622505</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002319638071187692</v>
+        <v>0.0001436021672830073</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0005353888383704848</v>
+        <v>0.0002609724089270402</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004920876033681214</v>
+        <v>0.0001014248483087344</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01174604066888109</v>
+        <v>0.002299906716893868</v>
       </c>
     </row>
     <row r="5">
@@ -2214,25 +2214,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1706867209454955</v>
+        <v>0.0569167075432664</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1953052406029023</v>
+        <v>0.09917064383130955</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04403078525697887</v>
+        <v>0.01480245524777057</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01523035807585525</v>
+        <v>0.01198341217195701</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02313847096008042</v>
+        <v>0.01615464047656401</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02218304765734685</v>
+        <v>0.01007099043335532</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0784291039164432</v>
+        <v>0.03484980828403714</v>
       </c>
     </row>
     <row r="6">
@@ -2242,25 +2242,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63.77184326654584</v>
+        <v>32.85579776426296</v>
       </c>
       <c r="C6" t="n">
-        <v>76.14763501369201</v>
+        <v>45.25641641732448</v>
       </c>
       <c r="D6" t="n">
-        <v>135.951006943091</v>
+        <v>36.73717077157774</v>
       </c>
       <c r="E6" t="n">
-        <v>51.12793604359983</v>
+        <v>43.10469517409049</v>
       </c>
       <c r="F6" t="n">
-        <v>616.9198280399702</v>
+        <v>758.9413714824506</v>
       </c>
       <c r="G6" t="n">
-        <v>156.6353970716035</v>
+        <v>116.2599084476543</v>
       </c>
       <c r="H6" t="n">
-        <v>183.4256077297504</v>
+        <v>172.1925600095601</v>
       </c>
     </row>
     <row r="7">
@@ -2270,25 +2270,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2631549367177645</v>
+        <v>0.03059437295381894</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1597675846939672</v>
+        <v>0.04230660334710058</v>
       </c>
       <c r="D7" t="n">
-        <v>1.205122627476848</v>
+        <v>0.06943184782470477</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2145344618965808</v>
+        <v>0.1333835503447938</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2830248413958511</v>
+        <v>0.184423541872099</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9990587156696654</v>
+        <v>0.1711513531381054</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5207771946417795</v>
+        <v>0.1052152115801038</v>
       </c>
     </row>
     <row r="8">
@@ -2298,25 +2298,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-54.10946509511469</v>
+        <v>-91.44965593455423</v>
       </c>
       <c r="C8" t="n">
-        <v>-42.99574823565924</v>
+        <v>-63.32739712820508</v>
       </c>
       <c r="D8" t="n">
-        <v>-125.1603814409253</v>
+        <v>-170.9444131077634</v>
       </c>
       <c r="E8" t="n">
-        <v>-169.7475132475909</v>
+        <v>-179.8177399882438</v>
       </c>
       <c r="F8" t="n">
-        <v>-197.3779664079223</v>
+        <v>-208.5284925979729</v>
       </c>
       <c r="G8" t="n">
-        <v>-184.4213450423931</v>
+        <v>-214.7086186673576</v>
       </c>
       <c r="H8" t="n">
-        <v>-128.9687365782676</v>
+        <v>-154.7960529040162</v>
       </c>
     </row>
     <row r="9">
@@ -2326,25 +2326,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-51.60982506294604</v>
+        <v>-88.95001590238559</v>
       </c>
       <c r="C9" t="n">
-        <v>-40.87159763235261</v>
+        <v>-61.20324652489845</v>
       </c>
       <c r="D9" t="n">
-        <v>-122.0268141277551</v>
+        <v>-167.8108457945931</v>
       </c>
       <c r="E9" t="n">
-        <v>-166.6139459344206</v>
+        <v>-176.6841726750735</v>
       </c>
       <c r="F9" t="n">
-        <v>-193.4904558099093</v>
+        <v>-204.7542029839084</v>
       </c>
       <c r="G9" t="n">
-        <v>-180.7647175677885</v>
+        <v>-211.1744571763138</v>
       </c>
       <c r="H9" t="n">
-        <v>-125.8962260225287</v>
+        <v>-151.7628235095288</v>
       </c>
     </row>
   </sheetData>
@@ -2405,25 +2405,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.388573642429357</v>
+        <v>0.8036829722983538</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08269627568224336</v>
+        <v>0.6473594987894209</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2763956449424692</v>
+        <v>0.5713603239105123</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.684415734905244</v>
+        <v>0.4831476738582021</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1252399153763205</v>
+        <v>0.2327266533954326</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.405520439325862</v>
+        <v>0.2720189575166814</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.369505115966786</v>
+        <v>0.5017160132947671</v>
       </c>
     </row>
     <row r="3">
@@ -2433,25 +2433,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09308377686957382</v>
+        <v>0.04370864659044143</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1204230468066506</v>
+        <v>0.088549214418588</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01696662440548801</v>
+        <v>0.01442663982445523</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02571396332236429</v>
+        <v>0.009382609504240429</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01677434970125955</v>
+        <v>0.01368370755899669</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01326734691044377</v>
+        <v>0.01000392675115135</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04770485133596336</v>
+        <v>0.02995912410797886</v>
       </c>
     </row>
     <row r="4">
@@ -2461,25 +2461,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02215019008348347</v>
+        <v>0.007111992190676111</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07978408347752361</v>
+        <v>0.03067151962897136</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007017754735841584</v>
+        <v>0.0004157089569489178</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001204457256925968</v>
+        <v>0.0001689620769672904</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004997367991519887</v>
+        <v>0.0003287231529984886</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004169139083701945</v>
+        <v>0.0001306201413744669</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01745952616650656</v>
+        <v>0.006471254357989439</v>
       </c>
     </row>
     <row r="5">
@@ -2489,25 +2489,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.148829399257954</v>
+        <v>0.08433262826851841</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2824607644922098</v>
+        <v>0.1751328627898584</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02649104515839567</v>
+        <v>0.02038894202622877</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0347052914830861</v>
+        <v>0.01299854133998467</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02235479365040055</v>
+        <v>0.01813072400646176</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02041846978522618</v>
+        <v>0.01142891689419723</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08920996063787873</v>
+        <v>0.05373543588754154</v>
       </c>
     </row>
     <row r="6">
@@ -2517,25 +2517,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>116.5479589393113</v>
+        <v>36.43576118676672</v>
       </c>
       <c r="C6" t="n">
-        <v>52.31405913473655</v>
+        <v>65.83178580115654</v>
       </c>
       <c r="D6" t="n">
-        <v>53.23628632182861</v>
+        <v>35.15055450541147</v>
       </c>
       <c r="E6" t="n">
-        <v>184.1310307870058</v>
+        <v>45.32874117324651</v>
       </c>
       <c r="F6" t="n">
-        <v>859.1947521575255</v>
+        <v>1179.505074566657</v>
       </c>
       <c r="G6" t="n">
-        <v>67.70501303635743</v>
+        <v>190.1514772581441</v>
       </c>
       <c r="H6" t="n">
-        <v>222.1881833961276</v>
+        <v>258.7338990818971</v>
       </c>
     </row>
     <row r="7">
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2009330403296314</v>
+        <v>0.06587350284396713</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3330399757295935</v>
+        <v>0.1292622141034537</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2195725493487682</v>
+        <v>0.1308828990967106</v>
       </c>
       <c r="E7" t="n">
-        <v>2.216335681102843</v>
+        <v>0.1571739712964165</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2647778411465103</v>
+        <v>0.2324121101884692</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8478959430672356</v>
+        <v>0.2204857468439577</v>
       </c>
       <c r="H7" t="n">
-        <v>0.680425838454097</v>
+        <v>0.1560150740621625</v>
       </c>
     </row>
     <row r="8">
@@ -2573,25 +2573,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-56.76845641497199</v>
+        <v>-76.0815389399409</v>
       </c>
       <c r="C8" t="n">
-        <v>-29.92646874383618</v>
+        <v>-44.26631131525626</v>
       </c>
       <c r="D8" t="n">
-        <v>-144.4998379092331</v>
+        <v>-155.496028470715</v>
       </c>
       <c r="E8" t="n">
-        <v>-133.1562506765798</v>
+        <v>-174.4025615621681</v>
       </c>
       <c r="F8" t="n">
-        <v>-197.2385829955752</v>
+        <v>-200.5276606839374</v>
       </c>
       <c r="G8" t="n">
-        <v>-186.5657703056981</v>
+        <v>-206.6372111477524</v>
       </c>
       <c r="H8" t="n">
-        <v>-124.6925611743157</v>
+        <v>-142.901885353295</v>
       </c>
     </row>
     <row r="9">
@@ -2601,25 +2601,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-53.43560303874713</v>
+        <v>-72.74868556371604</v>
       </c>
       <c r="C9" t="n">
-        <v>-27.09426793942734</v>
+        <v>-41.43411051084742</v>
       </c>
       <c r="D9" t="n">
-        <v>-140.3217481583394</v>
+        <v>-151.3179387198213</v>
       </c>
       <c r="E9" t="n">
-        <v>-128.9781609256861</v>
+        <v>-170.2244718112744</v>
       </c>
       <c r="F9" t="n">
-        <v>-192.0552355315579</v>
+        <v>-195.4952745318515</v>
       </c>
       <c r="G9" t="n">
-        <v>-181.6902670062253</v>
+        <v>-201.9249958263606</v>
       </c>
       <c r="H9" t="n">
-        <v>-120.5958804333305</v>
+        <v>-138.8575794939785</v>
       </c>
     </row>
   </sheetData>
@@ -2680,25 +2680,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4160371688545427</v>
+        <v>0.6091871904353768</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1744479621228598</v>
+        <v>0.3192841414117227</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5113001675652505</v>
+        <v>0.03531135761680015</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1940476005628766</v>
+        <v>-0.3854158469685276</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3781789969541642</v>
+        <v>-1.653782775033653</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.4923188150382027</v>
+        <v>-3.672574900106149</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07411699260833637</v>
+        <v>-0.7913318054407382</v>
       </c>
     </row>
     <row r="3">
@@ -2708,25 +2708,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08089614687204208</v>
+        <v>0.06543720209508468</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1603815088074834</v>
+        <v>0.1100648223636634</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01250813742399264</v>
+        <v>0.0143905110446029</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007964628447193176</v>
+        <v>0.008620451101219855</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01067223468603384</v>
+        <v>0.02027738792087542</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01208447606300628</v>
+        <v>0.0183788852209626</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0474178553832919</v>
+        <v>0.03952820995773481</v>
       </c>
     </row>
     <row r="4">
@@ -2736,25 +2736,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02115526678135816</v>
+        <v>0.01415800596708242</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1021496498552959</v>
+        <v>0.05920644323827909</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004739572861196061</v>
+        <v>0.0009355870015678716</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003903412104090321</v>
+        <v>0.0004529006200176796</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003552366450754184</v>
+        <v>0.001136960960578933</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004426605635207759</v>
+        <v>0.00083839050527011</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02082785205696315</v>
+        <v>0.01278804804879935</v>
       </c>
     </row>
     <row r="5">
@@ -2764,25 +2764,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1454485021626492</v>
+        <v>0.118987419364748</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3196085885192948</v>
+        <v>0.2433237416247726</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02177056007822505</v>
+        <v>0.03058736669881655</v>
       </c>
       <c r="E5" t="n">
-        <v>0.019757054699753</v>
+        <v>0.02128146188629155</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01884772254346446</v>
+        <v>0.03371885170908008</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02103950007772941</v>
+        <v>0.02895497375702679</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09107865468018599</v>
+        <v>0.07947563584012259</v>
       </c>
     </row>
     <row r="6">
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>87.11165220167459</v>
+        <v>61.25784289138527</v>
       </c>
       <c r="C6" t="n">
-        <v>105.1190193297718</v>
+        <v>78.16372995605754</v>
       </c>
       <c r="D6" t="n">
-        <v>80.17169683903896</v>
+        <v>97.2159466431858</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>92.18219227690216</v>
       </c>
       <c r="F6" t="n">
-        <v>680.6682464131393</v>
+        <v>2536.900252179159</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>607.9926535041488</v>
       </c>
       <c r="H6" t="n">
-        <v>192.1784357972708</v>
+        <v>578.9521029084731</v>
       </c>
     </row>
     <row r="7">
@@ -2820,25 +2820,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.191997536090588</v>
+        <v>0.1276544470463447</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8516782870711304</v>
+        <v>0.2461592678432786</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1489417198307086</v>
+        <v>0.2905615036160575</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7209750380322987</v>
+        <v>0.8328835690491414</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1887949665653036</v>
+        <v>1.594861410365002</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9000110138118509</v>
+        <v>2.805718686771068</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5003997602336466</v>
+        <v>0.9829731474484821</v>
       </c>
     </row>
     <row r="8">
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-57.54972852961666</v>
+        <v>-70.37707537683175</v>
       </c>
       <c r="C8" t="n">
-        <v>-26.21974578212182</v>
+        <v>-40.40087356795317</v>
       </c>
       <c r="D8" t="n">
-        <v>-152.7422604340293</v>
+        <v>-144.4610647465382</v>
       </c>
       <c r="E8" t="n">
-        <v>-156.8182753599861</v>
+        <v>-159.6965946065761</v>
       </c>
       <c r="F8" t="n">
-        <v>-206.4536123875911</v>
+        <v>-174.2643064069132</v>
       </c>
       <c r="G8" t="n">
-        <v>-185.0676825979553</v>
+        <v>-168.0166376627819</v>
       </c>
       <c r="H8" t="n">
-        <v>-130.8085508485501</v>
+        <v>-126.2027587279324</v>
       </c>
     </row>
     <row r="9">
@@ -2876,25 +2876,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-54.2168751533918</v>
+        <v>-69.54386203277554</v>
       </c>
       <c r="C9" t="n">
-        <v>-23.38754497771298</v>
+        <v>-39.69282336685096</v>
       </c>
       <c r="D9" t="n">
-        <v>-148.5641706831356</v>
+        <v>-143.4165423088147</v>
       </c>
       <c r="E9" t="n">
-        <v>-152.6401856090924</v>
+        <v>-158.6520721688527</v>
       </c>
       <c r="F9" t="n">
-        <v>-201.2702649235738</v>
+        <v>-173.0062098688917</v>
       </c>
       <c r="G9" t="n">
-        <v>-180.1921792984825</v>
+        <v>-166.838583832434</v>
       </c>
       <c r="H9" t="n">
-        <v>-126.7118701075648</v>
+        <v>-125.1916822631033</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/global/metrics_summary.xlsx
+++ b/results/cross_validation/global/metrics_summary.xlsx
@@ -480,25 +480,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8245235144174925</v>
+        <v>-0.00569260954202444</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7028825702379756</v>
+        <v>-0.02902236503450162</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6471994149263223</v>
+        <v>0.1793828628862283</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.135128212284497</v>
+        <v>-5.374731124294629</v>
       </c>
       <c r="F2" t="n">
-        <v>-8.432646046390996</v>
+        <v>-13.62331956417997</v>
       </c>
       <c r="G2" t="n">
-        <v>-10.14105545746683</v>
+        <v>-41.36112847118468</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.922370702760089</v>
+        <v>-10.03575187855826</v>
       </c>
     </row>
     <row r="3">
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05557159978665211</v>
+        <v>0.1006833003487474</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07787467265025019</v>
+        <v>0.1329326505874889</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00978186673668022</v>
+        <v>0.01408144330721298</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01539495580554709</v>
+        <v>0.02494998181195572</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04167585431337851</v>
+        <v>0.05278338982427788</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03286760052192549</v>
+        <v>0.06567351456425603</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03886109163573893</v>
+        <v>0.06518404674065649</v>
       </c>
     </row>
     <row r="4">
@@ -536,25 +536,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006357000254744677</v>
+        <v>0.04548958233556588</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02584230412494111</v>
+        <v>0.1044599529187567</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003421576942432357</v>
+        <v>0.0009413150312064544</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0006979860186216389</v>
+        <v>0.002324529699924091</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004041231411478198</v>
+        <v>0.006350210609159864</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001999016669377678</v>
+        <v>0.008062571426918654</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006546616028901089</v>
+        <v>0.02793802700358862</v>
       </c>
     </row>
     <row r="5">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07973079865864055</v>
+        <v>0.213282869297011</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1607554170936119</v>
+        <v>0.323202649925332</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01849750508158426</v>
+        <v>0.03068085773257414</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02641942502443304</v>
+        <v>0.04821337677371386</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06357068043900582</v>
+        <v>0.07968820872098872</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04471036422774565</v>
+        <v>0.08979182271743154</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0656140317541702</v>
+        <v>0.1308099641945085</v>
       </c>
     </row>
     <row r="6">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64.49544346753329</v>
+        <v>61.0683798080768</v>
       </c>
       <c r="C6" t="n">
-        <v>42.47463489742543</v>
+        <v>279.119451319774</v>
       </c>
       <c r="D6" t="n">
-        <v>34.00089466270601</v>
+        <v>116.7656548629729</v>
       </c>
       <c r="E6" t="n">
-        <v>104.5416530167692</v>
+        <v>7400.341352802471</v>
       </c>
       <c r="F6" t="n">
-        <v>5704.042675874145</v>
+        <v>4969.026358427033</v>
       </c>
       <c r="G6" t="n">
-        <v>805.9335525700744</v>
+        <v>1437.82360488394</v>
       </c>
       <c r="H6" t="n">
-        <v>1125.914809081442</v>
+        <v>2377.357467017378</v>
       </c>
     </row>
     <row r="7">
@@ -620,25 +620,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05859284585307353</v>
+        <v>0.6681009809950069</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1087248418160661</v>
+        <v>0.7646573531069605</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1075796859080736</v>
+        <v>0.2473440616559761</v>
       </c>
       <c r="E7" t="n">
-        <v>1.285054107796768</v>
+        <v>3.829093016156672</v>
       </c>
       <c r="F7" t="n">
-        <v>5.668245351810668</v>
+        <v>8.783882033360808</v>
       </c>
       <c r="G7" t="n">
-        <v>6.690431897817227</v>
+        <v>25.4289646827085</v>
       </c>
       <c r="H7" t="n">
-        <v>2.319771455166979</v>
+        <v>6.620340354663987</v>
       </c>
     </row>
     <row r="8">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-79.98937740623107</v>
+        <v>-50.53462296127262</v>
       </c>
       <c r="C8" t="n">
-        <v>-48.83613652681768</v>
+        <v>-31.8842726002723</v>
       </c>
       <c r="D8" t="n">
-        <v>-161.5850154907845</v>
+        <v>-144.3328865105298</v>
       </c>
       <c r="E8" t="n">
-        <v>-146.6135412066414</v>
+        <v>-125.3489883401394</v>
       </c>
       <c r="F8" t="n">
-        <v>-137.2913515444137</v>
+        <v>-129.5409497955986</v>
       </c>
       <c r="G8" t="n">
-        <v>-143.162397231369</v>
+        <v>-113.6925457059229</v>
       </c>
       <c r="H8" t="n">
-        <v>-119.5796365677095</v>
+        <v>-99.22237765228927</v>
       </c>
     </row>
     <row r="9">
@@ -676,25 +676,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-77.48973737406243</v>
+        <v>-49.7014096172164</v>
       </c>
       <c r="C9" t="n">
-        <v>-46.71198592351104</v>
+        <v>-31.17622239917009</v>
       </c>
       <c r="D9" t="n">
-        <v>-158.4514481776143</v>
+        <v>-143.2883640728064</v>
       </c>
       <c r="E9" t="n">
-        <v>-143.4799738934711</v>
+        <v>-124.304465902416</v>
       </c>
       <c r="F9" t="n">
-        <v>-133.5170619303492</v>
+        <v>-128.2828532575771</v>
       </c>
       <c r="G9" t="n">
-        <v>-139.6282357403251</v>
+        <v>-112.5144918755749</v>
       </c>
       <c r="H9" t="n">
-        <v>-116.5464071732222</v>
+        <v>-98.21130118746015</v>
       </c>
     </row>
   </sheetData>
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9602995013907358</v>
+        <v>0.3196435173169476</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9561599566955046</v>
+        <v>0.0959283729130217</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9448221858734958</v>
+        <v>-0.1684132388757311</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6342634465475654</v>
+        <v>-1.204058480254945</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.02137195166994377</v>
+        <v>-4.258528043469171</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1247326788059616</v>
+        <v>-14.9353956846101</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5998176362738866</v>
+        <v>-3.358470592829997</v>
       </c>
     </row>
     <row r="3">
@@ -783,25 +783,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02392232348444865</v>
+        <v>0.1347593910322981</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03544988279783913</v>
+        <v>0.1491242141326117</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004337362248359345</v>
+        <v>0.02769097136913941</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005613596395764563</v>
+        <v>0.02188718964521308</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01096022204060342</v>
+        <v>0.04112695629162537</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00736789239832406</v>
+        <v>0.05228602329115234</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01460854656088986</v>
+        <v>0.07114579096033999</v>
       </c>
     </row>
     <row r="4">
@@ -811,25 +811,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001438233042648428</v>
+        <v>0.0307739481655736</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003813063854358109</v>
+        <v>0.09177573083897274</v>
       </c>
       <c r="D4" t="n">
-        <v>5.351327195493111e-05</v>
+        <v>0.001340265630184931</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000119561438671417</v>
+        <v>0.000803704391263888</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004375866955667885</v>
+        <v>0.002283528061029223</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001570474154722732</v>
+        <v>0.003032975526390341</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001003167619778658</v>
+        <v>0.02166835876890245</v>
       </c>
     </row>
     <row r="5">
@@ -839,25 +839,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03792404306832841</v>
+        <v>0.1754250499945022</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06175001096646145</v>
+        <v>0.3029450954199007</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007315276615065975</v>
+        <v>0.03660963848749303</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01093441533285694</v>
+        <v>0.02834968062013906</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02091857298112824</v>
+        <v>0.04778627481850017</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01253185602663361</v>
+        <v>0.05507245705786461</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0252290291650791</v>
+        <v>0.1076980327330666</v>
       </c>
     </row>
     <row r="6">
@@ -867,25 +867,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.33087895072465</v>
+        <v>116.5729191752877</v>
       </c>
       <c r="C6" t="n">
-        <v>47.39739131029629</v>
+        <v>488.6382700983751</v>
       </c>
       <c r="D6" t="n">
-        <v>23.28075810671715</v>
+        <v>104.3503870530708</v>
       </c>
       <c r="E6" t="n">
-        <v>58.24117515621439</v>
+        <v>3860.193805672552</v>
       </c>
       <c r="F6" t="n">
-        <v>509.0185419865456</v>
+        <v>724.5540067803108</v>
       </c>
       <c r="G6" t="n">
-        <v>111.5875569865318</v>
+        <v>583.9341373207342</v>
       </c>
       <c r="H6" t="n">
-        <v>132.309383749505</v>
+        <v>979.7072543500552</v>
       </c>
     </row>
     <row r="7">
@@ -895,25 +895,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01441691271263315</v>
+        <v>0.2271487085208173</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01732115768939931</v>
+        <v>0.3369644997133744</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01809080352831973</v>
+        <v>0.7059243152076976</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1113046590428004</v>
+        <v>1.326560274300737</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6164357923757599</v>
+        <v>3.161313765366944</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2641901295490421</v>
+        <v>9.568483576503008</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1736265758163258</v>
+        <v>2.55439918993543</v>
       </c>
     </row>
     <row r="8">
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-105.2537795334761</v>
+        <v>-53.17847535700458</v>
       </c>
       <c r="C8" t="n">
-        <v>-77.53983377638646</v>
+        <v>-29.82611079380126</v>
       </c>
       <c r="D8" t="n">
-        <v>-200.5471980789759</v>
+        <v>-132.9126365168491</v>
       </c>
       <c r="E8" t="n">
-        <v>-183.6652839389968</v>
+        <v>-143.6518596079665</v>
       </c>
       <c r="F8" t="n">
-        <v>-195.0901284730635</v>
+        <v>-152.1328745570562</v>
       </c>
       <c r="G8" t="n">
-        <v>-204.215106932018</v>
+        <v>-133.1570668660303</v>
       </c>
       <c r="H8" t="n">
-        <v>-161.0518884554861</v>
+        <v>-107.4765039497847</v>
       </c>
     </row>
     <row r="9">
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-102.7541395013075</v>
+        <v>-50.67883532483593</v>
       </c>
       <c r="C9" t="n">
-        <v>-75.41568317307983</v>
+        <v>-27.70196019049463</v>
       </c>
       <c r="D9" t="n">
-        <v>-197.4136307658057</v>
+        <v>-129.7790692036788</v>
       </c>
       <c r="E9" t="n">
-        <v>-180.5317166258266</v>
+        <v>-140.5182922947963</v>
       </c>
       <c r="F9" t="n">
-        <v>-191.3158388589991</v>
+        <v>-148.3585849429917</v>
       </c>
       <c r="G9" t="n">
-        <v>-200.6809454409741</v>
+        <v>-129.6229053749864</v>
       </c>
       <c r="H9" t="n">
-        <v>-158.0186590609988</v>
+        <v>-104.4432745552973</v>
       </c>
     </row>
   </sheetData>
@@ -1030,25 +1030,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9583890237326176</v>
+        <v>0.3195229393527415</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9587807365876686</v>
+        <v>0.09749530441938414</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9403646022292164</v>
+        <v>-0.10359954258621</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6564548350897044</v>
+        <v>-1.126658646922068</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.001603093227251051</v>
+        <v>-4.332222271289967</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1859981204947476</v>
+        <v>-14.75547555307342</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6163973708177839</v>
+        <v>-3.316822961683256</v>
       </c>
     </row>
     <row r="3">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02372181626213336</v>
+        <v>0.1326501917530062</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03469444570080295</v>
+        <v>0.149231992880737</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005079727589309769</v>
+        <v>0.0272320296023932</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006334688357229453</v>
+        <v>0.02167959489939312</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01135506020129942</v>
+        <v>0.04137945885300191</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00726873306880133</v>
+        <v>0.05216819280448715</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01474241186326272</v>
+        <v>0.07072357679883642</v>
       </c>
     </row>
     <row r="4">
@@ -1086,25 +1086,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001507444064963047</v>
+        <v>0.03077940215934722</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003585116974661152</v>
+        <v>0.09161666569428459</v>
       </c>
       <c r="D4" t="n">
-        <v>5.783638423464707e-05</v>
+        <v>0.001265919014953427</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000112306942736655</v>
+        <v>0.0007754807363608969</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004291171175380187</v>
+        <v>0.00231552995124899</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001460546832611981</v>
+        <v>0.002998731421853753</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000972979361232453</v>
+        <v>0.02162528816300814</v>
       </c>
     </row>
     <row r="5">
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03882581699028428</v>
+        <v>0.1754405943883776</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05987584633774418</v>
+        <v>0.3026824502581618</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007605023618283317</v>
+        <v>0.0355797556899064</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01059749700338033</v>
+        <v>0.02784745475552293</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02071514222828361</v>
+        <v>0.04811995377438542</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01208530857120322</v>
+        <v>0.05476067404491797</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02495077245819649</v>
+        <v>0.1074051471518787</v>
       </c>
     </row>
     <row r="6">
@@ -1142,25 +1142,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46.20093768476104</v>
+        <v>111.7350222664646</v>
       </c>
       <c r="C6" t="n">
-        <v>47.4523253543209</v>
+        <v>491.6073639175594</v>
       </c>
       <c r="D6" t="n">
-        <v>25.0890561296105</v>
+        <v>101.4711954779222</v>
       </c>
       <c r="E6" t="n">
-        <v>56.29214912684242</v>
+        <v>3781.886018263005</v>
       </c>
       <c r="F6" t="n">
-        <v>435.4420171018974</v>
+        <v>716.1646420424106</v>
       </c>
       <c r="G6" t="n">
-        <v>117.9191023712806</v>
+        <v>603.9248051468317</v>
       </c>
       <c r="H6" t="n">
-        <v>121.3992646281188</v>
+        <v>967.7981745190322</v>
       </c>
     </row>
     <row r="7">
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01603850372568886</v>
+        <v>0.2271886997057206</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01737536090596223</v>
+        <v>0.336383074660184</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02043110480019935</v>
+        <v>0.6669320121726608</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1056421643330044</v>
+        <v>1.280080861184146</v>
       </c>
       <c r="F7" t="n">
-        <v>0.606562619900904</v>
+        <v>3.205575104705729</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2468028021298586</v>
+        <v>9.460483555834646</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1688087592992696</v>
+        <v>2.529440551377181</v>
       </c>
     </row>
     <row r="8">
@@ -1198,25 +1198,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-100.4547754874086</v>
+        <v>-53.17546275431425</v>
       </c>
       <c r="C8" t="n">
-        <v>-74.46446264821429</v>
+        <v>-29.85213125935756</v>
       </c>
       <c r="D8" t="n">
-        <v>-194.9157424013009</v>
+        <v>-134.1110954572848</v>
       </c>
       <c r="E8" t="n">
-        <v>-180.9797723751756</v>
+        <v>-144.4025757347135</v>
       </c>
       <c r="F8" t="n">
-        <v>-191.5982975510451</v>
+        <v>-151.7710341224252</v>
       </c>
       <c r="G8" t="n">
-        <v>-201.9567071238727</v>
+        <v>-133.4295825390324</v>
       </c>
       <c r="H8" t="n">
-        <v>-157.3949595978362</v>
+        <v>-107.7903136445213</v>
       </c>
     </row>
     <row r="9">
@@ -1226,25 +1226,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-96.28870876712753</v>
+        <v>-50.6758227221456</v>
       </c>
       <c r="C9" t="n">
-        <v>-70.92421164270324</v>
+        <v>-27.72798065605093</v>
       </c>
       <c r="D9" t="n">
-        <v>-189.6931302126837</v>
+        <v>-130.9775281441146</v>
       </c>
       <c r="E9" t="n">
-        <v>-175.7571601865585</v>
+        <v>-141.2690084215432</v>
       </c>
       <c r="F9" t="n">
-        <v>-185.3078148609377</v>
+        <v>-147.9967445083608</v>
       </c>
       <c r="G9" t="n">
-        <v>-196.066437972133</v>
+        <v>-129.8954210479885</v>
       </c>
       <c r="H9" t="n">
-        <v>-152.3395772736906</v>
+        <v>-104.7570842500339</v>
       </c>
     </row>
   </sheetData>
@@ -1305,25 +1305,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9599133534651896</v>
+        <v>0.3199548480555829</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9587748798422706</v>
+        <v>0.09721977930821202</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9441522489268525</v>
+        <v>-0.1771792367368519</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6418911746522162</v>
+        <v>-1.22121531971414</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00804518072053384</v>
+        <v>-4.317158864370665</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1679343801947063</v>
+        <v>-15.0024755656635</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6134518696336281</v>
+        <v>-3.383475726520227</v>
       </c>
     </row>
     <row r="3">
@@ -1333,25 +1333,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02403206999893837</v>
+        <v>0.1351245339424208</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03370779392908423</v>
+        <v>0.1492104082481111</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004290091295638785</v>
+        <v>0.02775730024548536</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005508380573490652</v>
+        <v>0.02193403331957024</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0105006652309145</v>
+        <v>0.04132965247195375</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007210507365215334</v>
+        <v>0.05235992650975244</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01420825139888031</v>
+        <v>0.07128597578954894</v>
       </c>
     </row>
     <row r="4">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001452222053500328</v>
+        <v>0.03075986602443587</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003585626375257002</v>
+        <v>0.09164463529059169</v>
       </c>
       <c r="D4" t="n">
-        <v>5.416299899805363e-05</v>
+        <v>0.001350320947307869</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001170678893190823</v>
+        <v>0.0008099605896983184</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004249835045992343</v>
+        <v>0.002308988631679981</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001492958230355173</v>
+        <v>0.003045742805068249</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000963893107451536</v>
+        <v>0.02165325238146366</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1389,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03810803135167608</v>
+        <v>0.1753849082003234</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05988009999371245</v>
+        <v>0.3027286496032242</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007359551548705508</v>
+        <v>0.03674671342185406</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0108197915561753</v>
+        <v>0.02845980656466798</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02061512805197276</v>
+        <v>0.04805193681507522</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01221866699094125</v>
+        <v>0.05518824879508543</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02483354491553055</v>
+        <v>0.1077600439000384</v>
       </c>
     </row>
     <row r="6">
@@ -1417,25 +1417,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.34980295984725</v>
+        <v>117.4587351620333</v>
       </c>
       <c r="C6" t="n">
-        <v>47.56636585836899</v>
+        <v>491.0871424018187</v>
       </c>
       <c r="D6" t="n">
-        <v>23.66570875591387</v>
+        <v>104.8083657417407</v>
       </c>
       <c r="E6" t="n">
-        <v>58.04798860781163</v>
+        <v>3876.767469049429</v>
       </c>
       <c r="F6" t="n">
-        <v>429.5888964430966</v>
+        <v>717.6620482146635</v>
       </c>
       <c r="G6" t="n">
-        <v>112.8978943347214</v>
+        <v>581.3464787487401</v>
       </c>
       <c r="H6" t="n">
-        <v>119.35277615996</v>
+        <v>981.5217065530709</v>
       </c>
     </row>
     <row r="7">
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01454254939789336</v>
+        <v>0.2270454518004303</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01637747450999872</v>
+        <v>0.3364853109109506</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01829223942124291</v>
+        <v>0.7111979913683423</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1090145951268585</v>
+        <v>1.336863136654061</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2993839342370594</v>
+        <v>3.196527902706752</v>
       </c>
       <c r="G7" t="n">
-        <v>0.251224193017713</v>
+        <v>9.608749379325198</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1181391642851276</v>
+        <v>2.569478195460956</v>
       </c>
     </row>
     <row r="8">
@@ -1473,25 +1473,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-105.0892275626898</v>
+        <v>-53.18625632773334</v>
       </c>
       <c r="C8" t="n">
-        <v>-78.46233148591278</v>
+        <v>-29.84755261732447</v>
       </c>
       <c r="D8" t="n">
-        <v>-200.2937637171649</v>
+        <v>-132.7556724968528</v>
       </c>
       <c r="E8" t="n">
-        <v>-184.1078873579834</v>
+        <v>-143.4890242896729</v>
       </c>
       <c r="F8" t="n">
-        <v>-195.8499652650201</v>
+        <v>-151.8445874747023</v>
       </c>
       <c r="G8" t="n">
-        <v>-205.4299399391919</v>
+        <v>-133.0562511604386</v>
       </c>
       <c r="H8" t="n">
-        <v>-161.5388525546605</v>
+        <v>-107.3632240611207</v>
       </c>
     </row>
     <row r="9">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-102.5895875305211</v>
+        <v>-50.68661629556469</v>
       </c>
       <c r="C9" t="n">
-        <v>-76.33818088260615</v>
+        <v>-27.72340201401784</v>
       </c>
       <c r="D9" t="n">
-        <v>-197.1601964039947</v>
+        <v>-129.6221051836825</v>
       </c>
       <c r="E9" t="n">
-        <v>-180.9743200448131</v>
+        <v>-140.3554569765027</v>
       </c>
       <c r="F9" t="n">
-        <v>-192.0756756509556</v>
+        <v>-148.0702978606378</v>
       </c>
       <c r="G9" t="n">
-        <v>-201.895778448148</v>
+        <v>-129.5220896693947</v>
       </c>
       <c r="H9" t="n">
-        <v>-158.5056231601731</v>
+        <v>-104.3299946666334</v>
       </c>
     </row>
   </sheetData>
@@ -1580,25 +1580,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5713644573991081</v>
+        <v>-0.103417294148894</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6181158218243014</v>
+        <v>-0.1581869919918826</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04366783323165824</v>
+        <v>0.7408991412309722</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3000636229541132</v>
+        <v>0.50164749916983</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7712169871726116</v>
+        <v>-1.346055464555919</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.379889255139418</v>
+        <v>-17.91594889909859</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2030036254685125</v>
+        <v>-3.046843668232414</v>
       </c>
     </row>
     <row r="3">
@@ -1608,25 +1608,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06601384471495238</v>
+        <v>0.1046845185123914</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08306954478431279</v>
+        <v>0.1478548275489611</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0141359557104953</v>
+        <v>0.008840500098057485</v>
       </c>
       <c r="E3" t="n">
-        <v>0.008859642238705478</v>
+        <v>0.007312964276981891</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01754324431866501</v>
+        <v>0.02385700944231687</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01432669395685222</v>
+        <v>0.03916961412523984</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03399148762066386</v>
+        <v>0.05528657233399144</v>
       </c>
     </row>
     <row r="4">
@@ -1636,25 +1636,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01552821305066142</v>
+        <v>0.04990987442527885</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03321503918778503</v>
+        <v>0.1175719428124695</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009274826147007622</v>
+        <v>0.0002972098947575017</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004249984740586878</v>
+        <v>0.0001817229882522077</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007588430319448275</v>
+        <v>0.001018780054372415</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004270186348554659</v>
+        <v>0.003600262660865335</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008546932499001033</v>
+        <v>0.0287632988059993</v>
       </c>
     </row>
     <row r="5">
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1246122508048924</v>
+        <v>0.223405179942809</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1822499360432948</v>
+        <v>0.342887653339209</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03045459923723775</v>
+        <v>0.0172397765286416</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02061549111854209</v>
+        <v>0.01348046691521505</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0275471056908857</v>
+        <v>0.0319183341415622</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02066442921678375</v>
+        <v>0.06000218880062072</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06769063535193942</v>
+        <v>0.1148222666113429</v>
       </c>
     </row>
     <row r="6">
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62.0702365003909</v>
+        <v>49.51420143594815</v>
       </c>
       <c r="C6" t="n">
-        <v>56.69006712006034</v>
+        <v>156.444946488089</v>
       </c>
       <c r="D6" t="n">
-        <v>102.6685174826312</v>
+        <v>43.82342110610183</v>
       </c>
       <c r="E6" t="n">
-        <v>132.7884231816046</v>
+        <v>1841.766024986806</v>
       </c>
       <c r="F6" t="n">
-        <v>2328.675278609207</v>
+        <v>1728.312002366989</v>
       </c>
       <c r="G6" t="n">
-        <v>387.2321028320212</v>
+        <v>776.3870741470328</v>
       </c>
       <c r="H6" t="n">
-        <v>511.687437620986</v>
+        <v>766.0412784218278</v>
       </c>
     </row>
     <row r="7">
@@ -1720,25 +1720,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1399604119157306</v>
+        <v>0.7389242006847269</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1383157808841591</v>
+        <v>0.866512915132587</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2880488878607931</v>
+        <v>0.0814383045570386</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7816331716361501</v>
+        <v>0.1531329563408276</v>
       </c>
       <c r="F7" t="n">
-        <v>1.06479257254829</v>
+        <v>1.416059570809673</v>
       </c>
       <c r="G7" t="n">
-        <v>1.429531379172448</v>
+        <v>11.36160970718437</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6403803673362619</v>
+        <v>2.436279609118203</v>
       </c>
     </row>
     <row r="8">
@@ -1748,25 +1748,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-68.80664411744465</v>
+        <v>-36.95811899595984</v>
       </c>
       <c r="C8" t="n">
-        <v>-49.07128777065565</v>
+        <v>-18.11057280263995</v>
       </c>
       <c r="D8" t="n">
-        <v>-144.6437666662422</v>
+        <v>-156.5425110006679</v>
       </c>
       <c r="E8" t="n">
-        <v>-161.0319245694255</v>
+        <v>-166.8735685317658</v>
       </c>
       <c r="F8" t="n">
-        <v>-184.7766058856992</v>
+        <v>-165.1178842081173</v>
       </c>
       <c r="G8" t="n">
-        <v>-184.208389704165</v>
+        <v>-121.0419633959234</v>
       </c>
       <c r="H8" t="n">
-        <v>-132.0897697856054</v>
+        <v>-110.7741031558457</v>
       </c>
     </row>
     <row r="9">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-67.97343077338843</v>
+        <v>-31.12562558756633</v>
       </c>
       <c r="C9" t="n">
-        <v>-48.36323756955344</v>
+        <v>-13.15422139492448</v>
       </c>
       <c r="D9" t="n">
-        <v>-143.5992442285188</v>
+        <v>-149.230853936604</v>
       </c>
       <c r="E9" t="n">
-        <v>-159.987402131702</v>
+        <v>-159.5619114677019</v>
       </c>
       <c r="F9" t="n">
-        <v>-183.5185093476777</v>
+        <v>-156.311208441967</v>
       </c>
       <c r="G9" t="n">
-        <v>-183.0303358738171</v>
+        <v>-112.7955865834878</v>
       </c>
       <c r="H9" t="n">
-        <v>-131.0786933207762</v>
+        <v>-103.6965679020419</v>
       </c>
     </row>
   </sheetData>
@@ -1855,25 +1855,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9542085305407768</v>
+        <v>-0.15002626937644</v>
       </c>
       <c r="C2" t="n">
-        <v>0.962750514330728</v>
+        <v>-0.09326792638924397</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9162628542538097</v>
+        <v>-0.0701763759244205</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7782291204858959</v>
+        <v>-1.922562287497254</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.06812133250092867</v>
+        <v>-8.263270778729369</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.4461008389656653</v>
+        <v>-27.31304845396973</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5162048080241027</v>
+        <v>-6.302058681981078</v>
       </c>
     </row>
     <row r="3">
@@ -1883,25 +1883,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02942697744209305</v>
+        <v>0.1214353767297386</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03401955114676428</v>
+        <v>0.1500239869151465</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006482692701807968</v>
+        <v>0.03124513809081009</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006840297290143872</v>
+        <v>0.02946624471876171</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0135091011708011</v>
+        <v>0.05358576285897866</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01081050918305486</v>
+        <v>0.06850719136278932</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01684818815577752</v>
+        <v>0.07571061677937081</v>
       </c>
     </row>
     <row r="4">
@@ -1911,25 +1911,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00165889111610082</v>
+        <v>0.05201809595944654</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003239838665587426</v>
+        <v>0.1109817628836261</v>
       </c>
       <c r="D4" t="n">
-        <v>8.121105781341823e-05</v>
+        <v>0.001227579906803777</v>
       </c>
       <c r="E4" t="n">
-        <v>7.249820987220567e-05</v>
+        <v>0.001065705000682232</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004576155469995863</v>
+        <v>0.004022596929270241</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002594708996584328</v>
+        <v>0.005388807704431671</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0009615875826719816</v>
+        <v>0.0291174247307101</v>
       </c>
     </row>
     <row r="5">
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04072948705914205</v>
+        <v>0.2280747595843226</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05691958068703095</v>
+        <v>0.333139254492211</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009011717805913489</v>
+        <v>0.0350368364268776</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008514588062390667</v>
+        <v>0.03264513747378364</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02139195051881867</v>
+        <v>0.06342394602411806</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01610810043606734</v>
+        <v>0.07340849885695573</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02544590409489386</v>
+        <v>0.1276214054763781</v>
       </c>
     </row>
     <row r="6">
@@ -1967,25 +1967,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41.42657081980384</v>
+        <v>66.34507034549844</v>
       </c>
       <c r="C6" t="n">
-        <v>49.95926746932337</v>
+        <v>209.9437102228751</v>
       </c>
       <c r="D6" t="n">
-        <v>26.27954298061155</v>
+        <v>84.57913142962265</v>
       </c>
       <c r="E6" t="n">
-        <v>31.22402326342302</v>
+        <v>3720.796762629502</v>
       </c>
       <c r="F6" t="n">
-        <v>400.6225654032144</v>
+        <v>2106.649306251878</v>
       </c>
       <c r="G6" t="n">
-        <v>192.8049226637588</v>
+        <v>877.2991477044801</v>
       </c>
       <c r="H6" t="n">
-        <v>123.7194821000225</v>
+        <v>1177.602188097309</v>
       </c>
     </row>
     <row r="7">
@@ -1995,25 +1995,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01789866461903753</v>
+        <v>0.7668410959690892</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0164427327666928</v>
+        <v>0.8153352238706231</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02817799146432648</v>
+        <v>0.6478244374241776</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0695820126011418</v>
+        <v>1.759029359499308</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6475134612663568</v>
+        <v>5.5675941029386</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8740237626389212</v>
+        <v>16.99937340316805</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2756064375594128</v>
+        <v>4.425999603811641</v>
       </c>
     </row>
     <row r="8">
@@ -2023,25 +2023,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-96.82730033698465</v>
+        <v>-42.25478156921056</v>
       </c>
       <c r="C8" t="n">
-        <v>-73.98347617484207</v>
+        <v>-24.97584084270948</v>
       </c>
       <c r="D8" t="n">
-        <v>-185.7876419421018</v>
+        <v>-132.7569226676587</v>
       </c>
       <c r="E8" t="n">
-        <v>-188.1709224443531</v>
+        <v>-135.7264932534823</v>
       </c>
       <c r="F8" t="n">
-        <v>-187.9265097281223</v>
+        <v>-135.411517147986</v>
       </c>
       <c r="G8" t="n">
-        <v>-186.1647840405857</v>
+        <v>-117.3623469674898</v>
       </c>
       <c r="H8" t="n">
-        <v>-153.1434391111649</v>
+        <v>-98.08131707475616</v>
       </c>
     </row>
     <row r="9">
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-91.82802027264735</v>
+        <v>-38.92192819298569</v>
       </c>
       <c r="C9" t="n">
-        <v>-69.7351749682288</v>
+        <v>-22.14364003830064</v>
       </c>
       <c r="D9" t="n">
-        <v>-179.5205073157613</v>
+        <v>-128.578832916765</v>
       </c>
       <c r="E9" t="n">
-        <v>-181.9037878180125</v>
+        <v>-131.5484035025886</v>
       </c>
       <c r="F9" t="n">
-        <v>-180.3779304999934</v>
+        <v>-130.3791309959001</v>
       </c>
       <c r="G9" t="n">
-        <v>-179.096461058498</v>
+        <v>-112.650131646098</v>
       </c>
       <c r="H9" t="n">
-        <v>-147.0769803221902</v>
+        <v>-94.03701121543969</v>
       </c>
     </row>
   </sheetData>
@@ -2130,25 +2130,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9105776172149236</v>
+        <v>0.1830053738079017</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8869258942381365</v>
+        <v>0.549838672248941</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7740717701741627</v>
+        <v>-1.48019232607482</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5607232372410142</v>
+        <v>-10.14549946568423</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3908637960471666</v>
+        <v>-0.05675636570207887</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4347321475190357</v>
+        <v>-1.663203836594571</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6596490770724066</v>
+        <v>-2.10213465799981</v>
       </c>
     </row>
     <row r="3">
@@ -2158,25 +2158,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03365908248070212</v>
+        <v>0.09847189734062323</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05798995378424721</v>
+        <v>0.1188867118193278</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01290522178020167</v>
+        <v>0.03178534692064586</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01121529641685443</v>
+        <v>0.04906857016177808</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01196166342597936</v>
+        <v>0.01355325404272496</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00925168441758816</v>
+        <v>0.01782074950474076</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02283048371759549</v>
+        <v>0.05493108829830678</v>
       </c>
     </row>
     <row r="4">
@@ -2186,25 +2186,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003239511597565719</v>
+        <v>0.03695437747405196</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009834816597916456</v>
+        <v>0.04569757927578573</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002191126813622505</v>
+        <v>0.002844983624188498</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001436021672830073</v>
+        <v>0.004064178398008565</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0002609724089270402</v>
+        <v>0.0004588989152104926</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001014248483087344</v>
+        <v>0.0005068861933551562</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002299906716893868</v>
+        <v>0.0150878173134334</v>
       </c>
     </row>
     <row r="5">
@@ -2214,25 +2214,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0569167075432664</v>
+        <v>0.192235213928281</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09917064383130955</v>
+        <v>0.2137699213542114</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01480245524777057</v>
+        <v>0.05333838790391492</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01198341217195701</v>
+        <v>0.06375090899750814</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01615464047656401</v>
+        <v>0.02142192603876908</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01007099043335532</v>
+        <v>0.02251413319129023</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03484980828403714</v>
+        <v>0.09450508190232913</v>
       </c>
     </row>
     <row r="6">
@@ -2242,25 +2242,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32.85579776426296</v>
+        <v>65.13325395782891</v>
       </c>
       <c r="C6" t="n">
-        <v>45.25641641732448</v>
+        <v>1032.873536379434</v>
       </c>
       <c r="D6" t="n">
-        <v>36.73717077157774</v>
+        <v>153.8928091347392</v>
       </c>
       <c r="E6" t="n">
-        <v>43.10469517409049</v>
+        <v>8220.504270410927</v>
       </c>
       <c r="F6" t="n">
-        <v>758.9413714824506</v>
+        <v>377.7565037692831</v>
       </c>
       <c r="G6" t="n">
-        <v>116.2599084476543</v>
+        <v>155.9056773266036</v>
       </c>
       <c r="H6" t="n">
-        <v>172.1925600095601</v>
+        <v>1667.677675163136</v>
       </c>
     </row>
     <row r="7">
@@ -2270,25 +2270,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03059437295381894</v>
+        <v>0.2724664520894659</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04230660334710058</v>
+        <v>0.1685367038183677</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06943184782470477</v>
+        <v>1.495098372718756</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1333835503447938</v>
+        <v>6.695989529167754</v>
       </c>
       <c r="F7" t="n">
-        <v>0.184423541872099</v>
+        <v>0.6376962779025421</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1711513531381054</v>
+        <v>1.60163194262744</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1052152115801038</v>
+        <v>1.811903213054054</v>
       </c>
     </row>
     <row r="8">
@@ -2298,25 +2298,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-91.44965593455423</v>
+        <v>-50.06720986280992</v>
       </c>
       <c r="C8" t="n">
-        <v>-63.32739712820508</v>
+        <v>-40.28564928570318</v>
       </c>
       <c r="D8" t="n">
-        <v>-170.9444131077634</v>
+        <v>-117.1061573157659</v>
       </c>
       <c r="E8" t="n">
-        <v>-179.8177399882438</v>
+        <v>-109.6164171229542</v>
       </c>
       <c r="F8" t="n">
-        <v>-208.5284925979729</v>
+        <v>-193.8536956118852</v>
       </c>
       <c r="G8" t="n">
-        <v>-214.7086186673576</v>
+        <v>-176.0933772064872</v>
       </c>
       <c r="H8" t="n">
-        <v>-154.7960529040162</v>
+        <v>-114.5037510676009</v>
       </c>
     </row>
     <row r="9">
@@ -2326,25 +2326,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-88.95001590238559</v>
+        <v>-47.56756983064127</v>
       </c>
       <c r="C9" t="n">
-        <v>-61.20324652489845</v>
+        <v>-38.16149868239655</v>
       </c>
       <c r="D9" t="n">
-        <v>-167.8108457945931</v>
+        <v>-113.9725900025956</v>
       </c>
       <c r="E9" t="n">
-        <v>-176.6841726750735</v>
+        <v>-106.482849809784</v>
       </c>
       <c r="F9" t="n">
-        <v>-204.7542029839084</v>
+        <v>-190.0794059978207</v>
       </c>
       <c r="G9" t="n">
-        <v>-211.1744571763138</v>
+        <v>-172.5592157154433</v>
       </c>
       <c r="H9" t="n">
-        <v>-151.7628235095288</v>
+        <v>-111.4705216731136</v>
       </c>
     </row>
   </sheetData>
@@ -2405,25 +2405,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8036829722983538</v>
+        <v>0.4541462992685739</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6473594987894209</v>
+        <v>0.2873789952312541</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5713603239105123</v>
+        <v>0.5737245416328327</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4831476738582021</v>
+        <v>-0.3875778401104402</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2327266533954326</v>
+        <v>0.1658011923084912</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2720189575166814</v>
+        <v>-3.52052253054685</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5017160132947671</v>
+        <v>-0.4045082237026897</v>
       </c>
     </row>
     <row r="3">
@@ -2433,25 +2433,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04370864659044143</v>
+        <v>0.0908766276681205</v>
       </c>
       <c r="C3" t="n">
-        <v>0.088549214418588</v>
+        <v>0.1142333034962122</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01442663982445523</v>
+        <v>0.01391522920406497</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009382609504240429</v>
+        <v>0.01601889963642343</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01368370755899669</v>
+        <v>0.01569939344097096</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01000392675115135</v>
+        <v>0.01597308435737965</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02995912410797886</v>
+        <v>0.04445275630052862</v>
       </c>
     </row>
     <row r="4">
@@ -2461,25 +2461,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007111992190676111</v>
+        <v>0.02469010573111699</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03067151962897136</v>
+        <v>0.0723408539371877</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004157089569489178</v>
+        <v>0.0004889728452500065</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001689620769672904</v>
+        <v>0.0005059767757106997</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003287231529984886</v>
+        <v>0.0003622527768405631</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001306201413744669</v>
+        <v>0.0008603886889916404</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006471254357989439</v>
+        <v>0.0165414251258496</v>
       </c>
     </row>
     <row r="5">
@@ -2489,25 +2489,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08433262826851841</v>
+        <v>0.157130855439398</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1751328627898584</v>
+        <v>0.2689625511798766</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02038894202622877</v>
+        <v>0.02211273038885082</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01299854133998467</v>
+        <v>0.02249392752968453</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01813072400646176</v>
+        <v>0.01903293925909929</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01142891689419723</v>
+        <v>0.02933238294090067</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05373543588754154</v>
+        <v>0.08651089778963496</v>
       </c>
     </row>
     <row r="6">
@@ -2517,25 +2517,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.43576118676672</v>
+        <v>74.85068118146413</v>
       </c>
       <c r="C6" t="n">
-        <v>65.83178580115654</v>
+        <v>576.6566464766095</v>
       </c>
       <c r="D6" t="n">
-        <v>35.15055450541147</v>
+        <v>36.47807246846528</v>
       </c>
       <c r="E6" t="n">
-        <v>45.32874117324651</v>
+        <v>3882.57514194831</v>
       </c>
       <c r="F6" t="n">
-        <v>1179.505074566657</v>
+        <v>923.732714306819</v>
       </c>
       <c r="G6" t="n">
-        <v>190.1514772581441</v>
+        <v>190.2834689659236</v>
       </c>
       <c r="H6" t="n">
-        <v>258.7338990818971</v>
+        <v>947.4294542245985</v>
       </c>
     </row>
     <row r="7">
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06587350284396713</v>
+        <v>0.1825391842312098</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1292622141034537</v>
+        <v>0.2659248991866552</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1308828990967106</v>
+        <v>0.1297249185018252</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1571739712964165</v>
+        <v>0.8362550715522592</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2324121101884692</v>
+        <v>0.2520132192512411</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2204857468439577</v>
+        <v>2.716518062492699</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1560150740621625</v>
+        <v>0.7304958925359815</v>
       </c>
     </row>
     <row r="8">
@@ -2573,25 +2573,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-76.0815389399409</v>
+        <v>-56.92299578590367</v>
       </c>
       <c r="C8" t="n">
-        <v>-44.26631131525626</v>
+        <v>-33.39549372048884</v>
       </c>
       <c r="D8" t="n">
-        <v>-155.496028470715</v>
+        <v>-154.0872756255653</v>
       </c>
       <c r="E8" t="n">
-        <v>-174.4025615621681</v>
+        <v>-153.3694155382368</v>
       </c>
       <c r="F8" t="n">
-        <v>-200.5276606839374</v>
+        <v>-200.0023760926679</v>
       </c>
       <c r="G8" t="n">
-        <v>-206.6372111477524</v>
+        <v>-163.3950313650694</v>
       </c>
       <c r="H8" t="n">
-        <v>-142.901885353295</v>
+        <v>-126.862098021322</v>
       </c>
     </row>
     <row r="9">
@@ -2601,25 +2601,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-72.74868556371604</v>
+        <v>-54.42335575373502</v>
       </c>
       <c r="C9" t="n">
-        <v>-41.43411051084742</v>
+        <v>-31.27134311718221</v>
       </c>
       <c r="D9" t="n">
-        <v>-151.3179387198213</v>
+        <v>-150.9537083123951</v>
       </c>
       <c r="E9" t="n">
-        <v>-170.2244718112744</v>
+        <v>-150.2358482250665</v>
       </c>
       <c r="F9" t="n">
-        <v>-195.4952745318515</v>
+        <v>-196.2280864786034</v>
       </c>
       <c r="G9" t="n">
-        <v>-201.9249958263606</v>
+        <v>-159.8608698740256</v>
       </c>
       <c r="H9" t="n">
-        <v>-138.8575794939785</v>
+        <v>-123.8288686268346</v>
       </c>
     </row>
   </sheetData>
@@ -2680,25 +2680,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6091871904353768</v>
+        <v>0.03646006140942337</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3192841414117227</v>
+        <v>0.4177025987246759</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03531135761680015</v>
+        <v>0.6759643153449957</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3854158469685276</v>
+        <v>-0.05016745446771687</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.653782775033653</v>
+        <v>-7.49912730706278</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.672574900106149</v>
+        <v>-0.1753818134437124</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7913318054407382</v>
+        <v>-1.099091599915852</v>
       </c>
     </row>
     <row r="3">
@@ -2708,25 +2708,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06543720209508468</v>
+        <v>0.09768270441216453</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1100648223636634</v>
+        <v>0.1317839803211954</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0143905110446029</v>
+        <v>0.00918982904124669</v>
       </c>
       <c r="E3" t="n">
-        <v>0.008620451101219855</v>
+        <v>0.008427496409112297</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02027738792087542</v>
+        <v>0.02696889791365034</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0183788852209626</v>
+        <v>0.008127379917367188</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03952820995773481</v>
+        <v>0.04703004800245608</v>
       </c>
     </row>
     <row r="4">
@@ -2736,25 +2736,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01415800596708242</v>
+        <v>0.04358292877391437</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05920644323827909</v>
+        <v>0.05911121195105933</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009355870015678716</v>
+        <v>0.0003716954555516939</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004529006200176796</v>
+        <v>0.0003829409256965333</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001136960960578933</v>
+        <v>0.003690765845404466</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00083839050527011</v>
+        <v>0.0002237098058243981</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01278804804879935</v>
+        <v>0.01789387545957513</v>
       </c>
     </row>
     <row r="5">
@@ -2764,25 +2764,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.118987419364748</v>
+        <v>0.2087652480033839</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2433237416247726</v>
+        <v>0.2431279744312845</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03058736669881655</v>
+        <v>0.01927940495844449</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02128146188629155</v>
+        <v>0.019568876454629</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03371885170908008</v>
+        <v>0.06075167360167509</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02895497375702679</v>
+        <v>0.01495693169819259</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07947563584012259</v>
+        <v>0.09440835152460159</v>
       </c>
     </row>
     <row r="6">
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.25784289138527</v>
+        <v>61.94942212493488</v>
       </c>
       <c r="C6" t="n">
-        <v>78.16372995605754</v>
+        <v>1872.792546796094</v>
       </c>
       <c r="D6" t="n">
-        <v>97.2159466431858</v>
+        <v>73.33421864540122</v>
       </c>
       <c r="E6" t="n">
-        <v>92.18219227690216</v>
+        <v>3746.38554813164</v>
       </c>
       <c r="F6" t="n">
-        <v>2536.900252179159</v>
+        <v>889.9985528473454</v>
       </c>
       <c r="G6" t="n">
-        <v>607.9926535041488</v>
+        <v>60.49524148216895</v>
       </c>
       <c r="H6" t="n">
-        <v>578.9521029084731</v>
+        <v>1117.492588337931</v>
       </c>
     </row>
     <row r="7">
@@ -2820,25 +2820,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1276544470463447</v>
+        <v>0.3210700317189131</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2461592678432786</v>
+        <v>0.2175670687483388</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2905615036160575</v>
+        <v>0.0989708922153875</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8328835690491414</v>
+        <v>0.6336365899766053</v>
       </c>
       <c r="F7" t="n">
-        <v>1.594861410365002</v>
+        <v>5.107643456421235</v>
       </c>
       <c r="G7" t="n">
-        <v>2.805718686771068</v>
+        <v>0.7085422817943817</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9829731474484821</v>
+        <v>1.181238386812477</v>
       </c>
     </row>
     <row r="8">
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-70.37707537683175</v>
+        <v>-47.26252570210052</v>
       </c>
       <c r="C8" t="n">
-        <v>-40.40087356795317</v>
+        <v>-36.4250199155879</v>
       </c>
       <c r="D8" t="n">
-        <v>-144.4610647465382</v>
+        <v>-159.8461498439438</v>
       </c>
       <c r="E8" t="n">
-        <v>-159.6965946065761</v>
+        <v>-159.2202262553055</v>
       </c>
       <c r="F8" t="n">
-        <v>-174.2643064069132</v>
+        <v>-139.6499537033933</v>
       </c>
       <c r="G8" t="n">
-        <v>-168.0166376627819</v>
+        <v>-195.7238605372782</v>
       </c>
       <c r="H8" t="n">
-        <v>-126.2027587279324</v>
+        <v>-123.0212893262682</v>
       </c>
     </row>
     <row r="9">
@@ -2876,25 +2876,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-69.54386203277554</v>
+        <v>-44.76288566993187</v>
       </c>
       <c r="C9" t="n">
-        <v>-39.69282336685096</v>
+        <v>-34.30086931228127</v>
       </c>
       <c r="D9" t="n">
-        <v>-143.4165423088147</v>
+        <v>-156.7125825307736</v>
       </c>
       <c r="E9" t="n">
-        <v>-158.6520721688527</v>
+        <v>-156.0866589421352</v>
       </c>
       <c r="F9" t="n">
-        <v>-173.0062098688917</v>
+        <v>-135.8756640893288</v>
       </c>
       <c r="G9" t="n">
-        <v>-166.838583832434</v>
+        <v>-192.1896990462344</v>
       </c>
       <c r="H9" t="n">
-        <v>-125.1916822631033</v>
+        <v>-119.9880599317809</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/global/metrics_summary.xlsx
+++ b/results/cross_validation/global/metrics_summary.xlsx
@@ -8,14 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="linear" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="LASSO_w" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ridge_w" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="elasticnet_w" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="rf_w" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="svm_linear" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="svm_rbf" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="svm_poly" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="knn" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="poisson" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="tweedie" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="LASSO_b" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Ridge_b" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="elasticnet_b" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="rf_b" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="svm_linear" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="svm_rbf" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="svm_poly" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="knn" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,15 +461,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>BR06</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>BR07</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>BR08</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -480,25 +487,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.00569260954202444</v>
+        <v>0.6799739263620631</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02902236503450162</v>
+        <v>0.3772364784831032</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1793828628862283</v>
+        <v>0.5946700480819316</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.374731124294629</v>
+        <v>0.03632388861825186</v>
       </c>
       <c r="F2" t="n">
-        <v>-13.62331956417997</v>
+        <v>-42.72312240109862</v>
       </c>
       <c r="G2" t="n">
-        <v>-41.36112847118468</v>
+        <v>-2.030524432047386</v>
       </c>
       <c r="H2" t="n">
-        <v>-10.03575187855826</v>
+        <v>-2.576892619846213</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-6.520333587349553</v>
       </c>
     </row>
     <row r="3">
@@ -508,25 +518,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1006833003487474</v>
+        <v>0.06498832554362319</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1329326505874889</v>
+        <v>0.1115862280332003</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01408144330721298</v>
+        <v>0.01317634023280503</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02494998181195572</v>
+        <v>0.0122421877039546</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05278338982427788</v>
+        <v>0.09731733065238747</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06567351456425603</v>
+        <v>0.02833122152892775</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06518404674065649</v>
+        <v>0.02366908292056449</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.05018724523078041</v>
       </c>
     </row>
     <row r="4">
@@ -536,25 +549,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04548958233556588</v>
+        <v>0.01447544934521314</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1044599529187567</v>
+        <v>0.06321908089431376</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009413150312064544</v>
+        <v>0.0004649466347736892</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002324529699924091</v>
+        <v>0.0003514020745874358</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006350210609159864</v>
+        <v>0.02750219260227047</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008062571426918654</v>
+        <v>0.001685213812444928</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02793802700358862</v>
+        <v>0.001088470100350564</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.01554096506627914</v>
       </c>
     </row>
     <row r="5">
@@ -564,25 +580,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.213282869297011</v>
+        <v>0.1203139615556447</v>
       </c>
       <c r="C5" t="n">
-        <v>0.323202649925332</v>
+        <v>0.2514340487967248</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03068085773257414</v>
+        <v>0.02156262124078817</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04821337677371386</v>
+        <v>0.01874572150085016</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07968820872098872</v>
+        <v>0.1658378503305879</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08979182271743154</v>
+        <v>0.0410513557930177</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1308099641945085</v>
+        <v>0.03299197024050798</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0931339327797316</v>
       </c>
     </row>
     <row r="6">
@@ -592,25 +611,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.0683798080768</v>
+        <v>50.30825140440611</v>
       </c>
       <c r="C6" t="n">
-        <v>279.119451319774</v>
+        <v>265.2418954029604</v>
       </c>
       <c r="D6" t="n">
-        <v>116.7656548629729</v>
+        <v>40.2033901899395</v>
       </c>
       <c r="E6" t="n">
-        <v>7400.341352802471</v>
+        <v>2176.193635484753</v>
       </c>
       <c r="F6" t="n">
-        <v>4969.026358427033</v>
+        <v>647.4949209940114</v>
       </c>
       <c r="G6" t="n">
-        <v>1437.82360488394</v>
+        <v>2325.002723639906</v>
       </c>
       <c r="H6" t="n">
-        <v>2377.357467017378</v>
+        <v>449.3100599017137</v>
+      </c>
+      <c r="I6" t="n">
+        <v>850.5364110025272</v>
       </c>
     </row>
     <row r="7">
@@ -620,25 +642,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6681009809950069</v>
+        <v>0.1071406366330303</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7646573531069605</v>
+        <v>0.2320824130810887</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2473440616559761</v>
+        <v>0.1229244482197621</v>
       </c>
       <c r="E7" t="n">
-        <v>3.829093016156672</v>
+        <v>0.2903488148667357</v>
       </c>
       <c r="F7" t="n">
-        <v>8.783882033360808</v>
+        <v>26.27437651030235</v>
       </c>
       <c r="G7" t="n">
-        <v>25.4289646827085</v>
+        <v>1.822673958565855</v>
       </c>
       <c r="H7" t="n">
-        <v>6.620340354663987</v>
+        <v>2.149659430048219</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.428458030245292</v>
       </c>
     </row>
     <row r="8">
@@ -648,25 +673,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-50.53462296127262</v>
+        <v>-68.00012062368094</v>
       </c>
       <c r="C8" t="n">
-        <v>-31.8842726002723</v>
+        <v>-37.41723665766706</v>
       </c>
       <c r="D8" t="n">
-        <v>-144.3328865105298</v>
+        <v>-157.1453463806974</v>
       </c>
       <c r="E8" t="n">
-        <v>-125.3489883401394</v>
+        <v>-163.025169047474</v>
       </c>
       <c r="F8" t="n">
-        <v>-129.5409497955986</v>
+        <v>-96.61770730189653</v>
       </c>
       <c r="G8" t="n">
-        <v>-113.6925457059229</v>
+        <v>-168.4182964523675</v>
       </c>
       <c r="H8" t="n">
-        <v>-99.22237765228927</v>
+        <v>-166.5745536584728</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-122.4569185888937</v>
       </c>
     </row>
     <row r="9">
@@ -676,25 +704,636 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-49.7014096172164</v>
+        <v>-66.3336939355685</v>
       </c>
       <c r="C9" t="n">
-        <v>-31.17622239917009</v>
+        <v>-36.00113625546264</v>
       </c>
       <c r="D9" t="n">
-        <v>-143.2883640728064</v>
+        <v>-155.0563015052505</v>
       </c>
       <c r="E9" t="n">
-        <v>-124.304465902416</v>
+        <v>-160.9361241720271</v>
       </c>
       <c r="F9" t="n">
-        <v>-128.2828532575771</v>
+        <v>-93.95329828154613</v>
       </c>
       <c r="G9" t="n">
-        <v>-112.5144918755749</v>
+        <v>-165.8266227203588</v>
       </c>
       <c r="H9" t="n">
-        <v>-98.21130118746015</v>
+        <v>-164.1368020087363</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-120.3205684112786</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>BR06</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>MEAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.8334279869388074</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.8838849646937742</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5167797619050813</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.613752514812032</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-18.48564718642167</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5015130046850875</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.2881067721566537</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-2.203485103649078</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.05107189312958658</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.05337714858079581</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.01564220576672538</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.01077803486046576</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05944811700085327</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.01329343754039825</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.01523016117638851</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.03126299972217336</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>MSE</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.007534400900488517</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.01178727648046935</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0005542931690431488</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0001408441757517686</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.01225662744267764</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0002771986131988807</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.000391978696752679</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.004706088496911711</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.08680092684118365</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.1085692243707642</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.02354343154774063</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.01186777888872929</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.110709653791698</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.01664928266319245</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.01979845187767667</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.05399124999728356</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>MAPE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>44.04792714225707</v>
+      </c>
+      <c r="C6" t="n">
+        <v>93.50076582327466</v>
+      </c>
+      <c r="D6" t="n">
+        <v>34.81660297538098</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1643.011679402289</v>
+      </c>
+      <c r="F6" t="n">
+        <v>447.7174024578019</v>
+      </c>
+      <c r="G6" t="n">
+        <v>459.9276183672584</v>
+      </c>
+      <c r="H6" t="n">
+        <v>201.5190722058889</v>
+      </c>
+      <c r="I6" t="n">
+        <v>417.7915811963073</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SCORE</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.05674568454869976</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.04458560412819629</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1468540766468058</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.1174728364794167</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11.71154759027275</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.151240137623713</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7764128334694461</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.857836966167005</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AIC</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-77.10069130228669</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-60.61101890434149</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-151.4541533289492</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-180.2249847194525</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-117.2472772316481</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-215.1509599258792</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-190.1075766167308</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-141.6995231470412</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>BIC</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-74.60105127011803</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-58.48686830103486</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-148.320586015779</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-177.0914174062823</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-113.2506637011225</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-211.2634493278662</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-186.4509491421262</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-138.4949978806184</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>BR06</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>MEAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.3098566023134449</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.17728042274786</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5968435644190448</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.4464085696249603</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-33.71419097014039</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6895408182640808</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6977048848616982</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-4.399508015415615</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.08474694131049205</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1229070874715903</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.01009238941208156</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.005856074538468041</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.07838539510378784</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.007860183180573719</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.006210000122838963</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.04515115301997608</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>MSE</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.03121663082192299</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.08351737651709497</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0004624534336130438</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0002018657252265882</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.02183550290243706</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0001726401198845509</v>
+      </c>
+      <c r="H4" t="n">
+        <v>9.199023545868133e-05</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.01964263710794827</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.1766822877990971</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.288993730930439</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.02150473049384818</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.01420794584824239</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1477684096904242</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.01313925872660063</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.00959115402121566</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.09598393107283816</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>MAPE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>49.4018299408194</v>
+      </c>
+      <c r="C6" t="n">
+        <v>247.1197070995661</v>
+      </c>
+      <c r="D6" t="n">
+        <v>54.98732623756622</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2884.224495977484</v>
+      </c>
+      <c r="F6" t="n">
+        <v>494.047499537845</v>
+      </c>
+      <c r="G6" t="n">
+        <v>394.8022531417145</v>
+      </c>
+      <c r="H6" t="n">
+        <v>80.54693827183414</v>
+      </c>
+      <c r="I6" t="n">
+        <v>600.7328643152613</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SCORE</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.2303946608813127</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.3067780367376085</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1227706480778157</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.1677187351201705</v>
+      </c>
+      <c r="F7" t="n">
+        <v>20.86208428614765</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.09475860260469497</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.09225292770631163</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.125251128182224</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AIC</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-52.93567287929602</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-31.24050850161612</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-155.2582584933743</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-172.6660639720488</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-101.0781056903208</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-227.9361367749551</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-226.3457030716693</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-138.2086356261829</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>BIC</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-50.43603284712737</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-29.11635789830949</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-152.1246911802041</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-169.5324966588785</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-97.08149215979519</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-224.0486261769421</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-222.6890755970647</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-135.0041103597602</v>
       </c>
     </row>
   </sheetData>
@@ -708,7 +1347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,15 +1373,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>BR06</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>BR07</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>BR08</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -755,25 +1399,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3196435173169476</v>
+        <v>0.7270839990847735</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0959283729130217</v>
+        <v>0.8671837373232321</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1684132388757311</v>
+        <v>0.6660864942246855</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.204058480254945</v>
+        <v>0.6453040628999822</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.258528043469171</v>
+        <v>0.5185746350085043</v>
       </c>
       <c r="G2" t="n">
-        <v>-14.9353956846101</v>
+        <v>0.483088269213498</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.358470592829997</v>
+        <v>-0.7918958477986668</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.4450607642794299</v>
       </c>
     </row>
     <row r="3">
@@ -783,25 +1430,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1347593910322981</v>
+        <v>0.05674417353102911</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1491242141326117</v>
+        <v>0.05318171266219202</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02769097136913941</v>
+        <v>0.008654604335730157</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02188718964521308</v>
+        <v>0.006024973373860417</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04112695629162537</v>
+        <v>0.01269352943207032</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05228602329115234</v>
+        <v>0.01071595076199815</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07114579096033999</v>
+        <v>0.01654527989776898</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.02350860342780703</v>
       </c>
     </row>
     <row r="4">
@@ -811,25 +1461,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0307739481655736</v>
+        <v>0.01234456212219763</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09177573083897274</v>
+        <v>0.01348268124920224</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001340265630184931</v>
+        <v>0.000383026124965715</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000803704391263888</v>
+        <v>0.0001293389829555565</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002283528061029223</v>
+        <v>0.0003028203930669368</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003032975526390341</v>
+        <v>0.0002874442388005162</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02166835876890245</v>
+        <v>0.000545284765455171</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.003925022553806252</v>
       </c>
     </row>
     <row r="5">
@@ -839,25 +1492,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1754250499945022</v>
+        <v>0.1111060849917665</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3029450954199007</v>
+        <v>0.1161149484312947</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03660963848749303</v>
+        <v>0.01957105324109346</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02834968062013906</v>
+        <v>0.01137272979348215</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04778627481850017</v>
+        <v>0.01740173534642269</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05507245705786461</v>
+        <v>0.01695418057001034</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1076980327330666</v>
+        <v>0.02335133326932685</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.04512458080619954</v>
       </c>
     </row>
     <row r="6">
@@ -867,25 +1523,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>116.5729191752877</v>
+        <v>32.99253600089397</v>
       </c>
       <c r="C6" t="n">
-        <v>488.6382700983751</v>
+        <v>233.9048846739289</v>
       </c>
       <c r="D6" t="n">
-        <v>104.3503870530708</v>
+        <v>34.74861739346013</v>
       </c>
       <c r="E6" t="n">
-        <v>3860.193805672552</v>
+        <v>1449.687194301786</v>
       </c>
       <c r="F6" t="n">
-        <v>724.5540067803108</v>
+        <v>66.36321025957632</v>
       </c>
       <c r="G6" t="n">
-        <v>583.9341373207342</v>
+        <v>770.198080201938</v>
       </c>
       <c r="H6" t="n">
-        <v>979.7072543500552</v>
+        <v>318.5722952130079</v>
+      </c>
+      <c r="I6" t="n">
+        <v>415.2095454349415</v>
       </c>
     </row>
     <row r="7">
@@ -895,25 +1554,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2271487085208173</v>
+        <v>0.0935159937601063</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3369644997133744</v>
+        <v>0.05228275567747195</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7059243152076976</v>
+        <v>0.1034421700200704</v>
       </c>
       <c r="E7" t="n">
-        <v>1.326560274300737</v>
+        <v>0.1094993184180742</v>
       </c>
       <c r="F7" t="n">
-        <v>3.161313765366944</v>
+        <v>0.1476395837725956</v>
       </c>
       <c r="G7" t="n">
-        <v>9.568483576503008</v>
+        <v>0.158274730203111</v>
       </c>
       <c r="H7" t="n">
-        <v>2.55439918993543</v>
+        <v>1.081900907350838</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.249507922743181</v>
       </c>
     </row>
     <row r="8">
@@ -923,25 +1585,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-53.17847535700458</v>
+        <v>-62.70717365673757</v>
       </c>
       <c r="C8" t="n">
-        <v>-29.82611079380126</v>
+        <v>-52.59523931324892</v>
       </c>
       <c r="D8" t="n">
-        <v>-132.9126365168491</v>
+        <v>-153.2155545539349</v>
       </c>
       <c r="E8" t="n">
-        <v>-143.6518596079665</v>
+        <v>-176.0145503316594</v>
       </c>
       <c r="F8" t="n">
-        <v>-152.1328745570562</v>
+        <v>-214.8663793301688</v>
       </c>
       <c r="G8" t="n">
-        <v>-133.1570668660303</v>
+        <v>-208.1710050504772</v>
       </c>
       <c r="H8" t="n">
-        <v>-107.4765039497847</v>
+        <v>-175.8550598584281</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-149.060708870665</v>
       </c>
     </row>
     <row r="9">
@@ -951,25 +1616,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-50.67883532483593</v>
+        <v>-57.70789359240027</v>
       </c>
       <c r="C9" t="n">
-        <v>-27.70196019049463</v>
+        <v>-48.34693810663566</v>
       </c>
       <c r="D9" t="n">
-        <v>-129.7790692036788</v>
+        <v>-146.9484199275944</v>
       </c>
       <c r="E9" t="n">
-        <v>-140.5182922947963</v>
+        <v>-169.7474157053188</v>
       </c>
       <c r="F9" t="n">
-        <v>-148.3585849429917</v>
+        <v>-206.8731522691176</v>
       </c>
       <c r="G9" t="n">
-        <v>-129.6229053749864</v>
+        <v>-200.3959838544513</v>
       </c>
       <c r="H9" t="n">
-        <v>-104.4432745552973</v>
+        <v>-168.5418049092189</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-142.6516583378196</v>
       </c>
     </row>
   </sheetData>
@@ -983,7 +1651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1009,15 +1677,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>BR06</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>BR07</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>BR08</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -1030,25 +1703,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3195229393527415</v>
+        <v>0.8588157505125056</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09749530441938414</v>
+        <v>0.8426183053811716</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.10359954258621</v>
+        <v>0.6449173189880136</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.126658646922068</v>
+        <v>0.6338540980966583</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.332222271289967</v>
+        <v>0.6881954051662047</v>
       </c>
       <c r="G2" t="n">
-        <v>-14.75547555307342</v>
+        <v>0.5270907353943324</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.316822961683256</v>
+        <v>-0.1886590956657799</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.5724046454104438</v>
       </c>
     </row>
     <row r="3">
@@ -1058,25 +1734,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1326501917530062</v>
+        <v>0.04219413868704863</v>
       </c>
       <c r="C3" t="n">
-        <v>0.149231992880737</v>
+        <v>0.06171323249477134</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0272320296023932</v>
+        <v>0.008224943739119214</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02167959489939312</v>
+        <v>0.00533247080094969</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04137945885300191</v>
+        <v>0.007849036635724003</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05216819280448715</v>
+        <v>0.009618685627567637</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07072357679883642</v>
+        <v>0.01304009048494022</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.02113894263858868</v>
       </c>
     </row>
     <row r="4">
@@ -1086,25 +1765,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03077940215934722</v>
+        <v>0.006386059200008552</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09161666569428459</v>
+        <v>0.01597641117314857</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001265919014953427</v>
+        <v>0.0004073089018506924</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007754807363608969</v>
+        <v>0.0001335141838745376</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00231552995124899</v>
+        <v>0.000196127576222152</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002998731421853753</v>
+        <v>0.0002629753505099554</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02162528816300814</v>
+        <v>0.0003617161661390801</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.003389158935964791</v>
       </c>
     </row>
     <row r="5">
@@ -1114,25 +1796,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1754405943883776</v>
+        <v>0.07991282250057591</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3026824502581618</v>
+        <v>0.1263978289890636</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0355797556899064</v>
+        <v>0.02018189539787313</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02784745475552293</v>
+        <v>0.01155483378826963</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04811995377438542</v>
+        <v>0.01400455555246763</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05476067404491797</v>
+        <v>0.01621651474608386</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1074051471518787</v>
+        <v>0.01901883713950672</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.04104104115912006</v>
       </c>
     </row>
     <row r="6">
@@ -1142,25 +1827,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111.7350222664646</v>
+        <v>31.69708240185204</v>
       </c>
       <c r="C6" t="n">
-        <v>491.6073639175594</v>
+        <v>163.2378869670133</v>
       </c>
       <c r="D6" t="n">
-        <v>101.4711954779222</v>
+        <v>35.47967184162529</v>
       </c>
       <c r="E6" t="n">
-        <v>3781.886018263005</v>
+        <v>1419.94289001194</v>
       </c>
       <c r="F6" t="n">
-        <v>716.1646420424106</v>
+        <v>52.52006770141914</v>
       </c>
       <c r="G6" t="n">
-        <v>603.9248051468317</v>
+        <v>705.4115149025249</v>
       </c>
       <c r="H6" t="n">
-        <v>967.7981745190322</v>
+        <v>266.0653329871478</v>
+      </c>
+      <c r="I6" t="n">
+        <v>382.0506352590747</v>
       </c>
     </row>
     <row r="7">
@@ -1170,25 +1858,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2271886997057206</v>
+        <v>0.05032551628625433</v>
       </c>
       <c r="C7" t="n">
-        <v>0.336383074660184</v>
+        <v>0.06189799620685255</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6669320121726608</v>
+        <v>0.1103099205348914</v>
       </c>
       <c r="E7" t="n">
-        <v>1.280080861184146</v>
+        <v>0.1134372304997147</v>
       </c>
       <c r="F7" t="n">
-        <v>3.205575104705729</v>
+        <v>0.09717866775349411</v>
       </c>
       <c r="G7" t="n">
-        <v>9.460483555834646</v>
+        <v>0.1455568621270573</v>
       </c>
       <c r="H7" t="n">
-        <v>2.529440551377181</v>
+        <v>0.7207018600320627</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1856297219200467</v>
       </c>
     </row>
     <row r="8">
@@ -1198,25 +1889,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-53.17546275431425</v>
+        <v>-71.91184454569151</v>
       </c>
       <c r="C8" t="n">
-        <v>-29.85213125935756</v>
+        <v>-48.04962919408953</v>
       </c>
       <c r="D8" t="n">
-        <v>-134.1110954572848</v>
+        <v>-149.9247124435819</v>
       </c>
       <c r="E8" t="n">
-        <v>-144.4025757347135</v>
+        <v>-173.3473596298462</v>
       </c>
       <c r="F8" t="n">
-        <v>-151.7710341224252</v>
+        <v>-225.0288659187543</v>
       </c>
       <c r="G8" t="n">
-        <v>-133.4295825390324</v>
+        <v>-208.5731568708427</v>
       </c>
       <c r="H8" t="n">
-        <v>-107.7903136445213</v>
+        <v>-184.1162681280572</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-151.5645481044091</v>
       </c>
     </row>
     <row r="9">
@@ -1226,25 +1920,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-50.6758227221456</v>
+        <v>-66.07935113729799</v>
       </c>
       <c r="C9" t="n">
-        <v>-27.72798065605093</v>
+        <v>-43.09327778637406</v>
       </c>
       <c r="D9" t="n">
-        <v>-130.9775281441146</v>
+        <v>-142.6130553795179</v>
       </c>
       <c r="E9" t="n">
-        <v>-141.2690084215432</v>
+        <v>-166.0357025657823</v>
       </c>
       <c r="F9" t="n">
-        <v>-147.9967445083608</v>
+        <v>-215.7034343475279</v>
       </c>
       <c r="G9" t="n">
-        <v>-129.8954210479885</v>
+        <v>-199.5022988088124</v>
       </c>
       <c r="H9" t="n">
-        <v>-104.7570842500339</v>
+        <v>-175.5841373539798</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-144.087322482756</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1284,15 +1981,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>BR06</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>BR07</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>BR08</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -1305,25 +2007,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3199548480555829</v>
+        <v>0.8780710150541366</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09721977930821202</v>
+        <v>0.9322226837731202</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1771792367368519</v>
+        <v>0.8209441212758773</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.22121531971414</v>
+        <v>0.8060361118460525</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.317158864370665</v>
+        <v>-6.989540974007508</v>
       </c>
       <c r="G2" t="n">
-        <v>-15.0024755656635</v>
+        <v>-0.7388527302353787</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.383475726520227</v>
+        <v>-2.451820875841862</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.9632772354479374</v>
       </c>
     </row>
     <row r="3">
@@ -1333,25 +2038,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1351245339424208</v>
+        <v>0.03988479778350688</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1492104082481111</v>
+        <v>0.04784898186453247</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02775730024548536</v>
+        <v>0.009854042837998237</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02193403331957024</v>
+        <v>0.0062102453402068</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04132965247195375</v>
+        <v>0.04448428175073987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05235992650975244</v>
+        <v>0.01953415501556069</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07128597578954894</v>
+        <v>0.01502534178120337</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.02612026376767834</v>
       </c>
     </row>
     <row r="4">
@@ -1361,25 +2069,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03075986602443587</v>
+        <v>0.005515103270285147</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09164463529059169</v>
+        <v>0.006880331762062497</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001350320947307869</v>
+        <v>0.0002053917502401962</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008099605896983184</v>
+        <v>7.072844484503577e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002308988631679981</v>
+        <v>0.00502548497463587</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003045742805068249</v>
+        <v>0.0009669411035965592</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02165325238146366</v>
+        <v>0.001050410010709604</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.002816341616624988</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +2100,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1753849082003234</v>
+        <v>0.07426374128930717</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3027286496032242</v>
+        <v>0.08294776526261873</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03674671342185406</v>
+        <v>0.01433149504553507</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02845980656466798</v>
+        <v>0.008410020502057993</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04805193681507522</v>
+        <v>0.07089065505858914</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05518824879508543</v>
+        <v>0.0310956766061869</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1077600439000384</v>
+        <v>0.03241002947714802</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.04490705474877758</v>
       </c>
     </row>
     <row r="6">
@@ -1417,25 +2131,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>117.4587351620333</v>
+        <v>33.58701911002775</v>
       </c>
       <c r="C6" t="n">
-        <v>491.0871424018187</v>
+        <v>232.9730646626906</v>
       </c>
       <c r="D6" t="n">
-        <v>104.8083657417407</v>
+        <v>32.56689926382521</v>
       </c>
       <c r="E6" t="n">
-        <v>3876.767469049429</v>
+        <v>484.3768460475366</v>
       </c>
       <c r="F6" t="n">
-        <v>717.6620482146635</v>
+        <v>246.1262094484494</v>
       </c>
       <c r="G6" t="n">
-        <v>581.3464787487401</v>
+        <v>902.5987279654688</v>
       </c>
       <c r="H6" t="n">
-        <v>981.5217065530709</v>
+        <v>174.6886329225677</v>
+      </c>
+      <c r="I6" t="n">
+        <v>300.9881999172238</v>
       </c>
     </row>
     <row r="7">
@@ -1445,25 +2162,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2270454518004303</v>
+        <v>0.04293926777295862</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3364853109109506</v>
+        <v>0.02764942710150768</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7111979913683423</v>
+        <v>0.05636053784240495</v>
       </c>
       <c r="E7" t="n">
-        <v>1.336863136654061</v>
+        <v>0.06073867635757579</v>
       </c>
       <c r="F7" t="n">
-        <v>3.196527902706752</v>
+        <v>4.805760263368995</v>
       </c>
       <c r="G7" t="n">
-        <v>9.608749379325198</v>
+        <v>1.049665355686262</v>
       </c>
       <c r="H7" t="n">
-        <v>2.569478195460956</v>
+        <v>2.077563099520111</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.160096661092831</v>
       </c>
     </row>
     <row r="8">
@@ -1473,25 +2193,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-53.18625632773334</v>
+        <v>-78.40450331879578</v>
       </c>
       <c r="C8" t="n">
-        <v>-29.84755261732447</v>
+        <v>-64.68632610454215</v>
       </c>
       <c r="D8" t="n">
-        <v>-132.7556724968528</v>
+        <v>-168.3024199383915</v>
       </c>
       <c r="E8" t="n">
-        <v>-143.4890242896729</v>
+        <v>-190.6899174216115</v>
       </c>
       <c r="F8" t="n">
-        <v>-151.8445874747023</v>
+        <v>-138.2105328852027</v>
       </c>
       <c r="G8" t="n">
-        <v>-133.0562511604386</v>
+        <v>-177.4170702082945</v>
       </c>
       <c r="H8" t="n">
-        <v>-107.3632240611207</v>
+        <v>-161.4643676160644</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-139.8821624989861</v>
       </c>
     </row>
     <row r="9">
@@ -1501,25 +2224,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-50.68661629556469</v>
+        <v>-74.2384365985147</v>
       </c>
       <c r="C9" t="n">
-        <v>-27.72340201401784</v>
+        <v>-61.14607509903109</v>
       </c>
       <c r="D9" t="n">
-        <v>-129.6221051836825</v>
+        <v>-163.0798077497744</v>
       </c>
       <c r="E9" t="n">
-        <v>-140.3554569765027</v>
+        <v>-185.4673052329944</v>
       </c>
       <c r="F9" t="n">
-        <v>-148.0702978606378</v>
+        <v>-131.5495103343267</v>
       </c>
       <c r="G9" t="n">
-        <v>-129.5220896693947</v>
+        <v>-170.9378858782728</v>
       </c>
       <c r="H9" t="n">
-        <v>-104.3299946666334</v>
+        <v>-155.3699884917234</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-134.5412870549482</v>
       </c>
     </row>
   </sheetData>
@@ -1533,7 +2259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1559,15 +2285,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>BR06</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>BR07</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>BR08</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -1580,25 +2311,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.103417294148894</v>
+        <v>0.8809377389493065</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1581869919918826</v>
+        <v>0.9426248579190262</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7408991412309722</v>
+        <v>0.817959489674621</v>
       </c>
       <c r="E2" t="n">
-        <v>0.50164749916983</v>
+        <v>0.8043104036625739</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.346055464555919</v>
+        <v>-6.485357730917563</v>
       </c>
       <c r="G2" t="n">
-        <v>-17.91594889909859</v>
+        <v>-0.8091045520168423</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.046843668232414</v>
+        <v>-2.581516742732962</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.9185923622088344</v>
       </c>
     </row>
     <row r="3">
@@ -1608,25 +2342,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1046845185123914</v>
+        <v>0.03975689533168547</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1478548275489611</v>
+        <v>0.04505358967513655</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008840500098057485</v>
+        <v>0.0100129570807155</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007312964276981891</v>
+        <v>0.006236440166364952</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02385700944231687</v>
+        <v>0.04319832264446207</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03916961412523984</v>
+        <v>0.02000703270910302</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05528657233399144</v>
+        <v>0.01533438120087568</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0256570884011919</v>
       </c>
     </row>
     <row r="4">
@@ -1636,25 +2373,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04990987442527885</v>
+        <v>0.005385435346482816</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1175719428124695</v>
+        <v>0.005824367714577857</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002972098947575017</v>
+        <v>0.0002088153670059364</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001817229882522077</v>
+        <v>7.135772000153765e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001018780054372415</v>
+        <v>0.00470834969479253</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003600262660865335</v>
+        <v>0.00100600673169828</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0287632988059993</v>
+        <v>0.001089877248967396</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.00261345854621805</v>
       </c>
     </row>
     <row r="5">
@@ -1664,25 +2404,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.223405179942809</v>
+        <v>0.07338552545620161</v>
       </c>
       <c r="C5" t="n">
-        <v>0.342887653339209</v>
+        <v>0.0763175452604305</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0172397765286416</v>
+        <v>0.01445044521826011</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01348046691521505</v>
+        <v>0.008447349880378914</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0319183341415622</v>
+        <v>0.06861741538991782</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06000218880062072</v>
+        <v>0.03171760917374259</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1148222666113429</v>
+        <v>0.03301328897531108</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.04370702562203466</v>
       </c>
     </row>
     <row r="6">
@@ -1692,25 +2435,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49.51420143594815</v>
+        <v>33.87520982205296</v>
       </c>
       <c r="C6" t="n">
-        <v>156.444946488089</v>
+        <v>229.066626990909</v>
       </c>
       <c r="D6" t="n">
-        <v>43.82342110610183</v>
+        <v>33.07765982435092</v>
       </c>
       <c r="E6" t="n">
-        <v>1841.766024986806</v>
+        <v>436.2638638273136</v>
       </c>
       <c r="F6" t="n">
-        <v>1728.312002366989</v>
+        <v>235.7113142483328</v>
       </c>
       <c r="G6" t="n">
-        <v>776.3870741470328</v>
+        <v>941.9851393675647</v>
       </c>
       <c r="H6" t="n">
-        <v>766.0412784218278</v>
+        <v>180.1629861587308</v>
+      </c>
+      <c r="I6" t="n">
+        <v>298.5918286056079</v>
       </c>
     </row>
     <row r="7">
@@ -1720,25 +2466,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7389242006847269</v>
+        <v>0.04198848305774603</v>
       </c>
       <c r="C7" t="n">
-        <v>0.866512915132587</v>
+        <v>0.02378960002449665</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0814383045570386</v>
+        <v>0.05725832385451788</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1531329563408276</v>
+        <v>0.06125682930522892</v>
       </c>
       <c r="F7" t="n">
-        <v>1.416059570809673</v>
+        <v>4.502806328123248</v>
       </c>
       <c r="G7" t="n">
-        <v>11.36160970718437</v>
+        <v>1.091871140634483</v>
       </c>
       <c r="H7" t="n">
-        <v>2.436279609118203</v>
+        <v>2.155435873788331</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.133486654112579</v>
       </c>
     </row>
     <row r="8">
@@ -1748,25 +2497,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-36.95811899595984</v>
+        <v>-78.8089711650351</v>
       </c>
       <c r="C8" t="n">
-        <v>-18.11057280263995</v>
+        <v>-67.18557248413393</v>
       </c>
       <c r="D8" t="n">
-        <v>-156.5425110006679</v>
+        <v>-167.9552622657356</v>
       </c>
       <c r="E8" t="n">
-        <v>-166.8735685317658</v>
+        <v>-190.5039054379351</v>
       </c>
       <c r="F8" t="n">
-        <v>-165.1178842081173</v>
+        <v>-140.0356988374607</v>
       </c>
       <c r="G8" t="n">
-        <v>-121.0419633959234</v>
+        <v>-176.3476959260058</v>
       </c>
       <c r="H8" t="n">
-        <v>-110.7741031558457</v>
+        <v>-160.5422551177236</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-140.1970516048614</v>
       </c>
     </row>
     <row r="9">
@@ -1776,25 +2528,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-31.12562558756633</v>
+        <v>-74.64290444475402</v>
       </c>
       <c r="C9" t="n">
-        <v>-13.15422139492448</v>
+        <v>-63.64532147862288</v>
       </c>
       <c r="D9" t="n">
-        <v>-149.230853936604</v>
+        <v>-162.7326500771185</v>
       </c>
       <c r="E9" t="n">
-        <v>-159.5619114677019</v>
+        <v>-185.281293249318</v>
       </c>
       <c r="F9" t="n">
-        <v>-156.311208441967</v>
+        <v>-133.3746762865847</v>
       </c>
       <c r="G9" t="n">
-        <v>-112.7955865834878</v>
+        <v>-169.8685115959841</v>
       </c>
       <c r="H9" t="n">
-        <v>-103.6965679020419</v>
+        <v>-154.4478759933826</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-134.8561761608235</v>
       </c>
     </row>
   </sheetData>
@@ -1808,7 +2563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1834,15 +2589,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>BR06</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>BR07</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>BR08</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -1855,25 +2615,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.15002626937644</v>
+        <v>0.8804353982262564</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.09326792638924397</v>
+        <v>0.9399674921393246</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0701763759244205</v>
+        <v>0.8185501917218796</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.922562287497254</v>
+        <v>0.8030386891205414</v>
       </c>
       <c r="F2" t="n">
-        <v>-8.263270778729369</v>
+        <v>-6.603574283788131</v>
       </c>
       <c r="G2" t="n">
-        <v>-27.31304845396973</v>
+        <v>-0.7855397427050956</v>
       </c>
       <c r="H2" t="n">
-        <v>-6.302058681981078</v>
+        <v>-2.530344888297004</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.9253524490831756</v>
       </c>
     </row>
     <row r="3">
@@ -1883,25 +2646,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1214353767297386</v>
+        <v>0.03978277082458172</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1500239869151465</v>
+        <v>0.04583046028778442</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03124513809081009</v>
+        <v>0.009998445192170372</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02946624471876171</v>
+        <v>0.006265963723180522</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05358576285897866</v>
+        <v>0.04351369014293686</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06850719136278932</v>
+        <v>0.01990913487171686</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07571061677937081</v>
+        <v>0.01527415646757938</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.02579637450142144</v>
       </c>
     </row>
     <row r="4">
@@ -1911,25 +2677,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05201809595944654</v>
+        <v>0.005408157269130831</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1109817628836261</v>
+        <v>0.006094126967309201</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001227579906803777</v>
+        <v>0.000208137783403424</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001065705000682232</v>
+        <v>7.182144751649337e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004022596929270241</v>
+        <v>0.004782708849109038</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005388807704431671</v>
+        <v>0.000992902814198114</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0291174247307101</v>
+        <v>0.001074305343558777</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.002661737210603697</v>
       </c>
     </row>
     <row r="5">
@@ -1939,25 +2708,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2280747595843226</v>
+        <v>0.07354017452475096</v>
       </c>
       <c r="C5" t="n">
-        <v>0.333139254492211</v>
+        <v>0.07806488946581043</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0350368364268776</v>
+        <v>0.01442698109111619</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03264513747378364</v>
+        <v>0.008474753537212358</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06342394602411806</v>
+        <v>0.06915713158531836</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07340849885695573</v>
+        <v>0.03151036042634413</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1276214054763781</v>
+        <v>0.03277659749819644</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0439929840183927</v>
       </c>
     </row>
     <row r="6">
@@ -1967,25 +2739,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66.34507034549844</v>
+        <v>33.8121749273835</v>
       </c>
       <c r="C6" t="n">
-        <v>209.9437102228751</v>
+        <v>230.205441171287</v>
       </c>
       <c r="D6" t="n">
-        <v>84.57913142962265</v>
+        <v>32.90959016861152</v>
       </c>
       <c r="E6" t="n">
-        <v>3720.796762629502</v>
+        <v>451.1880996741396</v>
       </c>
       <c r="F6" t="n">
-        <v>2106.649306251878</v>
+        <v>238.191242729454</v>
       </c>
       <c r="G6" t="n">
-        <v>877.2991477044801</v>
+        <v>932.242124982612</v>
       </c>
       <c r="H6" t="n">
-        <v>1177.602188097309</v>
+        <v>179.0259055026287</v>
+      </c>
+      <c r="I6" t="n">
+        <v>299.6535113080166</v>
       </c>
     </row>
     <row r="7">
@@ -1995,25 +2770,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7668410959690892</v>
+        <v>0.04215509062051467</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8153352238706231</v>
+        <v>0.02477564123531906</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6478244374241776</v>
+        <v>0.05708063893181853</v>
       </c>
       <c r="E7" t="n">
-        <v>1.759029359499308</v>
+        <v>0.06163866827709913</v>
       </c>
       <c r="F7" t="n">
-        <v>5.5675941029386</v>
+        <v>4.573840362661632</v>
       </c>
       <c r="G7" t="n">
-        <v>16.99937340316805</v>
+        <v>1.077713909562935</v>
       </c>
       <c r="H7" t="n">
-        <v>4.425999603811641</v>
+        <v>2.124710960459185</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.137416467392643</v>
       </c>
     </row>
     <row r="8">
@@ -2023,25 +2801,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-42.25478156921056</v>
+        <v>-78.73739661717644</v>
       </c>
       <c r="C8" t="n">
-        <v>-24.97584084270948</v>
+        <v>-66.50644645744138</v>
       </c>
       <c r="D8" t="n">
-        <v>-132.7569226676587</v>
+        <v>-168.0235158245098</v>
       </c>
       <c r="E8" t="n">
-        <v>-135.7264932534823</v>
+        <v>-190.3678757063216</v>
       </c>
       <c r="F8" t="n">
-        <v>-135.411517147986</v>
+        <v>-139.5969492685021</v>
       </c>
       <c r="G8" t="n">
-        <v>-117.3623469674898</v>
+        <v>-176.7016997793875</v>
       </c>
       <c r="H8" t="n">
-        <v>-98.08131707475616</v>
+        <v>-160.902025457823</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-140.1194155873088</v>
       </c>
     </row>
     <row r="9">
@@ -2051,25 +2832,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-38.92192819298569</v>
+        <v>-74.57132989689536</v>
       </c>
       <c r="C9" t="n">
-        <v>-22.14364003830064</v>
+        <v>-62.96619545193033</v>
       </c>
       <c r="D9" t="n">
-        <v>-128.578832916765</v>
+        <v>-162.8009036358927</v>
       </c>
       <c r="E9" t="n">
-        <v>-131.5484035025886</v>
+        <v>-185.1452635177045</v>
       </c>
       <c r="F9" t="n">
-        <v>-130.3791309959001</v>
+        <v>-132.9359267176261</v>
       </c>
       <c r="G9" t="n">
-        <v>-112.650131646098</v>
+        <v>-170.2225154493658</v>
       </c>
       <c r="H9" t="n">
-        <v>-94.03701121543969</v>
+        <v>-154.807646333482</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-134.778540143271</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2109,15 +2893,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>BR06</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>BR07</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>BR08</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -2130,25 +2919,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1830053738079017</v>
+        <v>0.5615673356621306</v>
       </c>
       <c r="C2" t="n">
-        <v>0.549838672248941</v>
+        <v>0.478431577769458</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.48019232607482</v>
+        <v>0.1493155558316565</v>
       </c>
       <c r="E2" t="n">
-        <v>-10.14549946568423</v>
+        <v>0.009884464697309858</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.05675636570207887</v>
+        <v>-62.75686302020578</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.663203836594571</v>
+        <v>-0.5169448528557667</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.10213465799981</v>
+        <v>-0.7617155288182211</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-8.976617781131315</v>
       </c>
     </row>
     <row r="3">
@@ -2158,25 +2950,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09847189734062323</v>
+        <v>0.06650739635891438</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1188867118193278</v>
+        <v>0.1040779154937664</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03178534692064586</v>
+        <v>0.01406025366405769</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04906857016177808</v>
+        <v>0.008079267947988598</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01355325404272496</v>
+        <v>0.0975662678830177</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01782074950474076</v>
+        <v>0.01798915173946346</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05493108829830678</v>
+        <v>0.01590804894748767</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.04631261457638513</v>
       </c>
     </row>
     <row r="4">
@@ -2186,25 +2981,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03695437747405196</v>
+        <v>0.01983122734896227</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04569757927578573</v>
+        <v>0.05294638355920081</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002844983624188498</v>
+        <v>0.0009758046936791555</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004064178398008565</v>
+        <v>0.0003610431441407676</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004588989152104926</v>
+        <v>0.04010357518415054</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0005068861933551562</v>
+        <v>0.0008435425867933757</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0150878173134334</v>
+        <v>0.0005361007114953206</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.01651395388977461</v>
       </c>
     </row>
     <row r="5">
@@ -2214,25 +3012,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.192235213928281</v>
+        <v>0.1408233906315363</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2137699213542114</v>
+        <v>0.2301008117308603</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05333838790391492</v>
+        <v>0.03123787274574175</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06375090899750814</v>
+        <v>0.0190011353382046</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02142192603876908</v>
+        <v>0.2002587705548762</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02251413319129023</v>
+        <v>0.02904380461980447</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09450508190232913</v>
+        <v>0.02315384874044315</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.09623137633735238</v>
       </c>
     </row>
     <row r="6">
@@ -2242,25 +3043,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65.13325395782891</v>
+        <v>44.70215901131075</v>
       </c>
       <c r="C6" t="n">
-        <v>1032.873536379434</v>
+        <v>241.4781898325374</v>
       </c>
       <c r="D6" t="n">
-        <v>153.8928091347392</v>
+        <v>86.16216717254143</v>
       </c>
       <c r="E6" t="n">
-        <v>8220.504270410927</v>
+        <v>3375.307997445354</v>
       </c>
       <c r="F6" t="n">
-        <v>377.7565037692831</v>
+        <v>775.2386885592178</v>
       </c>
       <c r="G6" t="n">
-        <v>155.9056773266036</v>
+        <v>1834.332765914248</v>
       </c>
       <c r="H6" t="n">
-        <v>1667.677675163136</v>
+        <v>383.1469958958971</v>
+      </c>
+      <c r="I6" t="n">
+        <v>962.9098519758724</v>
       </c>
     </row>
     <row r="7">
@@ -2270,25 +3074,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2724664520894659</v>
+        <v>0.1464116584456344</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1685367038183677</v>
+        <v>0.1945329951606032</v>
       </c>
       <c r="D7" t="n">
-        <v>1.495098372718756</v>
+        <v>0.2568883965360785</v>
       </c>
       <c r="E7" t="n">
-        <v>6.695989529167754</v>
+        <v>0.2982873907917056</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6376962779025421</v>
+        <v>38.31226281738129</v>
       </c>
       <c r="G7" t="n">
-        <v>1.60163194262744</v>
+        <v>0.913347871334971</v>
       </c>
       <c r="H7" t="n">
-        <v>1.811903213054054</v>
+        <v>1.059779858287026</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5.883072998276758</v>
       </c>
     </row>
     <row r="8">
@@ -2298,25 +3105,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-50.06720986280992</v>
+        <v>-62.64845656198297</v>
       </c>
       <c r="C8" t="n">
-        <v>-40.28564928570318</v>
+        <v>-40.07713262648676</v>
       </c>
       <c r="D8" t="n">
-        <v>-117.1061573157659</v>
+        <v>-141.5772101107297</v>
       </c>
       <c r="E8" t="n">
-        <v>-109.6164171229542</v>
+        <v>-162.4567749722606</v>
       </c>
       <c r="F8" t="n">
-        <v>-193.8536956118852</v>
+        <v>-86.05611417409189</v>
       </c>
       <c r="G8" t="n">
-        <v>-176.0933772064872</v>
+        <v>-187.1033045645303</v>
       </c>
       <c r="H8" t="n">
-        <v>-114.5037510676009</v>
+        <v>-184.2797129990657</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-123.4569580013068</v>
       </c>
     </row>
     <row r="9">
@@ -2326,25 +3136,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-47.56756983064127</v>
+        <v>-60.98202987387054</v>
       </c>
       <c r="C9" t="n">
-        <v>-38.16149868239655</v>
+        <v>-38.66103222428234</v>
       </c>
       <c r="D9" t="n">
-        <v>-113.9725900025956</v>
+        <v>-139.4881652352828</v>
       </c>
       <c r="E9" t="n">
-        <v>-106.482849809784</v>
+        <v>-160.3677300968138</v>
       </c>
       <c r="F9" t="n">
-        <v>-190.0794059978207</v>
+        <v>-83.39170515374148</v>
       </c>
       <c r="G9" t="n">
-        <v>-172.5592157154433</v>
+        <v>-184.5116308325217</v>
       </c>
       <c r="H9" t="n">
-        <v>-111.4705216731136</v>
+        <v>-181.8419613493292</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-121.3206078236917</v>
       </c>
     </row>
   </sheetData>
@@ -2358,7 +3171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2384,15 +3197,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>BR06</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>BR07</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>BR08</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -2405,25 +3223,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4541462992685739</v>
+        <v>0.802694360350638</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2873789952312541</v>
+        <v>0.9134638654275393</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5737245416328327</v>
+        <v>0.760792338287179</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3875778401104402</v>
+        <v>0.9085929099907585</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1658011923084912</v>
+        <v>-2.919263723779467</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.52052253054685</v>
+        <v>-2.371905434952264</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4045082237026897</v>
+        <v>-6.381896373751252</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-1.18393172263241</v>
       </c>
     </row>
     <row r="3">
@@ -2433,25 +3254,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0908766276681205</v>
+        <v>0.04856822190760488</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1142333034962122</v>
+        <v>0.05259129615701241</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01391522920406497</v>
+        <v>0.01070840902682608</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01601889963642343</v>
+        <v>0.003216108100639982</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01569939344097096</v>
+        <v>0.03213294952578368</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01597308435737965</v>
+        <v>0.01882445193672271</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04445275630052862</v>
+        <v>0.01359578414789312</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.02566246011464041</v>
       </c>
     </row>
     <row r="4">
@@ -2461,25 +3285,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02469010573111699</v>
+        <v>0.008924547177679236</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0723408539371877</v>
+        <v>0.008784610374243284</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004889728452500065</v>
+        <v>0.0002743907692958759</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0005059767757106997</v>
+        <v>3.333136588307913e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003622527768405631</v>
+        <v>0.002465248131221441</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008603886889916404</v>
+        <v>0.00187504893646435</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0165414251258496</v>
+        <v>0.002246355801159038</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.003514790365135186</v>
       </c>
     </row>
     <row r="5">
@@ -2489,25 +3316,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.157130855439398</v>
+        <v>0.09446982151819297</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2689625511798766</v>
+        <v>0.09372625232155228</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02211273038885082</v>
+        <v>0.01656474477001912</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02249392752968453</v>
+        <v>0.005773332303191903</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01903293925909929</v>
+        <v>0.04965126515227422</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02933238294090067</v>
+        <v>0.04330183525515229</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08651089778963496</v>
+        <v>0.04739573610736559</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.05012614106110691</v>
       </c>
     </row>
     <row r="6">
@@ -2517,25 +3347,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>74.85068118146413</v>
+        <v>35.64787452594123</v>
       </c>
       <c r="C6" t="n">
-        <v>576.6566464766095</v>
+        <v>152.8876987087037</v>
       </c>
       <c r="D6" t="n">
-        <v>36.47807246846528</v>
+        <v>42.27355630867075</v>
       </c>
       <c r="E6" t="n">
-        <v>3882.57514194831</v>
+        <v>52.98507327930712</v>
       </c>
       <c r="F6" t="n">
-        <v>923.732714306819</v>
+        <v>140.5864668019217</v>
       </c>
       <c r="G6" t="n">
-        <v>190.2834689659236</v>
+        <v>602.259710225057</v>
       </c>
       <c r="H6" t="n">
-        <v>947.4294542245985</v>
+        <v>100.750206630629</v>
+      </c>
+      <c r="I6" t="n">
+        <v>161.0557980686044</v>
       </c>
     </row>
     <row r="7">
@@ -2545,25 +3378,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1825391842312098</v>
+        <v>0.06693887491918407</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2659248991866552</v>
+        <v>0.03361006763370851</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1297249185018252</v>
+        <v>0.07345437205235344</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8362550715522592</v>
+        <v>0.02894545895889062</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2520132192512411</v>
+        <v>2.35800958165139</v>
       </c>
       <c r="G7" t="n">
-        <v>2.716518062492699</v>
+        <v>2.028768329482409</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7304958925359815</v>
+        <v>4.435282722372374</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.289287058152901</v>
       </c>
     </row>
     <row r="8">
@@ -2573,25 +3409,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-56.92299578590367</v>
+        <v>-74.22214471296688</v>
       </c>
       <c r="C8" t="n">
-        <v>-33.39549372048884</v>
+        <v>-65.02130864369282</v>
       </c>
       <c r="D8" t="n">
-        <v>-154.0872756255653</v>
+        <v>-166.2201033476838</v>
       </c>
       <c r="E8" t="n">
-        <v>-153.3694155382368</v>
+        <v>-210.4892454037714</v>
       </c>
       <c r="F8" t="n">
-        <v>-200.0023760926679</v>
+        <v>-162.1529588144117</v>
       </c>
       <c r="G8" t="n">
-        <v>-163.3950313650694</v>
+        <v>-163.5362540522227</v>
       </c>
       <c r="H8" t="n">
-        <v>-126.862098021322</v>
+        <v>-146.4611504934079</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-141.1575950668796</v>
       </c>
     </row>
     <row r="9">
@@ -2601,25 +3440,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-54.42335575373502</v>
+        <v>-71.72250468079824</v>
       </c>
       <c r="C9" t="n">
-        <v>-31.27134311718221</v>
+        <v>-62.89715804038619</v>
       </c>
       <c r="D9" t="n">
-        <v>-150.9537083123951</v>
+        <v>-163.0865360345135</v>
       </c>
       <c r="E9" t="n">
-        <v>-150.2358482250665</v>
+        <v>-207.3556780906011</v>
       </c>
       <c r="F9" t="n">
-        <v>-196.2280864786034</v>
+        <v>-158.1563452838861</v>
       </c>
       <c r="G9" t="n">
-        <v>-159.8608698740256</v>
+        <v>-159.6487434542098</v>
       </c>
       <c r="H9" t="n">
-        <v>-123.8288686268346</v>
+        <v>-142.8045230188033</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-137.9530698004569</v>
       </c>
     </row>
   </sheetData>
@@ -2633,7 +3475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2659,15 +3501,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>BR06</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>BR07</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>BR08</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -2680,25 +3527,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03646006140942337</v>
+        <v>0.8648824911921227</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4177025987246759</v>
+        <v>0.8683741961124882</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6759643153449957</v>
+        <v>0.7143281008520028</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.05016745446771687</v>
+        <v>0.9110665354913818</v>
       </c>
       <c r="F2" t="n">
-        <v>-7.49912730706278</v>
+        <v>-5.378906954922271</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1753818134437124</v>
+        <v>0.719028114035563</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.099091599915852</v>
+        <v>0.7853239729909827</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.07370050632110423</v>
       </c>
     </row>
     <row r="3">
@@ -2708,25 +3558,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09768270441216453</v>
+        <v>0.04316534346666429</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1317839803211954</v>
+        <v>0.06009095143378623</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00918982904124669</v>
+        <v>0.009455884828957397</v>
       </c>
       <c r="E3" t="n">
-        <v>0.008427496409112297</v>
+        <v>0.004189692401454045</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02696889791365034</v>
+        <v>0.03753162910258082</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008127379917367188</v>
+        <v>0.01031039775021643</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04703004800245608</v>
+        <v>0.005924134704830544</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.02438114766978425</v>
       </c>
     </row>
     <row r="4">
@@ -2736,25 +3589,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04358292877391437</v>
+        <v>0.006111647817210737</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05911121195105933</v>
+        <v>0.01336183327416989</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003716954555516939</v>
+        <v>0.0003276890531522281</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003829409256965333</v>
+        <v>3.242936455461918e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003690765845404466</v>
+        <v>0.004012383334769039</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002237098058243981</v>
+        <v>0.0001562428265315391</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01789387545957513</v>
+        <v>6.532721596529558e-05</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.003438221840907621</v>
       </c>
     </row>
     <row r="5">
@@ -2764,25 +3620,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2087652480033839</v>
+        <v>0.07817702870543711</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2431279744312845</v>
+        <v>0.1155933963259575</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01927940495844449</v>
+        <v>0.01810218365701299</v>
       </c>
       <c r="E5" t="n">
-        <v>0.019568876454629</v>
+        <v>0.005694678617325054</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06075167360167509</v>
+        <v>0.06334337640802738</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01495693169819259</v>
+        <v>0.01249971305796813</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09440835152460159</v>
+        <v>0.00808252534578739</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.04307041458821652</v>
       </c>
     </row>
     <row r="6">
@@ -2792,25 +3651,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.94942212493488</v>
+        <v>24.87829374107193</v>
       </c>
       <c r="C6" t="n">
-        <v>1872.792546796094</v>
+        <v>187.8650179290731</v>
       </c>
       <c r="D6" t="n">
-        <v>73.33421864540122</v>
+        <v>35.48271226245993</v>
       </c>
       <c r="E6" t="n">
-        <v>3746.38554813164</v>
+        <v>946.7387074446057</v>
       </c>
       <c r="F6" t="n">
-        <v>889.9985528473454</v>
+        <v>228.4753036946091</v>
       </c>
       <c r="G6" t="n">
-        <v>60.49524148216895</v>
+        <v>564.3769620519033</v>
       </c>
       <c r="H6" t="n">
-        <v>1117.492588337931</v>
+        <v>58.80254331132912</v>
+      </c>
+      <c r="I6" t="n">
+        <v>292.3742200621503</v>
       </c>
     </row>
     <row r="7">
@@ -2820,25 +3682,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3210700317189131</v>
+        <v>0.04681340611441072</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2175670687483388</v>
+        <v>0.05084102445817246</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0989708922153875</v>
+        <v>0.08793095208160573</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6336365899766053</v>
+        <v>0.02870273990777369</v>
       </c>
       <c r="F7" t="n">
-        <v>5.107643456421235</v>
+        <v>3.836961509622039</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7085422817943817</v>
+        <v>0.0864009357679032</v>
       </c>
       <c r="H7" t="n">
-        <v>1.181238386812477</v>
+        <v>0.06644853715388092</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.6005855864436836</v>
       </c>
     </row>
     <row r="8">
@@ -2848,25 +3713,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-47.26252570210052</v>
+        <v>-78.6585004552319</v>
       </c>
       <c r="C8" t="n">
-        <v>-36.4250199155879</v>
+        <v>-56.7302934875064</v>
       </c>
       <c r="D8" t="n">
-        <v>-159.8461498439438</v>
+        <v>-160.4923535660427</v>
       </c>
       <c r="E8" t="n">
-        <v>-159.2202262553055</v>
+        <v>-209.0653708763226</v>
       </c>
       <c r="F8" t="n">
-        <v>-139.6499537033933</v>
+        <v>-146.5143562590788</v>
       </c>
       <c r="G8" t="n">
-        <v>-195.7238605372782</v>
+        <v>-228.6306778761951</v>
       </c>
       <c r="H8" t="n">
-        <v>-123.0212893262682</v>
+        <v>-232.9025456242495</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-158.9991568778039</v>
       </c>
     </row>
     <row r="9">
@@ -2876,25 +3744,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-44.76288566993187</v>
+        <v>-75.32564707900704</v>
       </c>
       <c r="C9" t="n">
-        <v>-34.30086931228127</v>
+        <v>-53.89809268309756</v>
       </c>
       <c r="D9" t="n">
-        <v>-156.7125825307736</v>
+        <v>-156.314263815149</v>
       </c>
       <c r="E9" t="n">
-        <v>-156.0866589421352</v>
+        <v>-204.8872811254289</v>
       </c>
       <c r="F9" t="n">
-        <v>-135.8756640893288</v>
+        <v>-141.185538218378</v>
       </c>
       <c r="G9" t="n">
-        <v>-192.1896990462344</v>
+        <v>-223.4473304121778</v>
       </c>
       <c r="H9" t="n">
-        <v>-119.9880599317809</v>
+        <v>-228.0270423247767</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-154.7264565225736</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/global/metrics_summary.xlsx
+++ b/results/cross_validation/global/metrics_summary.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,20 +461,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>BR08</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -487,28 +482,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6799739263620631</v>
+        <v>0.0825092347399351</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3772364784831032</v>
+        <v>0.1872706478009866</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5946700480819316</v>
+        <v>0.02835321196247464</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03632388861825186</v>
+        <v>-2.003189247922549</v>
       </c>
       <c r="F2" t="n">
-        <v>-42.72312240109862</v>
+        <v>0.7221030667091743</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.030524432047386</v>
+        <v>0.2854268381889515</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.576892619846213</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-6.520333587349553</v>
+        <v>-0.1162543747535044</v>
       </c>
     </row>
     <row r="3">
@@ -518,28 +510,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06498832554362319</v>
+        <v>0.3442930559361242</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1115862280332003</v>
+        <v>0.2380562389141897</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01317634023280503</v>
+        <v>0.0540651357895153</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0122421877039546</v>
+        <v>0.07398903536396195</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09731733065238747</v>
+        <v>0.04901910952875807</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02833122152892775</v>
+        <v>0.1064915946142664</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02366908292056449</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.05018724523078041</v>
+        <v>0.1443190283578026</v>
       </c>
     </row>
     <row r="4">
@@ -549,28 +538,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01447544934521314</v>
+        <v>0.427242896757015</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06321908089431376</v>
+        <v>0.322833463515472</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004649466347736892</v>
+        <v>0.01275533028035903</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003514020745874358</v>
+        <v>0.02019473937774187</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02750219260227047</v>
+        <v>0.01181163141885905</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001685213812444928</v>
+        <v>0.02698628136422652</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001088470100350564</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.01554096506627914</v>
+        <v>0.1369707237856122</v>
       </c>
     </row>
     <row r="5">
@@ -580,28 +566,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1203139615556447</v>
+        <v>0.6536382001971848</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2514340487967248</v>
+        <v>0.5681843569788524</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02156262124078817</v>
+        <v>0.112939498318166</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01874572150085016</v>
+        <v>0.142108196025922</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1658378503305879</v>
+        <v>0.1086813296700912</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0410513557930177</v>
+        <v>0.1642750174683495</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03299197024050798</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.0931339327797316</v>
+        <v>0.2916377664430943</v>
       </c>
     </row>
     <row r="6">
@@ -611,28 +594,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50.30825140440611</v>
+        <v>67.46807256860427</v>
       </c>
       <c r="C6" t="n">
-        <v>265.2418954029604</v>
+        <v>55.46298446486946</v>
       </c>
       <c r="D6" t="n">
-        <v>40.2033901899395</v>
+        <v>123.6023338993809</v>
       </c>
       <c r="E6" t="n">
-        <v>2176.193635484753</v>
+        <v>220.3292345747089</v>
       </c>
       <c r="F6" t="n">
-        <v>647.4949209940114</v>
+        <v>65.90873036030047</v>
       </c>
       <c r="G6" t="n">
-        <v>2325.002723639906</v>
+        <v>128.8870861221701</v>
       </c>
       <c r="H6" t="n">
-        <v>449.3100599017137</v>
-      </c>
-      <c r="I6" t="n">
-        <v>850.5364110025272</v>
+        <v>110.276406998339</v>
       </c>
     </row>
     <row r="7">
@@ -642,28 +622,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1071406366330303</v>
+        <v>0.57481725730793</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2320824130810887</v>
+        <v>0.4703022301205345</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1229244482197621</v>
+        <v>0.300922767607509</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2903488148667357</v>
+        <v>1.831186183882368</v>
       </c>
       <c r="F7" t="n">
-        <v>26.27437651030235</v>
+        <v>0.09213722198044905</v>
       </c>
       <c r="G7" t="n">
-        <v>1.822673958565855</v>
+        <v>0.2337623454982731</v>
       </c>
       <c r="H7" t="n">
-        <v>2.149659430048219</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4.428458030245292</v>
+        <v>0.5838546677328439</v>
       </c>
     </row>
     <row r="8">
@@ -673,28 +650,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-68.00012062368094</v>
+        <v>-12.45684390454371</v>
       </c>
       <c r="C8" t="n">
-        <v>-37.41723665766706</v>
+        <v>-14.95928022331789</v>
       </c>
       <c r="D8" t="n">
-        <v>-157.1453463806974</v>
+        <v>-89.59792670426252</v>
       </c>
       <c r="E8" t="n">
-        <v>-163.025169047474</v>
+        <v>-79.94899584206439</v>
       </c>
       <c r="F8" t="n">
-        <v>-96.61770730189653</v>
+        <v>-117.8441040276985</v>
       </c>
       <c r="G8" t="n">
-        <v>-168.4182964523675</v>
+        <v>-88.31066599310962</v>
       </c>
       <c r="H8" t="n">
-        <v>-166.5745536584728</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-122.4569185888937</v>
+        <v>-67.18630278249942</v>
       </c>
     </row>
     <row r="9">
@@ -704,28 +678,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-66.3336939355685</v>
+        <v>-11.62363056048749</v>
       </c>
       <c r="C9" t="n">
-        <v>-36.00113625546264</v>
+        <v>-14.25123002221568</v>
       </c>
       <c r="D9" t="n">
-        <v>-155.0563015052505</v>
+        <v>-88.55340426653909</v>
       </c>
       <c r="E9" t="n">
-        <v>-160.9361241720271</v>
+        <v>-78.90447340434096</v>
       </c>
       <c r="F9" t="n">
-        <v>-93.95329828154613</v>
+        <v>-116.5482671616942</v>
       </c>
       <c r="G9" t="n">
-        <v>-165.8266227203588</v>
+        <v>-87.09179016824142</v>
       </c>
       <c r="H9" t="n">
-        <v>-164.1368020087363</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-120.3205684112786</v>
+        <v>-66.16213259725313</v>
       </c>
     </row>
   </sheetData>
@@ -739,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -765,20 +736,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>BR08</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -791,28 +757,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8334279869388074</v>
+        <v>0.02982192883159562</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8838849646937742</v>
+        <v>0.1262732500340942</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5167797619050813</v>
+        <v>0.5831114630800008</v>
       </c>
       <c r="E2" t="n">
-        <v>0.613752514812032</v>
+        <v>-0.4996756132836739</v>
       </c>
       <c r="F2" t="n">
-        <v>-18.48564718642167</v>
+        <v>0.6851975247036717</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5015130046850875</v>
+        <v>0.529213937264728</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2881067721566537</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-2.203485103649078</v>
+        <v>0.2423237484384027</v>
       </c>
     </row>
     <row r="3">
@@ -822,28 +785,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05107189312958658</v>
+        <v>0.3590593948517548</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05337714858079581</v>
+        <v>0.258228940889981</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01564220576672538</v>
+        <v>0.0414634281194974</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01077803486046576</v>
+        <v>0.05782565576405917</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05944811700085327</v>
+        <v>0.06806397452572623</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01329343754039825</v>
+        <v>0.07825746439318118</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01523016117638851</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.03126299972217336</v>
+        <v>0.1438164764240333</v>
       </c>
     </row>
     <row r="4">
@@ -853,28 +813,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007534400900488517</v>
+        <v>0.4517775057699148</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01178727648046935</v>
+        <v>0.3470629331823861</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0005542931690431488</v>
+        <v>0.005472720173603735</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001408441757517686</v>
+        <v>0.01008446543366156</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01225662744267764</v>
+        <v>0.01338025131804312</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002771986131988807</v>
+        <v>0.01777951626273072</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000391978696752679</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.004706088496911711</v>
+        <v>0.14092623202339</v>
       </c>
     </row>
     <row r="5">
@@ -884,28 +841,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08680092684118365</v>
+        <v>0.6721439620869288</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1085692243707642</v>
+        <v>0.5891204742515627</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02354343154774063</v>
+        <v>0.0739778356915349</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01186777888872929</v>
+        <v>0.1004214391136751</v>
       </c>
       <c r="F5" t="n">
-        <v>0.110709653791698</v>
+        <v>0.1156730362618839</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01664928266319245</v>
+        <v>0.133339852492534</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01979845187767667</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.05399124999728356</v>
+        <v>0.2807794333163532</v>
       </c>
     </row>
     <row r="6">
@@ -915,28 +869,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.04792714225707</v>
+        <v>67.00339197319198</v>
       </c>
       <c r="C6" t="n">
-        <v>93.50076582327466</v>
+        <v>57.15009278502276</v>
       </c>
       <c r="D6" t="n">
-        <v>34.81660297538098</v>
+        <v>81.02980515645326</v>
       </c>
       <c r="E6" t="n">
-        <v>1643.011679402289</v>
+        <v>158.8882847090654</v>
       </c>
       <c r="F6" t="n">
-        <v>447.7174024578019</v>
+        <v>54.53338112122095</v>
       </c>
       <c r="G6" t="n">
-        <v>459.9276183672584</v>
+        <v>89.93328471230232</v>
       </c>
       <c r="H6" t="n">
-        <v>201.5190722058889</v>
-      </c>
-      <c r="I6" t="n">
-        <v>417.7915811963073</v>
+        <v>84.75637340954279</v>
       </c>
     </row>
     <row r="7">
@@ -946,28 +897,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05674568454869976</v>
+        <v>0.6077976753894616</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04458560412819629</v>
+        <v>0.5055620782174419</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1468540766468058</v>
+        <v>0.1293974651975224</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1174728364794167</v>
+        <v>0.9149236195773307</v>
       </c>
       <c r="F7" t="n">
-        <v>11.71154759027275</v>
+        <v>0.1043069185115287</v>
       </c>
       <c r="G7" t="n">
-        <v>0.151240137623713</v>
+        <v>0.1541814802044931</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7764128334694461</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.857836966167005</v>
+        <v>0.4026948728496297</v>
       </c>
     </row>
     <row r="8">
@@ -977,28 +925,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-77.10069130228669</v>
+        <v>-11.50761289163056</v>
       </c>
       <c r="C8" t="n">
-        <v>-60.61101890434149</v>
+        <v>-13.87373727762511</v>
       </c>
       <c r="D8" t="n">
-        <v>-151.4541533289492</v>
+        <v>-107.3675694296209</v>
       </c>
       <c r="E8" t="n">
-        <v>-180.2249847194525</v>
+        <v>-94.53194141632258</v>
       </c>
       <c r="F8" t="n">
-        <v>-117.2472772316481</v>
+        <v>-114.4773369163451</v>
       </c>
       <c r="G8" t="n">
-        <v>-215.1509599258792</v>
+        <v>-98.74270640217588</v>
       </c>
       <c r="H8" t="n">
-        <v>-190.1075766167308</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-141.6995231470412</v>
+        <v>-73.41681738895336</v>
       </c>
     </row>
     <row r="9">
@@ -1008,28 +953,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-74.60105127011803</v>
+        <v>-10.67439954757435</v>
       </c>
       <c r="C9" t="n">
-        <v>-58.48686830103486</v>
+        <v>-13.1656870765229</v>
       </c>
       <c r="D9" t="n">
-        <v>-148.320586015779</v>
+        <v>-106.3230469918975</v>
       </c>
       <c r="E9" t="n">
-        <v>-177.0914174062823</v>
+        <v>-93.48741897859915</v>
       </c>
       <c r="F9" t="n">
-        <v>-113.2506637011225</v>
+        <v>-113.1815000503408</v>
       </c>
       <c r="G9" t="n">
-        <v>-211.2634493278662</v>
+        <v>-97.52383057730768</v>
       </c>
       <c r="H9" t="n">
-        <v>-186.4509491421262</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-138.4949978806184</v>
+        <v>-72.39264720370706</v>
       </c>
     </row>
   </sheetData>
@@ -1043,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1069,20 +1011,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>BR08</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -1095,28 +1032,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3098566023134449</v>
+        <v>0.3947916513362169</v>
       </c>
       <c r="C2" t="n">
-        <v>0.17728042274786</v>
+        <v>0.4294858041924047</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5968435644190448</v>
+        <v>0.9596972206746003</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4464085696249603</v>
+        <v>0.5378953851523645</v>
       </c>
       <c r="F2" t="n">
-        <v>-33.71419097014039</v>
+        <v>-0.4026005132566493</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6895408182640808</v>
+        <v>-1.42178167175561</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6977048848616982</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-4.399508015415615</v>
+        <v>0.08291464605722114</v>
       </c>
     </row>
     <row r="3">
@@ -1126,28 +1060,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08474694131049205</v>
+        <v>0.21135891101743</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1229070874715903</v>
+        <v>0.188813969529444</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01009238941208156</v>
+        <v>0.01126033176123501</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005856074538468041</v>
+        <v>0.02602605558989148</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07838539510378784</v>
+        <v>0.1296895473442054</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007860183180573719</v>
+        <v>0.188814821743617</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006210000122838963</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.04515115301997608</v>
+        <v>0.1259939394976371</v>
       </c>
     </row>
     <row r="4">
@@ -1157,28 +1088,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03121663082192299</v>
+        <v>0.2818240551460501</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08351737651709497</v>
+        <v>0.2266204282138559</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004624534336130438</v>
+        <v>0.0005290762732311373</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002018657252265882</v>
+        <v>0.003107390674282427</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02183550290243706</v>
+        <v>0.0596156283349565</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001726401198845509</v>
+        <v>0.09146002829309348</v>
       </c>
       <c r="H4" t="n">
-        <v>9.199023545868133e-05</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.01964263710794827</v>
+        <v>0.1105261011559116</v>
       </c>
     </row>
     <row r="5">
@@ -1188,28 +1116,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1766822877990971</v>
+        <v>0.5308710343822218</v>
       </c>
       <c r="C5" t="n">
-        <v>0.288993730930439</v>
+        <v>0.4760466660043487</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02150473049384818</v>
+        <v>0.0230016580539564</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01420794584824239</v>
+        <v>0.05574397433160311</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1477684096904242</v>
+        <v>0.2441631182938089</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01313925872660063</v>
+        <v>0.3024235908342692</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00959115402121566</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.09598393107283816</v>
+        <v>0.2720416736500347</v>
       </c>
     </row>
     <row r="6">
@@ -1219,28 +1144,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49.4018299408194</v>
+        <v>31.46977918139396</v>
       </c>
       <c r="C6" t="n">
-        <v>247.1197070995661</v>
+        <v>44.13767244721497</v>
       </c>
       <c r="D6" t="n">
-        <v>54.98732623756622</v>
+        <v>17.65810054282666</v>
       </c>
       <c r="E6" t="n">
-        <v>2884.224495977484</v>
+        <v>54.77410411814857</v>
       </c>
       <c r="F6" t="n">
-        <v>494.047499537845</v>
+        <v>69.63174783847005</v>
       </c>
       <c r="G6" t="n">
-        <v>394.8022531417145</v>
+        <v>117.0903816409419</v>
       </c>
       <c r="H6" t="n">
-        <v>80.54693827183414</v>
-      </c>
-      <c r="I6" t="n">
-        <v>600.7328643152613</v>
+        <v>55.79363096149935</v>
       </c>
     </row>
     <row r="7">
@@ -1250,28 +1172,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2303946608813127</v>
+        <v>0.37983934320137</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3067780367376085</v>
+        <v>0.3307885584919777</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1227706480778157</v>
+        <v>0.01346118718888171</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1677187351201705</v>
+        <v>0.1418065579262884</v>
       </c>
       <c r="F7" t="n">
-        <v>20.86208428614765</v>
+        <v>0.9270221876229288</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09475860260469497</v>
+        <v>1.583113042663697</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09225292770631163</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.125251128182224</v>
+        <v>0.5626718128491907</v>
       </c>
     </row>
     <row r="8">
@@ -1281,28 +1200,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-52.93567287929602</v>
+        <v>-17.53002945162144</v>
       </c>
       <c r="C8" t="n">
-        <v>-31.24050850161612</v>
+        <v>-18.26718175195546</v>
       </c>
       <c r="D8" t="n">
-        <v>-155.2582584933743</v>
+        <v>-154.4319370066515</v>
       </c>
       <c r="E8" t="n">
-        <v>-172.6660639720488</v>
+        <v>-117.2534102453004</v>
       </c>
       <c r="F8" t="n">
-        <v>-101.0781056903208</v>
+        <v>-72.13561301028416</v>
       </c>
       <c r="G8" t="n">
-        <v>-227.9361367749551</v>
+        <v>-55.79633128507261</v>
       </c>
       <c r="H8" t="n">
-        <v>-226.3457030716693</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-138.2086356261829</v>
+        <v>-72.56908379181425</v>
       </c>
     </row>
     <row r="9">
@@ -1312,28 +1228,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-50.43603284712737</v>
+        <v>-15.86360276350901</v>
       </c>
       <c r="C9" t="n">
-        <v>-29.11635789830949</v>
+        <v>-16.85108134975103</v>
       </c>
       <c r="D9" t="n">
-        <v>-152.1246911802041</v>
+        <v>-152.3428921312046</v>
       </c>
       <c r="E9" t="n">
-        <v>-169.5324966588785</v>
+        <v>-115.1643653698535</v>
       </c>
       <c r="F9" t="n">
-        <v>-97.08149215979519</v>
+        <v>-69.5439392782755</v>
       </c>
       <c r="G9" t="n">
-        <v>-224.0486261769421</v>
+        <v>-53.35857963533621</v>
       </c>
       <c r="H9" t="n">
-        <v>-222.6890755970647</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-135.0041103597602</v>
+        <v>-70.52074342132164</v>
       </c>
     </row>
   </sheetData>
@@ -1347,7 +1260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1373,20 +1286,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>BR08</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -1399,28 +1307,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7270839990847735</v>
+        <v>0.2205362040973438</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8671837373232321</v>
+        <v>0.2145633888012737</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6660864942246855</v>
+        <v>0.7035702359827276</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6453040628999822</v>
+        <v>0.7781476182107407</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5185746350085043</v>
+        <v>0.7296145987227001</v>
       </c>
       <c r="G2" t="n">
-        <v>0.483088269213498</v>
+        <v>-2.952238619149356</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7918958477986668</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.4450607642794299</v>
+        <v>-0.05096776222242842</v>
       </c>
     </row>
     <row r="3">
@@ -1430,28 +1335,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05674417353102911</v>
+        <v>0.3196436151710166</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05318171266219202</v>
+        <v>0.2438248456595596</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008654604335730157</v>
+        <v>0.04393473724802701</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006024973373860417</v>
+        <v>0.03235589527318093</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01269352943207032</v>
+        <v>0.06380581215352039</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01071595076199815</v>
+        <v>0.2754541262253822</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01654527989776898</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.02350860342780703</v>
+        <v>0.1631698386217811</v>
       </c>
     </row>
     <row r="4">
@@ -1461,28 +1363,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01234456212219763</v>
+        <v>0.3629686343320024</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01348268124920224</v>
+        <v>0.311992203651886</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000383026124965715</v>
+        <v>0.003891393036564196</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001293389829555565</v>
+        <v>0.001491831070474358</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003028203930669368</v>
+        <v>0.01149236396065405</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002874442388005162</v>
+        <v>0.1492586471126511</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000545284765455171</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.003925022553806252</v>
+        <v>0.1401825121940387</v>
       </c>
     </row>
     <row r="5">
@@ -1492,28 +1391,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1111060849917665</v>
+        <v>0.602468782869289</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1161149484312947</v>
+        <v>0.5585626228561001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01957105324109346</v>
+        <v>0.06238103106365105</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01137272979348215</v>
+        <v>0.03862422905993539</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01740173534642269</v>
+        <v>0.1072024438184785</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01695418057001034</v>
+        <v>0.3863400666675036</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02335133326932685</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.04512458080619954</v>
+        <v>0.2925965293891596</v>
       </c>
     </row>
     <row r="6">
@@ -1523,28 +1419,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32.99253600089397</v>
+        <v>73.05927900187694</v>
       </c>
       <c r="C6" t="n">
-        <v>233.9048846739289</v>
+        <v>54.65202981850885</v>
       </c>
       <c r="D6" t="n">
-        <v>34.74861739346013</v>
+        <v>63.76425094492009</v>
       </c>
       <c r="E6" t="n">
-        <v>1449.687194301786</v>
+        <v>47.5362339042551</v>
       </c>
       <c r="F6" t="n">
-        <v>66.36321025957632</v>
+        <v>54.56101835681456</v>
       </c>
       <c r="G6" t="n">
-        <v>770.198080201938</v>
+        <v>300.7180343399298</v>
       </c>
       <c r="H6" t="n">
-        <v>318.5722952130079</v>
-      </c>
-      <c r="I6" t="n">
-        <v>415.2095454349415</v>
+        <v>99.04847439438423</v>
       </c>
     </row>
     <row r="7">
@@ -1554,28 +1447,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0935159937601063</v>
+        <v>0.4889171828031986</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05228275567747195</v>
+        <v>0.4550255259159381</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1034421700200704</v>
+        <v>0.09265290433077668</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1094993184180742</v>
+        <v>0.06859999628610984</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1476395837725956</v>
+        <v>0.09016027515564783</v>
       </c>
       <c r="G7" t="n">
-        <v>0.158274730203111</v>
+        <v>2.582305277447325</v>
       </c>
       <c r="H7" t="n">
-        <v>1.081900907350838</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.249507922743181</v>
+        <v>0.6296101936564994</v>
       </c>
     </row>
     <row r="8">
@@ -1585,28 +1475,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-62.70717365673757</v>
+        <v>-13.22846053924082</v>
       </c>
       <c r="C8" t="n">
-        <v>-52.59523931324892</v>
+        <v>-13.47165619670157</v>
       </c>
       <c r="D8" t="n">
-        <v>-153.2155545539349</v>
+        <v>-112.5287496457891</v>
       </c>
       <c r="E8" t="n">
-        <v>-176.0145503316594</v>
+        <v>-132.6627711502233</v>
       </c>
       <c r="F8" t="n">
-        <v>-214.8663793301688</v>
+        <v>-116.5839566247201</v>
       </c>
       <c r="G8" t="n">
-        <v>-208.1710050504772</v>
+        <v>-43.55186478211312</v>
       </c>
       <c r="H8" t="n">
-        <v>-175.8550598584281</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-149.060708870665</v>
+        <v>-72.004576489798</v>
       </c>
     </row>
     <row r="9">
@@ -1616,28 +1503,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-57.70789359240027</v>
+        <v>-11.56203385112839</v>
       </c>
       <c r="C9" t="n">
-        <v>-48.34693810663566</v>
+        <v>-12.05555579449715</v>
       </c>
       <c r="D9" t="n">
-        <v>-146.9484199275944</v>
+        <v>-110.4397047703422</v>
       </c>
       <c r="E9" t="n">
-        <v>-169.7474157053188</v>
+        <v>-130.5737262747765</v>
       </c>
       <c r="F9" t="n">
-        <v>-206.8731522691176</v>
+        <v>-113.9922828927115</v>
       </c>
       <c r="G9" t="n">
-        <v>-200.3959838544513</v>
+        <v>-41.11411313237672</v>
       </c>
       <c r="H9" t="n">
-        <v>-168.5418049092189</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-142.6516583378196</v>
+        <v>-69.9562361193054</v>
       </c>
     </row>
   </sheetData>
@@ -1651,7 +1535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1677,20 +1561,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>BR08</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -1703,28 +1582,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8588157505125056</v>
+        <v>0.2323551186531873</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8426183053811716</v>
+        <v>0.1882398305424486</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6449173189880136</v>
+        <v>0.7475999573993114</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6338540980966583</v>
+        <v>0.302953435641652</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6881954051662047</v>
+        <v>0.5139247423039637</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5270907353943324</v>
+        <v>-3.343744077285102</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1886590956657799</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.5724046454104438</v>
+        <v>-0.2264451654574231</v>
       </c>
     </row>
     <row r="3">
@@ -1734,28 +1610,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04219413868704863</v>
+        <v>0.3139842509732681</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06171323249477134</v>
+        <v>0.237857126642708</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008224943739119214</v>
+        <v>0.02329914952902029</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00533247080094969</v>
+        <v>0.03245045129203557</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007849036635724003</v>
+        <v>0.08378279064873546</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009618685627567637</v>
+        <v>0.2879326488468568</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01304009048494022</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.02113894263858868</v>
+        <v>0.163217736322104</v>
       </c>
     </row>
     <row r="4">
@@ -1765,28 +1638,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006386059200008552</v>
+        <v>0.3574649851591076</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01597641117314857</v>
+        <v>0.3224484834229492</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004073089018506924</v>
+        <v>0.003313391188840255</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001335141838745376</v>
+        <v>0.004687241641899433</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000196127576222152</v>
+        <v>0.02065996813186874</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002629753505099554</v>
+        <v>0.1640440840889077</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0003617161661390801</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.003389158935964791</v>
+        <v>0.1454363589389288</v>
       </c>
     </row>
     <row r="5">
@@ -1796,28 +1666,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07991282250057591</v>
+        <v>0.597883755557138</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1263978289890636</v>
+        <v>0.567845474951548</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02018189539787313</v>
+        <v>0.0575620637993484</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01155483378826963</v>
+        <v>0.06846343288135232</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01400455555246763</v>
+        <v>0.1437357580140333</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01621651474608386</v>
+        <v>0.4050235599183184</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01901883713950672</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.04104104115912006</v>
+        <v>0.3067523408536231</v>
       </c>
     </row>
     <row r="6">
@@ -1827,28 +1694,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.69708240185204</v>
+        <v>73.60957050946612</v>
       </c>
       <c r="C6" t="n">
-        <v>163.2378869670133</v>
+        <v>55.47245781752397</v>
       </c>
       <c r="D6" t="n">
-        <v>35.47967184162529</v>
+        <v>36.18589442622444</v>
       </c>
       <c r="E6" t="n">
-        <v>1419.94289001194</v>
+        <v>59.38998620943401</v>
       </c>
       <c r="F6" t="n">
-        <v>52.52006770141914</v>
+        <v>56.86102952222636</v>
       </c>
       <c r="G6" t="n">
-        <v>705.4115149025249</v>
+        <v>314.0998173725787</v>
       </c>
       <c r="H6" t="n">
-        <v>266.0653329871478</v>
-      </c>
-      <c r="I6" t="n">
-        <v>382.0506352590747</v>
+        <v>99.26979264290894</v>
       </c>
     </row>
     <row r="7">
@@ -1858,28 +1722,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05032551628625433</v>
+        <v>0.4815189540154192</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06189799620685255</v>
+        <v>0.4702419892333298</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1103099205348914</v>
+        <v>0.07903938661239478</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1134372304997147</v>
+        <v>0.213395038456834</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09717866775349411</v>
+        <v>0.161284555001119</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1455568621270573</v>
+        <v>2.837908164095532</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7207018600320627</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.1856297219200467</v>
+        <v>0.7072313479024381</v>
       </c>
     </row>
     <row r="8">
@@ -1889,28 +1750,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-71.91184454569151</v>
+        <v>-13.48820370934777</v>
       </c>
       <c r="C8" t="n">
-        <v>-48.04962919408953</v>
+        <v>-12.97717845245754</v>
       </c>
       <c r="D8" t="n">
-        <v>-149.9247124435819</v>
+        <v>-115.9054447999859</v>
       </c>
       <c r="E8" t="n">
-        <v>-173.3473596298462</v>
+        <v>-108.6211311175866</v>
       </c>
       <c r="F8" t="n">
-        <v>-225.0288659187543</v>
+        <v>-100.7480486604857</v>
       </c>
       <c r="G8" t="n">
-        <v>-208.5731568708427</v>
+        <v>-41.19050204648685</v>
       </c>
       <c r="H8" t="n">
-        <v>-184.1162681280572</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-151.5645481044091</v>
+        <v>-65.4884181310584</v>
       </c>
     </row>
     <row r="9">
@@ -1920,28 +1778,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-66.07935113729799</v>
+        <v>-11.82177702123534</v>
       </c>
       <c r="C9" t="n">
-        <v>-43.09327778637406</v>
+        <v>-11.56107805025312</v>
       </c>
       <c r="D9" t="n">
-        <v>-142.6130553795179</v>
+        <v>-113.816399924539</v>
       </c>
       <c r="E9" t="n">
-        <v>-166.0357025657823</v>
+        <v>-106.5320862421397</v>
       </c>
       <c r="F9" t="n">
-        <v>-215.7034343475279</v>
+        <v>-98.15637492847706</v>
       </c>
       <c r="G9" t="n">
-        <v>-199.5022988088124</v>
+        <v>-38.75275039675045</v>
       </c>
       <c r="H9" t="n">
-        <v>-175.5841373539798</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-144.087322482756</v>
+        <v>-63.44007776056579</v>
       </c>
     </row>
   </sheetData>
@@ -1955,7 +1810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1981,20 +1836,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>BR08</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -2007,28 +1857,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8780710150541366</v>
+        <v>0.1205647447782366</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9322226837731202</v>
+        <v>0.2091067165166794</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8209441212758773</v>
+        <v>0.2775828190881146</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8060361118460525</v>
+        <v>-0.4551939676037569</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.989540974007508</v>
+        <v>0.73669320965941</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.7388527302353787</v>
+        <v>-0.1062133804332686</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.451820875841862</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-0.9632772354479374</v>
+        <v>0.1304233570009025</v>
       </c>
     </row>
     <row r="3">
@@ -2038,28 +1885,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03988479778350688</v>
+        <v>0.3389867915160705</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04784898186453247</v>
+        <v>0.2422288714214376</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009854042837998237</v>
+        <v>0.05732603815164675</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0062102453402068</v>
+        <v>0.05931413906731789</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04448428175073987</v>
+        <v>0.05488653472768618</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01953415501556069</v>
+        <v>0.152499626772279</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01502534178120337</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.02612026376767834</v>
+        <v>0.1508736669427397</v>
       </c>
     </row>
     <row r="4">
@@ -2069,28 +1913,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005515103270285147</v>
+        <v>0.4095217959438411</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006880331762062497</v>
+        <v>0.3141597104709002</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002053917502401962</v>
+        <v>0.009483559104176345</v>
       </c>
       <c r="E4" t="n">
-        <v>7.072844484503577e-05</v>
+        <v>0.009785351669112628</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00502548497463587</v>
+        <v>0.01119149722437228</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0009669411035965592</v>
+        <v>0.04177680765057633</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001050410010709604</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.002816341616624988</v>
+        <v>0.1326531203438298</v>
       </c>
     </row>
     <row r="5">
@@ -2100,28 +1941,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07426374128930717</v>
+        <v>0.6399389001645713</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08294776526261873</v>
+        <v>0.5604995187071085</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01433149504553507</v>
+        <v>0.09738356691031781</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008410020502057993</v>
+        <v>0.09892093645489122</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07089065505858914</v>
+        <v>0.1057898729764446</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0310956766061869</v>
+        <v>0.2043937563884385</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03241002947714802</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.04490705474877758</v>
+        <v>0.2844877586002953</v>
       </c>
     </row>
     <row r="6">
@@ -2131,28 +1969,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33.58701911002775</v>
+        <v>68.90384842029944</v>
       </c>
       <c r="C6" t="n">
-        <v>232.9730646626906</v>
+        <v>54.8103536147401</v>
       </c>
       <c r="D6" t="n">
-        <v>32.56689926382521</v>
+        <v>104.8714288597183</v>
       </c>
       <c r="E6" t="n">
-        <v>484.3768460475366</v>
+        <v>156.2150483312212</v>
       </c>
       <c r="F6" t="n">
-        <v>246.1262094484494</v>
+        <v>60.61739490320169</v>
       </c>
       <c r="G6" t="n">
-        <v>902.5987279654688</v>
+        <v>165.2628234037178</v>
       </c>
       <c r="H6" t="n">
-        <v>174.6886329225677</v>
-      </c>
-      <c r="I6" t="n">
-        <v>300.9881999172238</v>
+        <v>101.7801495888164</v>
       </c>
     </row>
     <row r="7">
@@ -2162,28 +1997,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04293926777295862</v>
+        <v>0.5514958337272179</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02764942710150768</v>
+        <v>0.4581797823746263</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05636053784240495</v>
+        <v>0.2243636456464891</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06073867635757579</v>
+        <v>0.888815872899012</v>
       </c>
       <c r="F7" t="n">
-        <v>4.805760263368995</v>
+        <v>0.08782608515923762</v>
       </c>
       <c r="G7" t="n">
-        <v>1.049665355686262</v>
+        <v>0.7242155589707682</v>
       </c>
       <c r="H7" t="n">
-        <v>2.077563099520111</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.160096661092831</v>
+        <v>0.4891494631295585</v>
       </c>
     </row>
     <row r="8">
@@ -2193,28 +2025,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-78.40450331879578</v>
+        <v>-11.17700757307524</v>
       </c>
       <c r="C8" t="n">
-        <v>-64.68632610454215</v>
+        <v>-13.367806854656</v>
       </c>
       <c r="D8" t="n">
-        <v>-168.3024199383915</v>
+        <v>-93.82210760509294</v>
       </c>
       <c r="E8" t="n">
-        <v>-190.6899174216115</v>
+        <v>-93.16424352250634</v>
       </c>
       <c r="F8" t="n">
-        <v>-138.2105328852027</v>
+        <v>-117.3002260657123</v>
       </c>
       <c r="G8" t="n">
-        <v>-177.4170702082945</v>
+        <v>-75.38534835819746</v>
       </c>
       <c r="H8" t="n">
-        <v>-161.4643676160644</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-139.8821624989861</v>
+        <v>-67.36945666320672</v>
       </c>
     </row>
     <row r="9">
@@ -2224,28 +2053,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-74.2384365985147</v>
+        <v>-9.510580884962806</v>
       </c>
       <c r="C9" t="n">
-        <v>-61.14607509903109</v>
+        <v>-11.95170645245158</v>
       </c>
       <c r="D9" t="n">
-        <v>-163.0798077497744</v>
+        <v>-91.73306272964609</v>
       </c>
       <c r="E9" t="n">
-        <v>-185.4673052329944</v>
+        <v>-91.07519864705949</v>
       </c>
       <c r="F9" t="n">
-        <v>-131.5495103343267</v>
+        <v>-114.7085523337037</v>
       </c>
       <c r="G9" t="n">
-        <v>-170.9378858782728</v>
+        <v>-72.94759670846106</v>
       </c>
       <c r="H9" t="n">
-        <v>-155.3699884917234</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-134.5412870549482</v>
+        <v>-65.32111629271411</v>
       </c>
     </row>
   </sheetData>
@@ -2259,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2285,20 +2111,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>BR08</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -2311,28 +2132,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8809377389493065</v>
+        <v>0.1083765126294903</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9426248579190262</v>
+        <v>0.1767459016268772</v>
       </c>
       <c r="D2" t="n">
-        <v>0.817959489674621</v>
+        <v>0.5315434881965275</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8043104036625739</v>
+        <v>0.0376920034428232</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.485357730917563</v>
+        <v>0.7498584731270099</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8091045520168423</v>
+        <v>-0.03112210491011069</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.581516742732962</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-0.9185923622088344</v>
+        <v>0.2621823790187696</v>
       </c>
     </row>
     <row r="3">
@@ -2342,28 +2160,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03975689533168547</v>
+        <v>0.3378416617405293</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04505358967513655</v>
+        <v>0.2433986875352218</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0100129570807155</v>
+        <v>0.0396206028673055</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006236440166364952</v>
+        <v>0.04479781753338839</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04319832264446207</v>
+        <v>0.04982246253450821</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02000703270910302</v>
+        <v>0.1451831370025418</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01533438120087568</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.0256570884011919</v>
+        <v>0.1434440615355825</v>
       </c>
     </row>
     <row r="4">
@@ -2373,28 +2188,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005385435346482816</v>
+        <v>0.4151974232163416</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005824367714577857</v>
+        <v>0.3270141175681596</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002088153670059364</v>
+        <v>0.00614968073131471</v>
       </c>
       <c r="E4" t="n">
-        <v>7.135772000153765e-05</v>
+        <v>0.006470973883857715</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00470834969479253</v>
+        <v>0.0106319255955313</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00100600673169828</v>
+        <v>0.0389409408736452</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001089877248967396</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.00261345854621805</v>
+        <v>0.134067510311475</v>
       </c>
     </row>
     <row r="5">
@@ -2404,28 +2216,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07338552545620161</v>
+        <v>0.6443581482501339</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0763175452604305</v>
+        <v>0.5718514820896765</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01445044521826011</v>
+        <v>0.07841990009758179</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008447349880378914</v>
+        <v>0.08044236373862788</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06861741538991782</v>
+        <v>0.1031112292407151</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03171760917374259</v>
+        <v>0.1973345911735832</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03301328897531108</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.04370702562203466</v>
+        <v>0.2792529524317197</v>
       </c>
     </row>
     <row r="6">
@@ -2435,28 +2244,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33.87520982205296</v>
+        <v>68.30587006069726</v>
       </c>
       <c r="C6" t="n">
-        <v>229.066626990909</v>
+        <v>55.77219071966596</v>
       </c>
       <c r="D6" t="n">
-        <v>33.07765982435092</v>
+        <v>86.47628650854168</v>
       </c>
       <c r="E6" t="n">
-        <v>436.2638638273136</v>
+        <v>128.9144443662769</v>
       </c>
       <c r="F6" t="n">
-        <v>235.7113142483328</v>
+        <v>55.25119779100749</v>
       </c>
       <c r="G6" t="n">
-        <v>941.9851393675647</v>
+        <v>159.3685729203491</v>
       </c>
       <c r="H6" t="n">
-        <v>180.1629861587308</v>
-      </c>
-      <c r="I6" t="n">
-        <v>298.5918286056079</v>
+        <v>92.34809372775639</v>
       </c>
     </row>
     <row r="7">
@@ -2466,28 +2272,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04198848305774603</v>
+        <v>0.559125242462592</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02378960002449665</v>
+        <v>0.4768861118096486</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05725832385451788</v>
+        <v>0.1458417300529621</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06125682930522892</v>
+        <v>0.2942220806858535</v>
       </c>
       <c r="F7" t="n">
-        <v>4.502806328123248</v>
+        <v>0.08348480597876895</v>
       </c>
       <c r="G7" t="n">
-        <v>1.091871140634483</v>
+        <v>0.6751905801691698</v>
       </c>
       <c r="H7" t="n">
-        <v>2.155435873788331</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.133486654112579</v>
+        <v>0.3724584251931658</v>
       </c>
     </row>
     <row r="8">
@@ -2497,28 +2300,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-78.8089711650351</v>
+        <v>-10.94301960569304</v>
       </c>
       <c r="C8" t="n">
-        <v>-67.18557248413393</v>
+        <v>-12.76627904038245</v>
       </c>
       <c r="D8" t="n">
-        <v>-167.9552622657356</v>
+        <v>-102.9184573544913</v>
       </c>
       <c r="E8" t="n">
-        <v>-190.5039054379351</v>
+        <v>-101.8490018345775</v>
       </c>
       <c r="F8" t="n">
-        <v>-140.0356988374607</v>
+        <v>-118.6851368054836</v>
       </c>
       <c r="G8" t="n">
-        <v>-176.3476959260058</v>
+        <v>-77.14272792980505</v>
       </c>
       <c r="H8" t="n">
-        <v>-160.5422551177236</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-140.1970516048614</v>
+        <v>-70.71743709507216</v>
       </c>
     </row>
     <row r="9">
@@ -2528,28 +2328,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-74.64290444475402</v>
+        <v>-9.276592917580606</v>
       </c>
       <c r="C9" t="n">
-        <v>-63.64532147862288</v>
+        <v>-11.35017863817803</v>
       </c>
       <c r="D9" t="n">
-        <v>-162.7326500771185</v>
+        <v>-100.8294124790444</v>
       </c>
       <c r="E9" t="n">
-        <v>-185.281293249318</v>
+        <v>-99.75995695913063</v>
       </c>
       <c r="F9" t="n">
-        <v>-133.3746762865847</v>
+        <v>-116.0934630734749</v>
       </c>
       <c r="G9" t="n">
-        <v>-169.8685115959841</v>
+        <v>-74.70497628006865</v>
       </c>
       <c r="H9" t="n">
-        <v>-154.4478759933826</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-134.8561761608235</v>
+        <v>-68.66909672457955</v>
       </c>
     </row>
   </sheetData>
@@ -2563,7 +2360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2589,20 +2386,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>BR08</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -2615,28 +2407,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8804353982262564</v>
+        <v>0.1130844365975627</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9399674921393246</v>
+        <v>0.2074115500011636</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8185501917218796</v>
+        <v>0.3245706006307363</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8030386891205414</v>
+        <v>-0.3316689377169386</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.603574283788131</v>
+        <v>0.7419378484597297</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.7855397427050956</v>
+        <v>-0.1078300884228398</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.530344888297004</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-0.9253524490831756</v>
+        <v>0.1579175682582356</v>
       </c>
     </row>
     <row r="3">
@@ -2646,28 +2435,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03978277082458172</v>
+        <v>0.3390182124058693</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04583046028778442</v>
+        <v>0.2422721922287964</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009998445192170372</v>
+        <v>0.05410683676160886</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006265963723180522</v>
+        <v>0.05517460461160976</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04351369014293686</v>
+        <v>0.05325210167657968</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01990913487171686</v>
+        <v>0.1526528891461077</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01527415646757938</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.02579637450142144</v>
+        <v>0.1494128061384286</v>
       </c>
     </row>
     <row r="4">
@@ -2677,28 +2463,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005408157269130831</v>
+        <v>0.4130051100618208</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006094126967309201</v>
+        <v>0.3148330668298883</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000208137783403424</v>
+        <v>0.00886672520929154</v>
       </c>
       <c r="E4" t="n">
-        <v>7.182144751649337e-05</v>
+        <v>0.008954716108294184</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004782708849109038</v>
+        <v>0.01096858098092603</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000992902814198114</v>
+        <v>0.0418378635914121</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001074305343558777</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.002661737210603697</v>
+        <v>0.1330776771302722</v>
       </c>
     </row>
     <row r="5">
@@ -2708,28 +2491,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07354017452475096</v>
+        <v>0.6426547362789921</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07806488946581043</v>
+        <v>0.5610998724201319</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01442698109111619</v>
+        <v>0.09416329013629218</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008474753537212358</v>
+        <v>0.09462936176628364</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06915713158531836</v>
+        <v>0.1047309934113395</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03151036042634413</v>
+        <v>0.2045430604821686</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03277659749819644</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.0439929840183927</v>
+        <v>0.2836368857492013</v>
       </c>
     </row>
     <row r="6">
@@ -2739,28 +2519,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33.8121749273835</v>
+        <v>68.56666941747955</v>
       </c>
       <c r="C6" t="n">
-        <v>230.205441171287</v>
+        <v>54.86245475348394</v>
       </c>
       <c r="D6" t="n">
-        <v>32.90959016861152</v>
+        <v>101.9941873471218</v>
       </c>
       <c r="E6" t="n">
-        <v>451.1880996741396</v>
+        <v>150.1176682994445</v>
       </c>
       <c r="F6" t="n">
-        <v>238.191242729454</v>
+        <v>59.41134778773597</v>
       </c>
       <c r="G6" t="n">
-        <v>932.242124982612</v>
+        <v>165.3858844195957</v>
       </c>
       <c r="H6" t="n">
-        <v>179.0259055026287</v>
-      </c>
-      <c r="I6" t="n">
-        <v>299.6535113080166</v>
+        <v>100.0563686708102</v>
       </c>
     </row>
     <row r="7">
@@ -2770,28 +2547,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04215509062051467</v>
+        <v>0.5561782460640058</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02477564123531906</v>
+        <v>0.4591596817805728</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05708063893181853</v>
+        <v>0.2098355274572832</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06163866827709913</v>
+        <v>0.8135379651817751</v>
       </c>
       <c r="F7" t="n">
-        <v>4.573840362661632</v>
+        <v>0.08609665214872934</v>
       </c>
       <c r="G7" t="n">
-        <v>1.077713909562935</v>
+        <v>0.7252710620816809</v>
       </c>
       <c r="H7" t="n">
-        <v>2.124710960459185</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.137416467392643</v>
+        <v>0.4750131891190079</v>
       </c>
     </row>
     <row r="8">
@@ -2801,28 +2575,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-78.73739661717644</v>
+        <v>-11.03302032213231</v>
       </c>
       <c r="C8" t="n">
-        <v>-66.50644645744138</v>
+        <v>-13.33569090799403</v>
       </c>
       <c r="D8" t="n">
-        <v>-168.0235158245098</v>
+        <v>-95.23444473598697</v>
       </c>
       <c r="E8" t="n">
-        <v>-190.3678757063216</v>
+        <v>-95.02707386610533</v>
       </c>
       <c r="F8" t="n">
-        <v>-139.5969492685021</v>
+        <v>-117.8434499246887</v>
       </c>
       <c r="G8" t="n">
-        <v>-176.7016997793875</v>
+        <v>-75.34883804799678</v>
       </c>
       <c r="H8" t="n">
-        <v>-160.902025457823</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-140.1194155873088</v>
+        <v>-67.97041963415069</v>
       </c>
     </row>
     <row r="9">
@@ -2832,28 +2603,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-74.57132989689536</v>
+        <v>-9.36659363401988</v>
       </c>
       <c r="C9" t="n">
-        <v>-62.96619545193033</v>
+        <v>-11.91959050578961</v>
       </c>
       <c r="D9" t="n">
-        <v>-162.8009036358927</v>
+        <v>-93.14539986054012</v>
       </c>
       <c r="E9" t="n">
-        <v>-185.1452635177045</v>
+        <v>-92.93802899065848</v>
       </c>
       <c r="F9" t="n">
-        <v>-132.9359267176261</v>
+        <v>-115.2517761926801</v>
       </c>
       <c r="G9" t="n">
-        <v>-170.2225154493658</v>
+        <v>-72.91108639826038</v>
       </c>
       <c r="H9" t="n">
-        <v>-154.807646333482</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-134.778540143271</v>
+        <v>-65.92207926365809</v>
       </c>
     </row>
   </sheetData>
@@ -2867,7 +2635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2893,20 +2661,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>BR08</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -2919,28 +2682,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5615673356621306</v>
+        <v>0.7208430806439172</v>
       </c>
       <c r="C2" t="n">
-        <v>0.478431577769458</v>
+        <v>0.7451917529142491</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1493155558316565</v>
+        <v>0.9574990767915718</v>
       </c>
       <c r="E2" t="n">
-        <v>0.009884464697309858</v>
+        <v>0.6414302066940498</v>
       </c>
       <c r="F2" t="n">
-        <v>-62.75686302020578</v>
+        <v>0.4142515155798496</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.5169448528557667</v>
+        <v>0.540836745906047</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7617155288182211</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-8.976617781131315</v>
+        <v>0.6700087297549474</v>
       </c>
     </row>
     <row r="3">
@@ -2950,28 +2710,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06650739635891438</v>
+        <v>0.1668035412876785</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1040779154937664</v>
+        <v>0.1430680658249957</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01406025366405769</v>
+        <v>0.01055253855202177</v>
       </c>
       <c r="E3" t="n">
-        <v>0.008079267947988598</v>
+        <v>0.02252214102604668</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0975662678830177</v>
+        <v>0.06681178631217757</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01798915173946346</v>
+        <v>0.05984313190806356</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01590804894748767</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.04631261457638513</v>
+        <v>0.07826686748516394</v>
       </c>
     </row>
     <row r="4">
@@ -2981,28 +2738,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01983122734896227</v>
+        <v>0.1299934728407326</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05294638355920081</v>
+        <v>0.1012152799901041</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009758046936791555</v>
+        <v>0.0005579324909194697</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003610431441407676</v>
+        <v>0.00241117789348558</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04010357518415054</v>
+        <v>0.02489644315320886</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008435425867933757</v>
+        <v>0.01734057396682605</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0005361007114953206</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.01651395388977461</v>
+        <v>0.04606914672254612</v>
       </c>
     </row>
     <row r="5">
@@ -3012,28 +2766,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1408233906315363</v>
+        <v>0.360546075891463</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2301008117308603</v>
+        <v>0.3181434896239496</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03123787274574175</v>
+        <v>0.02362059463517948</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0190011353382046</v>
+        <v>0.04910374622659232</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2002587705548762</v>
+        <v>0.1577860676777543</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02904380461980447</v>
+        <v>0.1316836131294477</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02315384874044315</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.09623137633735238</v>
+        <v>0.1734805978640644</v>
       </c>
     </row>
     <row r="6">
@@ -3043,28 +2794,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.70215901131075</v>
+        <v>31.46654344196542</v>
       </c>
       <c r="C6" t="n">
-        <v>241.4781898325374</v>
+        <v>40.53053043016151</v>
       </c>
       <c r="D6" t="n">
-        <v>86.16216717254143</v>
+        <v>16.36674143746162</v>
       </c>
       <c r="E6" t="n">
-        <v>3375.307997445354</v>
+        <v>47.06719460515103</v>
       </c>
       <c r="F6" t="n">
-        <v>775.2386885592178</v>
+        <v>42.17704685940674</v>
       </c>
       <c r="G6" t="n">
-        <v>1834.332765914248</v>
+        <v>38.78982994156211</v>
       </c>
       <c r="H6" t="n">
-        <v>383.1469958958971</v>
-      </c>
-      <c r="I6" t="n">
-        <v>962.9098519758724</v>
+        <v>36.06631445261807</v>
       </c>
     </row>
     <row r="7">
@@ -3074,28 +2822,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1464116584456344</v>
+        <v>0.1762425067953377</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1945329951606032</v>
+        <v>0.1487931701187982</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2568883965360785</v>
+        <v>0.0146408297061721</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2982873907917056</v>
+        <v>0.110758762517225</v>
       </c>
       <c r="F7" t="n">
-        <v>38.31226281738129</v>
+        <v>0.1946520555332913</v>
       </c>
       <c r="G7" t="n">
-        <v>0.913347871334971</v>
+        <v>0.1513873780049642</v>
       </c>
       <c r="H7" t="n">
-        <v>1.059779858287026</v>
-      </c>
-      <c r="I7" t="n">
-        <v>5.883072998276758</v>
+        <v>0.132745783779298</v>
       </c>
     </row>
     <row r="8">
@@ -3105,28 +2850,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-62.64845656198297</v>
+        <v>-28.6846076579766</v>
       </c>
       <c r="C8" t="n">
-        <v>-40.07713262648676</v>
+        <v>-28.35758318222718</v>
       </c>
       <c r="D8" t="n">
-        <v>-141.5772101107297</v>
+        <v>-151.3167243252655</v>
       </c>
       <c r="E8" t="n">
-        <v>-162.4567749722606</v>
+        <v>-120.580437866327</v>
       </c>
       <c r="F8" t="n">
-        <v>-86.05611417409189</v>
+        <v>-93.71181893612213</v>
       </c>
       <c r="G8" t="n">
-        <v>-187.1033045645303</v>
+        <v>-95.36765518594697</v>
       </c>
       <c r="H8" t="n">
-        <v>-184.2797129990657</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-123.4569580013068</v>
+        <v>-86.3364711923109</v>
       </c>
     </row>
     <row r="9">
@@ -3136,28 +2878,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-60.98202987387054</v>
+        <v>-26.18496762580795</v>
       </c>
       <c r="C9" t="n">
-        <v>-38.66103222428234</v>
+        <v>-26.23343257892055</v>
       </c>
       <c r="D9" t="n">
-        <v>-139.4881652352828</v>
+        <v>-148.1831570120953</v>
       </c>
       <c r="E9" t="n">
-        <v>-160.3677300968138</v>
+        <v>-117.4468705531567</v>
       </c>
       <c r="F9" t="n">
-        <v>-83.39170515374148</v>
+        <v>-89.82430833810915</v>
       </c>
       <c r="G9" t="n">
-        <v>-184.5116308325217</v>
+        <v>-91.71102771134237</v>
       </c>
       <c r="H9" t="n">
-        <v>-181.8419613493292</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-121.3206078236917</v>
+        <v>-83.26396063657199</v>
       </c>
     </row>
   </sheetData>
@@ -3171,7 +2910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3197,20 +2936,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>BR08</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -3223,28 +2957,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.802694360350638</v>
+        <v>0.03566129260567674</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9134638654275393</v>
+        <v>0.1177427686871962</v>
       </c>
       <c r="D2" t="n">
-        <v>0.760792338287179</v>
+        <v>0.4726406901628158</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9085929099907585</v>
+        <v>-0.4360248214067879</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.919263723779467</v>
+        <v>0.7976864693130382</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.371905434952264</v>
+        <v>0.6040170158537173</v>
       </c>
       <c r="H2" t="n">
-        <v>-6.381896373751252</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-1.18393172263241</v>
+        <v>0.2652872358692761</v>
       </c>
     </row>
     <row r="3">
@@ -3254,28 +2985,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04856822190760488</v>
+        <v>0.3549020218632694</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05259129615701241</v>
+        <v>0.2571929683402966</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01070840902682608</v>
+        <v>0.07464656806897094</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003216108100639982</v>
+        <v>0.08658833812240115</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03213294952578368</v>
+        <v>0.08042799957605082</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01882445193672271</v>
+        <v>0.1099122267133724</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01359578414789312</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.02566246011464041</v>
+        <v>0.1606116871140602</v>
       </c>
     </row>
     <row r="4">
@@ -3285,28 +3013,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008924547177679236</v>
+        <v>0.4490583212412845</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008784610374243284</v>
+        <v>0.3504514226361284</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002743907692958759</v>
+        <v>0.00692292945976958</v>
       </c>
       <c r="E4" t="n">
-        <v>3.333136588307913e-05</v>
+        <v>0.009656450064989809</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002465248131221441</v>
+        <v>0.008599061627720787</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00187504893646435</v>
+        <v>0.01495453341479303</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002246355801159038</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.003514790365135186</v>
+        <v>0.1399404530741144</v>
       </c>
     </row>
     <row r="5">
@@ -3316,28 +3041,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09446982151819297</v>
+        <v>0.6701181397643885</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09372625232155228</v>
+        <v>0.5919893771311513</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01656474477001912</v>
+        <v>0.08320414328487241</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005773332303191903</v>
+        <v>0.09826723800427999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04965126515227422</v>
+        <v>0.0927311254526806</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04330183525515229</v>
+        <v>0.1222887297128931</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04739573610736559</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.05012614106110691</v>
+        <v>0.2764331255583777</v>
       </c>
     </row>
     <row r="6">
@@ -3347,28 +3069,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.64787452594123</v>
+        <v>66.30174522112979</v>
       </c>
       <c r="C6" t="n">
-        <v>152.8876987087037</v>
+        <v>56.88328764562542</v>
       </c>
       <c r="D6" t="n">
-        <v>42.27355630867075</v>
+        <v>68.87029291295899</v>
       </c>
       <c r="E6" t="n">
-        <v>52.98507327930712</v>
+        <v>129.4932491344202</v>
       </c>
       <c r="F6" t="n">
-        <v>140.5864668019217</v>
+        <v>47.09925182873661</v>
       </c>
       <c r="G6" t="n">
-        <v>602.259710225057</v>
+        <v>89.26250264091766</v>
       </c>
       <c r="H6" t="n">
-        <v>100.750206630629</v>
-      </c>
-      <c r="I6" t="n">
-        <v>161.0557980686044</v>
+        <v>76.31838823063146</v>
       </c>
     </row>
     <row r="7">
@@ -3378,28 +3097,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06693887491918407</v>
+        <v>0.6046424370871962</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03361006763370851</v>
+        <v>0.5109931652391311</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07345437205235344</v>
+        <v>0.164053843572994</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02894545895889062</v>
+        <v>0.8771339229350587</v>
       </c>
       <c r="F7" t="n">
-        <v>2.35800958165139</v>
+        <v>0.0677134023454931</v>
       </c>
       <c r="G7" t="n">
-        <v>2.028768329482409</v>
+        <v>0.13026306863424</v>
       </c>
       <c r="H7" t="n">
-        <v>4.435282722372374</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.289287058152901</v>
+        <v>0.3924666399690188</v>
       </c>
     </row>
     <row r="8">
@@ -3409,28 +3125,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-74.22214471296688</v>
+        <v>-9.610242640574057</v>
       </c>
       <c r="C8" t="n">
-        <v>-65.02130864369282</v>
+        <v>-11.72799764883035</v>
       </c>
       <c r="D8" t="n">
-        <v>-166.2201033476838</v>
+        <v>-100.4312415985111</v>
       </c>
       <c r="E8" t="n">
-        <v>-210.4892454037714</v>
+        <v>-93.44271291428034</v>
       </c>
       <c r="F8" t="n">
-        <v>-162.1529588144117</v>
+        <v>-124.4147592577548</v>
       </c>
       <c r="G8" t="n">
-        <v>-163.5362540522227</v>
+        <v>-101.0685196666308</v>
       </c>
       <c r="H8" t="n">
-        <v>-146.4611504934079</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-141.1575950668796</v>
+        <v>-73.44924562109692</v>
       </c>
     </row>
     <row r="9">
@@ -3440,28 +3153,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-71.72250468079824</v>
+        <v>-7.943815952461625</v>
       </c>
       <c r="C9" t="n">
-        <v>-62.89715804038619</v>
+        <v>-10.31189724662593</v>
       </c>
       <c r="D9" t="n">
-        <v>-163.0865360345135</v>
+        <v>-98.34219672306428</v>
       </c>
       <c r="E9" t="n">
-        <v>-207.3556780906011</v>
+        <v>-91.35366803883349</v>
       </c>
       <c r="F9" t="n">
-        <v>-158.1563452838861</v>
+        <v>-121.8230855257462</v>
       </c>
       <c r="G9" t="n">
-        <v>-159.6487434542098</v>
+        <v>-98.63076801689442</v>
       </c>
       <c r="H9" t="n">
-        <v>-142.8045230188033</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-137.9530698004569</v>
+        <v>-71.40090525060432</v>
       </c>
     </row>
   </sheetData>
@@ -3475,7 +3185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3501,20 +3211,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>BR08</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
@@ -3527,28 +3232,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8648824911921227</v>
+        <v>0.03753504332220126</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8683741961124882</v>
+        <v>0.1295677552464112</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7143281008520028</v>
+        <v>0.5831125404311054</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9110665354913818</v>
+        <v>-0.4996713329249021</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.378906954922271</v>
+        <v>0.6921118834220494</v>
       </c>
       <c r="G2" t="n">
-        <v>0.719028114035563</v>
+        <v>0.5266650493768907</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7853239729909827</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-0.07370050632110423</v>
+        <v>0.244886823145626</v>
       </c>
     </row>
     <row r="3">
@@ -3558,28 +3260,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04316534346666429</v>
+        <v>0.3572939001738104</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06009095143378623</v>
+        <v>0.2574955452571561</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009455884828957397</v>
+        <v>0.04146351600279981</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004189692401454045</v>
+        <v>0.0578257168607038</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03753162910258082</v>
+        <v>0.06699169404254424</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01031039775021643</v>
+        <v>0.07877634078574337</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005924134704830544</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.02438114766978425</v>
+        <v>0.1433077855204596</v>
       </c>
     </row>
     <row r="4">
@@ -3589,28 +3288,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006111647817210737</v>
+        <v>0.4481857820133811</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01336183327416989</v>
+        <v>0.3457542853214662</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003276890531522281</v>
+        <v>0.005472706030636007</v>
       </c>
       <c r="E4" t="n">
-        <v>3.242936455461918e-05</v>
+        <v>0.01008443665068363</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004012383334769039</v>
+        <v>0.01308636589904217</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001562428265315391</v>
+        <v>0.01787577653303351</v>
       </c>
       <c r="H4" t="n">
-        <v>6.532721596529558e-05</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.003438221840907621</v>
+        <v>0.1400765587413738</v>
       </c>
     </row>
     <row r="5">
@@ -3620,28 +3316,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07817702870543711</v>
+        <v>0.6694667893281795</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1155933963259575</v>
+        <v>0.5880087459566109</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01810218365701299</v>
+        <v>0.07397774010224972</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005694678617325054</v>
+        <v>0.1004212958026515</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06334337640802738</v>
+        <v>0.1143956550706458</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01249971305796813</v>
+        <v>0.1337003236085594</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00808252534578739</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.04307041458821652</v>
+        <v>0.2799950916448161</v>
       </c>
     </row>
     <row r="6">
@@ -3651,28 +3344,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24.87829374107193</v>
+        <v>66.83965160643319</v>
       </c>
       <c r="C6" t="n">
-        <v>187.8650179290731</v>
+        <v>57.06260404071929</v>
       </c>
       <c r="D6" t="n">
-        <v>35.48271226245993</v>
+        <v>81.02967136050982</v>
       </c>
       <c r="E6" t="n">
-        <v>946.7387074446057</v>
+        <v>158.8880484996165</v>
       </c>
       <c r="F6" t="n">
-        <v>228.4753036946091</v>
+        <v>54.54346519536675</v>
       </c>
       <c r="G6" t="n">
-        <v>564.3769620519033</v>
+        <v>90.61858185435658</v>
       </c>
       <c r="H6" t="n">
-        <v>58.80254331132912</v>
-      </c>
-      <c r="I6" t="n">
-        <v>292.3742200621503</v>
+        <v>84.8303370928337</v>
       </c>
     </row>
     <row r="7">
@@ -3682,28 +3372,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04681340611441072</v>
+        <v>0.6029695344127064</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05084102445817246</v>
+        <v>0.503657673151103</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08793095208160573</v>
+        <v>0.1293971320921136</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02870273990777369</v>
+        <v>0.9149210110658984</v>
       </c>
       <c r="F7" t="n">
-        <v>3.836961509622039</v>
+        <v>0.1020268911027147</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0864009357679032</v>
+        <v>0.1550135287600563</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06644853715388092</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.6005855864436836</v>
+        <v>0.4013309617640988</v>
       </c>
     </row>
     <row r="8">
@@ -3713,28 +3400,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-78.6585004552319</v>
+        <v>-11.6433064890773</v>
       </c>
       <c r="C8" t="n">
-        <v>-56.7302934875064</v>
+        <v>-13.93040371354777</v>
       </c>
       <c r="D8" t="n">
-        <v>-160.4923535660427</v>
+        <v>-107.3676236992888</v>
       </c>
       <c r="E8" t="n">
-        <v>-209.0653708763226</v>
+        <v>-94.53200135439299</v>
       </c>
       <c r="F8" t="n">
-        <v>-146.5143562590788</v>
+        <v>-115.0769777691077</v>
       </c>
       <c r="G8" t="n">
-        <v>-228.6306778761951</v>
+        <v>-98.60771872345478</v>
       </c>
       <c r="H8" t="n">
-        <v>-232.9025456242495</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-158.9991568778039</v>
+        <v>-73.52633862481154</v>
       </c>
     </row>
     <row r="9">
@@ -3744,28 +3428,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-75.32564707900704</v>
+        <v>-10.81009314502108</v>
       </c>
       <c r="C9" t="n">
-        <v>-53.89809268309756</v>
+        <v>-13.22235351244556</v>
       </c>
       <c r="D9" t="n">
-        <v>-156.314263815149</v>
+        <v>-106.3231012615653</v>
       </c>
       <c r="E9" t="n">
-        <v>-204.8872811254289</v>
+        <v>-93.48747891666956</v>
       </c>
       <c r="F9" t="n">
-        <v>-141.185538218378</v>
+        <v>-113.7811409031033</v>
       </c>
       <c r="G9" t="n">
-        <v>-223.4473304121778</v>
+        <v>-97.38884289858657</v>
       </c>
       <c r="H9" t="n">
-        <v>-228.0270423247767</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-154.7264565225736</v>
+        <v>-72.50216843956524</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/global/metrics_summary.xlsx
+++ b/results/cross_validation/global/metrics_summary.xlsx
@@ -482,25 +482,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0825092347399351</v>
+        <v>0.7731888835334902</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1872706478009866</v>
+        <v>0.8725112218547966</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02835321196247464</v>
+        <v>0.9831207109723542</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.003189247922549</v>
+        <v>0.9027960099415565</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7221030667091743</v>
+        <v>0.8957367555224912</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2854268381889515</v>
+        <v>0.8870421897632809</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1162543747535044</v>
+        <v>0.885732628597995</v>
       </c>
     </row>
     <row r="3">
@@ -510,25 +510,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3442930559361242</v>
+        <v>0.137344214703369</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2380562389141897</v>
+        <v>0.1014033310516529</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0540651357895153</v>
+        <v>0.005609288257706873</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07398903536396195</v>
+        <v>0.01296072863041777</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04901910952875807</v>
+        <v>0.03377388732444474</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1064915946142664</v>
+        <v>0.0361330391110217</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1443190283578026</v>
+        <v>0.0545374148464355</v>
       </c>
     </row>
     <row r="4">
@@ -538,25 +538,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.427242896757015</v>
+        <v>0.1056178896671258</v>
       </c>
       <c r="C4" t="n">
-        <v>0.322833463515472</v>
+        <v>0.05064126661183183</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01275533028035903</v>
+        <v>0.0002215835106912817</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02019473937774187</v>
+        <v>0.0006536415402608362</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01181163141885905</v>
+        <v>0.004431567486978748</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02698628136422652</v>
+        <v>0.004265919030053162</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1369707237856122</v>
+        <v>0.02763864464115695</v>
       </c>
     </row>
     <row r="5">
@@ -566,25 +566,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6536382001971848</v>
+        <v>0.3249890608422471</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5681843569788524</v>
+        <v>0.2250361451230265</v>
       </c>
       <c r="D5" t="n">
-        <v>0.112939498318166</v>
+        <v>0.01488568139828613</v>
       </c>
       <c r="E5" t="n">
-        <v>0.142108196025922</v>
+        <v>0.02556641430198682</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1086813296700912</v>
+        <v>0.06657001943051202</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1642750174683495</v>
+        <v>0.06531400332281863</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2916377664430943</v>
+        <v>0.1203935540698129</v>
       </c>
     </row>
     <row r="6">
@@ -594,25 +594,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>67.46807256860427</v>
+        <v>27.93408076496081</v>
       </c>
       <c r="C6" t="n">
-        <v>55.46298446486946</v>
+        <v>29.80296874871599</v>
       </c>
       <c r="D6" t="n">
-        <v>123.6023338993809</v>
+        <v>8.764258404308217</v>
       </c>
       <c r="E6" t="n">
-        <v>220.3292345747089</v>
+        <v>31.57536297007722</v>
       </c>
       <c r="F6" t="n">
-        <v>65.90873036030047</v>
+        <v>19.76093796416055</v>
       </c>
       <c r="G6" t="n">
-        <v>128.8870861221701</v>
+        <v>26.95523531728998</v>
       </c>
       <c r="H6" t="n">
-        <v>110.276406998339</v>
+        <v>24.13214069491879</v>
       </c>
     </row>
     <row r="7">
@@ -622,25 +622,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.57481725730793</v>
+        <v>0.142975857706941</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4703022301205345</v>
+        <v>0.07469552007184332</v>
       </c>
       <c r="D7" t="n">
-        <v>0.300922767607509</v>
+        <v>0.006218895165777636</v>
       </c>
       <c r="E7" t="n">
-        <v>1.831186183882368</v>
+        <v>0.03061874609571564</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09213722198044905</v>
+        <v>0.03538107058413777</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2337623454982731</v>
+        <v>0.03787348639205296</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5838546677328439</v>
+        <v>0.05462726266941139</v>
       </c>
     </row>
     <row r="8">
@@ -650,25 +650,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-12.45684390454371</v>
+        <v>-34.21476770963743</v>
       </c>
       <c r="C8" t="n">
-        <v>-14.95928022331789</v>
+        <v>-40.74482734065539</v>
       </c>
       <c r="D8" t="n">
-        <v>-89.59792670426252</v>
+        <v>-172.7089313380501</v>
       </c>
       <c r="E8" t="n">
-        <v>-79.94899584206439</v>
+        <v>-149.9919806672965</v>
       </c>
       <c r="F8" t="n">
-        <v>-117.8441040276985</v>
+        <v>-142.3130519203876</v>
       </c>
       <c r="G8" t="n">
-        <v>-88.31066599310962</v>
+        <v>-132.4274409852517</v>
       </c>
       <c r="H8" t="n">
-        <v>-67.18630278249942</v>
+        <v>-112.0668333268798</v>
       </c>
     </row>
     <row r="9">
@@ -678,25 +678,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-11.62363056048749</v>
+        <v>-32.548341021525</v>
       </c>
       <c r="C9" t="n">
-        <v>-14.25123002221568</v>
+        <v>-39.32872693845097</v>
       </c>
       <c r="D9" t="n">
-        <v>-88.55340426653909</v>
+        <v>-170.6198864626032</v>
       </c>
       <c r="E9" t="n">
-        <v>-78.90447340434096</v>
+        <v>-147.9029357918496</v>
       </c>
       <c r="F9" t="n">
-        <v>-116.5482671616942</v>
+        <v>-139.7213781883789</v>
       </c>
       <c r="G9" t="n">
-        <v>-87.09179016824142</v>
+        <v>-129.9896893355153</v>
       </c>
       <c r="H9" t="n">
-        <v>-66.16213259725313</v>
+        <v>-110.0184929563872</v>
       </c>
     </row>
   </sheetData>
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02982192883159562</v>
+        <v>0.6121564601983727</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1262732500340942</v>
+        <v>0.8698955032248902</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5831114630800008</v>
+        <v>0.977451133537302</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4996756132836739</v>
+        <v>0.9461970375981978</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6851975247036717</v>
+        <v>0.9214353229687969</v>
       </c>
       <c r="G2" t="n">
-        <v>0.529213937264728</v>
+        <v>0.8987935181479894</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2423237484384027</v>
+        <v>0.8709881626125915</v>
       </c>
     </row>
     <row r="3">
@@ -785,25 +785,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3590593948517548</v>
+        <v>0.1689854375460691</v>
       </c>
       <c r="C3" t="n">
-        <v>0.258228940889981</v>
+        <v>0.1113839974738382</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0414634281194974</v>
+        <v>0.01300915847487365</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05782565576405917</v>
+        <v>0.01274105594382345</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06806397452572623</v>
+        <v>0.0373319157115065</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07825746439318118</v>
+        <v>0.02666956452588106</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1438164764240333</v>
+        <v>0.06168685494599866</v>
       </c>
     </row>
     <row r="4">
@@ -813,25 +813,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4517775057699148</v>
+        <v>0.1806049757747402</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3470629331823861</v>
+        <v>0.05168028593922516</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005472720173603735</v>
+        <v>0.0002960111047763965</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01008446543366156</v>
+        <v>0.0003617943172267443</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01338025131804312</v>
+        <v>0.003339284808382977</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01777951626273072</v>
+        <v>0.003822123109437519</v>
       </c>
       <c r="H4" t="n">
-        <v>0.14092623202339</v>
+        <v>0.04001741250896484</v>
       </c>
     </row>
     <row r="5">
@@ -841,25 +841,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6721439620869288</v>
+        <v>0.4249764414349814</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5891204742515627</v>
+        <v>0.2273329847145485</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0739778356915349</v>
+        <v>0.01720497325706717</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1004214391136751</v>
+        <v>0.0190208915991534</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1156730362618839</v>
+        <v>0.05778654521930669</v>
       </c>
       <c r="G5" t="n">
-        <v>0.133339852492534</v>
+        <v>0.06182332172762572</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2807794333163532</v>
+        <v>0.1346908596587805</v>
       </c>
     </row>
     <row r="6">
@@ -869,25 +869,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>67.00339197319198</v>
+        <v>26.86905887367338</v>
       </c>
       <c r="C6" t="n">
-        <v>57.15009278502276</v>
+        <v>29.72821302799129</v>
       </c>
       <c r="D6" t="n">
-        <v>81.02980515645326</v>
+        <v>10.63193795583293</v>
       </c>
       <c r="E6" t="n">
-        <v>158.8882847090654</v>
+        <v>14.8265130339079</v>
       </c>
       <c r="F6" t="n">
-        <v>54.53338112122095</v>
+        <v>21.61918230398741</v>
       </c>
       <c r="G6" t="n">
-        <v>89.93328471230232</v>
+        <v>14.44268565383375</v>
       </c>
       <c r="H6" t="n">
-        <v>84.75637340954279</v>
+        <v>19.68626514153778</v>
       </c>
     </row>
     <row r="7">
@@ -897,25 +897,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6077976753894616</v>
+        <v>0.2462765449828064</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5055620782174419</v>
+        <v>0.07870754918999057</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1293974651975224</v>
+        <v>0.01047186771215289</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9149236195773307</v>
+        <v>0.01989414474259937</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1043069185115287</v>
+        <v>0.029406902475229</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1541814802044931</v>
+        <v>0.03653743073220946</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4026948728496297</v>
+        <v>0.07021573997249794</v>
       </c>
     </row>
     <row r="8">
@@ -925,25 +925,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-11.50761289163056</v>
+        <v>-15.09453247940176</v>
       </c>
       <c r="C8" t="n">
-        <v>-13.87373727762511</v>
+        <v>-30.4401832996503</v>
       </c>
       <c r="D8" t="n">
-        <v>-107.3675694296209</v>
+        <v>-156.6273853523565</v>
       </c>
       <c r="E8" t="n">
-        <v>-94.53194141632258</v>
+        <v>-152.4131285335323</v>
       </c>
       <c r="F8" t="n">
-        <v>-114.4773369163451</v>
+        <v>-139.9539628520262</v>
       </c>
       <c r="G8" t="n">
-        <v>-98.74270640217588</v>
+        <v>-125.1737305736407</v>
       </c>
       <c r="H8" t="n">
-        <v>-73.41681738895336</v>
+        <v>-103.2838205151013</v>
       </c>
     </row>
     <row r="9">
@@ -953,25 +953,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-10.67439954757435</v>
+        <v>-9.262039071008246</v>
       </c>
       <c r="C9" t="n">
-        <v>-13.1656870765229</v>
+        <v>-25.48383189193483</v>
       </c>
       <c r="D9" t="n">
-        <v>-106.3230469918975</v>
+        <v>-149.3157282882925</v>
       </c>
       <c r="E9" t="n">
-        <v>-93.48741897859915</v>
+        <v>-145.1014714694684</v>
       </c>
       <c r="F9" t="n">
-        <v>-113.1815000503408</v>
+        <v>-130.8831047899959</v>
       </c>
       <c r="G9" t="n">
-        <v>-97.52383057730768</v>
+        <v>-116.6415997995633</v>
       </c>
       <c r="H9" t="n">
-        <v>-72.39264720370706</v>
+        <v>-96.11462921837717</v>
       </c>
     </row>
   </sheetData>
@@ -1032,25 +1032,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3947916513362169</v>
+        <v>0.9322547539081764</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4294858041924047</v>
+        <v>0.8707490903463868</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9596972206746003</v>
+        <v>0.886701103291085</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5378953851523645</v>
+        <v>0.875492042273109</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4026005132566493</v>
+        <v>0.9169156346243755</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.42178167175561</v>
+        <v>0.873101387393599</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08291464605722114</v>
+        <v>0.8925356686394553</v>
       </c>
     </row>
     <row r="3">
@@ -1060,25 +1060,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.21135891101743</v>
+        <v>0.08057855596760877</v>
       </c>
       <c r="C3" t="n">
-        <v>0.188813969529444</v>
+        <v>0.1018966926052491</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01126033176123501</v>
+        <v>0.01806707805812173</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02602605558989148</v>
+        <v>0.01358435692549985</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1296895473442054</v>
+        <v>0.03421539133747273</v>
       </c>
       <c r="G3" t="n">
-        <v>0.188814821743617</v>
+        <v>0.04145526427771951</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1259939394976371</v>
+        <v>0.04829955652861195</v>
       </c>
     </row>
     <row r="4">
@@ -1088,25 +1088,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2818240551460501</v>
+        <v>0.03154655749977325</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2266204282138559</v>
+        <v>0.05134122289677524</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0005290762732311373</v>
+        <v>0.001487335589140733</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003107390674282427</v>
+        <v>0.0008372451914206881</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0596156283349565</v>
+        <v>0.003531388018088249</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09146002829309348</v>
+        <v>0.004792401740707764</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1105261011559116</v>
+        <v>0.01558935848931765</v>
       </c>
     </row>
     <row r="5">
@@ -1116,25 +1116,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5308710343822218</v>
+        <v>0.1776135059610424</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4760466660043487</v>
+        <v>0.2265860165517176</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0230016580539564</v>
+        <v>0.03856599005783117</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05574397433160311</v>
+        <v>0.02893518950034176</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2441631182938089</v>
+        <v>0.05942548290159912</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3024235908342692</v>
+        <v>0.06922717487163378</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2720416736500347</v>
+        <v>0.100058893307361</v>
       </c>
     </row>
     <row r="6">
@@ -1144,25 +1144,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.46977918139396</v>
+        <v>20.498398824979</v>
       </c>
       <c r="C6" t="n">
-        <v>44.13767244721497</v>
+        <v>24.00269452055293</v>
       </c>
       <c r="D6" t="n">
-        <v>17.65810054282666</v>
+        <v>30.40051159010692</v>
       </c>
       <c r="E6" t="n">
-        <v>54.77410411814857</v>
+        <v>26.54890738708907</v>
       </c>
       <c r="F6" t="n">
-        <v>69.63174783847005</v>
+        <v>20.25531126558197</v>
       </c>
       <c r="G6" t="n">
-        <v>117.0903816409419</v>
+        <v>29.37057757740349</v>
       </c>
       <c r="H6" t="n">
-        <v>55.79363096149935</v>
+        <v>25.17940019428556</v>
       </c>
     </row>
     <row r="7">
@@ -1172,25 +1172,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.37983934320137</v>
+        <v>0.04590616407738837</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3307885584919777</v>
+        <v>0.07821412892382662</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01346118718888171</v>
+        <v>0.03853080392507303</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1418065579262884</v>
+        <v>0.04143845895206181</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9270221876229288</v>
+        <v>0.03089728122534912</v>
       </c>
       <c r="G7" t="n">
-        <v>1.583113042663697</v>
+        <v>0.04492426500041575</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5626718128491907</v>
+        <v>0.04665185035068578</v>
       </c>
     </row>
     <row r="8">
@@ -1200,25 +1200,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-17.53002945162144</v>
+        <v>-44.75694374407698</v>
       </c>
       <c r="C8" t="n">
-        <v>-18.26718175195546</v>
+        <v>-30.53891926377734</v>
       </c>
       <c r="D8" t="n">
-        <v>-154.4319370066515</v>
+        <v>-122.7261480542008</v>
       </c>
       <c r="E8" t="n">
-        <v>-117.2534102453004</v>
+        <v>-134.7932653817703</v>
       </c>
       <c r="F8" t="n">
-        <v>-72.13561301028416</v>
+        <v>-138.4437355347539</v>
       </c>
       <c r="G8" t="n">
-        <v>-55.79633128507261</v>
+        <v>-119.518089649401</v>
       </c>
       <c r="H8" t="n">
-        <v>-72.56908379181425</v>
+        <v>-98.46285027133007</v>
       </c>
     </row>
     <row r="9">
@@ -1228,25 +1228,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-15.86360276350901</v>
+        <v>-38.92445033568347</v>
       </c>
       <c r="C9" t="n">
-        <v>-16.85108134975103</v>
+        <v>-25.58256785606187</v>
       </c>
       <c r="D9" t="n">
-        <v>-152.3428921312046</v>
+        <v>-115.4144909901369</v>
       </c>
       <c r="E9" t="n">
-        <v>-115.1643653698535</v>
+        <v>-127.4816083177063</v>
       </c>
       <c r="F9" t="n">
-        <v>-69.5439392782755</v>
+        <v>-129.3728774727236</v>
       </c>
       <c r="G9" t="n">
-        <v>-53.35857963533621</v>
+        <v>-110.9859588753236</v>
       </c>
       <c r="H9" t="n">
-        <v>-70.52074342132164</v>
+        <v>-91.29365897460595</v>
       </c>
     </row>
   </sheetData>
@@ -1307,25 +1307,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2205362040973438</v>
+        <v>0.8960692204861581</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2145633888012737</v>
+        <v>0.7335908679028591</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7035702359827276</v>
+        <v>0.9444042366793606</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7781476182107407</v>
+        <v>0.4418566954778872</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7296145987227001</v>
+        <v>0.7381738461561784</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.952238619149356</v>
+        <v>0.4269911398723414</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.05096776222242842</v>
+        <v>0.6968476677624641</v>
       </c>
     </row>
     <row r="3">
@@ -1335,25 +1335,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3196436151710166</v>
+        <v>0.1494843116063806</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2438248456595596</v>
+        <v>0.1281726514469019</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04393473724802701</v>
+        <v>0.01391987074565544</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03235589527318093</v>
+        <v>0.03002118295049415</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06380581215352039</v>
+        <v>0.06666962778779177</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2754541262253822</v>
+        <v>0.07693044199786293</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1631698386217811</v>
+        <v>0.07753301442251447</v>
       </c>
     </row>
     <row r="4">
@@ -1363,25 +1363,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3629686343320024</v>
+        <v>0.04839687654962076</v>
       </c>
       <c r="C4" t="n">
-        <v>0.311992203651886</v>
+        <v>0.1058233993818038</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003891393036564196</v>
+        <v>0.0007298355040885887</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001491831070474358</v>
+        <v>0.003753196232322942</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01149236396065405</v>
+        <v>0.01112856478262836</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1492586471126511</v>
+        <v>0.02164002113430707</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1401825121940387</v>
+        <v>0.03191198226412859</v>
       </c>
     </row>
     <row r="5">
@@ -1391,25 +1391,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.602468782869289</v>
+        <v>0.2199929011346065</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5585626228561001</v>
+        <v>0.3253050866214727</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06238103106365105</v>
+        <v>0.02701546786729019</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03862422905993539</v>
+        <v>0.06126333513875116</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1072024438184785</v>
+        <v>0.1054920128854709</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3863400666675036</v>
+        <v>0.1471054762213395</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2925965293891596</v>
+        <v>0.1476957133114885</v>
       </c>
     </row>
     <row r="6">
@@ -1419,25 +1419,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>73.05927900187694</v>
+        <v>66.31057875340855</v>
       </c>
       <c r="C6" t="n">
-        <v>54.65202981850885</v>
+        <v>27.42718140943695</v>
       </c>
       <c r="D6" t="n">
-        <v>63.76425094492009</v>
+        <v>21.89216716569163</v>
       </c>
       <c r="E6" t="n">
-        <v>47.5362339042551</v>
+        <v>70.81136374929459</v>
       </c>
       <c r="F6" t="n">
-        <v>54.56101835681456</v>
+        <v>39.9373724820466</v>
       </c>
       <c r="G6" t="n">
-        <v>300.7180343399298</v>
+        <v>40.45205589056192</v>
       </c>
       <c r="H6" t="n">
-        <v>99.04847439438423</v>
+        <v>44.47178657507337</v>
       </c>
     </row>
     <row r="7">
@@ -1447,25 +1447,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4889171828031986</v>
+        <v>0.0670570474388871</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4550255259159381</v>
+        <v>0.155999119196405</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09265290433077668</v>
+        <v>0.01918961384905384</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06859999628610984</v>
+        <v>0.1720702287192599</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09016027515564783</v>
+        <v>0.08833784150098634</v>
       </c>
       <c r="G7" t="n">
-        <v>2.582305277447325</v>
+        <v>0.1890506728323126</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6296101936564994</v>
+        <v>0.1152840872561508</v>
       </c>
     </row>
     <row r="8">
@@ -1475,25 +1475,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-13.22846053924082</v>
+        <v>-43.48144002449207</v>
       </c>
       <c r="C8" t="n">
-        <v>-13.47165619670157</v>
+        <v>-25.68975426747927</v>
       </c>
       <c r="D8" t="n">
-        <v>-112.5287496457891</v>
+        <v>-143.676519107658</v>
       </c>
       <c r="E8" t="n">
-        <v>-132.6627711502233</v>
+        <v>-109.2880969415289</v>
       </c>
       <c r="F8" t="n">
-        <v>-116.5839566247201</v>
+        <v>-113.4524819536485</v>
       </c>
       <c r="G8" t="n">
-        <v>-43.55186478211312</v>
+        <v>-87.83027120931919</v>
       </c>
       <c r="H8" t="n">
-        <v>-72.004576489798</v>
+        <v>-87.23642725068765</v>
       </c>
     </row>
     <row r="9">
@@ -1503,25 +1503,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-11.56203385112839</v>
+        <v>-40.14858664826721</v>
       </c>
       <c r="C9" t="n">
-        <v>-12.05555579449715</v>
+        <v>-22.85755346307043</v>
       </c>
       <c r="D9" t="n">
-        <v>-110.4397047703422</v>
+        <v>-139.4984293567643</v>
       </c>
       <c r="E9" t="n">
-        <v>-130.5737262747765</v>
+        <v>-105.1100071906353</v>
       </c>
       <c r="F9" t="n">
-        <v>-113.9922828927115</v>
+        <v>-108.2691344896311</v>
       </c>
       <c r="G9" t="n">
-        <v>-41.11411313237672</v>
+        <v>-82.9547679098464</v>
       </c>
       <c r="H9" t="n">
-        <v>-69.9562361193054</v>
+        <v>-83.13974650970245</v>
       </c>
     </row>
   </sheetData>
@@ -1582,25 +1582,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2323551186531873</v>
+        <v>0.3649808836908726</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1882398305424486</v>
+        <v>0.006842187883637441</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7475999573993114</v>
+        <v>0.7361808303316463</v>
       </c>
       <c r="E2" t="n">
-        <v>0.302953435641652</v>
+        <v>0.8355718671592859</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5139247423039637</v>
+        <v>0.8898722665862924</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.343744077285102</v>
+        <v>-0.8353534731670564</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2264451654574231</v>
+        <v>0.333015760414113</v>
       </c>
     </row>
     <row r="3">
@@ -1610,25 +1610,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3139842509732681</v>
+        <v>0.2919943856347123</v>
       </c>
       <c r="C3" t="n">
-        <v>0.237857126642708</v>
+        <v>0.2965741852309667</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02329914952902029</v>
+        <v>0.02306048540544114</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03245045129203557</v>
+        <v>0.01511410032868808</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08378279064873546</v>
+        <v>0.05952263207637042</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2879326488468568</v>
+        <v>0.185429179009242</v>
       </c>
       <c r="H3" t="n">
-        <v>0.163217736322104</v>
+        <v>0.1452824946142368</v>
       </c>
     </row>
     <row r="4">
@@ -1638,25 +1638,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3574649851591076</v>
+        <v>0.2957058719507534</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3224484834229492</v>
+        <v>0.3945035028394818</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003313391188840255</v>
+        <v>0.003463296215085071</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004687241641899433</v>
+        <v>0.00110568566112973</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02065996813186874</v>
+        <v>0.004680829617920888</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1640440840889077</v>
+        <v>0.0693132178434563</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1454363589389288</v>
+        <v>0.1281287340213046</v>
       </c>
     </row>
     <row r="5">
@@ -1666,25 +1666,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.597883755557138</v>
+        <v>0.5437884441129228</v>
       </c>
       <c r="C5" t="n">
-        <v>0.567845474951548</v>
+        <v>0.6280951383663799</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0575620637993484</v>
+        <v>0.05884977667829395</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06846343288135232</v>
+        <v>0.03325185199548635</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1437357580140333</v>
+        <v>0.06841658876267427</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4050235599183184</v>
+        <v>0.2632740356424391</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3067523408536231</v>
+        <v>0.2659459725930327</v>
       </c>
     </row>
     <row r="6">
@@ -1694,25 +1694,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>73.60957050946612</v>
+        <v>57.64472177160614</v>
       </c>
       <c r="C6" t="n">
-        <v>55.47245781752397</v>
+        <v>76.640841679392</v>
       </c>
       <c r="D6" t="n">
-        <v>36.18589442622444</v>
+        <v>28.74932697048213</v>
       </c>
       <c r="E6" t="n">
-        <v>59.38998620943401</v>
+        <v>34.21747731001079</v>
       </c>
       <c r="F6" t="n">
-        <v>56.86102952222636</v>
+        <v>35.898122408214</v>
       </c>
       <c r="G6" t="n">
-        <v>314.0998173725787</v>
+        <v>142.6644679421298</v>
       </c>
       <c r="H6" t="n">
-        <v>99.26979264290894</v>
+        <v>62.63582634697247</v>
       </c>
     </row>
     <row r="7">
@@ -1722,25 +1722,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4815189540154192</v>
+        <v>0.4014998452582656</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4702419892333298</v>
+        <v>0.5780997956225461</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07903938661239478</v>
+        <v>0.08557005825106569</v>
       </c>
       <c r="E7" t="n">
-        <v>0.213395038456834</v>
+        <v>0.05410241981500505</v>
       </c>
       <c r="F7" t="n">
-        <v>0.161284555001119</v>
+        <v>0.04031490075665692</v>
       </c>
       <c r="G7" t="n">
-        <v>2.837908164095532</v>
+        <v>1.206250588881073</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7072313479024381</v>
+        <v>0.3943062680974354</v>
       </c>
     </row>
     <row r="8">
@@ -1750,25 +1750,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-13.48820370934777</v>
+        <v>-4.712629906895394</v>
       </c>
       <c r="C8" t="n">
-        <v>-12.97717845245754</v>
+        <v>2.048091106778578</v>
       </c>
       <c r="D8" t="n">
-        <v>-115.9054447999859</v>
+        <v>-102.9762240818653</v>
       </c>
       <c r="E8" t="n">
-        <v>-108.6211311175866</v>
+        <v>-126.9530822013997</v>
       </c>
       <c r="F8" t="n">
-        <v>-100.7480486604857</v>
+        <v>-128.8355577313607</v>
       </c>
       <c r="G8" t="n">
-        <v>-41.19050204648685</v>
+        <v>-50.72799143254564</v>
       </c>
       <c r="H8" t="n">
-        <v>-65.4884181310584</v>
+        <v>-68.69289904121469</v>
       </c>
     </row>
     <row r="9">
@@ -1778,25 +1778,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-11.82177702123534</v>
+        <v>1.953076845554335</v>
       </c>
       <c r="C9" t="n">
-        <v>-11.56107805025312</v>
+        <v>7.712492715596259</v>
       </c>
       <c r="D9" t="n">
-        <v>-113.816399924539</v>
+        <v>-94.6200445800779</v>
       </c>
       <c r="E9" t="n">
-        <v>-106.5320862421397</v>
+        <v>-118.5969026996123</v>
       </c>
       <c r="F9" t="n">
-        <v>-98.15637492847706</v>
+        <v>-118.4688628033261</v>
       </c>
       <c r="G9" t="n">
-        <v>-38.75275039675045</v>
+        <v>-40.97698483360003</v>
       </c>
       <c r="H9" t="n">
-        <v>-63.44007776056579</v>
+        <v>-60.49953755924429</v>
       </c>
     </row>
   </sheetData>
@@ -1857,25 +1857,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1205647447782366</v>
+        <v>0.7742858394957591</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2091067165166794</v>
+        <v>0.8522812276291934</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2775828190881146</v>
+        <v>0.9837499537097349</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4551939676037569</v>
+        <v>0.9257703957739791</v>
       </c>
       <c r="F2" t="n">
-        <v>0.73669320965941</v>
+        <v>0.9036491499330408</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1062133804332686</v>
+        <v>0.8894622404613096</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1304233570009025</v>
+        <v>0.8881998011671696</v>
       </c>
     </row>
     <row r="3">
@@ -1885,25 +1885,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3389867915160705</v>
+        <v>0.1371235456025501</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2422288714214376</v>
+        <v>0.1119640387571579</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05732603815164675</v>
+        <v>0.009921641426106284</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05931413906731789</v>
+        <v>0.01482341117047158</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05488653472768618</v>
+        <v>0.03449732074526119</v>
       </c>
       <c r="G3" t="n">
-        <v>0.152499626772279</v>
+        <v>0.03336345081789293</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1508736669427397</v>
+        <v>0.05694890141990666</v>
       </c>
     </row>
     <row r="4">
@@ -1913,25 +1913,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4095217959438411</v>
+        <v>0.1051070761955572</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3141597104709002</v>
+        <v>0.05867705255346009</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009483559104176345</v>
+        <v>0.000213323102649364</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009785351669112628</v>
+        <v>0.0004991518641372274</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01119149722437228</v>
+        <v>0.004095261917459395</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04177680765057633</v>
+        <v>0.004174524373014577</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1326531203438298</v>
+        <v>0.02879439833437964</v>
       </c>
     </row>
     <row r="5">
@@ -1941,25 +1941,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6399389001645713</v>
+        <v>0.324202214976328</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5604995187071085</v>
+        <v>0.242233467038434</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09738356691031781</v>
+        <v>0.01460558463908118</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09892093645489122</v>
+        <v>0.0223417068313329</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1057898729764446</v>
+        <v>0.06399423347036352</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2043937563884385</v>
+        <v>0.06461055929965764</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2844877586002953</v>
+        <v>0.1219979610425328</v>
       </c>
     </row>
     <row r="6">
@@ -1969,25 +1969,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68.90384842029944</v>
+        <v>27.9240205646043</v>
       </c>
       <c r="C6" t="n">
-        <v>54.8103536147401</v>
+        <v>31.31328864700969</v>
       </c>
       <c r="D6" t="n">
-        <v>104.8714288597183</v>
+        <v>9.305540586436976</v>
       </c>
       <c r="E6" t="n">
-        <v>156.2150483312212</v>
+        <v>27.20068142963095</v>
       </c>
       <c r="F6" t="n">
-        <v>60.61739490320169</v>
+        <v>16.92878018429704</v>
       </c>
       <c r="G6" t="n">
-        <v>165.2628234037178</v>
+        <v>22.79676209996704</v>
       </c>
       <c r="H6" t="n">
-        <v>101.7801495888164</v>
+        <v>22.57817891865767</v>
       </c>
     </row>
     <row r="7">
@@ -1997,25 +1997,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5514958337272179</v>
+        <v>0.1422892014881623</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4581797823746263</v>
+        <v>0.08638956849866403</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2243636456464891</v>
+        <v>0.006024340058934072</v>
       </c>
       <c r="E7" t="n">
-        <v>0.888815872899012</v>
+        <v>0.02361828757270232</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08782608515923762</v>
+        <v>0.03277193836230934</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7242155589707682</v>
+        <v>0.03708349492271733</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4891494631295585</v>
+        <v>0.05469613848391491</v>
       </c>
     </row>
     <row r="8">
@@ -2025,25 +2025,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-11.17700757307524</v>
+        <v>-34.29718647753548</v>
       </c>
       <c r="C8" t="n">
-        <v>-13.367806854656</v>
+        <v>-38.53559834178781</v>
       </c>
       <c r="D8" t="n">
-        <v>-93.82210760509294</v>
+        <v>-173.506755182954</v>
       </c>
       <c r="E8" t="n">
-        <v>-93.16424352250634</v>
+        <v>-155.6546036028755</v>
       </c>
       <c r="F8" t="n">
-        <v>-117.3002260657123</v>
+        <v>-144.4439642922032</v>
       </c>
       <c r="G8" t="n">
-        <v>-75.38534835819746</v>
+        <v>-132.9688712450058</v>
       </c>
       <c r="H8" t="n">
-        <v>-67.36945666320672</v>
+        <v>-113.234496523727</v>
       </c>
     </row>
     <row r="9">
@@ -2053,25 +2053,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-9.510580884962806</v>
+        <v>-32.63075978942305</v>
       </c>
       <c r="C9" t="n">
-        <v>-11.95170645245158</v>
+        <v>-37.11949793958339</v>
       </c>
       <c r="D9" t="n">
-        <v>-91.73306272964609</v>
+        <v>-171.4177103075071</v>
       </c>
       <c r="E9" t="n">
-        <v>-91.07519864705949</v>
+        <v>-153.5655587274286</v>
       </c>
       <c r="F9" t="n">
-        <v>-114.7085523337037</v>
+        <v>-141.8522905601945</v>
       </c>
       <c r="G9" t="n">
-        <v>-72.94759670846106</v>
+        <v>-130.5311195952694</v>
       </c>
       <c r="H9" t="n">
-        <v>-65.32111629271411</v>
+        <v>-111.1861561532344</v>
       </c>
     </row>
   </sheetData>
@@ -2132,25 +2132,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1083765126294903</v>
+        <v>0.7388049093520619</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1767459016268772</v>
+        <v>0.8577708012712317</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5315434881965275</v>
+        <v>0.9499652573049657</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0376920034428232</v>
+        <v>0.7365243664140038</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7498584731270099</v>
+        <v>0.9053226462049749</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.03112210491011069</v>
+        <v>0.8715637705300524</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2621823790187696</v>
+        <v>0.8433252918462152</v>
       </c>
     </row>
     <row r="3">
@@ -2160,25 +2160,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3378416617405293</v>
+        <v>0.1439453803047641</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2433986875352218</v>
+        <v>0.1072821667145773</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0396206028673055</v>
+        <v>0.01683692430117755</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04479781753338839</v>
+        <v>0.02901271390053664</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04982246253450821</v>
+        <v>0.03400282181403558</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1451831370025418</v>
+        <v>0.04258782996654237</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1434440615355825</v>
+        <v>0.0622779728336056</v>
       </c>
     </row>
     <row r="4">
@@ -2188,25 +2188,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4151974232163416</v>
+        <v>0.121629286498055</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3270141175681596</v>
+        <v>0.05649647661229673</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00614968073131471</v>
+        <v>0.0006568329936611648</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006470973883857715</v>
+        <v>0.001771723762108989</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0106319255955313</v>
+        <v>0.004024132233116191</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0389409408736452</v>
+        <v>0.004850470758028374</v>
       </c>
       <c r="H4" t="n">
-        <v>0.134067510311475</v>
+        <v>0.03157148714287775</v>
       </c>
     </row>
     <row r="5">
@@ -2216,25 +2216,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6443581482501339</v>
+        <v>0.3487539053516893</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5718514820896765</v>
+        <v>0.2376898748628067</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07841990009758179</v>
+        <v>0.02562875325998448</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08044236373862788</v>
+        <v>0.04209184911724584</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1031112292407151</v>
+        <v>0.06343604837248448</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1973345911735832</v>
+        <v>0.0696453211495817</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2792529524317197</v>
+        <v>0.1312076253522987</v>
       </c>
     </row>
     <row r="6">
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68.30587006069726</v>
+        <v>22.40264952955293</v>
       </c>
       <c r="C6" t="n">
-        <v>55.77219071966596</v>
+        <v>28.13007562840134</v>
       </c>
       <c r="D6" t="n">
-        <v>86.47628650854168</v>
+        <v>21.04306862074701</v>
       </c>
       <c r="E6" t="n">
-        <v>128.9144443662769</v>
+        <v>50.4995424251799</v>
       </c>
       <c r="F6" t="n">
-        <v>55.25119779100749</v>
+        <v>16.38709811027314</v>
       </c>
       <c r="G6" t="n">
-        <v>159.3685729203491</v>
+        <v>30.40488573384484</v>
       </c>
       <c r="H6" t="n">
-        <v>92.34809372775639</v>
+        <v>28.14455334133319</v>
       </c>
     </row>
     <row r="7">
@@ -2272,25 +2272,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.559125242462592</v>
+        <v>0.1659990277430199</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4768861118096486</v>
+        <v>0.0847162932472382</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1458417300529621</v>
+        <v>0.0179702059040731</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2942220806858535</v>
+        <v>0.08278289670927517</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08348480597876895</v>
+        <v>0.03372009870168886</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6751905801691698</v>
+        <v>0.04442619837160415</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3724584251931658</v>
+        <v>0.07160245344614992</v>
       </c>
     </row>
     <row r="8">
@@ -2300,25 +2300,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-10.94301960569304</v>
+        <v>-25.81521742411935</v>
       </c>
       <c r="C8" t="n">
-        <v>-12.76627904038245</v>
+        <v>-33.10365505427849</v>
       </c>
       <c r="D8" t="n">
-        <v>-102.9184573544913</v>
+        <v>-143.8896961098028</v>
       </c>
       <c r="E8" t="n">
-        <v>-101.8490018345775</v>
+        <v>-123.0518489175913</v>
       </c>
       <c r="F8" t="n">
-        <v>-118.6851368054836</v>
+        <v>-138.9170416115305</v>
       </c>
       <c r="G8" t="n">
-        <v>-77.14272792980505</v>
+        <v>-123.2169878808025</v>
       </c>
       <c r="H8" t="n">
-        <v>-70.71743709507216</v>
+        <v>-97.99907449968748</v>
       </c>
     </row>
     <row r="9">
@@ -2328,25 +2328,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-9.276592917580606</v>
+        <v>-21.64915070383827</v>
       </c>
       <c r="C9" t="n">
-        <v>-11.35017863817803</v>
+        <v>-29.56340404876744</v>
       </c>
       <c r="D9" t="n">
-        <v>-100.8294124790444</v>
+        <v>-138.6670839211857</v>
       </c>
       <c r="E9" t="n">
-        <v>-99.75995695913063</v>
+        <v>-117.8292367289742</v>
       </c>
       <c r="F9" t="n">
-        <v>-116.0934630734749</v>
+        <v>-132.4378572815089</v>
       </c>
       <c r="G9" t="n">
-        <v>-74.70497628006865</v>
+        <v>-117.1226087564615</v>
       </c>
       <c r="H9" t="n">
-        <v>-68.66909672457955</v>
+        <v>-92.87822357345597</v>
       </c>
     </row>
   </sheetData>
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1130844365975627</v>
+        <v>0.7736964146988832</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2074115500011636</v>
+        <v>0.858601813513064</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3245706006307363</v>
+        <v>0.9782094616359909</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3316689377169386</v>
+        <v>0.8889193018310366</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7419378484597297</v>
+        <v>0.9034751457947169</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1078300884228398</v>
+        <v>0.8778047364121809</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1579175682582356</v>
+        <v>0.8801178123143121</v>
       </c>
     </row>
     <row r="3">
@@ -2435,25 +2435,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3390182124058693</v>
+        <v>0.1372206164809731</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2422721922287964</v>
+        <v>0.1071668293816007</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05410683676160886</v>
+        <v>0.01181013054535976</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05517460461160976</v>
+        <v>0.01863804697535517</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05325210167657968</v>
+        <v>0.03312225494784676</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1526528891461077</v>
+        <v>0.03680084791729295</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1494128061384286</v>
+        <v>0.0574597877080714</v>
       </c>
     </row>
     <row r="4">
@@ -2463,25 +2463,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4130051100618208</v>
+        <v>0.105381550410637</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3148330668298883</v>
+        <v>0.05616638079438568</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00886672520929154</v>
+        <v>0.0002860561237290228</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008954716108294184</v>
+        <v>0.0007469545087681651</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01096858098092603</v>
+        <v>0.00410265772684419</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0418378635914121</v>
+        <v>0.004614776961674747</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1330776771302722</v>
+        <v>0.02854972942100646</v>
       </c>
     </row>
     <row r="5">
@@ -2491,25 +2491,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6426547362789921</v>
+        <v>0.3246252461079344</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5610998724201319</v>
+        <v>0.2369944741853398</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09416329013629218</v>
+        <v>0.01691319377672422</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09462936176628364</v>
+        <v>0.02733046850619588</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1047309934113395</v>
+        <v>0.0640519923721674</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2045430604821686</v>
+        <v>0.06793214969125257</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2836368857492013</v>
+        <v>0.1229745874399357</v>
       </c>
     </row>
     <row r="6">
@@ -2519,25 +2519,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68.56666941747955</v>
+        <v>27.91759303961165</v>
       </c>
       <c r="C6" t="n">
-        <v>54.86245475348394</v>
+        <v>30.17874157627624</v>
       </c>
       <c r="D6" t="n">
-        <v>101.9941873471218</v>
+        <v>12.28330468743393</v>
       </c>
       <c r="E6" t="n">
-        <v>150.1176682994445</v>
+        <v>36.47160599518342</v>
       </c>
       <c r="F6" t="n">
-        <v>59.41134778773597</v>
+        <v>18.41352907818878</v>
       </c>
       <c r="G6" t="n">
-        <v>165.3858844195957</v>
+        <v>27.36120425701802</v>
       </c>
       <c r="H6" t="n">
-        <v>100.0563686708102</v>
+        <v>25.43766310561868</v>
       </c>
     </row>
     <row r="7">
@@ -2547,25 +2547,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5561782460640058</v>
+        <v>0.1426581608777809</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4591596817805728</v>
+        <v>0.08273592250215078</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2098355274572832</v>
+        <v>0.007737400795813055</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8135379651817751</v>
+        <v>0.03484707760682674</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08609665214872934</v>
+        <v>0.03282931667037588</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7252710620816809</v>
+        <v>0.04088892294951805</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4750131891190079</v>
+        <v>0.05694946690041091</v>
       </c>
     </row>
     <row r="8">
@@ -2575,25 +2575,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-11.03302032213231</v>
+        <v>-34.25285092956518</v>
       </c>
       <c r="C8" t="n">
-        <v>-13.33569090799403</v>
+        <v>-39.19155361377477</v>
       </c>
       <c r="D8" t="n">
-        <v>-95.23444473598697</v>
+        <v>-167.3457731212132</v>
       </c>
       <c r="E8" t="n">
-        <v>-95.02707386610533</v>
+        <v>-147.1896317383741</v>
       </c>
       <c r="F8" t="n">
-        <v>-117.8434499246887</v>
+        <v>-144.3952478089421</v>
       </c>
       <c r="G8" t="n">
-        <v>-75.34883804799678</v>
+        <v>-130.4622935298273</v>
       </c>
       <c r="H8" t="n">
-        <v>-67.97041963415069</v>
+        <v>-110.4728917902828</v>
       </c>
     </row>
     <row r="9">
@@ -2603,25 +2603,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-9.36659363401988</v>
+        <v>-32.58642424145275</v>
       </c>
       <c r="C9" t="n">
-        <v>-11.91959050578961</v>
+        <v>-37.77545321157035</v>
       </c>
       <c r="D9" t="n">
-        <v>-93.14539986054012</v>
+        <v>-165.2567282457664</v>
       </c>
       <c r="E9" t="n">
-        <v>-92.93802899065848</v>
+        <v>-145.1005868629273</v>
       </c>
       <c r="F9" t="n">
-        <v>-115.2517761926801</v>
+        <v>-141.8035740769334</v>
       </c>
       <c r="G9" t="n">
-        <v>-72.91108639826038</v>
+        <v>-128.0245418800909</v>
       </c>
       <c r="H9" t="n">
-        <v>-65.92207926365809</v>
+        <v>-108.4245514197902</v>
       </c>
     </row>
   </sheetData>
@@ -2682,25 +2682,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7208430806439172</v>
+        <v>0.920063742598861</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7451917529142491</v>
+        <v>0.8550242300706042</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9574990767915718</v>
+        <v>0.8915637178429319</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6414302066940498</v>
+        <v>0.7651314696749565</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4142515155798496</v>
+        <v>0.7913946740127938</v>
       </c>
       <c r="G2" t="n">
-        <v>0.540836745906047</v>
+        <v>0.8751218123077869</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6700087297549474</v>
+        <v>0.8497166077513224</v>
       </c>
     </row>
     <row r="3">
@@ -2710,25 +2710,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1668035412876785</v>
+        <v>0.09994106982728319</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1430680658249957</v>
+        <v>0.1247466765543966</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01055253855202177</v>
+        <v>0.0212527111239967</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02252214102604668</v>
+        <v>0.02253931476548243</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06681178631217757</v>
+        <v>0.05233457662683261</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05984313190806356</v>
+        <v>0.04210461578349364</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07826686748516394</v>
+        <v>0.06048649411358086</v>
       </c>
     </row>
     <row r="4">
@@ -2738,25 +2738,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1299934728407326</v>
+        <v>0.03722347892874592</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1012152799901041</v>
+        <v>0.05758747337658399</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0005579324909194697</v>
+        <v>0.00142350143109225</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00241117789348558</v>
+        <v>0.001579357265356671</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02489644315320886</v>
+        <v>0.008866485834851643</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01734057396682605</v>
+        <v>0.004716099189585667</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04606914672254612</v>
+        <v>0.01856606600436935</v>
       </c>
     </row>
     <row r="5">
@@ -2766,25 +2766,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.360546075891463</v>
+        <v>0.1929338719062724</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3181434896239496</v>
+        <v>0.2399739014488534</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02362059463517948</v>
+        <v>0.03772931792508646</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04910374622659232</v>
+        <v>0.0397411281339203</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1577860676777543</v>
+        <v>0.09416201906741191</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1316836131294477</v>
+        <v>0.06867386103595506</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1734805978640644</v>
+        <v>0.1122023499195833</v>
       </c>
     </row>
     <row r="6">
@@ -2794,25 +2794,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.46654344196542</v>
+        <v>31.56551495638706</v>
       </c>
       <c r="C6" t="n">
-        <v>40.53053043016151</v>
+        <v>42.48157774250674</v>
       </c>
       <c r="D6" t="n">
-        <v>16.36674143746162</v>
+        <v>34.14502427166043</v>
       </c>
       <c r="E6" t="n">
-        <v>47.06719460515103</v>
+        <v>44.10323909287983</v>
       </c>
       <c r="F6" t="n">
-        <v>42.17704685940674</v>
+        <v>31.4921229351972</v>
       </c>
       <c r="G6" t="n">
-        <v>38.78982994156211</v>
+        <v>27.65186461863813</v>
       </c>
       <c r="H6" t="n">
-        <v>36.06631445261807</v>
+        <v>35.23989060287823</v>
       </c>
     </row>
     <row r="7">
@@ -2822,25 +2822,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1762425067953377</v>
+        <v>0.05053731247046384</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1487931701187982</v>
+        <v>0.08430396234242751</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0146408297061721</v>
+        <v>0.03402733564888502</v>
       </c>
       <c r="E7" t="n">
-        <v>0.110758762517225</v>
+        <v>0.07206610918326273</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1946520555332913</v>
+        <v>0.06928813788055802</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1513873780049642</v>
+        <v>0.04126472574037392</v>
       </c>
       <c r="H7" t="n">
-        <v>0.132745783779298</v>
+        <v>0.05858126387766183</v>
       </c>
     </row>
     <row r="8">
@@ -2850,25 +2850,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-28.6846076579766</v>
+        <v>-53.94386456757291</v>
       </c>
       <c r="C8" t="n">
-        <v>-28.35758318222718</v>
+        <v>-40.8167531654893</v>
       </c>
       <c r="D8" t="n">
-        <v>-151.3167243252655</v>
+        <v>-135.6473485641768</v>
       </c>
       <c r="E8" t="n">
-        <v>-120.580437866327</v>
+        <v>-133.465483484474</v>
       </c>
       <c r="F8" t="n">
-        <v>-93.71181893612213</v>
+        <v>-125.5878721591766</v>
       </c>
       <c r="G8" t="n">
-        <v>-95.36765518594697</v>
+        <v>-131.9193315990315</v>
       </c>
       <c r="H8" t="n">
-        <v>-86.3364711923109</v>
+        <v>-103.5634422566535</v>
       </c>
     </row>
     <row r="9">
@@ -2878,25 +2878,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-26.18496762580795</v>
+        <v>-53.11065122351669</v>
       </c>
       <c r="C9" t="n">
-        <v>-26.23343257892055</v>
+        <v>-40.10870296438709</v>
       </c>
       <c r="D9" t="n">
-        <v>-148.1831570120953</v>
+        <v>-134.6028261264533</v>
       </c>
       <c r="E9" t="n">
-        <v>-117.4468705531567</v>
+        <v>-132.4209610467505</v>
       </c>
       <c r="F9" t="n">
-        <v>-89.82430833810915</v>
+        <v>-124.2920352931722</v>
       </c>
       <c r="G9" t="n">
-        <v>-91.71102771134237</v>
+        <v>-130.7004557741633</v>
       </c>
       <c r="H9" t="n">
-        <v>-83.26396063657199</v>
+        <v>-102.5392720714072</v>
       </c>
     </row>
   </sheetData>
@@ -2957,25 +2957,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03566129260567674</v>
+        <v>0.9431105538204944</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1177427686871962</v>
+        <v>0.8627538647097533</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4726406901628158</v>
+        <v>0.9731380511535257</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4360248214067879</v>
+        <v>0.9613841049536853</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7976864693130382</v>
+        <v>0.9021899275116455</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6040170158537173</v>
+        <v>0.8889921836585174</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2652872358692761</v>
+        <v>0.9219281143012702</v>
       </c>
     </row>
     <row r="3">
@@ -2985,25 +2985,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3549020218632694</v>
+        <v>0.08902164925173872</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2571929683402966</v>
+        <v>0.1123331645170063</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07464656806897094</v>
+        <v>0.01535722088767351</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08658833812240115</v>
+        <v>0.01362723528795824</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08042799957605082</v>
+        <v>0.03428372433901413</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1099122267133724</v>
+        <v>0.02921886286595593</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1606116871140602</v>
+        <v>0.04897364285822448</v>
       </c>
     </row>
     <row r="4">
@@ -3013,25 +3013,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4490583212412845</v>
+        <v>0.0264913966450058</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3504514226361284</v>
+        <v>0.05451709734609628</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00692292945976958</v>
+        <v>0.0003526312583227071</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009656450064989809</v>
+        <v>0.0002596699281731947</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008599061627720787</v>
+        <v>0.004157284183036607</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01495453341479303</v>
+        <v>0.0041922763483409</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1399404530741144</v>
+        <v>0.01499505928482925</v>
       </c>
     </row>
     <row r="5">
@@ -3041,25 +3041,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6701181397643885</v>
+        <v>0.1627617788210912</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5919893771311513</v>
+        <v>0.2334889662191691</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08320414328487241</v>
+        <v>0.01877847859446306</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09826723800427999</v>
+        <v>0.01611427715329467</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0927311254526806</v>
+        <v>0.06447700507185959</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1222887297128931</v>
+        <v>0.06474779029697383</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2764331255583777</v>
+        <v>0.09339471602614191</v>
       </c>
     </row>
     <row r="6">
@@ -3069,25 +3069,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66.30174522112979</v>
+        <v>24.32232643016287</v>
       </c>
       <c r="C6" t="n">
-        <v>56.88328764562542</v>
+        <v>32.19006526294063</v>
       </c>
       <c r="D6" t="n">
-        <v>68.87029291295899</v>
+        <v>13.81811905620815</v>
       </c>
       <c r="E6" t="n">
-        <v>129.4932491344202</v>
+        <v>14.26791006591968</v>
       </c>
       <c r="F6" t="n">
-        <v>47.09925182873661</v>
+        <v>15.49034871354317</v>
       </c>
       <c r="G6" t="n">
-        <v>89.26250264091766</v>
+        <v>15.54575743996481</v>
       </c>
       <c r="H6" t="n">
-        <v>76.31838823063146</v>
+        <v>19.27242116145655</v>
       </c>
     </row>
     <row r="7">
@@ -3097,25 +3097,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6046424370871962</v>
+        <v>0.03661081150535575</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5109931652391311</v>
+        <v>0.0803358087293414</v>
       </c>
       <c r="D7" t="n">
-        <v>0.164053843572994</v>
+        <v>0.009305426534768187</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8771339229350587</v>
+        <v>0.01276653746361564</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0677134023454931</v>
+        <v>0.03325312067463198</v>
       </c>
       <c r="G7" t="n">
-        <v>0.13026306863424</v>
+        <v>0.03723693834628342</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3924666399690188</v>
+        <v>0.0349181072089994</v>
       </c>
     </row>
     <row r="8">
@@ -3125,25 +3125,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-9.610242640574057</v>
+        <v>-57.72589931132265</v>
       </c>
       <c r="C8" t="n">
-        <v>-11.72799764883035</v>
+        <v>-39.63861370607138</v>
       </c>
       <c r="D8" t="n">
-        <v>-100.4312415985111</v>
+        <v>-162.9518404607099</v>
       </c>
       <c r="E8" t="n">
-        <v>-93.44271291428034</v>
+        <v>-169.3780840501139</v>
       </c>
       <c r="F8" t="n">
-        <v>-124.4147592577548</v>
+        <v>-144.0381179799966</v>
       </c>
       <c r="G8" t="n">
-        <v>-101.0685196666308</v>
+        <v>-132.862785283624</v>
       </c>
       <c r="H8" t="n">
-        <v>-73.44924562109692</v>
+        <v>-117.7658901319731</v>
       </c>
     </row>
     <row r="9">
@@ -3153,25 +3153,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-7.943815952461625</v>
+        <v>-56.05947262321022</v>
       </c>
       <c r="C9" t="n">
-        <v>-10.31189724662593</v>
+        <v>-38.22251330386696</v>
       </c>
       <c r="D9" t="n">
-        <v>-98.34219672306428</v>
+        <v>-160.862795585263</v>
       </c>
       <c r="E9" t="n">
-        <v>-91.35366803883349</v>
+        <v>-167.2890391746671</v>
       </c>
       <c r="F9" t="n">
-        <v>-121.8230855257462</v>
+        <v>-141.446444247988</v>
       </c>
       <c r="G9" t="n">
-        <v>-98.63076801689442</v>
+        <v>-130.4250336338876</v>
       </c>
       <c r="H9" t="n">
-        <v>-71.40090525060432</v>
+        <v>-115.7175497614805</v>
       </c>
     </row>
   </sheetData>
@@ -3232,25 +3232,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03753504332220126</v>
+        <v>0.8019640205902898</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1295677552464112</v>
+        <v>0.8822141585107374</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5831125404311054</v>
+        <v>0.908873563489608</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4996713329249021</v>
+        <v>0.9251973998991592</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6921118834220494</v>
+        <v>0.8806182812863445</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5266650493768907</v>
+        <v>0.8798960873609061</v>
       </c>
       <c r="H2" t="n">
-        <v>0.244886823145626</v>
+        <v>0.8797939185228408</v>
       </c>
     </row>
     <row r="3">
@@ -3260,25 +3260,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3572939001738104</v>
+        <v>0.1441004245883649</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2574955452571561</v>
+        <v>0.1088601503959113</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04146351600279981</v>
+        <v>0.02372084910291132</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0578257168607038</v>
+        <v>0.01682948735854642</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06699169404254424</v>
+        <v>0.04634280159462015</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07877634078574337</v>
+        <v>0.03154098610558934</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1433077855204596</v>
+        <v>0.06189911652432389</v>
       </c>
     </row>
     <row r="4">
@@ -3288,25 +3288,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4481857820133811</v>
+        <v>0.09221832928327557</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3457542853214662</v>
+        <v>0.04678705285859022</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005472706030636007</v>
+        <v>0.001196265771957996</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01008443665068363</v>
+        <v>0.0005030049354561645</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01308636589904217</v>
+        <v>0.005074157684640267</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01787577653303351</v>
+        <v>0.004535795846584166</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1400765587413738</v>
+        <v>0.02505243439675073</v>
       </c>
     </row>
     <row r="5">
@@ -3316,25 +3316,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6694667893281795</v>
+        <v>0.3036747096537273</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5880087459566109</v>
+        <v>0.2163031503667716</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07397774010224972</v>
+        <v>0.03458707521543266</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1004212958026515</v>
+        <v>0.02242777152229273</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1143956550706458</v>
+        <v>0.07123312210369744</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1337003236085594</v>
+        <v>0.06734831732555882</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2799950916448161</v>
+        <v>0.1192623576979134</v>
       </c>
     </row>
     <row r="6">
@@ -3344,25 +3344,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66.83965160643319</v>
+        <v>36.24222264746874</v>
       </c>
       <c r="C6" t="n">
-        <v>57.06260404071929</v>
+        <v>37.8798940825658</v>
       </c>
       <c r="D6" t="n">
-        <v>81.02967136050982</v>
+        <v>32.65960157139312</v>
       </c>
       <c r="E6" t="n">
-        <v>158.8880484996165</v>
+        <v>29.97016863609783</v>
       </c>
       <c r="F6" t="n">
-        <v>54.54346519536675</v>
+        <v>28.28077476680975</v>
       </c>
       <c r="G6" t="n">
-        <v>90.61858185435658</v>
+        <v>19.90828236020199</v>
       </c>
       <c r="H6" t="n">
-        <v>84.8303370928337</v>
+        <v>30.82349067742287</v>
       </c>
     </row>
     <row r="7">
@@ -3372,25 +3372,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6029695344127064</v>
+        <v>0.124463624321206</v>
       </c>
       <c r="C7" t="n">
-        <v>0.503657673151103</v>
+        <v>0.06858668944779195</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1293971320921136</v>
+        <v>0.0286753169934882</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9149210110658984</v>
+        <v>0.02329288348507157</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1020268911027147</v>
+        <v>0.03986642599334485</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1550135287600563</v>
+        <v>0.0397062308843371</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4013309617640988</v>
+        <v>0.05409852852087327</v>
       </c>
     </row>
     <row r="8">
@@ -3400,25 +3400,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-11.6433064890773</v>
+        <v>-38.52113827316452</v>
       </c>
       <c r="C8" t="n">
-        <v>-13.93040371354777</v>
+        <v>-43.93223143980195</v>
       </c>
       <c r="D8" t="n">
-        <v>-107.3676236992888</v>
+        <v>-139.2995590464668</v>
       </c>
       <c r="E8" t="n">
-        <v>-94.53200135439299</v>
+        <v>-157.4931220933243</v>
       </c>
       <c r="F8" t="n">
-        <v>-115.0769777691077</v>
+        <v>-140.6570580150812</v>
       </c>
       <c r="G8" t="n">
-        <v>-98.60771872345478</v>
+        <v>-132.8938680234089</v>
       </c>
       <c r="H8" t="n">
-        <v>-73.52633862481154</v>
+        <v>-108.7994961485413</v>
       </c>
     </row>
     <row r="9">
@@ -3428,25 +3428,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-10.81009314502108</v>
+        <v>-37.6879249291083</v>
       </c>
       <c r="C9" t="n">
-        <v>-13.22235351244556</v>
+        <v>-43.22418123869974</v>
       </c>
       <c r="D9" t="n">
-        <v>-106.3231012615653</v>
+        <v>-138.2550366087434</v>
       </c>
       <c r="E9" t="n">
-        <v>-93.48747891666956</v>
+        <v>-156.4485996556008</v>
       </c>
       <c r="F9" t="n">
-        <v>-113.7811409031033</v>
+        <v>-139.3612211490769</v>
       </c>
       <c r="G9" t="n">
-        <v>-97.38884289858657</v>
+        <v>-131.6749921985407</v>
       </c>
       <c r="H9" t="n">
-        <v>-72.50216843956524</v>
+        <v>-107.775325963295</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/global/metrics_summary.xlsx
+++ b/results/cross_validation/global/metrics_summary.xlsx
@@ -482,25 +482,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7731888835334902</v>
+        <v>0.1976663776707422</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8725112218547966</v>
+        <v>0.2834899052365473</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9831207109723542</v>
+        <v>0.3544706790577623</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9027960099415565</v>
+        <v>-1.348275342440982</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8957367555224912</v>
+        <v>0.7756189814622407</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8870421897632809</v>
+        <v>0.5263922246879603</v>
       </c>
       <c r="H2" t="n">
-        <v>0.885732628597995</v>
+        <v>0.1315604709457118</v>
       </c>
     </row>
     <row r="3">
@@ -510,25 +510,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.137344214703369</v>
+        <v>0.3312790716453166</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1014033310516529</v>
+        <v>0.2334488868229029</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005609288257706873</v>
+        <v>0.0758037974624562</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01296072863041777</v>
+        <v>0.09252231678204231</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03377388732444474</v>
+        <v>0.07600437648687226</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0361330391110217</v>
+        <v>0.1083351994284809</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0545374148464355</v>
+        <v>0.1528989414380119</v>
       </c>
     </row>
     <row r="4">
@@ -538,25 +538,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1056178896671258</v>
+        <v>0.3736183010761268</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05064126661183183</v>
+        <v>0.2846131186358859</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002215835106912817</v>
+        <v>0.008474210788989019</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0006536415402608362</v>
+        <v>0.01579081590032257</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004431567486978748</v>
+        <v>0.009537010203644758</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004265919030053162</v>
+        <v>0.01788607992002319</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02763864464115695</v>
+        <v>0.1183199227541654</v>
       </c>
     </row>
     <row r="5">
@@ -566,25 +566,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3249890608422471</v>
+        <v>0.6112432421517041</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2250361451230265</v>
+        <v>0.5334914419518704</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01488568139828613</v>
+        <v>0.09205547669198731</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02556641430198682</v>
+        <v>0.1256615132024224</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06657001943051202</v>
+        <v>0.0976576172330902</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06531400332281863</v>
+        <v>0.1337388497035293</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1203935540698129</v>
+        <v>0.2656413568224339</v>
       </c>
     </row>
     <row r="6">
@@ -594,25 +594,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.93408076496081</v>
+        <v>57.47912594050217</v>
       </c>
       <c r="C6" t="n">
-        <v>29.80296874871599</v>
+        <v>46.74812787068655</v>
       </c>
       <c r="D6" t="n">
-        <v>8.764258404308217</v>
+        <v>83.73984386171685</v>
       </c>
       <c r="E6" t="n">
-        <v>31.57536297007722</v>
+        <v>161.7018281472745</v>
       </c>
       <c r="F6" t="n">
-        <v>19.76093796416055</v>
+        <v>45.13625242061012</v>
       </c>
       <c r="G6" t="n">
-        <v>26.95523531728998</v>
+        <v>94.84539752853622</v>
       </c>
       <c r="H6" t="n">
-        <v>24.13214069491879</v>
+        <v>81.60842929488773</v>
       </c>
     </row>
     <row r="7">
@@ -622,25 +622,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.142975857706941</v>
+        <v>0.5042328974520661</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07469552007184332</v>
+        <v>0.416182211474156</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006218895165777636</v>
+        <v>0.2015907438349636</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03061874609571564</v>
+        <v>1.435072347725041</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03538107058413777</v>
+        <v>0.07599021270387912</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03787348639205296</v>
+        <v>0.1566025885376282</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05462726266941139</v>
+        <v>0.4649451669546223</v>
       </c>
     </row>
     <row r="8">
@@ -650,25 +650,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-34.21476770963743</v>
+        <v>-8.736849997315936</v>
       </c>
       <c r="C8" t="n">
-        <v>-40.74482734065539</v>
+        <v>-10.84936749088962</v>
       </c>
       <c r="D8" t="n">
-        <v>-172.7089313380501</v>
+        <v>-92.18528279819398</v>
       </c>
       <c r="E8" t="n">
-        <v>-149.9919806672965</v>
+        <v>-79.11486238178162</v>
       </c>
       <c r="F8" t="n">
-        <v>-142.3130519203876</v>
+        <v>-117.6195314390963</v>
       </c>
       <c r="G8" t="n">
-        <v>-132.4274409852517</v>
+        <v>-92.59331316919014</v>
       </c>
       <c r="H8" t="n">
-        <v>-112.0668333268798</v>
+        <v>-66.84986787941126</v>
       </c>
     </row>
     <row r="9">
@@ -678,25 +678,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-32.548341021525</v>
+        <v>-5.403996621091071</v>
       </c>
       <c r="C9" t="n">
-        <v>-39.32872693845097</v>
+        <v>-8.017166686480779</v>
       </c>
       <c r="D9" t="n">
-        <v>-170.6198864626032</v>
+        <v>-88.00719304730029</v>
       </c>
       <c r="E9" t="n">
-        <v>-147.9029357918496</v>
+        <v>-74.93677263088793</v>
       </c>
       <c r="F9" t="n">
-        <v>-139.7213781883789</v>
+        <v>-112.436183975079</v>
       </c>
       <c r="G9" t="n">
-        <v>-129.9896893355153</v>
+        <v>-87.71780986971734</v>
       </c>
       <c r="H9" t="n">
-        <v>-110.0184929563872</v>
+        <v>-62.75318713842606</v>
       </c>
     </row>
   </sheetData>
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6121564601983727</v>
+        <v>0.8993423560191121</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8698955032248902</v>
+        <v>0.4704503519994442</v>
       </c>
       <c r="D2" t="n">
-        <v>0.977451133537302</v>
+        <v>-0.3143669507920797</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9461970375981978</v>
+        <v>0.6389779037375329</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9214353229687969</v>
+        <v>0.255343219810068</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8987935181479894</v>
+        <v>-3.419031327115063</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8709881626125915</v>
+        <v>-0.244880741056831</v>
       </c>
     </row>
     <row r="3">
@@ -785,25 +785,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1689854375460691</v>
+        <v>0.1899207933408533</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1113839974738382</v>
+        <v>0.2039762243061733</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01300915847487365</v>
+        <v>0.1256851547415206</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01274105594382345</v>
+        <v>0.03292652375455817</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0373319157115065</v>
+        <v>0.1251701488618647</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02666956452588106</v>
+        <v>0.3079648122218118</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06168685494599866</v>
+        <v>0.1642739428711303</v>
       </c>
     </row>
     <row r="4">
@@ -813,25 +813,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1806049757747402</v>
+        <v>0.04687269346295922</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05168028593922516</v>
+        <v>0.2103484345740183</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002960111047763965</v>
+        <v>0.01725440229242429</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003617943172267443</v>
+        <v>0.002427668235916175</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003339284808382977</v>
+        <v>0.03165062426922503</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003822123109437519</v>
+        <v>0.1668873519523422</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04001741250896484</v>
+        <v>0.0792401957978142</v>
       </c>
     </row>
     <row r="5">
@@ -841,25 +841,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4249764414349814</v>
+        <v>0.2165010241614557</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2273329847145485</v>
+        <v>0.4586375852173678</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01720497325706717</v>
+        <v>0.1313560135373493</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0190208915991534</v>
+        <v>0.04927137339182028</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05778654521930669</v>
+        <v>0.1779062232447899</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06182332172762572</v>
+        <v>0.4085184842235932</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1346908596587805</v>
+        <v>0.2403651172960627</v>
       </c>
     </row>
     <row r="6">
@@ -869,25 +869,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.86905887367338</v>
+        <v>49.13274132115505</v>
       </c>
       <c r="C6" t="n">
-        <v>29.72821302799129</v>
+        <v>42.63571246132688</v>
       </c>
       <c r="D6" t="n">
-        <v>10.63193795583293</v>
+        <v>64.5007419751291</v>
       </c>
       <c r="E6" t="n">
-        <v>14.8265130339079</v>
+        <v>46.09915640913847</v>
       </c>
       <c r="F6" t="n">
-        <v>21.61918230398741</v>
+        <v>61.55702471844994</v>
       </c>
       <c r="G6" t="n">
-        <v>14.44268565383375</v>
+        <v>250.7010664415048</v>
       </c>
       <c r="H6" t="n">
-        <v>19.68626514153778</v>
+        <v>85.77107388778404</v>
       </c>
     </row>
     <row r="7">
@@ -897,25 +897,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2462765449828064</v>
+        <v>0.06700817861833784</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07870754918999057</v>
+        <v>0.3101087986019796</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01047186771215289</v>
+        <v>0.8207763336846419</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01989414474259937</v>
+        <v>0.1140059966438815</v>
       </c>
       <c r="F7" t="n">
-        <v>0.029406902475229</v>
+        <v>0.2495524710454372</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03653743073220946</v>
+        <v>2.893061089002317</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07021573997249794</v>
+        <v>0.7424188112660991</v>
       </c>
     </row>
     <row r="8">
@@ -925,25 +925,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-15.09453247940176</v>
+        <v>-36.02544003443792</v>
       </c>
       <c r="C8" t="n">
-        <v>-30.4401832996503</v>
+        <v>-7.384848664690882</v>
       </c>
       <c r="D8" t="n">
-        <v>-156.6273853523565</v>
+        <v>-69.25344721682991</v>
       </c>
       <c r="E8" t="n">
-        <v>-152.4131285335323</v>
+        <v>-110.4373051762583</v>
       </c>
       <c r="F8" t="n">
-        <v>-139.9539628520262</v>
+        <v>-77.23092997388916</v>
       </c>
       <c r="G8" t="n">
-        <v>-125.1737305736407</v>
+        <v>-28.76090583442107</v>
       </c>
       <c r="H8" t="n">
-        <v>-103.2838205151013</v>
+        <v>-54.84881281675453</v>
       </c>
     </row>
     <row r="9">
@@ -953,25 +953,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-9.262039071008246</v>
+        <v>-29.35973328198819</v>
       </c>
       <c r="C9" t="n">
-        <v>-25.48383189193483</v>
+        <v>-1.720447055873201</v>
       </c>
       <c r="D9" t="n">
-        <v>-149.3157282882925</v>
+        <v>-60.89726771504253</v>
       </c>
       <c r="E9" t="n">
-        <v>-145.1014714694684</v>
+        <v>-102.0811256744709</v>
       </c>
       <c r="F9" t="n">
-        <v>-130.8831047899959</v>
+        <v>-66.86423504585453</v>
       </c>
       <c r="G9" t="n">
-        <v>-116.6415997995633</v>
+        <v>-19.00989923547546</v>
       </c>
       <c r="H9" t="n">
-        <v>-96.11462921837717</v>
+        <v>-46.65545133478414</v>
       </c>
     </row>
   </sheetData>
@@ -1032,25 +1032,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9322547539081764</v>
+        <v>0.8688950948458743</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8707490903463868</v>
+        <v>0.9184098962007062</v>
       </c>
       <c r="D2" t="n">
-        <v>0.886701103291085</v>
+        <v>0.7639331374052144</v>
       </c>
       <c r="E2" t="n">
-        <v>0.875492042273109</v>
+        <v>0.8701651020985333</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9169156346243755</v>
+        <v>0.9223722895751213</v>
       </c>
       <c r="G2" t="n">
-        <v>0.873101387393599</v>
+        <v>0.7290193634425375</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8925356686394553</v>
+        <v>0.8454658139279978</v>
       </c>
     </row>
     <row r="3">
@@ -1060,25 +1060,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08057855596760877</v>
+        <v>0.1174371246339853</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1018966926052491</v>
+        <v>0.08063647277549375</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01806707805812173</v>
+        <v>0.02609243649317531</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01358435692549985</v>
+        <v>0.01317981080501577</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03421539133747273</v>
+        <v>0.03297359540111087</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04145526427771951</v>
+        <v>0.05177196471575596</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04829955652861195</v>
+        <v>0.05368190080408949</v>
       </c>
     </row>
     <row r="4">
@@ -1088,25 +1088,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03154655749977325</v>
+        <v>0.06105090272077578</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05134122289677524</v>
+        <v>0.03240933248792397</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001487335589140733</v>
+        <v>0.003098976745167125</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008372451914206881</v>
+        <v>0.0008730658339528877</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003531388018088249</v>
+        <v>0.003299460316350529</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004792401740707764</v>
+        <v>0.01023374525270873</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01558935848931765</v>
+        <v>0.01849424722614651</v>
       </c>
     </row>
     <row r="5">
@@ -1116,25 +1116,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1776135059610424</v>
+        <v>0.2470848087616391</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2265860165517176</v>
+        <v>0.1800259217110802</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03856599005783117</v>
+        <v>0.05566845377022003</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02893518950034176</v>
+        <v>0.02954768745524576</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05942548290159912</v>
+        <v>0.05744092893008024</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06922717487163378</v>
+        <v>0.1011619753302037</v>
       </c>
       <c r="H5" t="n">
-        <v>0.100058893307361</v>
+        <v>0.1118216293264115</v>
       </c>
     </row>
     <row r="6">
@@ -1144,25 +1144,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.498398824979</v>
+        <v>26.37741035006173</v>
       </c>
       <c r="C6" t="n">
-        <v>24.00269452055293</v>
+        <v>24.26671134951604</v>
       </c>
       <c r="D6" t="n">
-        <v>30.40051159010692</v>
+        <v>42.49977455893399</v>
       </c>
       <c r="E6" t="n">
-        <v>26.54890738708907</v>
+        <v>23.99208358450983</v>
       </c>
       <c r="F6" t="n">
-        <v>20.25531126558197</v>
+        <v>22.58422612572181</v>
       </c>
       <c r="G6" t="n">
-        <v>29.37057757740349</v>
+        <v>38.28069000917452</v>
       </c>
       <c r="H6" t="n">
-        <v>25.17940019428556</v>
+        <v>29.66681599631965</v>
       </c>
     </row>
     <row r="7">
@@ -1172,25 +1172,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04590616407738837</v>
+        <v>0.08506710345078075</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07821412892382662</v>
+        <v>0.05016356388133492</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03853080392507303</v>
+        <v>0.07598934250005268</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04143845895206181</v>
+        <v>0.04256161545420705</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03089728122534912</v>
+        <v>0.02859793534890898</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04492426500041575</v>
+        <v>0.09145781264413488</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04665185035068578</v>
+        <v>0.0623062288799032</v>
       </c>
     </row>
     <row r="8">
@@ -1200,25 +1200,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-44.75694374407698</v>
+        <v>-35.53280396321205</v>
       </c>
       <c r="C8" t="n">
-        <v>-30.53891926377734</v>
+        <v>-39.43963286862898</v>
       </c>
       <c r="D8" t="n">
-        <v>-122.7261480542008</v>
+        <v>-109.3103493878705</v>
       </c>
       <c r="E8" t="n">
-        <v>-134.7932653817703</v>
+        <v>-135.9134914697214</v>
       </c>
       <c r="F8" t="n">
-        <v>-138.4437355347539</v>
+        <v>-142.2779018383612</v>
       </c>
       <c r="G8" t="n">
-        <v>-119.518089649401</v>
+        <v>-102.551616528988</v>
       </c>
       <c r="H8" t="n">
-        <v>-98.46285027133007</v>
+        <v>-94.17096600946371</v>
       </c>
     </row>
     <row r="9">
@@ -1228,25 +1228,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-38.92445033568347</v>
+        <v>-30.53352389887475</v>
       </c>
       <c r="C9" t="n">
-        <v>-25.58256785606187</v>
+        <v>-35.19133166201571</v>
       </c>
       <c r="D9" t="n">
-        <v>-115.4144909901369</v>
+        <v>-103.04321476153</v>
       </c>
       <c r="E9" t="n">
-        <v>-127.4816083177063</v>
+        <v>-129.6463568433809</v>
       </c>
       <c r="F9" t="n">
-        <v>-129.3728774727236</v>
+        <v>-134.5028806423352</v>
       </c>
       <c r="G9" t="n">
-        <v>-110.9859588753236</v>
+        <v>-95.2383615797788</v>
       </c>
       <c r="H9" t="n">
-        <v>-91.29365897460595</v>
+        <v>-88.02594489798589</v>
       </c>
     </row>
   </sheetData>
@@ -1582,25 +1582,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3649808836908726</v>
+        <v>0.9312334534953024</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006842187883637441</v>
+        <v>0.9361687079093279</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7361808303316463</v>
+        <v>0.9098130984259211</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8355718671592859</v>
+        <v>0.6085067670360935</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8898722665862924</v>
+        <v>0.6071193009776117</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8353534731670564</v>
+        <v>-0.9285105797763178</v>
       </c>
       <c r="H2" t="n">
-        <v>0.333015760414113</v>
+        <v>0.5107217913446565</v>
       </c>
     </row>
     <row r="3">
@@ -1610,25 +1610,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2919943856347123</v>
+        <v>0.0800390014471514</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2965741852309667</v>
+        <v>0.06973092412027639</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02306048540544114</v>
+        <v>0.01408566284576012</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01511410032868808</v>
+        <v>0.01777861365224019</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05952263207637042</v>
+        <v>0.07930506973908301</v>
       </c>
       <c r="G3" t="n">
-        <v>0.185429179009242</v>
+        <v>0.154291098654353</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1452824946142368</v>
+        <v>0.06920506174314402</v>
       </c>
     </row>
     <row r="4">
@@ -1638,25 +1638,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2957058719507534</v>
+        <v>0.03202214086625183</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3945035028394818</v>
+        <v>0.02535515304146834</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003463296215085071</v>
+        <v>0.001183931991236286</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00110568566112973</v>
+        <v>0.002632569297231171</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004680829617920888</v>
+        <v>0.01669886008990135</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0693132178434563</v>
+        <v>0.07283135149916661</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1281287340213046</v>
+        <v>0.0251206677975426</v>
       </c>
     </row>
     <row r="5">
@@ -1666,25 +1666,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5437884441129228</v>
+        <v>0.1789473131015155</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6280951383663799</v>
+        <v>0.159233014923</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05884977667829395</v>
+        <v>0.03440831282170467</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03325185199548635</v>
+        <v>0.05130856943270949</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06841658876267427</v>
+        <v>0.1292240693133495</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2632740356424391</v>
+        <v>0.2698728432042887</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2659459725930327</v>
+        <v>0.1371656871327613</v>
       </c>
     </row>
     <row r="6">
@@ -1694,25 +1694,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57.64472177160614</v>
+        <v>16.88309192410653</v>
       </c>
       <c r="C6" t="n">
-        <v>76.640841679392</v>
+        <v>20.11525247383939</v>
       </c>
       <c r="D6" t="n">
-        <v>28.74932697048213</v>
+        <v>18.49556494262038</v>
       </c>
       <c r="E6" t="n">
-        <v>34.21747731001079</v>
+        <v>34.30205163861444</v>
       </c>
       <c r="F6" t="n">
-        <v>35.898122408214</v>
+        <v>46.50810423900686</v>
       </c>
       <c r="G6" t="n">
-        <v>142.6644679421298</v>
+        <v>91.00086533547925</v>
       </c>
       <c r="H6" t="n">
-        <v>62.63582634697247</v>
+        <v>37.88415509227781</v>
       </c>
     </row>
     <row r="7">
@@ -1722,25 +1722,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4014998452582656</v>
+        <v>0.04504546255778556</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5780997956225461</v>
+        <v>0.03889799475622946</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08557005825106569</v>
+        <v>0.02988482286608909</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05410241981500505</v>
+        <v>0.1212907683972338</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04031490075665692</v>
+        <v>0.1315534117696475</v>
       </c>
       <c r="G7" t="n">
-        <v>1.206250588881073</v>
+        <v>1.263070239964624</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3943062680974354</v>
+        <v>0.2716237833852682</v>
       </c>
     </row>
     <row r="8">
@@ -1750,25 +1750,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-4.712629906895394</v>
+        <v>-50.50257112722071</v>
       </c>
       <c r="C8" t="n">
-        <v>2.048091106778578</v>
+        <v>-47.12159940707654</v>
       </c>
       <c r="D8" t="n">
-        <v>-102.9762240818653</v>
+        <v>-133.5171978640897</v>
       </c>
       <c r="E8" t="n">
-        <v>-126.9530822013997</v>
+        <v>-116.7356948019295</v>
       </c>
       <c r="F8" t="n">
-        <v>-128.8355577313607</v>
+        <v>-102.4952001394291</v>
       </c>
       <c r="G8" t="n">
-        <v>-50.72799143254564</v>
+        <v>-57.49021910056435</v>
       </c>
       <c r="H8" t="n">
-        <v>-68.69289904121469</v>
+        <v>-84.64374707338497</v>
       </c>
     </row>
     <row r="9">
@@ -1778,25 +1778,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.953076845554335</v>
+        <v>-47.16971775099584</v>
       </c>
       <c r="C9" t="n">
-        <v>7.712492715596259</v>
+        <v>-44.2893986026677</v>
       </c>
       <c r="D9" t="n">
-        <v>-94.6200445800779</v>
+        <v>-129.339108113196</v>
       </c>
       <c r="E9" t="n">
-        <v>-118.5969026996123</v>
+        <v>-112.5576050510358</v>
       </c>
       <c r="F9" t="n">
-        <v>-118.4688628033261</v>
+        <v>-97.3118526754118</v>
       </c>
       <c r="G9" t="n">
-        <v>-40.97698483360003</v>
+        <v>-52.61471580109154</v>
       </c>
       <c r="H9" t="n">
-        <v>-60.49953755924429</v>
+        <v>-80.54706633239978</v>
       </c>
     </row>
   </sheetData>
@@ -1857,25 +1857,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7742858394957591</v>
+        <v>0.09889484127984349</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8522812276291934</v>
+        <v>0.1763499024048283</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9837499537097349</v>
+        <v>-0.2729382278028016</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9257703957739791</v>
+        <v>-4.827697156941836</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9036491499330408</v>
+        <v>0.4426369112681671</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8894622404613096</v>
+        <v>0.6402444639199151</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8881998011671696</v>
+        <v>-0.6237515443119807</v>
       </c>
     </row>
     <row r="3">
@@ -1885,25 +1885,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1371235456025501</v>
+        <v>0.3441535538509446</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1119640387571579</v>
+        <v>0.2548422155919852</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009921641426106284</v>
+        <v>0.1173305580172787</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01482341117047158</v>
+        <v>0.140393589270286</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03449732074526119</v>
+        <v>0.1208409687503152</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03336345081789293</v>
+        <v>0.07725885001891726</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05694890141990666</v>
+        <v>0.1758032892499545</v>
       </c>
     </row>
     <row r="4">
@@ -1913,25 +1913,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1051070761955572</v>
+        <v>0.4196127011536328</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05867705255346009</v>
+        <v>0.3271714169200995</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000213323102649364</v>
+        <v>0.01671054515078844</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004991518641372274</v>
+        <v>0.03918794839128393</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004095261917459395</v>
+        <v>0.02368996049225053</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004174524373014577</v>
+        <v>0.0135863822458567</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02879439833437964</v>
+        <v>0.1399931590589853</v>
       </c>
     </row>
     <row r="5">
@@ -1941,25 +1941,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.324202214976328</v>
+        <v>0.6477751933762459</v>
       </c>
       <c r="C5" t="n">
-        <v>0.242233467038434</v>
+        <v>0.571989000698527</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01460558463908118</v>
+        <v>0.1292692738077709</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0223417068313329</v>
+        <v>0.197959461484628</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06399423347036352</v>
+        <v>0.1539154329242215</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06461055929965764</v>
+        <v>0.1165606376349096</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1219979610425328</v>
+        <v>0.3029114999877172</v>
       </c>
     </row>
     <row r="6">
@@ -1969,25 +1969,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.9240205646043</v>
+        <v>63.32267037234308</v>
       </c>
       <c r="C6" t="n">
-        <v>31.31328864700969</v>
+        <v>53.51522446621205</v>
       </c>
       <c r="D6" t="n">
-        <v>9.305540586436976</v>
+        <v>103.9313656776203</v>
       </c>
       <c r="E6" t="n">
-        <v>27.20068142963095</v>
+        <v>263.3582875568143</v>
       </c>
       <c r="F6" t="n">
-        <v>16.92878018429704</v>
+        <v>39.03103174196716</v>
       </c>
       <c r="G6" t="n">
-        <v>22.79676209996704</v>
+        <v>35.62750364008171</v>
       </c>
       <c r="H6" t="n">
-        <v>22.57817891865767</v>
+        <v>93.13101390917312</v>
       </c>
     </row>
     <row r="7">
@@ -1997,25 +1997,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1422892014881623</v>
+        <v>0.5690604384235899</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08638956849866403</v>
+        <v>0.4811150211226212</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006024340058934072</v>
+        <v>0.7971576998927848</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02361828757270232</v>
+        <v>3.561481421912899</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03277193836230934</v>
+        <v>0.1887918989641253</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03708349492271733</v>
+        <v>0.1224371283961252</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05469613848391491</v>
+        <v>0.9533406014520245</v>
       </c>
     </row>
     <row r="8">
@@ -2025,25 +2025,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-34.29718647753548</v>
+        <v>5.236806734786176</v>
       </c>
       <c r="C8" t="n">
-        <v>-38.53559834178781</v>
+        <v>3.240934479942229</v>
       </c>
       <c r="D8" t="n">
-        <v>-173.506755182954</v>
+        <v>-65.92602156633606</v>
       </c>
       <c r="E8" t="n">
-        <v>-155.6546036028755</v>
+        <v>-48.02710638750537</v>
       </c>
       <c r="F8" t="n">
-        <v>-144.4439642922032</v>
+        <v>-81.0530060697741</v>
       </c>
       <c r="G8" t="n">
-        <v>-132.9688712450058</v>
+        <v>-87.46718233332599</v>
       </c>
       <c r="H8" t="n">
-        <v>-113.234496523727</v>
+        <v>-45.66592919036885</v>
       </c>
     </row>
     <row r="9">
@@ -2053,25 +2053,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-32.63075978942305</v>
+        <v>13.56894017534834</v>
       </c>
       <c r="C9" t="n">
-        <v>-37.11949793958339</v>
+        <v>10.32143649096433</v>
       </c>
       <c r="D9" t="n">
-        <v>-171.4177103075071</v>
+        <v>-55.48079718910184</v>
       </c>
       <c r="E9" t="n">
-        <v>-153.5655587274286</v>
+        <v>-37.58188201027114</v>
       </c>
       <c r="F9" t="n">
-        <v>-141.8522905601945</v>
+        <v>-68.09463740973081</v>
       </c>
       <c r="G9" t="n">
-        <v>-130.5311195952694</v>
+        <v>-75.27842408464399</v>
       </c>
       <c r="H9" t="n">
-        <v>-111.1861561532344</v>
+        <v>-35.42422733790585</v>
       </c>
     </row>
   </sheetData>
@@ -2132,25 +2132,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7388049093520619</v>
+        <v>0.1130861187168157</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8577708012712317</v>
+        <v>0.2033282490118992</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9499652573049657</v>
+        <v>-0.4225667783003679</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7365243664140038</v>
+        <v>-3.377250713582629</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9053226462049749</v>
+        <v>0.4717190389513835</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8715637705300524</v>
+        <v>0.7267780433666391</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8433252918462152</v>
+        <v>-0.3808176736393765</v>
       </c>
     </row>
     <row r="3">
@@ -2160,25 +2160,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1439453803047641</v>
+        <v>0.3405491397571973</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1072821667145773</v>
+        <v>0.2416279038585004</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01683692430117755</v>
+        <v>0.1273807160377483</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02901271390053664</v>
+        <v>0.1134301350595568</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03400282181403558</v>
+        <v>0.1204446634265555</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04258782996654237</v>
+        <v>0.07322022915326605</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0622779728336056</v>
+        <v>0.1694421312154707</v>
       </c>
     </row>
     <row r="4">
@@ -2188,25 +2188,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.121629286498055</v>
+        <v>0.4130043267585664</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05649647661229673</v>
+        <v>0.3164550412268676</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006568329936611648</v>
+        <v>0.01867479965609344</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001771723762108989</v>
+        <v>0.02943452112216524</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004024132233116191</v>
+        <v>0.02245386418488013</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004850470758028374</v>
+        <v>0.01031839004127341</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03157148714287775</v>
+        <v>0.1350568238316411</v>
       </c>
     </row>
     <row r="5">
@@ -2216,25 +2216,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3487539053516893</v>
+        <v>0.6426541268509574</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2376898748628067</v>
+        <v>0.5625433683076067</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02562875325998448</v>
+        <v>0.136655770665177</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04209184911724584</v>
+        <v>0.1715649180985589</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06343604837248448</v>
+        <v>0.1498461350348421</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0696453211495817</v>
+        <v>0.1015794764766653</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1312076253522987</v>
+        <v>0.2941406325723012</v>
       </c>
     </row>
     <row r="6">
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.40264952955293</v>
+        <v>62.22221744413092</v>
       </c>
       <c r="C6" t="n">
-        <v>28.13007562840134</v>
+        <v>52.07483853457941</v>
       </c>
       <c r="D6" t="n">
-        <v>21.04306862074701</v>
+        <v>109.9823622282129</v>
       </c>
       <c r="E6" t="n">
-        <v>50.4995424251799</v>
+        <v>230.1755335844067</v>
       </c>
       <c r="F6" t="n">
-        <v>16.38709811027314</v>
+        <v>39.48506754799362</v>
       </c>
       <c r="G6" t="n">
-        <v>30.40488573384484</v>
+        <v>72.96655181913506</v>
       </c>
       <c r="H6" t="n">
-        <v>28.14455334133319</v>
+        <v>94.48442852640977</v>
       </c>
     </row>
     <row r="7">
@@ -2272,25 +2272,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1659990277430199</v>
+        <v>0.5606771931159517</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0847162932472382</v>
+        <v>0.4660200541552376</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0179702059040731</v>
+        <v>0.8906847864987517</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08278289670927517</v>
+        <v>2.678558757720609</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03372009870168886</v>
+        <v>0.1797019932440011</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04442619837160415</v>
+        <v>0.09468946001889966</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07160245344614992</v>
+        <v>0.8117220407922418</v>
       </c>
     </row>
     <row r="8">
@@ -2300,25 +2300,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-25.81521742411935</v>
+        <v>6.966947435729205</v>
       </c>
       <c r="C8" t="n">
-        <v>-33.10365505427849</v>
+        <v>4.741388540139084</v>
       </c>
       <c r="D8" t="n">
-        <v>-143.8896961098028</v>
+        <v>-61.59218579475746</v>
       </c>
       <c r="E8" t="n">
-        <v>-123.0518489175913</v>
+        <v>-52.03732921819073</v>
       </c>
       <c r="F8" t="n">
-        <v>-138.9170416115305</v>
+        <v>-80.49989900004995</v>
       </c>
       <c r="G8" t="n">
-        <v>-123.2169878808025</v>
+        <v>-92.34568837127873</v>
       </c>
       <c r="H8" t="n">
-        <v>-97.99907449968748</v>
+        <v>-45.7944610680681</v>
       </c>
     </row>
     <row r="9">
@@ -2328,25 +2328,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-21.64915070383827</v>
+        <v>16.13229422034758</v>
       </c>
       <c r="C9" t="n">
-        <v>-29.56340404876744</v>
+        <v>12.5299407522634</v>
       </c>
       <c r="D9" t="n">
-        <v>-138.6670839211857</v>
+        <v>-50.1024389797998</v>
       </c>
       <c r="E9" t="n">
-        <v>-117.8292367289742</v>
+        <v>-40.54758240323308</v>
       </c>
       <c r="F9" t="n">
-        <v>-132.4378572815089</v>
+        <v>-66.24569347400234</v>
       </c>
       <c r="G9" t="n">
-        <v>-117.1226087564615</v>
+        <v>-78.93805429772851</v>
       </c>
       <c r="H9" t="n">
-        <v>-92.87822357345597</v>
+        <v>-34.52858903035879</v>
       </c>
     </row>
   </sheetData>
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7736964146988832</v>
+        <v>0.09212463267433868</v>
       </c>
       <c r="C2" t="n">
-        <v>0.858601813513064</v>
+        <v>0.1501112108538304</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9782094616359909</v>
+        <v>-0.4149964112243847</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8889193018310366</v>
+        <v>-4.484551565726319</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9034751457947169</v>
+        <v>0.5198555107245972</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8778047364121809</v>
+        <v>0.6317895762553571</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8801178123143121</v>
+        <v>-0.5842778410737633</v>
       </c>
     </row>
     <row r="3">
@@ -2435,25 +2435,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1372206164809731</v>
+        <v>0.3456196508269823</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1071668293816007</v>
+        <v>0.2602372492759303</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01181013054535976</v>
+        <v>0.1264606903518904</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01863804697535517</v>
+        <v>0.1283459030488752</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03312225494784676</v>
+        <v>0.1119945783097384</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03680084791729295</v>
+        <v>0.07948121999984278</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0574597877080714</v>
+        <v>0.1753565486355432</v>
       </c>
     </row>
     <row r="4">
@@ -2463,25 +2463,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.105381550410637</v>
+        <v>0.4227653470938295</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05616638079438568</v>
+        <v>0.3375939858215468</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002860561237290228</v>
+        <v>0.01857541937347782</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007469545087681651</v>
+        <v>0.03688048948305424</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00410265772684419</v>
+        <v>0.02040788888153091</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004614776961674747</v>
+        <v>0.01390568611789188</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02854972942100646</v>
+        <v>0.1416881361285552</v>
       </c>
     </row>
     <row r="5">
@@ -2491,25 +2491,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3246252461079344</v>
+        <v>0.6502040811113304</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2369944741853398</v>
+        <v>0.581028386416315</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01691319377672422</v>
+        <v>0.1362916702277796</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02733046850619588</v>
+        <v>0.1920429365612134</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0640519923721674</v>
+        <v>0.1428561825107017</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06793214969125257</v>
+        <v>0.1179223732711137</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1229745874399357</v>
+        <v>0.3033909383497423</v>
       </c>
     </row>
     <row r="6">
@@ -2519,25 +2519,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.91759303961165</v>
+        <v>63.54941805166595</v>
       </c>
       <c r="C6" t="n">
-        <v>30.17874157627624</v>
+        <v>54.40376189025745</v>
       </c>
       <c r="D6" t="n">
-        <v>12.28330468743393</v>
+        <v>110.5248649180972</v>
       </c>
       <c r="E6" t="n">
-        <v>36.47160599518342</v>
+        <v>253.4112200154135</v>
       </c>
       <c r="F6" t="n">
-        <v>18.41352907818878</v>
+        <v>37.97287630262323</v>
       </c>
       <c r="G6" t="n">
-        <v>27.36120425701802</v>
+        <v>37.74504154817007</v>
       </c>
       <c r="H6" t="n">
-        <v>25.43766310561868</v>
+        <v>92.93453045437126</v>
       </c>
     </row>
     <row r="7">
@@ -2547,25 +2547,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1426581608777809</v>
+        <v>0.573798353163379</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08273592250215078</v>
+        <v>0.4967824268189336</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007737400795813055</v>
+        <v>0.8860034338574999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03484707760682674</v>
+        <v>3.353363624712068</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03282931667037588</v>
+        <v>0.1638288689996925</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04088892294951805</v>
+        <v>0.1256971074059172</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05694946690041091</v>
+        <v>0.9332456358262481</v>
       </c>
     </row>
     <row r="8">
@@ -2575,25 +2575,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-34.25285092956518</v>
+        <v>7.364054189362752</v>
       </c>
       <c r="C8" t="n">
-        <v>-39.19155361377477</v>
+        <v>5.711330036070226</v>
       </c>
       <c r="D8" t="n">
-        <v>-167.3457731212132</v>
+        <v>-61.70423833784939</v>
       </c>
       <c r="E8" t="n">
-        <v>-147.1896317383741</v>
+        <v>-47.30152476935936</v>
       </c>
       <c r="F8" t="n">
-        <v>-144.3952478089421</v>
+        <v>-83.07951106116184</v>
       </c>
       <c r="G8" t="n">
-        <v>-130.4622935298273</v>
+        <v>-84.88643623158755</v>
       </c>
       <c r="H8" t="n">
-        <v>-110.4728917902828</v>
+        <v>-43.98272102908752</v>
       </c>
     </row>
     <row r="9">
@@ -2603,25 +2603,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-32.58642424145275</v>
+        <v>16.52940097398113</v>
       </c>
       <c r="C9" t="n">
-        <v>-37.77545321157035</v>
+        <v>13.49988224819454</v>
       </c>
       <c r="D9" t="n">
-        <v>-165.2567282457664</v>
+        <v>-50.21449152289173</v>
       </c>
       <c r="E9" t="n">
-        <v>-145.1005868629273</v>
+        <v>-35.81177795440171</v>
       </c>
       <c r="F9" t="n">
-        <v>-141.8035740769334</v>
+        <v>-68.82530553511421</v>
       </c>
       <c r="G9" t="n">
-        <v>-128.0245418800909</v>
+        <v>-71.47880215803735</v>
       </c>
       <c r="H9" t="n">
-        <v>-108.4245514197902</v>
+        <v>-32.71684899137822</v>
       </c>
     </row>
   </sheetData>
@@ -2682,25 +2682,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.920063742598861</v>
+        <v>0.726411779233697</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8550242300706042</v>
+        <v>0.7258531696082796</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8915637178429319</v>
+        <v>0.9708809804326931</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7651314696749565</v>
+        <v>0.4674560621939903</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7913946740127938</v>
+        <v>0.9254129066991602</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8751218123077869</v>
+        <v>0.7872243118184897</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8497166077513224</v>
+        <v>0.7672065349977183</v>
       </c>
     </row>
     <row r="3">
@@ -2710,25 +2710,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09994106982728319</v>
+        <v>0.159877489240433</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1247466765543966</v>
+        <v>0.1490922546980404</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0212527111239967</v>
+        <v>0.009058483378029343</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02253931476548243</v>
+        <v>0.02830952337359156</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05233457662683261</v>
+        <v>0.03279428303835275</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04210461578349364</v>
+        <v>0.05647602664676972</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06048649411358086</v>
+        <v>0.07260134339586945</v>
       </c>
     </row>
     <row r="4">
@@ -2738,25 +2738,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03722347892874592</v>
+        <v>0.1274003274852153</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05758747337658399</v>
+        <v>0.108896978468517</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00142350143109225</v>
+        <v>0.0003822610403224964</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001579357265356671</v>
+        <v>0.003581055052933547</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008866485834851643</v>
+        <v>0.003170223018443993</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004716099189585667</v>
+        <v>0.008035600685282246</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01856606600436935</v>
+        <v>0.04191107429178575</v>
       </c>
     </row>
     <row r="5">
@@ -2766,25 +2766,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1929338719062724</v>
+        <v>0.3569318247021625</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2399739014488534</v>
+        <v>0.3299954218902393</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03772931792508646</v>
+        <v>0.01955149713762341</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0397411281339203</v>
+        <v>0.05984191718965517</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09416201906741191</v>
+        <v>0.05630473353497016</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06867386103595506</v>
+        <v>0.08964151206490353</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1122023499195833</v>
+        <v>0.1520444844199257</v>
       </c>
     </row>
     <row r="6">
@@ -2794,25 +2794,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.56551495638706</v>
+        <v>25.14079915399827</v>
       </c>
       <c r="C6" t="n">
-        <v>42.48157774250674</v>
+        <v>39.74336976680024</v>
       </c>
       <c r="D6" t="n">
-        <v>34.14502427166043</v>
+        <v>13.63992424374445</v>
       </c>
       <c r="E6" t="n">
-        <v>44.10323909287983</v>
+        <v>59.95922179819762</v>
       </c>
       <c r="F6" t="n">
-        <v>31.4921229351972</v>
+        <v>19.29338845990508</v>
       </c>
       <c r="G6" t="n">
-        <v>27.65186461863813</v>
+        <v>35.60052916064681</v>
       </c>
       <c r="H6" t="n">
-        <v>35.23989060287823</v>
+        <v>32.22953876388208</v>
       </c>
     </row>
     <row r="7">
@@ -2822,25 +2822,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05053731247046384</v>
+        <v>0.1732566954695416</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08430396234242751</v>
+        <v>0.160471934045478</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03402733564888502</v>
+        <v>0.01100328859841782</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07206610918326273</v>
+        <v>0.1642699198788564</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06928813788055802</v>
+        <v>0.02659528410316274</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04126472574037392</v>
+        <v>0.07145762693415067</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05858126387766183</v>
+        <v>0.1011757915049345</v>
       </c>
     </row>
     <row r="8">
@@ -2850,25 +2850,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-53.94386456757291</v>
+        <v>-27.02715641043635</v>
       </c>
       <c r="C8" t="n">
-        <v>-40.8167531654893</v>
+        <v>-25.26029493033172</v>
       </c>
       <c r="D8" t="n">
-        <v>-135.6473485641768</v>
+        <v>-157.2575434532373</v>
       </c>
       <c r="E8" t="n">
-        <v>-133.465483484474</v>
+        <v>-110.2740541037424</v>
       </c>
       <c r="F8" t="n">
-        <v>-125.5878721591766</v>
+        <v>-147.3567402001459</v>
       </c>
       <c r="G8" t="n">
-        <v>-131.9193315990315</v>
+        <v>-112.5968380998875</v>
       </c>
       <c r="H8" t="n">
-        <v>-103.5634422566535</v>
+        <v>-96.62877119963019</v>
       </c>
     </row>
     <row r="9">
@@ -2878,25 +2878,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-53.11065122351669</v>
+        <v>-23.69430303421149</v>
       </c>
       <c r="C9" t="n">
-        <v>-40.10870296438709</v>
+        <v>-22.42809412592288</v>
       </c>
       <c r="D9" t="n">
-        <v>-134.6028261264533</v>
+        <v>-153.0794537023436</v>
       </c>
       <c r="E9" t="n">
-        <v>-132.4209610467505</v>
+        <v>-106.0959643528487</v>
       </c>
       <c r="F9" t="n">
-        <v>-124.2920352931722</v>
+        <v>-142.1733927361285</v>
       </c>
       <c r="G9" t="n">
-        <v>-130.7004557741633</v>
+        <v>-107.7213348004148</v>
       </c>
       <c r="H9" t="n">
-        <v>-102.5392720714072</v>
+        <v>-92.53209045864499</v>
       </c>
     </row>
   </sheetData>
@@ -2957,25 +2957,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9431105538204944</v>
+        <v>0.4204253555122824</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8627538647097533</v>
+        <v>0.4880593710856301</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9731380511535257</v>
+        <v>0.05239166535507711</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9613841049536853</v>
+        <v>-0.1716856824784851</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9021899275116455</v>
+        <v>0.7592406713082724</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8889921836585174</v>
+        <v>0.5314895472077679</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9219281143012702</v>
+        <v>0.3466534879984242</v>
       </c>
     </row>
     <row r="3">
@@ -2985,25 +2985,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08902164925173872</v>
+        <v>0.2761769702829606</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1123331645170063</v>
+        <v>0.2305937592937447</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01535722088767351</v>
+        <v>0.1067363590841978</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01362723528795824</v>
+        <v>0.07654976174873182</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03428372433901413</v>
+        <v>0.08522472772514221</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02921886286595593</v>
+        <v>0.1000657341971677</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04897364285822448</v>
+        <v>0.1458912187219908</v>
       </c>
     </row>
     <row r="4">
@@ -3013,25 +3013,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0264913966450058</v>
+        <v>0.2698873485965402</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05451709734609628</v>
+        <v>0.203353755957672</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003526312583227071</v>
+        <v>0.01243976456632939</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002596699281731947</v>
+        <v>0.007878919720644542</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004157284183036607</v>
+        <v>0.01023314801456466</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0041922763483409</v>
+        <v>0.0176935764968956</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01499505928482925</v>
+        <v>0.08691441889210773</v>
       </c>
     </row>
     <row r="5">
@@ -3041,25 +3041,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1627617788210912</v>
+        <v>0.5195068320980392</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2334889662191691</v>
+        <v>0.4509476199711802</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01877847859446306</v>
+        <v>0.1115336925163396</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01611427715329467</v>
+        <v>0.08876327912287008</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06447700507185959</v>
+        <v>0.1011590233966534</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06474779029697383</v>
+        <v>0.1330172037628802</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09339471602614191</v>
+        <v>0.2341546084779938</v>
       </c>
     </row>
     <row r="6">
@@ -3069,25 +3069,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24.32232643016287</v>
+        <v>59.27281927258762</v>
       </c>
       <c r="C6" t="n">
-        <v>32.19006526294063</v>
+        <v>48.78328787332875</v>
       </c>
       <c r="D6" t="n">
-        <v>13.81811905620815</v>
+        <v>79.32415761684642</v>
       </c>
       <c r="E6" t="n">
-        <v>14.26791006591968</v>
+        <v>94.58225484610304</v>
       </c>
       <c r="F6" t="n">
-        <v>15.49034871354317</v>
+        <v>33.32517274829666</v>
       </c>
       <c r="G6" t="n">
-        <v>15.54575743996481</v>
+        <v>45.794143357096</v>
       </c>
       <c r="H6" t="n">
-        <v>19.27242116145655</v>
+        <v>60.18030595237641</v>
       </c>
     </row>
     <row r="7">
@@ -3097,25 +3097,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03661081150535575</v>
+        <v>0.3687935373638934</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0803358087293414</v>
+        <v>0.3019298178446813</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009305426534768187</v>
+        <v>0.2989903355899075</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01276653746361564</v>
+        <v>0.7260418970959935</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03325312067463198</v>
+        <v>0.08539100221771355</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03723693834628342</v>
+        <v>0.1589386393854966</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0349181072089994</v>
+        <v>0.3233475382496143</v>
       </c>
     </row>
     <row r="8">
@@ -3125,25 +3125,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-57.72589931132265</v>
+        <v>1.734239214051453</v>
       </c>
       <c r="C8" t="n">
-        <v>-39.63861370607138</v>
+        <v>0.1078773541429427</v>
       </c>
       <c r="D8" t="n">
-        <v>-162.9518404607099</v>
+        <v>-68.12399946511474</v>
       </c>
       <c r="E8" t="n">
-        <v>-169.3780840501139</v>
+        <v>-77.71485399177863</v>
       </c>
       <c r="F8" t="n">
-        <v>-144.0381179799966</v>
+        <v>-99.717321608769</v>
       </c>
       <c r="G8" t="n">
-        <v>-132.862785283624</v>
+        <v>-76.86384037624885</v>
       </c>
       <c r="H8" t="n">
-        <v>-117.7658901319731</v>
+        <v>-53.42964981228613</v>
       </c>
     </row>
     <row r="9">
@@ -3153,25 +3153,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-56.05947262321022</v>
+        <v>11.73279934272605</v>
       </c>
       <c r="C9" t="n">
-        <v>-38.22251330386696</v>
+        <v>8.604479767369462</v>
       </c>
       <c r="D9" t="n">
-        <v>-160.862795585263</v>
+        <v>-55.58973021243366</v>
       </c>
       <c r="E9" t="n">
-        <v>-167.2890391746671</v>
+        <v>-65.18058473909755</v>
       </c>
       <c r="F9" t="n">
-        <v>-141.446444247988</v>
+        <v>-84.16727921671705</v>
       </c>
       <c r="G9" t="n">
-        <v>-130.4250336338876</v>
+        <v>-62.23733047783044</v>
       </c>
       <c r="H9" t="n">
-        <v>-115.7175497614805</v>
+        <v>-41.13960758933053</v>
       </c>
     </row>
   </sheetData>
@@ -3232,25 +3232,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8019640205902898</v>
+        <v>0.9695101197845015</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8822141585107374</v>
+        <v>0.8581468750836957</v>
       </c>
       <c r="D2" t="n">
-        <v>0.908873563489608</v>
+        <v>0.9693048680841891</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9251973998991592</v>
+        <v>0.9384987207843132</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8806182812863445</v>
+        <v>0.8022037546634957</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8798960873609061</v>
+        <v>0.6611073136951809</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8797939185228408</v>
+        <v>0.8664619420158961</v>
       </c>
     </row>
     <row r="3">
@@ -3260,25 +3260,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1441004245883649</v>
+        <v>0.07231995806291859</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1088601503959113</v>
+        <v>0.1019771427970955</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02372084910291132</v>
+        <v>0.01538470349670535</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01682948735854642</v>
+        <v>0.01439940736048355</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04634280159462015</v>
+        <v>0.08400206074545007</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03154098610558934</v>
+        <v>0.101110126919187</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06189911652432389</v>
+        <v>0.06486556656364001</v>
       </c>
     </row>
     <row r="4">
@@ -3288,25 +3288,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09221832928327557</v>
+        <v>0.0141980554336714</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04678705285859022</v>
+        <v>0.05634709205877136</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001196265771957996</v>
+        <v>0.0004029515153095287</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0005030049354561645</v>
+        <v>0.0004135611187399137</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005074157684640267</v>
+        <v>0.008407060554007688</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004535795846584166</v>
+        <v>0.01279848428916883</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02505243439675073</v>
+        <v>0.01542786749494479</v>
       </c>
     </row>
     <row r="5">
@@ -3316,25 +3316,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3036747096537273</v>
+        <v>0.1191555933797125</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2163031503667716</v>
+        <v>0.2373754242940312</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03458707521543266</v>
+        <v>0.02007365226632983</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02242777152229273</v>
+        <v>0.02033620217100316</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07123312210369744</v>
+        <v>0.09169002428840167</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06734831732555882</v>
+        <v>0.1131303862327396</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1192623576979134</v>
+        <v>0.1002935471053697</v>
       </c>
     </row>
     <row r="6">
@@ -3344,25 +3344,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.24222264746874</v>
+        <v>19.67142695695851</v>
       </c>
       <c r="C6" t="n">
-        <v>37.8798940825658</v>
+        <v>24.4297786904916</v>
       </c>
       <c r="D6" t="n">
-        <v>32.65960157139312</v>
+        <v>14.13290174552041</v>
       </c>
       <c r="E6" t="n">
-        <v>29.97016863609783</v>
+        <v>20.35271219204454</v>
       </c>
       <c r="F6" t="n">
-        <v>28.28077476680975</v>
+        <v>30.31799706002684</v>
       </c>
       <c r="G6" t="n">
-        <v>19.90828236020199</v>
+        <v>61.43410228487064</v>
       </c>
       <c r="H6" t="n">
-        <v>30.82349067742287</v>
+        <v>28.38981982165209</v>
       </c>
     </row>
     <row r="7">
@@ -3372,25 +3372,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.124463624321206</v>
+        <v>0.02208560286821952</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06858668944779195</v>
+        <v>0.08499890191603125</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0286753169934882</v>
+        <v>0.01249060563545993</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02329288348507157</v>
+        <v>0.02173987654782399</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03986642599334485</v>
+        <v>0.06822381598875668</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0397062308843371</v>
+        <v>0.1136267448938639</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05409852852087327</v>
+        <v>0.05386092464169254</v>
       </c>
     </row>
     <row r="8">
@@ -3400,25 +3400,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-38.52113827316452</v>
+        <v>-60.32905450573071</v>
       </c>
       <c r="C8" t="n">
-        <v>-43.93223143980195</v>
+        <v>-31.14336967228024</v>
       </c>
       <c r="D8" t="n">
-        <v>-139.2995590464668</v>
+        <v>-152.1505805658807</v>
       </c>
       <c r="E8" t="n">
-        <v>-157.4931220933243</v>
+        <v>-151.6048101681858</v>
       </c>
       <c r="F8" t="n">
-        <v>-140.6570580150812</v>
+        <v>-117.0244513692641</v>
       </c>
       <c r="G8" t="n">
-        <v>-132.8938680234089</v>
+        <v>-96.96071324942123</v>
       </c>
       <c r="H8" t="n">
-        <v>-108.7994961485413</v>
+        <v>-101.5354965884604</v>
       </c>
     </row>
     <row r="9">
@@ -3428,25 +3428,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-37.6879249291083</v>
+        <v>-55.32977444139341</v>
       </c>
       <c r="C9" t="n">
-        <v>-43.22418123869974</v>
+        <v>-26.89506846566698</v>
       </c>
       <c r="D9" t="n">
-        <v>-138.2550366087434</v>
+        <v>-145.8834459395401</v>
       </c>
       <c r="E9" t="n">
-        <v>-156.4485996556008</v>
+        <v>-145.3376755418452</v>
       </c>
       <c r="F9" t="n">
-        <v>-139.3612211490769</v>
+        <v>-109.2494301732381</v>
       </c>
       <c r="G9" t="n">
-        <v>-131.6749921985407</v>
+        <v>-89.64745830021204</v>
       </c>
       <c r="H9" t="n">
-        <v>-107.775325963295</v>
+        <v>-95.39047547698264</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/global/metrics_summary.xlsx
+++ b/results/cross_validation/global/metrics_summary.xlsx
@@ -1032,25 +1032,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8688950948458743</v>
+        <v>0.8635161308356141</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9184098962007062</v>
+        <v>0.9274242924144508</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7639331374052144</v>
+        <v>0.6919865208624193</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8701651020985333</v>
+        <v>0.8367877654053377</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9223722895751213</v>
+        <v>0.8569794175205069</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7290193634425375</v>
+        <v>0.7113787418530546</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8454658139279978</v>
+        <v>0.8146788114818971</v>
       </c>
     </row>
     <row r="3">
@@ -1060,25 +1060,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1174371246339853</v>
+        <v>0.1200258956670411</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08063647277549375</v>
+        <v>0.07220455354837098</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02609243649317531</v>
+        <v>0.03194159361800907</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01317981080501577</v>
+        <v>0.01568313517011858</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03297359540111087</v>
+        <v>0.03748530671438891</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05177196471575596</v>
+        <v>0.05938689209233557</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05368190080408949</v>
+        <v>0.05612122946837737</v>
       </c>
     </row>
     <row r="4">
@@ -1088,25 +1088,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06105090272077578</v>
+        <v>0.0635556954144046</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03240933248792397</v>
+        <v>0.02882862170971729</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003098976745167125</v>
+        <v>0.004043458698749472</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008730658339528877</v>
+        <v>0.00109750943706864</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003299460316350529</v>
+        <v>0.006078895457944489</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01023374525270873</v>
+        <v>0.01089995384140958</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01849424722614651</v>
+        <v>0.01908402242654901</v>
       </c>
     </row>
     <row r="5">
@@ -1116,25 +1116,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2470848087616391</v>
+        <v>0.2521025494008433</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1800259217110802</v>
+        <v>0.1697899340647651</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05566845377022003</v>
+        <v>0.06358819622185766</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02954768745524576</v>
+        <v>0.03312867997775704</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05744092893008024</v>
+        <v>0.0779672717102791</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1011619753302037</v>
+        <v>0.1044028440293155</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1118216293264115</v>
+        <v>0.1168299125674696</v>
       </c>
     </row>
     <row r="6">
@@ -1144,25 +1144,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.37741035006173</v>
+        <v>28.40922376265657</v>
       </c>
       <c r="C6" t="n">
-        <v>24.26671134951604</v>
+        <v>20.81703741030798</v>
       </c>
       <c r="D6" t="n">
-        <v>42.49977455893399</v>
+        <v>62.48614474318907</v>
       </c>
       <c r="E6" t="n">
-        <v>23.99208358450983</v>
+        <v>29.36515904949455</v>
       </c>
       <c r="F6" t="n">
-        <v>22.58422612572181</v>
+        <v>25.54810794497702</v>
       </c>
       <c r="G6" t="n">
-        <v>38.28069000917452</v>
+        <v>48.55059624043687</v>
       </c>
       <c r="H6" t="n">
-        <v>29.66681599631965</v>
+        <v>35.86271152517701</v>
       </c>
     </row>
     <row r="7">
@@ -1172,25 +1172,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08506710345078075</v>
+        <v>0.08793414753939902</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05016356388133492</v>
+        <v>0.04445274747246687</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07598934250005268</v>
+        <v>0.09773446483039885</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04256161545420705</v>
+        <v>0.05223192698434674</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02859793534890898</v>
+        <v>0.04966140156440908</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09145781264413488</v>
+        <v>0.09671634513307034</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0623062288799032</v>
+        <v>0.07145517225401515</v>
       </c>
     </row>
     <row r="8">
@@ -1200,25 +1200,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-35.53280396321205</v>
+        <v>-36.84925729419962</v>
       </c>
       <c r="C8" t="n">
-        <v>-39.43963286862898</v>
+        <v>-43.19579863964965</v>
       </c>
       <c r="D8" t="n">
-        <v>-109.3103493878705</v>
+        <v>-105.7237516339817</v>
       </c>
       <c r="E8" t="n">
-        <v>-135.9134914697214</v>
+        <v>-133.1089481014785</v>
       </c>
       <c r="F8" t="n">
-        <v>-142.2779018383612</v>
+        <v>-127.7791712254415</v>
       </c>
       <c r="G8" t="n">
-        <v>-102.551616528988</v>
+        <v>-102.9749181122268</v>
       </c>
       <c r="H8" t="n">
-        <v>-94.17096600946371</v>
+        <v>-91.60530750116294</v>
       </c>
     </row>
     <row r="9">
@@ -1228,25 +1228,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-30.53352389887475</v>
+        <v>-32.68319057391854</v>
       </c>
       <c r="C9" t="n">
-        <v>-35.19133166201571</v>
+        <v>-39.65554763413859</v>
       </c>
       <c r="D9" t="n">
-        <v>-103.04321476153</v>
+        <v>-100.5011394453645</v>
       </c>
       <c r="E9" t="n">
-        <v>-129.6463568433809</v>
+        <v>-127.8863359128613</v>
       </c>
       <c r="F9" t="n">
-        <v>-134.5028806423352</v>
+        <v>-121.2999868954199</v>
       </c>
       <c r="G9" t="n">
-        <v>-95.2383615797788</v>
+        <v>-96.8805389878858</v>
       </c>
       <c r="H9" t="n">
-        <v>-88.02594489798589</v>
+        <v>-86.48445657493146</v>
       </c>
     </row>
   </sheetData>
@@ -1582,25 +1582,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9312334534953024</v>
+        <v>0.8958903074130051</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9361687079093279</v>
+        <v>0.7439100695931469</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9098130984259211</v>
+        <v>0.9486896870641257</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6085067670360935</v>
+        <v>0.4555070504342578</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6071193009776117</v>
+        <v>0.7158218439461952</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.9285105797763178</v>
+        <v>-0.5077678548462505</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5107217913446565</v>
+        <v>0.5420085172674134</v>
       </c>
     </row>
     <row r="3">
@@ -1610,25 +1610,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0800390014471514</v>
+        <v>0.1441878508100221</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06973092412027639</v>
+        <v>0.1256409906147258</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01408566284576012</v>
+        <v>0.01328333157446684</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01777861365224019</v>
+        <v>0.02957469910117699</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07930506973908301</v>
+        <v>0.06822458151453083</v>
       </c>
       <c r="G3" t="n">
-        <v>0.154291098654353</v>
+        <v>0.115807023248655</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06920506174314402</v>
+        <v>0.08278641281059625</v>
       </c>
     </row>
     <row r="4">
@@ -1638,25 +1638,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03202214086625183</v>
+        <v>0.04848019001994208</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02535515304146834</v>
+        <v>0.1017243919897655</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001183931991236286</v>
+        <v>0.0006735780906635165</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002632569297231171</v>
+        <v>0.003661405360020019</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01669886008990135</v>
+        <v>0.01207860625466414</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07283135149916661</v>
+        <v>0.05694175171607746</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0251206677975426</v>
+        <v>0.03725998723852211</v>
       </c>
     </row>
     <row r="5">
@@ -1666,25 +1666,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1789473131015155</v>
+        <v>0.2201821746189779</v>
       </c>
       <c r="C5" t="n">
-        <v>0.159233014923</v>
+        <v>0.3189426155122038</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03440831282170467</v>
+        <v>0.02595338302926068</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05130856943270949</v>
+        <v>0.06050954767654456</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1292240693133495</v>
+        <v>0.1099027126810987</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2698728432042887</v>
+        <v>0.2386247089386962</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1371656871327613</v>
+        <v>0.162352523742797</v>
       </c>
     </row>
     <row r="6">
@@ -1694,25 +1694,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.88309192410653</v>
+        <v>62.48899674820906</v>
       </c>
       <c r="C6" t="n">
-        <v>20.11525247383939</v>
+        <v>27.04661798728282</v>
       </c>
       <c r="D6" t="n">
-        <v>18.49556494262038</v>
+        <v>21.4002615390904</v>
       </c>
       <c r="E6" t="n">
-        <v>34.30205163861444</v>
+        <v>70.541200845416</v>
       </c>
       <c r="F6" t="n">
-        <v>46.50810423900686</v>
+        <v>40.70773732539109</v>
       </c>
       <c r="G6" t="n">
-        <v>91.00086533547925</v>
+        <v>56.32509077886773</v>
       </c>
       <c r="H6" t="n">
-        <v>37.88415509227781</v>
+        <v>46.41831753737619</v>
       </c>
     </row>
     <row r="7">
@@ -1722,25 +1722,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04504546255778556</v>
+        <v>0.06716904079005792</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03889799475622946</v>
+        <v>0.1500340535148918</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02988482286608909</v>
+        <v>0.01786459854422675</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1212907683972338</v>
+        <v>0.1679108686217367</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1315534117696475</v>
+        <v>0.09570847119440636</v>
       </c>
       <c r="G7" t="n">
-        <v>1.263070239964624</v>
+        <v>0.9883791653102588</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2716237833852682</v>
+        <v>0.2478443663292631</v>
       </c>
     </row>
     <row r="8">
@@ -1750,25 +1750,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-50.50257112722071</v>
+        <v>-43.45220030048348</v>
       </c>
       <c r="C8" t="n">
-        <v>-47.12159940707654</v>
+        <v>-26.28232243167034</v>
       </c>
       <c r="D8" t="n">
-        <v>-133.5171978640897</v>
+        <v>-145.361039047346</v>
       </c>
       <c r="E8" t="n">
-        <v>-116.7356948019295</v>
+        <v>-109.8080727695632</v>
       </c>
       <c r="F8" t="n">
-        <v>-102.4952001394291</v>
+        <v>-111.2406256738364</v>
       </c>
       <c r="G8" t="n">
-        <v>-57.49021910056435</v>
+        <v>-63.64316083402579</v>
       </c>
       <c r="H8" t="n">
-        <v>-84.64374707338497</v>
+        <v>-83.29790350948753</v>
       </c>
     </row>
     <row r="9">
@@ -1778,25 +1778,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-47.16971775099584</v>
+        <v>-40.11934692425861</v>
       </c>
       <c r="C9" t="n">
-        <v>-44.2893986026677</v>
+        <v>-23.4501216272615</v>
       </c>
       <c r="D9" t="n">
-        <v>-129.339108113196</v>
+        <v>-141.1829492964523</v>
       </c>
       <c r="E9" t="n">
-        <v>-112.5576050510358</v>
+        <v>-105.6299830186695</v>
       </c>
       <c r="F9" t="n">
-        <v>-97.3118526754118</v>
+        <v>-106.057278209819</v>
       </c>
       <c r="G9" t="n">
-        <v>-52.61471580109154</v>
+        <v>-58.76765753455299</v>
       </c>
       <c r="H9" t="n">
-        <v>-80.54706633239978</v>
+        <v>-79.20122276850235</v>
       </c>
     </row>
   </sheetData>
@@ -1857,25 +1857,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09889484127984349</v>
+        <v>0.1032321143282143</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1763499024048283</v>
+        <v>0.4431147490055106</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2729382278028016</v>
+        <v>-0.1339146844465979</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.827697156941836</v>
+        <v>-4.584769980722569</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4426369112681671</v>
+        <v>0.7117462886343042</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6402444639199151</v>
+        <v>0.8940036128561037</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6237515443119807</v>
+        <v>-0.4277646500575056</v>
       </c>
     </row>
     <row r="3">
@@ -1885,25 +1885,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3441535538509446</v>
+        <v>0.343326201652348</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2548422155919852</v>
+        <v>0.2198393712871891</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1173305580172787</v>
+        <v>0.09457654006830352</v>
       </c>
       <c r="E3" t="n">
-        <v>0.140393589270286</v>
+        <v>0.1241508862805502</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1208409687503152</v>
+        <v>0.09312698184382569</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07725885001891726</v>
+        <v>0.04817259362934441</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1758032892499545</v>
+        <v>0.1538654291269268</v>
       </c>
     </row>
     <row r="4">
@@ -1913,25 +1913,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4196127011536328</v>
+        <v>0.4175929869817012</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3271714169200995</v>
+        <v>0.2212067201372725</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01671054515078844</v>
+        <v>0.01488550828133531</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03918794839128393</v>
+        <v>0.03755440131631604</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02368996049225053</v>
+        <v>0.01225183219350835</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0135863822458567</v>
+        <v>0.004003016737722151</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1399931590589853</v>
+        <v>0.1179157442746426</v>
       </c>
     </row>
     <row r="5">
@@ -1941,25 +1941,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6477751933762459</v>
+        <v>0.646214350646673</v>
       </c>
       <c r="C5" t="n">
-        <v>0.571989000698527</v>
+        <v>0.4703261848305625</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1292692738077709</v>
+        <v>0.1220061813242891</v>
       </c>
       <c r="E5" t="n">
-        <v>0.197959461484628</v>
+        <v>0.1937895799993282</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1539154329242215</v>
+        <v>0.1106879948029972</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1165606376349096</v>
+        <v>0.06326939811411321</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3029114999877172</v>
+        <v>0.267715614952994</v>
       </c>
     </row>
     <row r="6">
@@ -1969,25 +1969,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63.32267037234308</v>
+        <v>63.14897183776691</v>
       </c>
       <c r="C6" t="n">
-        <v>53.51522446621205</v>
+        <v>39.11604667153943</v>
       </c>
       <c r="D6" t="n">
-        <v>103.9313656776203</v>
+        <v>115.0037425913568</v>
       </c>
       <c r="E6" t="n">
-        <v>263.3582875568143</v>
+        <v>255.9946428701832</v>
       </c>
       <c r="F6" t="n">
-        <v>39.03103174196716</v>
+        <v>30.74711178745021</v>
       </c>
       <c r="G6" t="n">
-        <v>35.62750364008171</v>
+        <v>31.4650324959228</v>
       </c>
       <c r="H6" t="n">
-        <v>93.13101390917312</v>
+        <v>89.24592470903654</v>
       </c>
     </row>
     <row r="7">
@@ -1997,25 +1997,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5690604384235899</v>
+        <v>0.5648454565887265</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4811150211226212</v>
+        <v>0.3254102793944376</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7971576998927848</v>
+        <v>0.7081885222618283</v>
       </c>
       <c r="E7" t="n">
-        <v>3.561481421912899</v>
+        <v>3.410438150276384</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1887918989641253</v>
+        <v>0.09855239594516459</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1224371283961252</v>
+        <v>0.03810102785957439</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9533406014520245</v>
+        <v>0.8575893053876859</v>
       </c>
     </row>
     <row r="8">
@@ -2025,25 +2025,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.236806734786176</v>
+        <v>-0.8452166150755875</v>
       </c>
       <c r="C8" t="n">
-        <v>3.240934479942229</v>
+        <v>-8.629864441420224</v>
       </c>
       <c r="D8" t="n">
-        <v>-65.92602156633606</v>
+        <v>-74.35470989547393</v>
       </c>
       <c r="E8" t="n">
-        <v>-48.02710638750537</v>
+        <v>-54.92125860526009</v>
       </c>
       <c r="F8" t="n">
-        <v>-81.0530060697741</v>
+        <v>-104.8561542316766</v>
       </c>
       <c r="G8" t="n">
-        <v>-87.46718233332599</v>
+        <v>-124.0176754421469</v>
       </c>
       <c r="H8" t="n">
-        <v>-45.66592919036885</v>
+        <v>-61.27081320517556</v>
       </c>
     </row>
     <row r="9">
@@ -2053,25 +2053,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13.56894017534834</v>
+        <v>4.987276793317927</v>
       </c>
       <c r="C9" t="n">
-        <v>10.32143649096433</v>
+        <v>-3.673513033704754</v>
       </c>
       <c r="D9" t="n">
-        <v>-55.48079718910184</v>
+        <v>-67.04305283140997</v>
       </c>
       <c r="E9" t="n">
-        <v>-37.58188201027114</v>
+        <v>-47.60960154119613</v>
       </c>
       <c r="F9" t="n">
-        <v>-68.09463740973081</v>
+        <v>-95.78529616964633</v>
       </c>
       <c r="G9" t="n">
-        <v>-75.27842408464399</v>
+        <v>-115.4855446680695</v>
       </c>
       <c r="H9" t="n">
-        <v>-35.42422733790585</v>
+        <v>-54.10162190845145</v>
       </c>
     </row>
   </sheetData>
@@ -2132,25 +2132,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1130861187168157</v>
+        <v>0.2228024187830777</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2033282490118992</v>
+        <v>0.3151396057332018</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4225667783003679</v>
+        <v>-0.1334914745895861</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.377250713582629</v>
+        <v>-4.534726973031763</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4717190389513835</v>
+        <v>0.707467656043358</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7267780433666391</v>
+        <v>0.8943743467389862</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3808176736393765</v>
+        <v>-0.4214057367204542</v>
       </c>
     </row>
     <row r="3">
@@ -2160,25 +2160,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3405491397571973</v>
+        <v>0.3245494073843124</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2416279038585004</v>
+        <v>0.2238456824888949</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1273807160377483</v>
+        <v>0.09463628074493259</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1134301350595568</v>
+        <v>0.1233594474640085</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1204446634265555</v>
+        <v>0.09380194386886602</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07322022915326605</v>
+        <v>0.04817289223688312</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1694421312154707</v>
+        <v>0.1513942756979829</v>
       </c>
     </row>
     <row r="4">
@@ -2188,25 +2188,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4130043267585664</v>
+        <v>0.3619133385582822</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3164550412268676</v>
+        <v>0.2720411813692959</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01867479965609344</v>
+        <v>0.01487995257779103</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02943452112216524</v>
+        <v>0.03721789055573269</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02245386418488013</v>
+        <v>0.01243368965606654</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01031839004127341</v>
+        <v>0.003989015751665857</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1350568238316411</v>
+        <v>0.117079178078139</v>
       </c>
     </row>
     <row r="5">
@@ -2216,25 +2216,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6426541268509574</v>
+        <v>0.6015923358540085</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5625433683076067</v>
+        <v>0.5215756717575082</v>
       </c>
       <c r="D5" t="n">
-        <v>0.136655770665177</v>
+        <v>0.1219834110762239</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1715649180985589</v>
+        <v>0.1929193887501531</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1498461350348421</v>
+        <v>0.1115064556699142</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1015794764766653</v>
+        <v>0.06315865539786179</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2941406325723012</v>
+        <v>0.2687893197509449</v>
       </c>
     </row>
     <row r="6">
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62.22221744413092</v>
+        <v>59.35395510683754</v>
       </c>
       <c r="C6" t="n">
-        <v>52.07483853457941</v>
+        <v>46.33354123968762</v>
       </c>
       <c r="D6" t="n">
-        <v>109.9823622282129</v>
+        <v>114.867591256249</v>
       </c>
       <c r="E6" t="n">
-        <v>230.1755335844067</v>
+        <v>254.8196279404303</v>
       </c>
       <c r="F6" t="n">
-        <v>39.48506754799362</v>
+        <v>30.76776262222773</v>
       </c>
       <c r="G6" t="n">
-        <v>72.96655181913506</v>
+        <v>31.20479972250245</v>
       </c>
       <c r="H6" t="n">
-        <v>94.48442852640977</v>
+        <v>89.55787964798911</v>
       </c>
     </row>
     <row r="7">
@@ -2272,25 +2272,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5606771931159517</v>
+        <v>0.4899986113558742</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4660200541552376</v>
+        <v>0.3993869452385466</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8906847864987517</v>
+        <v>0.7079268183626592</v>
       </c>
       <c r="E7" t="n">
-        <v>2.678558757720609</v>
+        <v>3.379941230597084</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1797019932440011</v>
+        <v>0.09996328594623918</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09468946001889966</v>
+        <v>0.03798000700447025</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8117220407922418</v>
+        <v>0.8525328164174789</v>
       </c>
     </row>
     <row r="8">
@@ -2300,25 +2300,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.966947435729205</v>
+        <v>-3.277958365089034</v>
       </c>
       <c r="C8" t="n">
-        <v>4.741388540139084</v>
+        <v>-5.527027330799203</v>
       </c>
       <c r="D8" t="n">
-        <v>-61.59218579475746</v>
+        <v>-74.36254916773227</v>
       </c>
       <c r="E8" t="n">
-        <v>-52.03732921819073</v>
+        <v>-55.11027979228949</v>
       </c>
       <c r="F8" t="n">
-        <v>-80.49989900004995</v>
+        <v>-104.458330734149</v>
       </c>
       <c r="G8" t="n">
-        <v>-92.34568837127873</v>
+        <v>-124.1052689322767</v>
       </c>
       <c r="H8" t="n">
-        <v>-45.7944610680681</v>
+        <v>-61.14023572038928</v>
       </c>
     </row>
     <row r="9">
@@ -2328,25 +2328,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.13229422034758</v>
+        <v>2.55453504330448</v>
       </c>
       <c r="C9" t="n">
-        <v>12.5299407522634</v>
+        <v>-0.5706759230837335</v>
       </c>
       <c r="D9" t="n">
-        <v>-50.1024389797998</v>
+        <v>-67.0508921036683</v>
       </c>
       <c r="E9" t="n">
-        <v>-40.54758240323308</v>
+        <v>-47.79862272822552</v>
       </c>
       <c r="F9" t="n">
-        <v>-66.24569347400234</v>
+        <v>-95.38747267211869</v>
       </c>
       <c r="G9" t="n">
-        <v>-78.93805429772851</v>
+        <v>-115.5731381581993</v>
       </c>
       <c r="H9" t="n">
-        <v>-34.52858903035879</v>
+        <v>-53.97104442366517</v>
       </c>
     </row>
   </sheetData>
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09212463267433868</v>
+        <v>0.2615587057335811</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1501112108538304</v>
+        <v>0.2564187240916866</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4149964112243847</v>
+        <v>-0.1335370176946005</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.484551565726319</v>
+        <v>-4.54159848603698</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5198555107245972</v>
+        <v>0.7085919375856677</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6317895762553571</v>
+        <v>0.8942846481558921</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5842778410737633</v>
+        <v>-0.4257135813607921</v>
       </c>
     </row>
     <row r="3">
@@ -2435,25 +2435,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3456196508269823</v>
+        <v>0.3263199051325608</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2602372492759303</v>
+        <v>0.2312335867429536</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1264606903518904</v>
+        <v>0.09462261037364431</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1283459030488752</v>
+        <v>0.123475784139429</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1119945783097384</v>
+        <v>0.0936311281809776</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07948121999984278</v>
+        <v>0.04818258138928063</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1753565486355432</v>
+        <v>0.1529109326598077</v>
       </c>
     </row>
     <row r="4">
@@ -2463,25 +2463,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4227653470938295</v>
+        <v>0.3438659108007007</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3375939858215468</v>
+        <v>0.2953663701910358</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01857541937347782</v>
+        <v>0.01488055044663967</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03688048948305424</v>
+        <v>0.03726409757194624</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02040788888153091</v>
+        <v>0.01238590359728737</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01390568611789188</v>
+        <v>0.003992403272119624</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1416881361285552</v>
+        <v>0.1179592059799549</v>
       </c>
     </row>
     <row r="5">
@@ -2491,25 +2491,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6502040811113304</v>
+        <v>0.5864008107094505</v>
       </c>
       <c r="C5" t="n">
-        <v>0.581028386416315</v>
+        <v>0.5434761910065939</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1362916702277796</v>
+        <v>0.1219858616669968</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1920429365612134</v>
+        <v>0.1930391089182351</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1428561825107017</v>
+        <v>0.1112919745412371</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1179223732711137</v>
+        <v>0.06318546725410538</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3033909383497423</v>
+        <v>0.2698965690161031</v>
       </c>
     </row>
     <row r="6">
@@ -2519,25 +2519,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63.54941805166595</v>
+        <v>59.58637786633564</v>
       </c>
       <c r="C6" t="n">
-        <v>54.40376189025745</v>
+        <v>49.06688890144709</v>
       </c>
       <c r="D6" t="n">
-        <v>110.5248649180972</v>
+        <v>114.8942289385894</v>
       </c>
       <c r="E6" t="n">
-        <v>253.4112200154135</v>
+        <v>254.9928781137801</v>
       </c>
       <c r="F6" t="n">
-        <v>37.97287630262323</v>
+        <v>30.76155448237342</v>
       </c>
       <c r="G6" t="n">
-        <v>37.74504154817007</v>
+        <v>31.27309484987233</v>
       </c>
       <c r="H6" t="n">
-        <v>92.93453045437126</v>
+        <v>90.09583719206633</v>
       </c>
     </row>
     <row r="7">
@@ -2547,25 +2547,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.573798353163379</v>
+        <v>0.4657385258404163</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4967824268189336</v>
+        <v>0.4333308419062191</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8860034338574999</v>
+        <v>0.7079549812420559</v>
       </c>
       <c r="E7" t="n">
-        <v>3.353363624712068</v>
+        <v>3.384128828222913</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1638288689996925</v>
+        <v>0.09959255124240085</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1256971074059172</v>
+        <v>0.0380092878437161</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9332456358262481</v>
+        <v>0.8547925027162867</v>
       </c>
     </row>
     <row r="8">
@@ -2575,25 +2575,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.364054189362752</v>
+        <v>-4.147559360298224</v>
       </c>
       <c r="C8" t="n">
-        <v>5.711330036070226</v>
+        <v>-4.293081405280414</v>
       </c>
       <c r="D8" t="n">
-        <v>-61.70423833784939</v>
+        <v>-74.36170541547358</v>
       </c>
       <c r="E8" t="n">
-        <v>-47.30152476935936</v>
+        <v>-55.08422389637794</v>
       </c>
       <c r="F8" t="n">
-        <v>-83.07951106116184</v>
+        <v>-104.5622990118014</v>
       </c>
       <c r="G8" t="n">
-        <v>-84.88643623158755</v>
+        <v>-124.0840476391264</v>
       </c>
       <c r="H8" t="n">
-        <v>-43.98272102908752</v>
+        <v>-61.08881945472634</v>
       </c>
     </row>
     <row r="9">
@@ -2603,25 +2603,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.52940097398113</v>
+        <v>1.68493404809529</v>
       </c>
       <c r="C9" t="n">
-        <v>13.49988224819454</v>
+        <v>0.6632700024350555</v>
       </c>
       <c r="D9" t="n">
-        <v>-50.21449152289173</v>
+        <v>-67.05004835140961</v>
       </c>
       <c r="E9" t="n">
-        <v>-35.81177795440171</v>
+        <v>-47.77256683231397</v>
       </c>
       <c r="F9" t="n">
-        <v>-68.82530553511421</v>
+        <v>-95.49144094977115</v>
       </c>
       <c r="G9" t="n">
-        <v>-71.47880215803735</v>
+        <v>-115.551916865049</v>
       </c>
       <c r="H9" t="n">
-        <v>-32.71684899137822</v>
+        <v>-53.91962815800223</v>
       </c>
     </row>
   </sheetData>
@@ -2682,25 +2682,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.726411779233697</v>
+        <v>0.6492136149968124</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7258531696082796</v>
+        <v>0.7127207001777148</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9708809804326931</v>
+        <v>0.9313560595191384</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4674560621939903</v>
+        <v>0.7758969442282651</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9254129066991602</v>
+        <v>0.5531335544191168</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7872243118184897</v>
+        <v>0.5937064546383888</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7672065349977183</v>
+        <v>0.702671221329906</v>
       </c>
     </row>
     <row r="3">
@@ -2710,25 +2710,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.159877489240433</v>
+        <v>0.2291428899927372</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1490922546980404</v>
+        <v>0.1760607914061154</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009058483378029343</v>
+        <v>0.01430886831766466</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02830952337359156</v>
+        <v>0.0143060413059407</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03279428303835275</v>
+        <v>0.09246823557999828</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05647602664676972</v>
+        <v>0.07431914357334114</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07260134339586945</v>
+        <v>0.1001009950292995</v>
       </c>
     </row>
     <row r="4">
@@ -2738,25 +2738,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1274003274852153</v>
+        <v>0.1633487735750692</v>
       </c>
       <c r="C4" t="n">
-        <v>0.108896978468517</v>
+        <v>0.1141134759154336</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003822610403224964</v>
+        <v>0.0009011259475751816</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003581055052933547</v>
+        <v>0.001506965572747833</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003170223018443993</v>
+        <v>0.01899345086738774</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008035600685282246</v>
+        <v>0.01534391790451378</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04191107429178575</v>
+        <v>0.05236795163045455</v>
       </c>
     </row>
     <row r="5">
@@ -2766,25 +2766,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3569318247021625</v>
+        <v>0.404164290326433</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3299954218902393</v>
+        <v>0.3378068618536834</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01955149713762341</v>
+        <v>0.03001875992733847</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05984191718965517</v>
+        <v>0.03881965446455999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05630473353497016</v>
+        <v>0.137816729272566</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08964151206490353</v>
+        <v>0.1238705691619837</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1520444844199257</v>
+        <v>0.1787494775010941</v>
       </c>
     </row>
     <row r="6">
@@ -2794,25 +2794,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.14079915399827</v>
+        <v>59.28925478113571</v>
       </c>
       <c r="C6" t="n">
-        <v>39.74336976680024</v>
+        <v>55.69589401987594</v>
       </c>
       <c r="D6" t="n">
-        <v>13.63992424374445</v>
+        <v>24.36338624649646</v>
       </c>
       <c r="E6" t="n">
-        <v>59.95922179819762</v>
+        <v>27.16672118310719</v>
       </c>
       <c r="F6" t="n">
-        <v>19.29338845990508</v>
+        <v>53.37038758291267</v>
       </c>
       <c r="G6" t="n">
-        <v>35.60052916064681</v>
+        <v>45.41378828723694</v>
       </c>
       <c r="H6" t="n">
-        <v>32.22953876388208</v>
+        <v>44.21657201679415</v>
       </c>
     </row>
     <row r="7">
@@ -2822,25 +2822,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1732566954695416</v>
+        <v>0.2200800570035047</v>
       </c>
       <c r="C7" t="n">
-        <v>0.160471934045478</v>
+        <v>0.1665632230874891</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01100328859841782</v>
+        <v>0.02172397030756112</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1642699198788564</v>
+        <v>0.06878579263244398</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02659528410316274</v>
+        <v>0.1478553492814364</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07145762693415067</v>
+        <v>0.133128806141643</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1011757915049345</v>
+        <v>0.1263561997423464</v>
       </c>
     </row>
     <row r="8">
@@ -2850,25 +2850,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-27.02715641043635</v>
+        <v>-28.80175003166024</v>
       </c>
       <c r="C8" t="n">
-        <v>-25.26029493033172</v>
+        <v>-30.55842884358254</v>
       </c>
       <c r="D8" t="n">
-        <v>-157.2575434532373</v>
+        <v>-145.2491759975573</v>
       </c>
       <c r="E8" t="n">
-        <v>-110.2740541037424</v>
+        <v>-134.4508012943042</v>
       </c>
       <c r="F8" t="n">
-        <v>-147.3567402001459</v>
+        <v>-105.0188483614879</v>
       </c>
       <c r="G8" t="n">
-        <v>-112.5968380998875</v>
+        <v>-102.4259027796712</v>
       </c>
       <c r="H8" t="n">
-        <v>-96.62877119963019</v>
+        <v>-91.08415121804391</v>
       </c>
     </row>
     <row r="9">
@@ -2878,25 +2878,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-23.69430303421149</v>
+        <v>-27.96853668760402</v>
       </c>
       <c r="C9" t="n">
-        <v>-22.42809412592288</v>
+        <v>-29.85037864248033</v>
       </c>
       <c r="D9" t="n">
-        <v>-153.0794537023436</v>
+        <v>-144.2046535598339</v>
       </c>
       <c r="E9" t="n">
-        <v>-106.0959643528487</v>
+        <v>-133.4062788565808</v>
       </c>
       <c r="F9" t="n">
-        <v>-142.1733927361285</v>
+        <v>-103.7230114954836</v>
       </c>
       <c r="G9" t="n">
-        <v>-107.7213348004148</v>
+        <v>-101.207026954803</v>
       </c>
       <c r="H9" t="n">
-        <v>-92.53209045864499</v>
+        <v>-90.05998103279758</v>
       </c>
     </row>
   </sheetData>
@@ -2957,25 +2957,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4204253555122824</v>
+        <v>0.2755735807534549</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4880593710856301</v>
+        <v>0.3356289635652778</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05239166535507711</v>
+        <v>0.4955216958660851</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1716856824784851</v>
+        <v>-2.093278310961987</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7592406713082724</v>
+        <v>0.6381238830901704</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5314895472077679</v>
+        <v>0.8643604401134461</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3466534879984242</v>
+        <v>0.08598837540440797</v>
       </c>
     </row>
     <row r="3">
@@ -2985,25 +2985,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2761769702829606</v>
+        <v>0.321237250204006</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2305937592937447</v>
+        <v>0.2187470108949263</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1067363590841978</v>
+        <v>0.06751218685642668</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07654976174873182</v>
+        <v>0.09875963757406063</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08522472772514221</v>
+        <v>0.1034965082917802</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1000657341971677</v>
+        <v>0.04367018997561321</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1458912187219908</v>
+        <v>0.1422371306328022</v>
       </c>
     </row>
     <row r="4">
@@ -3013,25 +3013,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2698873485965402</v>
+        <v>0.3373396807525093</v>
       </c>
       <c r="C4" t="n">
-        <v>0.203353755957672</v>
+        <v>0.2639023706615989</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01243976456632939</v>
+        <v>0.006622558184440764</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007878919720644542</v>
+        <v>0.02080053708100846</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01023314801456466</v>
+        <v>0.01538105247010282</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0176935764968956</v>
+        <v>0.005122508824626557</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08691441889210773</v>
+        <v>0.1081947846623811</v>
       </c>
     </row>
     <row r="5">
@@ -3041,25 +3041,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5195068320980392</v>
+        <v>0.5808095047022812</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4509476199711802</v>
+        <v>0.5137142889404566</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1115336925163396</v>
+        <v>0.08137910164434579</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08876327912287008</v>
+        <v>0.1442239129999199</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1011590233966534</v>
+        <v>0.1240203711899897</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1330172037628802</v>
+        <v>0.07157170407798431</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2341546084779938</v>
+        <v>0.2526198139258296</v>
       </c>
     </row>
     <row r="6">
@@ -3069,25 +3069,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59.27281927258762</v>
+        <v>58.46687292845737</v>
       </c>
       <c r="C6" t="n">
-        <v>48.78328787332875</v>
+        <v>44.94043466242394</v>
       </c>
       <c r="D6" t="n">
-        <v>79.32415761684642</v>
+        <v>74.03925528936223</v>
       </c>
       <c r="E6" t="n">
-        <v>94.58225484610304</v>
+        <v>191.2501179331832</v>
       </c>
       <c r="F6" t="n">
-        <v>33.32517274829666</v>
+        <v>34.20518932334087</v>
       </c>
       <c r="G6" t="n">
-        <v>45.794143357096</v>
+        <v>30.68745205828062</v>
       </c>
       <c r="H6" t="n">
-        <v>60.18030595237641</v>
+        <v>72.26488703250804</v>
       </c>
     </row>
     <row r="7">
@@ -3097,25 +3097,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3687935373638934</v>
+        <v>0.45696570230072</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3019298178446813</v>
+        <v>0.3875429703935359</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2989903355899075</v>
+        <v>0.159479281969283</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7260418970959935</v>
+        <v>1.892087738490604</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08539100221771355</v>
+        <v>0.1228295718020209</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1589386393854966</v>
+        <v>0.04777762414320475</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3233475382496143</v>
+        <v>0.5111138148498947</v>
       </c>
     </row>
     <row r="8">
@@ -3125,25 +3125,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.734239214051453</v>
+        <v>-4.473303325837545</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1078773541429427</v>
+        <v>-5.982640784975548</v>
       </c>
       <c r="D8" t="n">
-        <v>-68.12399946511474</v>
+        <v>-91.36274457066661</v>
       </c>
       <c r="E8" t="n">
-        <v>-77.71485399177863</v>
+        <v>-67.32830589952383</v>
       </c>
       <c r="F8" t="n">
-        <v>-99.717321608769</v>
+        <v>-98.71470992631811</v>
       </c>
       <c r="G8" t="n">
-        <v>-76.86384037624885</v>
+        <v>-117.85277387835</v>
       </c>
       <c r="H8" t="n">
-        <v>-53.42964981228613</v>
+        <v>-64.28574639761194</v>
       </c>
     </row>
     <row r="9">
@@ -3153,25 +3153,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11.73279934272605</v>
+        <v>1.359190082555969</v>
       </c>
       <c r="C9" t="n">
-        <v>8.604479767369462</v>
+        <v>-1.026289377260078</v>
       </c>
       <c r="D9" t="n">
-        <v>-55.58973021243366</v>
+        <v>-84.05108750660264</v>
       </c>
       <c r="E9" t="n">
-        <v>-65.18058473909755</v>
+        <v>-60.01664883545986</v>
       </c>
       <c r="F9" t="n">
-        <v>-84.16727921671705</v>
+        <v>-89.6438518642878</v>
       </c>
       <c r="G9" t="n">
-        <v>-62.23733047783044</v>
+        <v>-109.3206431042726</v>
       </c>
       <c r="H9" t="n">
-        <v>-41.13960758933053</v>
+        <v>-57.11655510088784</v>
       </c>
     </row>
   </sheetData>
@@ -3232,25 +3232,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9695101197845015</v>
+        <v>0.9919257342009422</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8581468750836957</v>
+        <v>0.8774672230312726</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9693048680841891</v>
+        <v>0.9546371639058925</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9384987207843132</v>
+        <v>0.9371883675420041</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8022037546634957</v>
+        <v>0.8931866182229208</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6611073136951809</v>
+        <v>0.9067970121823146</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8664619420158961</v>
+        <v>0.9268670198475578</v>
       </c>
     </row>
     <row r="3">
@@ -3260,25 +3260,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07231995806291859</v>
+        <v>0.03915359818155867</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1019771427970955</v>
+        <v>0.08993122932287537</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01538470349670535</v>
+        <v>0.01640765850005425</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01439940736048355</v>
+        <v>0.01439816998486352</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08400206074545007</v>
+        <v>0.04084089984451476</v>
       </c>
       <c r="G3" t="n">
-        <v>0.101110126919187</v>
+        <v>0.04351976984197183</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06486556656364001</v>
+        <v>0.0407085542793064</v>
       </c>
     </row>
     <row r="4">
@@ -3288,25 +3288,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0141980554336714</v>
+        <v>0.003759899107210859</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05634709205877136</v>
+        <v>0.04867263705432979</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004029515153095287</v>
+        <v>0.0005955023615143024</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004135611187399137</v>
+        <v>0.000422372498921671</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008407060554007688</v>
+        <v>0.004539957606629645</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01279848428916883</v>
+        <v>0.003519866386893105</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01542786749494479</v>
+        <v>0.01025170583591656</v>
       </c>
     </row>
     <row r="5">
@@ -3316,25 +3316,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1191555933797125</v>
+        <v>0.06131801617152058</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2373754242940312</v>
+        <v>0.2206187595249547</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02007365226632983</v>
+        <v>0.02440291706977472</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02033620217100316</v>
+        <v>0.02055170306621013</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09169002428840167</v>
+        <v>0.06737920752450005</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1131303862327396</v>
+        <v>0.05932846186185096</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1002935471053697</v>
+        <v>0.07559984420313519</v>
       </c>
     </row>
     <row r="6">
@@ -3344,25 +3344,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.67142695695851</v>
+        <v>11.90790942326184</v>
       </c>
       <c r="C6" t="n">
-        <v>24.4297786904916</v>
+        <v>17.93308089473858</v>
       </c>
       <c r="D6" t="n">
-        <v>14.13290174552041</v>
+        <v>20.94083207110794</v>
       </c>
       <c r="E6" t="n">
-        <v>20.35271219204454</v>
+        <v>27.90669677965536</v>
       </c>
       <c r="F6" t="n">
-        <v>30.31799706002684</v>
+        <v>29.74059228330202</v>
       </c>
       <c r="G6" t="n">
-        <v>61.43410228487064</v>
+        <v>41.18301735835296</v>
       </c>
       <c r="H6" t="n">
-        <v>28.38981982165209</v>
+        <v>24.93535480173645</v>
       </c>
     </row>
     <row r="7">
@@ -3372,25 +3372,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02208560286821952</v>
+        <v>0.007554209114764938</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08499890191603125</v>
+        <v>0.07333067902864909</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01249060563545993</v>
+        <v>0.01652570248129227</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02173987654782399</v>
+        <v>0.02163915048664395</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06822381598875668</v>
+        <v>0.03772198485776453</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1136267448938639</v>
+        <v>0.0329248028161308</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05386092464169254</v>
+        <v>0.03161608813087426</v>
       </c>
     </row>
     <row r="8">
@@ -3400,25 +3400,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-60.32905450573071</v>
+        <v>-84.91717363719218</v>
       </c>
       <c r="C8" t="n">
-        <v>-31.14336967228024</v>
+        <v>-35.33957411401745</v>
       </c>
       <c r="D8" t="n">
-        <v>-152.1505805658807</v>
+        <v>-145.94820927513</v>
       </c>
       <c r="E8" t="n">
-        <v>-151.6048101681858</v>
+        <v>-153.162081622637</v>
       </c>
       <c r="F8" t="n">
-        <v>-117.0244513692641</v>
+        <v>-135.6606153274198</v>
       </c>
       <c r="G8" t="n">
-        <v>-96.96071324942123</v>
+        <v>-131.2333062090392</v>
       </c>
       <c r="H8" t="n">
-        <v>-101.5354965884604</v>
+        <v>-114.3768266975726</v>
       </c>
     </row>
     <row r="9">
@@ -3428,25 +3428,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-55.32977444139341</v>
+        <v>-80.7511069169111</v>
       </c>
       <c r="C9" t="n">
-        <v>-26.89506846566698</v>
+        <v>-31.7993231085064</v>
       </c>
       <c r="D9" t="n">
-        <v>-145.8834459395401</v>
+        <v>-140.7255970865129</v>
       </c>
       <c r="E9" t="n">
-        <v>-145.3376755418452</v>
+        <v>-147.9394694340199</v>
       </c>
       <c r="F9" t="n">
-        <v>-109.2494301732381</v>
+        <v>-129.1814309973981</v>
       </c>
       <c r="G9" t="n">
-        <v>-89.64745830021204</v>
+        <v>-125.1389270846982</v>
       </c>
       <c r="H9" t="n">
-        <v>-95.39047547698264</v>
+        <v>-109.2559757713411</v>
       </c>
     </row>
   </sheetData>
